--- a/data/goya-model-reference.xlsx
+++ b/data/goya-model-reference.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Model reference" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Model reference'!$B$1:$AB$178</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Model reference'!$B$1:$AC$178</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -4869,7 +4869,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB178"/>
+  <dimension ref="A1:AC178"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4893,13 +4893,14 @@
     <col width="12" customWidth="1" min="19" max="19"/>
     <col width="10" customWidth="1" min="20" max="20"/>
     <col width="11" customWidth="1" min="21" max="21"/>
-    <col width="30" customWidth="1" min="22" max="22"/>
-    <col width="34" customWidth="1" min="23" max="23"/>
-    <col width="40" customWidth="1" min="24" max="24"/>
+    <col width="44" customWidth="1" min="22" max="22"/>
+    <col width="26" customWidth="1" min="23" max="23"/>
+    <col width="30" customWidth="1" min="24" max="24"/>
     <col width="40" customWidth="1" min="25" max="25"/>
     <col width="40" customWidth="1" min="26" max="26"/>
-    <col width="46" customWidth="1" min="27" max="27"/>
-    <col width="80" customWidth="1" min="28" max="28"/>
+    <col width="40" customWidth="1" min="27" max="27"/>
+    <col width="46" customWidth="1" min="28" max="28"/>
+    <col width="80" customWidth="1" min="29" max="29"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5010,35 +5011,40 @@
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
+          <t>image_live_url</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
           <t>local_image_path</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>all_local_images</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>image_url</t>
-        </is>
-      </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
+          <t>source_image_url</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
           <t>old_full_name</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>old_slug</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>new_url</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>old_description</t>
         </is>
@@ -5126,35 +5132,40 @@
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/587_2.jpg</t>
+        </is>
+      </c>
+      <c r="W2" s="2" t="inlineStr">
+        <is>
           <t>/products/587_2.jpg</t>
         </is>
       </c>
-      <c r="W2" s="2" t="inlineStr">
+      <c r="X2" s="2" t="inlineStr">
         <is>
           <t>/products/587_2.jpg; /products/587_1.jpg</t>
         </is>
       </c>
-      <c r="X2" s="2" t="inlineStr">
+      <c r="Y2" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2022/11/587_2.jpg</t>
         </is>
       </c>
-      <c r="Y2" s="2" t="inlineStr">
+      <c r="Z2" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary korekcyjne - G 2622 C4</t>
         </is>
       </c>
-      <c r="Z2" s="2" t="inlineStr">
+      <c r="AA2" s="2" t="inlineStr">
         <is>
           <t>goya-okulary-korekcyjne-g-2622-c4</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
+      <c r="AB2" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-okulary-korekcyjne-g-2622-c4</t>
         </is>
       </c>
-      <c r="AB2" s="3" t="inlineStr">
+      <c r="AC2" s="3" t="inlineStr">
         <is>
           <t>OKULARY KOREKCYJNE GOYA G 2622 C4 Produkt nowy - posiadają oryginalne zabezpieczenia, metkę oraz instrukcję użytkowania, dodatkowo w zestawie twarde etui na zawias sprężynowy Marki GOYA oraz miękką ściereczkę czyszczącą. NASZE PRODUKTY WYSYŁAMY BARDZO DOBRZE ZABEZPIECZONE W FOLIĘ TRANSPORTOWĄ I ZAPAKOWANE W WYTRZYMAŁY KARTONIK</t>
         </is>
@@ -5244,35 +5255,40 @@
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/3150_6.jpg</t>
+        </is>
+      </c>
+      <c r="W3" s="2" t="inlineStr">
+        <is>
           <t>/products/3150_6.jpg</t>
         </is>
       </c>
-      <c r="W3" s="2" t="inlineStr">
+      <c r="X3" s="2" t="inlineStr">
         <is>
           <t>/products/3150_6.jpg; /products/3148_1.jpg</t>
         </is>
       </c>
-      <c r="X3" s="2" t="inlineStr">
+      <c r="Y3" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2022/11/3150_6.jpg</t>
         </is>
       </c>
-      <c r="Y3" s="2" t="inlineStr">
+      <c r="Z3" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary przeciwsłoneczne z filtrem polaryzacyjnym - G 182</t>
         </is>
       </c>
-      <c r="Z3" s="2" t="inlineStr">
+      <c r="AA3" s="2" t="inlineStr">
         <is>
           <t>goya-g-182-zx-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
+      <c r="AB3" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-g-182-zx-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym</t>
         </is>
       </c>
-      <c r="AB3" s="3" t="inlineStr">
+      <c r="AC3" s="3" t="inlineStr">
         <is>
           <t>OKULARY PRZECIWSŁONECZNE DLA KIEROWCÓW GOYA Z FILTREM POLARYZACYJNYM I UV400 Oprawka wykonana w technologii - wycinania z płyty. Ręcznie obrabiana. Soczewki okularów GOYA o grubości 1,1 wyposażone są w filtr polaryzacyjny oraz filtr ochronny UV-400 (UV-A, UV-B, UV-C) OPRAWKA WYKONANA W TECHNOLOGII TR-90 Wysokiej jakości odmiana nylonu, wyjątkowo odporna na rozciąganie i wyginanie. Materiał wytrzymały na uderzenia, elastyczny, przyjemny w dotyku, o właściwościach antyalergicznych. Okulary wykonane z TR-90 są lekkie, wytrzymałe i wygodne w użytkowaniu. ZAUSZNIKI POŁĄCZONE Z OPRAWKĄ SYSTEMEM FLEX: FLEX - elastyczne połączenie zausznika z frontem oprawy. Zwiększony zakres odchylenia zausznika do ponad 110° gwarantuje wygodę noszenia i ułatwia zakładanie oraz zdejmowanie okularów. OKULARY POSIADAJĄ CERTYFIKAT CE. Produkt odpowiada Wytycznej Europejskiej 89/686/EWG zgodnie z normą PN-EN ISO 12312-1:2014-02/A1:2016-01. Każda para okularów posiada oryginalne oznaczenia znajdujące się na wewnętrznej stronie zauszników ; logo producenta, numer modelu, kat</t>
         </is>
@@ -5364,35 +5380,40 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/G_55004_BR_A.jpg</t>
+        </is>
+      </c>
+      <c r="W4" s="2" t="inlineStr">
+        <is>
           <t>/products/G_55004_BR_A.jpg</t>
         </is>
       </c>
-      <c r="W4" s="2" t="inlineStr">
+      <c r="X4" s="2" t="inlineStr">
         <is>
           <t>/products/G_55004_BR_A.jpg; /products/G_55004_BR_MODkw.jpg; /products/G_55004_BR_G.jpg; /products/G_55004_BR_MOD1.jpg; /products/G_55004_BR_F.jpg; /products/G_55004_BR_MOD.jpg; /products/G_55004_BR_B.jpg; /products/G_55004_BR_S.jpg; /products/G_55004_BR_T.jpg; /products/G_55004_BR_F1.jpg</t>
         </is>
       </c>
-      <c r="X4" s="2" t="inlineStr">
+      <c r="Y4" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2025/01/G_55004_BR_A.jpg</t>
         </is>
       </c>
-      <c r="Y4" s="2" t="inlineStr">
+      <c r="Z4" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary przeciwsłoneczne z filtrem polaryzacyjnym - G 55004 BR</t>
         </is>
       </c>
-      <c r="Z4" s="2" t="inlineStr">
+      <c r="AA4" s="2" t="inlineStr">
         <is>
           <t>goya-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym-g-55004-br</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
+      <c r="AB4" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym-g-55004-br</t>
         </is>
       </c>
-      <c r="AB4" s="3" t="inlineStr">
+      <c r="AC4" s="3" t="inlineStr">
         <is>
           <t>OKULARY PRZECIWSŁONECZNE DLA KIEROWCÓW GOYA Z FILTREM POLARYZACYJNYM I UV400 Oprawki wykonane w całości z aluminium - co sprawia, że okulary są bardzo lekkie i wytrzymałe. Soczewki okularów GOYA o grubości 1,1 wyposażone są w filtr polaryzacyjny oraz filtr ochronny UV-400 (UV-A, UV-B, UV-C) ZAUSZNIKI POŁĄCZONE Z OPRAWKĄ SYSTEMEM FLEX: FLEX - elastyczne połączenie zausznika z frontem oprawy. Zwiększony zakres odchylenia zausznika do ponad 110° gwarantuje wygodę noszenia i ułatwia zakładanie oraz zdejmowanie okularów. OKULARY POSIADAJĄ CERTYFIKAT CE. Produkt odpowiada Wytycznej Europejskiej 89/686/EWG zgodnie z normą PN-EN ISO 12312-1:2014-02/A1:2016-01. Każda para okularów posiada oryginalne oznaczenia znajdujące się na wewnętrznej stronie zauszników ; logo producenta, numer modelu, kategoria filtra oraz oznaczenie CE. O POLARYZACJI: Soczewki polaryzacyjne neutralizują oślepiające refleksy, powstające wówczas gdy światło odbija się od mokrej drogi, powierzchni wody lub śniegu. Eliminacja światła odbitego zwiększ kontrast widzenia i pozwala</t>
         </is>
@@ -5480,35 +5501,40 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/575_6.jpg</t>
+        </is>
+      </c>
+      <c r="W5" s="2" t="inlineStr">
+        <is>
           <t>/products/575_6.jpg</t>
         </is>
       </c>
-      <c r="W5" s="2" t="inlineStr">
+      <c r="X5" s="2" t="inlineStr">
         <is>
           <t>/products/575_6.jpg; /products/575_5.jpg</t>
         </is>
       </c>
-      <c r="X5" s="2" t="inlineStr">
+      <c r="Y5" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2022/11/575_6.jpg</t>
         </is>
       </c>
-      <c r="Y5" s="2" t="inlineStr">
+      <c r="Z5" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary korekcyjne G 2742 C2</t>
         </is>
       </c>
-      <c r="Z5" s="2" t="inlineStr">
+      <c r="AA5" s="2" t="inlineStr">
         <is>
           <t>goya-okulary-korekcyjne-g-2742-c2</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
+      <c r="AB5" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-okulary-korekcyjne-g-2742-c2</t>
         </is>
       </c>
-      <c r="AB5" s="3" t="inlineStr">
+      <c r="AC5" s="3" t="inlineStr">
         <is>
           <t>OKULARY KOREKCYJNE GOYA G 2742 C2 Produkt nowy ! - posiadają oryginalne zabezpieczenia, metkę oraz instrukcję użytkowania, dodatkowo w zestawie twarde etui na zawias sprężynowy Marki GOYA oraz miękką ściereczkę czyszczącą. NASZE PRODUKTY SĄ BARDZO DOBRZE ZABEZPIECZONE W FOLIĘ TRANSPORTOWĄ I ZAPAKOWANE W WYTRZYMAŁY KARTONIK</t>
         </is>
@@ -5598,35 +5624,40 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/3119_1.jpg</t>
+        </is>
+      </c>
+      <c r="W6" s="2" t="inlineStr">
+        <is>
           <t>/products/3119_1.jpg</t>
         </is>
       </c>
-      <c r="W6" s="2" t="inlineStr">
+      <c r="X6" s="2" t="inlineStr">
         <is>
           <t>/products/3119_1.jpg</t>
         </is>
       </c>
-      <c r="X6" s="2" t="inlineStr">
+      <c r="Y6" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2022/11/3119_1.jpg</t>
         </is>
       </c>
-      <c r="Y6" s="2" t="inlineStr">
+      <c r="Z6" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary przeciwsłoneczne z filtrem polaryzacyjnym - G 205</t>
         </is>
       </c>
-      <c r="Z6" s="2" t="inlineStr">
+      <c r="AA6" s="2" t="inlineStr">
         <is>
           <t>goya-g-205-z-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
+      <c r="AB6" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-g-205-z-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym</t>
         </is>
       </c>
-      <c r="AB6" s="3" t="inlineStr">
+      <c r="AC6" s="3" t="inlineStr">
         <is>
           <t>OKULARY PRZECIWSŁONECZNE DLA KIEROWCÓW GOYA Z FILTREM POLARYZACYJNYM I UV400 Oprawka okularów wykonana w technologii wycinania z płyty, Ręcznie obrabiane i składane. Soczewki okularów GOYA o grubości 1,1 wyposażone są w filtr polaryzacyjny oraz filtr ochronny UV-400 (UV-A, UV-B, UV-C) OKULARY POSIADAJĄ CERTYFIKAT CE. Produkt odpowiada Wytycznej Europejskiej 89/686/EWG zgodnie z normą PN-EN ISO 12312-1:2014-02/A1:2016-01. Każda para okularów posiada oryginalne oznaczenia znajdujące się na wewnętrznej stronie zauszników ; logo producenta, numer modelu, kategoria filtra oraz oznaczenie CE. O POLARYZACJI: Soczewki polaryzacyjne neutralizują oślepiające refleksy, powstające wówczas gdy światło odbija się od mokrej drogi, powierzchni wody lub śniegu. Eliminacja światła odbitego zwiększ kontrast widzenia i pozwala na bardziej komfortowe widzenie. Dlatego okulary z filtrem polaryzacyjnym to idealne rozwiązanie do wszelkiego rodzaju aktywności na świeżym powietrzu, pozwalające pełniej korzystać z życia. ZALETY: Eliminują oślepiające od</t>
         </is>
@@ -5718,35 +5749,40 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/974_3.jpg</t>
+        </is>
+      </c>
+      <c r="W7" s="2" t="inlineStr">
+        <is>
           <t>/products/974_3.jpg</t>
         </is>
       </c>
-      <c r="W7" s="2" t="inlineStr">
+      <c r="X7" s="2" t="inlineStr">
         <is>
           <t>/products/974_3.jpg; /products/974_2.jpg; /products/974_6.jpg; /products/974_1.jpg</t>
         </is>
       </c>
-      <c r="X7" s="2" t="inlineStr">
+      <c r="Y7" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2022/11/974_3.jpg</t>
         </is>
       </c>
-      <c r="Y7" s="2" t="inlineStr">
+      <c r="Z7" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary przeciwsłoneczne z filtrem polaryzacyjnym - G1923 C1</t>
         </is>
       </c>
-      <c r="Z7" s="2" t="inlineStr">
+      <c r="AA7" s="2" t="inlineStr">
         <is>
           <t>goya-g1923-c1-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
+      <c r="AB7" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-g1923-c1-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym</t>
         </is>
       </c>
-      <c r="AB7" s="3" t="inlineStr">
+      <c r="AC7" s="3" t="inlineStr">
         <is>
           <t>OKULARY PRZECIWSŁONECZNE DLA KIEROWCÓW GOYA Z FILTREM POLARYZACYJNYM I UV400 Soczewki okularów GOYA o grubości 1,1 wyposażone są w filtr polaryzacyjny oraz filtr ochronny UV-400 (UV-A, UV-B, UV-C) OPRAWKA WYKONANA W TECHNOLOGII TR-90 Wysokiej jakości odmiana nylonu, wyjątkowo odporna na rozciąganie i wyginanie. Materiał wytrzymały na uderzenia, elastyczny, przyjemny w dotyku, o właściwościach antyalergicznych. Okulary wykonane z TR-90 są lekkie, wytrzymałe i wygodne w użytkowaniu. ZAUSZNIKI POŁĄCZONE Z OPRAWKĄ SYSTEMEM FLEX: FLEX - elastyczne połączenie zausznika z frontem oprawy. Zwiększony zakres odchylenia zausznika do ponad 110° gwarantuje wygodę noszenia i ułatwia zakładanie oraz zdejmowanie okularów. OKULARY POSIADAJĄ CERTYFIKAT CE. Produkt odpowiada Wytycznej Europejskiej 89/686/EWG zgodnie z normą PN-EN ISO 12312-1:2014-02/A1:2016-01. Każda para okularów posiada oryginalne oznaczenia znajdujące się na wewnętrznej stronie zauszników ; logo producenta, numer modelu, kategoria filtra oraz oznaczenie CE. O POLARYZACJI: Soczewki pol</t>
         </is>
@@ -5832,35 +5868,40 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/625_4.jpg</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
           <t>/products/625_4.jpg</t>
         </is>
       </c>
-      <c r="W8" s="2" t="inlineStr">
+      <c r="X8" s="2" t="inlineStr">
         <is>
           <t>/products/625_4.jpg</t>
         </is>
       </c>
-      <c r="X8" s="2" t="inlineStr">
+      <c r="Y8" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2022/11/625_4.jpg</t>
         </is>
       </c>
-      <c r="Y8" s="2" t="inlineStr">
+      <c r="Z8" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary korekcyjne - G 89020</t>
         </is>
       </c>
-      <c r="Z8" s="2" t="inlineStr">
+      <c r="AA8" s="2" t="inlineStr">
         <is>
           <t>goya-okulary-korekcyjne-g-89020-c4</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
+      <c r="AB8" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-okulary-korekcyjne-g-89020-c4</t>
         </is>
       </c>
-      <c r="AB8" s="3" t="inlineStr">
+      <c r="AC8" s="3" t="inlineStr">
         <is>
           <t>OKULARY KOREKCYJNE GOYA G 89020 Produkt nowy - posiadają oryginalne zabezpieczenia, metkę oraz instrukcję użytkowania, dodatkowo w zestawie twarde etui na zawias sprężynowy Marki GOYA oraz miękką ściereczkę czyszczącą. NASZE PRODUKTY WYSYŁAMY BARDZO DOBRZE ZABEZPIECZONE W FOLIĘ TRANSPORTOWĄ I ZAPAKOWANE W WYTRZYMAŁY KARTONIK</t>
         </is>
@@ -5950,35 +5991,40 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/194_1.jpg</t>
+        </is>
+      </c>
+      <c r="W9" s="2" t="inlineStr">
+        <is>
           <t>/products/194_1.jpg</t>
         </is>
       </c>
-      <c r="W9" s="2" t="inlineStr">
+      <c r="X9" s="2" t="inlineStr">
         <is>
           <t>/products/194_1.jpg</t>
         </is>
       </c>
-      <c r="X9" s="2" t="inlineStr">
+      <c r="Y9" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2022/11/194_1.jpg</t>
         </is>
       </c>
-      <c r="Y9" s="2" t="inlineStr">
+      <c r="Z9" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary przeciwsłoneczne z filtrem polaryzacyjnym - G 15217</t>
         </is>
       </c>
-      <c r="Z9" s="2" t="inlineStr">
+      <c r="AA9" s="2" t="inlineStr">
         <is>
           <t>goya-g-15217-cz-okulary-przeciwsloneczne-kocie-oczy-z-filtrem-polaryzacyjnym</t>
         </is>
       </c>
-      <c r="AA9" s="2" t="inlineStr">
+      <c r="AB9" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-g-15217-cz-okulary-przeciwsloneczne-kocie-oczy-z-filtrem-polaryzacyjnym</t>
         </is>
       </c>
-      <c r="AB9" s="3" t="inlineStr">
+      <c r="AC9" s="3" t="inlineStr">
         <is>
           <t>OKULARY PRZECIWSŁONECZNE GOYA Z FILTREM POLARYZACYJNYM I UV400 Oprawka wykonana w technologii - wycinania z płyty. Ręcznie obrabiana. Soczewki okularów GOYA o grubości 1,1 wyposażone są w filtr polaryzacyjny oraz filtr ochronny UV-400 (UV-A, UV-B, UV-C) OKULARY POSIADAJĄ CERTYFIKAT CE. Produkt odpowiada Wytycznej Europejskiej 89/686/EWG zgodnie z normą PN-EN ISO 12312-1:2014-02/A1:2016-01. Każda para okularów posiada oryginalne oznaczenia znajdujące się na wewnętrznej stronie zauszników ; logo producenta, numer modelu, kategoria filtra oraz oznaczenie CE. O POLARYZACJI: Soczewki polaryzacyjne neutralizują oślepiające refleksy, powstające wówczas gdy światło odbija się od mokrej drogi, powierzchni wody lub śniegu. Eliminacja światła odbitego zwiększ kontrast widzenia i pozwala na bardziej komfortowe widzenie. Dlatego okulary z filtrem polaryzacyjnym to idealne rozwiązanie do wszelkiego rodzaju aktywności na świeżym powietrzu, pozwalające pełniej korzystać z życia. ZALETY: Eliminują oślepiające odblaski, zmniejszając zmęczenie oczu</t>
         </is>
@@ -6066,35 +6112,40 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/667_4.jpg</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
           <t>/products/667_4.jpg</t>
         </is>
       </c>
-      <c r="W10" s="2" t="inlineStr">
+      <c r="X10" s="2" t="inlineStr">
         <is>
           <t>/products/667_4.jpg; /products/667_1.jpg; /products/667_3.jpg; /products/667_2.jpg</t>
         </is>
       </c>
-      <c r="X10" s="2" t="inlineStr">
+      <c r="Y10" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2022/11/667_4.jpg</t>
         </is>
       </c>
-      <c r="Y10" s="2" t="inlineStr">
+      <c r="Z10" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary korekcyjne - G 94312 C1</t>
         </is>
       </c>
-      <c r="Z10" s="2" t="inlineStr">
+      <c r="AA10" s="2" t="inlineStr">
         <is>
           <t>goya-okulary-korekcyjne-g-94312-c1</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
+      <c r="AB10" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-okulary-korekcyjne-g-94312-c1</t>
         </is>
       </c>
-      <c r="AB10" s="3" t="inlineStr">
+      <c r="AC10" s="3" t="inlineStr">
         <is>
           <t>OKULARY KOREKCYJNE GOYA G 94312 C1 Produkt nowy - posiadają oryginalne zabezpieczenia, metkę oraz instrukcję użytkowania, dodatkowo w zestawie twarde etui na zawias sprężynowy Marki GOYA oraz miękką ściereczkę czyszczącą. NASZE PRODUKTY WYSYŁAMY BARDZO DOBRZE ZABEZPIECZONE W FOLIĘ TRANSPORTOWĄ I ZAPAKOWANE W WYTRZYMAŁY KARTONIK</t>
         </is>
@@ -6184,35 +6235,40 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/GOYA-CJ1943-P-A.jpg</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
           <t>/products/GOYA-CJ1943-P-A.jpg</t>
         </is>
       </c>
-      <c r="W11" s="2" t="inlineStr">
+      <c r="X11" s="2" t="inlineStr">
         <is>
           <t>/products/GOYA-CJ1943-P-A.jpg; /products/3431_7-e1681285160954.jpg</t>
         </is>
       </c>
-      <c r="X11" s="2" t="inlineStr">
+      <c r="Y11" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2023/04/GOYA-CJ1943-P-A.jpg</t>
         </is>
       </c>
-      <c r="Y11" s="2" t="inlineStr">
+      <c r="Z11" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary przeciwsłoneczne z filtrem polaryzacyjnym - GOYA CJ 1943</t>
         </is>
       </c>
-      <c r="Z11" s="2" t="inlineStr">
+      <c r="AA11" s="2" t="inlineStr">
         <is>
           <t>goya-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym-goya-cj-1943</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
+      <c r="AB11" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym-goya-cj-1943</t>
         </is>
       </c>
-      <c r="AB11" s="3" t="inlineStr">
+      <c r="AC11" s="3" t="inlineStr">
         <is>
           <t>OKULARY PRZECIWSŁONECZNE GOYA Z FILTREM POLARYZACYJNYM I UV400 Soczewki okularów GOYA o grubości 1,1 wyposażone są w filtr polaryzacyjny oraz filtr ochronny UV-400 (UV-A, UV-B, UV-C) OKULARY POSIADAJĄ CERTYFIKAT CE. Produkt odpowiada Wytycznej Europejskiej 89/686/EWG zgodnie z normą PN-EN ISO 12312-1:2014-02/A1:2016-01. Każda para okularów posiada oryginalne oznaczenia znajdujące się na wewnętrznej stronie zauszników ; logo producenta, numer modelu, kategoria filtra oraz oznaczenie CE. O POLARYZACJI: Soczewki polaryzacyjne neutralizują oślepiające refleksy, powstające wówczas gdy światło odbija się od mokrej drogi, powierzchni wody lub śniegu. Eliminacja światła odbitego zwiększ kontrast widzenia i pozwala na bardziej komfortowe widzenie. Dlatego okulary z filtrem polaryzacyjnym to idealne rozwiązanie do wszelkiego rodzaju aktywności na świeżym powietrzu, pozwalające pełniej korzystać z życia. ZALETY: Eliminują oślepiające odblaski, zmniejszając zmęczenie oczu Chronią przed szkodliwym promieniowaniem UV Zwiększają kontrast</t>
         </is>
@@ -6300,35 +6356,40 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/610_4.jpg</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
           <t>/products/610_4.jpg</t>
         </is>
       </c>
-      <c r="W12" s="2" t="inlineStr">
+      <c r="X12" s="2" t="inlineStr">
         <is>
           <t>/products/610_4.jpg; /products/610_1.jpg; /products/610_3.jpg; /products/610_2.jpg; /products/575_6.jpg; /products/575_5.jpg</t>
         </is>
       </c>
-      <c r="X12" s="2" t="inlineStr">
+      <c r="Y12" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2022/11/610_4.jpg</t>
         </is>
       </c>
-      <c r="Y12" s="2" t="inlineStr">
+      <c r="Z12" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary korekcyjne G 2694 C1</t>
         </is>
       </c>
-      <c r="Z12" s="2" t="inlineStr">
+      <c r="AA12" s="2" t="inlineStr">
         <is>
           <t>goya-okulary-korekcyjne-g-2694-c1</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
+      <c r="AB12" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-okulary-korekcyjne-g-2694-c1</t>
         </is>
       </c>
-      <c r="AB12" s="3" t="inlineStr">
+      <c r="AC12" s="3" t="inlineStr">
         <is>
           <t>OKULARY KOREKCYJNE GOYA G 2694 C1 Produkt nowy ! - posiadają oryginalne zabezpieczenia, metkę oraz instrukcję użytkowania, dodatkowo w zestawie twarde etui na zawias sprężynowy Marki GOYA oraz miękką ściereczkę czyszczącą. NASZE PRODUKTY SĄ BARDZO DOBRZE ZABEZPIECZONE W FOLIĘ TRANSPORTOWĄ I ZAPAKOWANE W WYTRZYMAŁY KARTONIK</t>
         </is>
@@ -6416,35 +6477,40 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/575_6.jpg</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
           <t>/products/575_6.jpg</t>
         </is>
       </c>
-      <c r="W13" s="2" t="inlineStr">
+      <c r="X13" s="2" t="inlineStr">
         <is>
           <t>/products/575_6.jpg; /products/575_5.jpg</t>
         </is>
       </c>
-      <c r="X13" s="2" t="inlineStr">
+      <c r="Y13" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2022/11/575_6.jpg</t>
         </is>
       </c>
-      <c r="Y13" s="2" t="inlineStr">
+      <c r="Z13" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary korekcyjne G 2742 C4</t>
         </is>
       </c>
-      <c r="Z13" s="2" t="inlineStr">
+      <c r="AA13" s="2" t="inlineStr">
         <is>
           <t>goya-okulary-korekcyjne-g-2742-c4</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="inlineStr">
+      <c r="AB13" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-okulary-korekcyjne-g-2742-c4</t>
         </is>
       </c>
-      <c r="AB13" s="3" t="inlineStr">
+      <c r="AC13" s="3" t="inlineStr">
         <is>
           <t>OKULARY KOREKCYJNE GOYA G 2742 C4 Produkt nowy ! - posiadają oryginalne zabezpieczenia, metkę oraz instrukcję użytkowania, dodatkowo w zestawie twarde etui na zawias sprężynowy Marki GOYA oraz miękką ściereczkę czyszczącą. NASZE PRODUKTY SĄ BARDZO DOBRZE ZABEZPIECZONE W FOLIĘ TRANSPORTOWĄ I ZAPAKOWANE W WYTRZYMAŁY KARTONIK</t>
         </is>
@@ -6536,35 +6602,40 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/G_55029_CZ_A.jpg</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
           <t>/products/G_55029_CZ_A.jpg</t>
         </is>
       </c>
-      <c r="W14" s="2" t="inlineStr">
+      <c r="X14" s="2" t="inlineStr">
         <is>
           <t>/products/G_55029_CZ_A.jpg; /products/G_55029_CZ_MOD1kw.jpg; /products/G_55029_CZ_G.jpg; /products/G_55029_CZ_B.jpg; /products/G_55029_CZ_F.jpg; /products/G_55029_CZ_S.jpg; /products/G_55029_CZ_F1.jpg; /products/G_55029_CZ_T.jpg</t>
         </is>
       </c>
-      <c r="X14" s="2" t="inlineStr">
+      <c r="Y14" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2025/02/G_55029_CZ_A.jpg</t>
         </is>
       </c>
-      <c r="Y14" s="2" t="inlineStr">
+      <c r="Z14" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary przeciwsłoneczne z filtrem polaryzacyjnym - G 55029 CZ</t>
         </is>
       </c>
-      <c r="Z14" s="2" t="inlineStr">
+      <c r="AA14" s="2" t="inlineStr">
         <is>
           <t>goya-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym-g-55029-cz</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
+      <c r="AB14" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym-g-55029-cz</t>
         </is>
       </c>
-      <c r="AB14" s="3" t="inlineStr">
+      <c r="AC14" s="3" t="inlineStr">
         <is>
           <t>OKULARY PRZECIWSŁONECZNE DLA KIEROWCÓW GOYA Z FILTREM POLARYZACYJNYM I UV400 Oprawki wykonane w całości z aluminium - co sprawia, że okulary są bardzo lekkie i wytrzymałe. Soczewki okularów GOYA o grubości 1,1 wyposażone są w filtr polaryzacyjny oraz filtr ochronny UV-400 (UV-A, UV-B, UV-C) ZAUSZNIKI POŁĄCZONE Z OPRAWKĄ SYSTEMEM FLEX: FLEX - elastyczne połączenie zausznika z frontem oprawy. Zwiększony zakres odchylenia zausznika do ponad 110° gwarantuje wygodę noszenia i ułatwia zakładanie oraz zdejmowanie okularów. OKULARY POSIADAJĄ CERTYFIKAT CE. Produkt odpowiada Wytycznej Europejskiej 89/686/EWG zgodnie z normą PN-EN ISO 12312-1:2014-02/A1:2016-01. Każda para okularów posiada oryginalne oznaczenia znajdujące się na wewnętrznej stronie zauszników ; logo producenta, numer modelu, kategoria filtra oraz oznaczenie CE. O POLARYZACJI: Soczewki polaryzacyjne neutralizują oślepiające refleksy, powstające wówczas gdy światło odbija się od mokrej drogi, powierzchni wody lub śniegu. Eliminacja światła odbitego zwiększ kontrast widzenia i pozwala</t>
         </is>
@@ -6656,35 +6727,40 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/3124_1.jpg</t>
+        </is>
+      </c>
+      <c r="W15" s="2" t="inlineStr">
+        <is>
           <t>/products/3124_1.jpg</t>
         </is>
       </c>
-      <c r="W15" s="2" t="inlineStr">
+      <c r="X15" s="2" t="inlineStr">
         <is>
           <t>/products/3124_1.jpg; /products/3124_6.jpg; /products/3124_2.jpg; /products/3124_3.jpg; /products/3124_4.jpg; /products/3124_5.jpg</t>
         </is>
       </c>
-      <c r="X15" s="2" t="inlineStr">
+      <c r="Y15" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2022/11/3124_1.jpg</t>
         </is>
       </c>
-      <c r="Y15" s="2" t="inlineStr">
+      <c r="Z15" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary przeciwsłoneczn z filtrem polaryzacyjnym - G 196 BR</t>
         </is>
       </c>
-      <c r="Z15" s="2" t="inlineStr">
+      <c r="AA15" s="2" t="inlineStr">
         <is>
           <t>goya-g-196-br-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym</t>
         </is>
       </c>
-      <c r="AA15" s="2" t="inlineStr">
+      <c r="AB15" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-g-196-br-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym</t>
         </is>
       </c>
-      <c r="AB15" s="3" t="inlineStr">
+      <c r="AC15" s="3" t="inlineStr">
         <is>
           <t>OKULARY PRZECIWSŁONECZNE DLA KIEROWCÓW GOYA Z FILTREM POLARYZACYJNYM I UV400 Soczewki okularów GOYA o grubości 1,1 wyposażone są w filtr polaryzacyjny oraz filtr ochronny UV-400 (UV-A, UV-B, UV-C) OKULARY POSIADAJĄ CERTYFIKAT CE. Produkt odpowiada Wytycznej Europejskiej 89/686/EWG zgodnie z normą PN-EN ISO 12312-1:2014-02/A1:2016-01. Każda para okularów posiada oryginalne oznaczenia znajdujące się na wewnętrznej stronie zauszników ; logo producenta, numer modelu, kategoria filtra oraz oznaczenie CE. O POLARYZACJI: Soczewki polaryzacyjne neutralizują oślepiające refleksy, powstające wówczas gdy światło odbija się od mokrej drogi, powierzchni wody lub śniegu. Eliminacja światła odbitego zwiększ kontrast widzenia i pozwala na bardziej komfortowe widzenie. Dlatego okulary z filtrem polaryzacyjnym to idealne rozwiązanie do wszelkiego rodzaju aktywności na świeżym powietrzu, pozwalające pełniej korzystać z życia. ZALETY: Eliminują oślepiające odblaski, zmniejszając zmęczenie oczu Chronią przed szkodliwym promieniowaniem UV Zwiększ</t>
         </is>
@@ -6774,35 +6850,40 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/689_4.jpg</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
           <t>/products/689_4.jpg</t>
         </is>
       </c>
-      <c r="W16" s="2" t="inlineStr">
+      <c r="X16" s="2" t="inlineStr">
         <is>
           <t>/products/689_4.jpg</t>
         </is>
       </c>
-      <c r="X16" s="2" t="inlineStr">
+      <c r="Y16" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2022/11/689_4.jpg</t>
         </is>
       </c>
-      <c r="Y16" s="2" t="inlineStr">
+      <c r="Z16" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary przeciwsłoneczne - G 96514S C21</t>
         </is>
       </c>
-      <c r="Z16" s="2" t="inlineStr">
+      <c r="AA16" s="2" t="inlineStr">
         <is>
           <t>goya-g-96514s-c21-okulary-przeciwsloneczne</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
+      <c r="AB16" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-g-96514s-c21-okulary-przeciwsloneczne</t>
         </is>
       </c>
-      <c r="AB16" s="3" t="inlineStr">
+      <c r="AC16" s="3" t="inlineStr">
         <is>
           <t>OKULARY PRZECIWSŁONECZNE MARKI GOYA OKULARY POSIADAJĄ CERTYFIKAT CE. Produkt odpowiada Wytycznej Europejskiej 89/686/EWG zgodnie z normą PN-EN ISO 12312-1:2014-02/A1:2016-01. Każda para okularów posiada oryginalne oznaczenia znajdujące się na wewnętrznej stronie zauszników ; logo producenta, numer modelu, kategoria filtra oraz oznaczenie CE. Produkt nowy - posiadają oryginalne zabezpieczenia, metkę oraz instrukcję użytkowania, dodatkowo w zestawie twarde etui na zawias sprężynowy Marki GOYA oraz miękką ściereczkę czyszczącą. NASZE PRODUKTY WYSYŁAMY BARDZO DOBRZE ZABEZPIECZONE W FOLIĘ TRANSPORTOWĄ I ZAPAKOWANE W WYTRZYMAŁY KARTONIK</t>
         </is>
@@ -6894,35 +6975,40 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/prof-233.jpeg</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
           <t>/products/prof-233.jpeg</t>
         </is>
       </c>
-      <c r="W17" s="2" t="inlineStr">
+      <c r="X17" s="2" t="inlineStr">
         <is>
           <t>/products/prof-233.jpeg; /products/1865_2.jpeg; /products/1865_3.jpeg; /products/1865_4.jpeg; /products/1865_5.jpeg; /products/1865_6.jpeg; /products/1865_7.jpeg</t>
         </is>
       </c>
-      <c r="X17" s="2" t="inlineStr">
+      <c r="Y17" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2022/03/prof-233.jpeg</t>
         </is>
       </c>
-      <c r="Y17" s="2" t="inlineStr">
+      <c r="Z17" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary przeciwsłoneczne z filtrem polaryzacyjnym - G 221</t>
         </is>
       </c>
-      <c r="Z17" s="2" t="inlineStr">
+      <c r="AA17" s="2" t="inlineStr">
         <is>
           <t>okulary-przeciwsloneczne-polaryzacyjne-kujonki-goya-g-221</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
+      <c r="AB17" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/okulary-przeciwsloneczne-polaryzacyjne-kujonki-goya-g-221</t>
         </is>
       </c>
-      <c r="AB17" s="3" t="inlineStr">
+      <c r="AC17" s="3" t="inlineStr">
         <is>
           <t>OKULARY PRZECIWSŁONECZNE GOYA Z FILTREM POLARYZACYJNYM I UV400 Oprawka wykonana w technologii - wycinania z płyty. Ręcznie obrabiana. Soczewki okularów GOYA o grubości 1,1 wyposażone są w filtr polaryzacyjny oraz filtr ochronny UV-400 (UV-A, UV-B, UV-C) OKULARY POSIADAJĄ CERTYFIKAT CE. Produkt odpowiada Wytycznej Europejskiej 89/686/EWG zgodnie z normą PN-EN ISO 12312-1:2014-02/A1:2016-01. Każda para okularów posiada oryginalne oznaczenia znajdujące się na wewnętrznej stronie zauszników ; logo producenta, numer modelu, kategoria filtra oraz oznaczenie CE. O POLARYZACJI: Soczewki polaryzacyjne neutralizują oślepiające refleksy, powstające wówczas gdy światło odbija się od mokrej drogi, powierzchni wody lub śniegu. Eliminacja światła odbitego zwiększ kontrast widzenia i pozwala na bardziej komfortowe widzenie. Dlatego okulary z filtrem polaryzacyjnym to idealne rozwiązanie do wszelkiego rodzaju aktywności na świeżym powietrzu, pozwalające pełniej korzystać z życia. ZALETY: Eliminują oślepiające odblaski, zmniejszając zmęczenie oczu</t>
         </is>
@@ -7010,35 +7096,40 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/605_4.jpg</t>
+        </is>
+      </c>
+      <c r="W18" s="2" t="inlineStr">
+        <is>
           <t>/products/605_4.jpg</t>
         </is>
       </c>
-      <c r="W18" s="2" t="inlineStr">
+      <c r="X18" s="2" t="inlineStr">
         <is>
           <t>/products/605_4.jpg; /products/605_1.jpg; /products/605_3.jpg; /products/605_2.jpg</t>
         </is>
       </c>
-      <c r="X18" s="2" t="inlineStr">
+      <c r="Y18" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2022/11/605_4.jpg</t>
         </is>
       </c>
-      <c r="Y18" s="2" t="inlineStr">
+      <c r="Z18" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary korekcyjne - G 2655 C1</t>
         </is>
       </c>
-      <c r="Z18" s="2" t="inlineStr">
+      <c r="AA18" s="2" t="inlineStr">
         <is>
           <t>goya-okulary-korekcyjne-g-2655-c1</t>
         </is>
       </c>
-      <c r="AA18" s="2" t="inlineStr">
+      <c r="AB18" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-okulary-korekcyjne-g-2655-c1</t>
         </is>
       </c>
-      <c r="AB18" s="3" t="inlineStr">
+      <c r="AC18" s="3" t="inlineStr">
         <is>
           <t>OKULARY KOREKCYJNE GOYA G 2655 C1 Produkt nowy - posiadają oryginalne zabezpieczenia, metkę oraz instrukcję użytkowania, dodatkowo w zestawie twarde etui na zawias sprężynowy Marki GOYA oraz miękką ściereczkę czyszczącą. NASZE PRODUKTY WYSYŁAMY BARDZO DOBRZE ZABEZPIECZONE W FOLIĘ TRANSPORTOWĄ I ZAPAKOWANE W WYTRZYMAŁY KARTONIK</t>
         </is>
@@ -7128,35 +7219,40 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/3136_1.jpg</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
           <t>/products/3136_1.jpg</t>
         </is>
       </c>
-      <c r="W19" s="2" t="inlineStr">
+      <c r="X19" s="2" t="inlineStr">
         <is>
           <t>/products/3136_1.jpg; /products/3135_6.jpg</t>
         </is>
       </c>
-      <c r="X19" s="2" t="inlineStr">
+      <c r="Y19" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2022/11/3136_1.jpg</t>
         </is>
       </c>
-      <c r="Y19" s="2" t="inlineStr">
+      <c r="Z19" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary przeciwsłoneczne z filtrem polaryzacyjnym - G 187</t>
         </is>
       </c>
-      <c r="Z19" s="2" t="inlineStr">
+      <c r="AA19" s="2" t="inlineStr">
         <is>
           <t>goya-g-187-cz-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym</t>
         </is>
       </c>
-      <c r="AA19" s="2" t="inlineStr">
+      <c r="AB19" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-g-187-cz-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym</t>
         </is>
       </c>
-      <c r="AB19" s="3" t="inlineStr">
+      <c r="AC19" s="3" t="inlineStr">
         <is>
           <t>OKULARY PRZECIWSŁONECZNE DLA KIEROWCÓW GOYA Z FILTREM POLARYZACYJNYM I UV400 Soczewki okularów GOYA o grubości 1,1 wyposażone są w filtr polaryzacyjny oraz filtr ochronny UV-400 (UV-A, UV-B, UV-C) OPRAWKA WYKONANA W TECHNOLOGII TR-90 Wysokiej jakości odmiana nylonu, wyjątkowo odporna na rozciąganie i wyginanie. Materiał wytrzymały na uderzenia, elastyczny, przyjemny w dotyku, o właściwościach antyalergicznych. Okulary wykonane z TR-90 są lekkie, wytrzymałe i wygodne w użytkowaniu. OKULARY POSIADAJĄ CERTYFIKAT CE. Produkt odpowiada Wytycznej Europejskiej 89/686/EWG zgodnie z normą PN-EN ISO 12312-1:2014-02/A1:2016-01. Każda para okularów posiada oryginalne oznaczenia znajdujące się na wewnętrznej stronie zauszników ; logo producenta, numer modelu, kategoria filtra oraz oznaczenie CE. O POLARYZACJI: Soczewki polaryzacyjne neutralizują oślepiające refleksy, powstające wówczas gdy światło odbija się od mokrej drogi, powierzchni wody lub śniegu. Eliminacja światła odbitego zwiększ kontrast widzenia i pozwala na bardziej komfortowe widzenie. Dlatego o</t>
         </is>
@@ -7248,35 +7344,40 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/G_55015_CZ_A.jpg</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
           <t>/products/G_55015_CZ_A.jpg</t>
         </is>
       </c>
-      <c r="W20" s="2" t="inlineStr">
+      <c r="X20" s="2" t="inlineStr">
         <is>
           <t>/products/G_55015_CZ_A.jpg; /products/G_55015_CZ_MOD2kw.jpg; /products/G_55015_CZ_G.jpg; /products/G_55015_CZ_B.jpg; /products/G_55015_CZ_F.jpg; /products/G_55015_CZ_S.jpg; /products/G_55015_CZ_F1.jpg; /products/G_55015_CZ_T.jpg</t>
         </is>
       </c>
-      <c r="X20" s="2" t="inlineStr">
+      <c r="Y20" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2025/01/G_55015_CZ_A.jpg</t>
         </is>
       </c>
-      <c r="Y20" s="2" t="inlineStr">
+      <c r="Z20" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary przeciwsłoneczne z filtrem polaryzacyjnym - G 55015 CZ</t>
         </is>
       </c>
-      <c r="Z20" s="2" t="inlineStr">
+      <c r="AA20" s="2" t="inlineStr">
         <is>
           <t>goya-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym-g-55015-cz</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
+      <c r="AB20" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym-g-55015-cz</t>
         </is>
       </c>
-      <c r="AB20" s="3" t="inlineStr">
+      <c r="AC20" s="3" t="inlineStr">
         <is>
           <t>OKULARY PRZECIWSŁONECZNE DLA KIEROWCÓW GOYA Z FILTREM POLARYZACYJNYM I UV400 Zausznik wykonane w całości z aluminium - co sprawia, że okulary są bardzo lekkie i wytrzymałe. Soczewki okularów GOYA o grubości 1,1 wyposażone są w filtr polaryzacyjny oraz filtr ochronny UV-400 (UV-A, UV-B, UV-C) ZAUSZNIKI POŁĄCZONE Z OPRAWKĄ SYSTEMEM FLEX: FLEX - elastyczne połączenie zausznika z frontem oprawy. Zwiększony zakres odchylenia zausznika do ponad 110° gwarantuje wygodę noszenia i ułatwia zakładanie oraz zdejmowanie okularów. OKULARY POSIADAJĄ CERTYFIKAT CE. Produkt odpowiada Wytycznej Europejskiej 89/686/EWG zgodnie z normą PN-EN ISO 12312-1:2014-02/A1:2016-01. Każda para okularów posiada oryginalne oznaczenia znajdujące się na wewnętrznej stronie zauszników ; logo producenta, numer modelu, kategoria filtra oraz oznaczenie CE. O POLARYZACJI: Soczewki polaryzacyjne neutralizują oślepiające refleksy, powstające wówczas gdy światło odbija się od mokrej drogi, powierzchni wody lub śniegu. Eliminacja światła odbitego zwiększ kontrast widzenia i pozwala</t>
         </is>
@@ -7364,35 +7465,40 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/575_6.jpg</t>
+        </is>
+      </c>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
           <t>/products/575_6.jpg</t>
         </is>
       </c>
-      <c r="W21" s="2" t="inlineStr">
+      <c r="X21" s="2" t="inlineStr">
         <is>
           <t>/products/575_6.jpg; /products/575_5.jpg</t>
         </is>
       </c>
-      <c r="X21" s="2" t="inlineStr">
+      <c r="Y21" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2022/11/575_6.jpg</t>
         </is>
       </c>
-      <c r="Y21" s="2" t="inlineStr">
+      <c r="Z21" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary korekcyjne G 89087 C2</t>
         </is>
       </c>
-      <c r="Z21" s="2" t="inlineStr">
+      <c r="AA21" s="2" t="inlineStr">
         <is>
           <t>goya-okulary-korekcyjne-g-89087-c2</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
+      <c r="AB21" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-okulary-korekcyjne-g-89087-c2</t>
         </is>
       </c>
-      <c r="AB21" s="3" t="inlineStr">
+      <c r="AC21" s="3" t="inlineStr">
         <is>
           <t>OKULARY KOREKCYJNE GOYA G 89087 C2 Produkt nowy ! - posiadają oryginalne zabezpieczenia, metkę oraz instrukcję użytkowania, dodatkowo w zestawie twarde etui na zawias sprężynowy Marki GOYA oraz miękką ściereczkę czyszczącą. NASZE PRODUKTY SĄ BARDZO DOBRZE ZABEZPIECZONE W FOLIĘ TRANSPORTOWĄ I ZAPAKOWANE W WYTRZYMAŁY KARTONIK</t>
         </is>
@@ -7478,35 +7584,40 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/649_4.jpg</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
           <t>/products/649_4.jpg</t>
         </is>
       </c>
-      <c r="W22" s="2" t="inlineStr">
+      <c r="X22" s="2" t="inlineStr">
         <is>
           <t>/products/649_4.jpg</t>
         </is>
       </c>
-      <c r="X22" s="2" t="inlineStr">
+      <c r="Y22" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2022/11/649_4.jpg</t>
         </is>
       </c>
-      <c r="Y22" s="2" t="inlineStr">
+      <c r="Z22" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary korekcyjne - M 9004</t>
         </is>
       </c>
-      <c r="Z22" s="2" t="inlineStr">
+      <c r="AA22" s="2" t="inlineStr">
         <is>
           <t>goya-okulary-korekcyjne-m-9004-c1</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="inlineStr">
+      <c r="AB22" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-okulary-korekcyjne-m-9004-c1</t>
         </is>
       </c>
-      <c r="AB22" s="3" t="inlineStr">
+      <c r="AC22" s="3" t="inlineStr">
         <is>
           <t>OKULARY KOREKCYJNE GOYA M 9004 Produkt nowy - posiadają oryginalne zabezpieczenia, metkę oraz instrukcję użytkowania, dodatkowo w zestawie twarde etui na zawias sprężynowy Marki GOYA oraz miękką ściereczkę czyszczącą. NASZE PRODUKTY WYSYŁAMY BARDZO DOBRZE ZABEZPIECZONE W FOLIĘ TRANSPORTOWĄ I ZAPAKOWANE W WYTRZYMAŁY KARTONIK</t>
         </is>
@@ -7596,35 +7707,40 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/3123_1.jpg</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
           <t>/products/3123_1.jpg</t>
         </is>
       </c>
-      <c r="W23" s="2" t="inlineStr">
+      <c r="X23" s="2" t="inlineStr">
         <is>
           <t>/products/3123_1.jpg</t>
         </is>
       </c>
-      <c r="X23" s="2" t="inlineStr">
+      <c r="Y23" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2022/11/3123_1.jpg</t>
         </is>
       </c>
-      <c r="Y23" s="2" t="inlineStr">
+      <c r="Z23" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary przeciwsłoneczne z filtrem polaryzacyjnym - G 199</t>
         </is>
       </c>
-      <c r="Z23" s="2" t="inlineStr">
+      <c r="AA23" s="2" t="inlineStr">
         <is>
           <t>goya-g-199-br-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym</t>
         </is>
       </c>
-      <c r="AA23" s="2" t="inlineStr">
+      <c r="AB23" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-g-199-br-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym</t>
         </is>
       </c>
-      <c r="AB23" s="3" t="inlineStr">
+      <c r="AC23" s="3" t="inlineStr">
         <is>
           <t>OKULARY PRZECIWSŁONECZNE DLA KIEROWCÓW GOYA Z FILTREM POLARYZACYJNYM I UV400 Zauszniki oprawek wykonane z aluminium - co sprawia, że okulary są bardzo lekkie i wytrzymałe. Oprawki wykonane z monelu. Soczewki okularów GOYA o grubości 1,1 wyposażone są w filtr polaryzacyjny oraz filtr ochronny UV-400 (UV-A, UV-B, UV-C) ZAUSZNIKI POŁĄCZONE Z OPRAWKĄ SYSTEMEM FLEX: FLEX - elastyczne połączenie zausznika z frontem oprawy. Zwiększony zakres odchylenia zausznika do ponad 110° gwarantuje wygodę noszenia i ułatwia zakładanie oraz zdejmowanie okularów. OKULARY POSIADAJĄ CERTYFIKAT CE. Produkt odpowiada Wytycznej Europejskiej 89/686/EWG zgodnie z normą PN-EN ISO 12312-1:2014-02/A1:2016-01. Każda para okularów posiada oryginalne oznaczenia znajdujące się na wewnętrznej stronie zauszników ; logo producenta, numer modelu, kategoria filtra oraz oznaczenie CE. O POLARYZACJI: Soczewki polaryzacyjne neutralizują oślepiające refleksy, powstające wówczas gdy światło odbija się od mokrej drogi, powierzchni wody lub śniegu. Eliminacja światła odbitego zwiększ</t>
         </is>
@@ -7714,35 +7830,40 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/3147_6.jpg</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
           <t>/products/3147_6.jpg</t>
         </is>
       </c>
-      <c r="W24" s="2" t="inlineStr">
+      <c r="X24" s="2" t="inlineStr">
         <is>
           <t>/products/3147_6.jpg; /products/3144_1.jpg</t>
         </is>
       </c>
-      <c r="X24" s="2" t="inlineStr">
+      <c r="Y24" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2022/11/3147_6.jpg</t>
         </is>
       </c>
-      <c r="Y24" s="2" t="inlineStr">
+      <c r="Z24" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary przeciwsłoneczne z filtrem polaryzacyjnym - G 183</t>
         </is>
       </c>
-      <c r="Z24" s="2" t="inlineStr">
+      <c r="AA24" s="2" t="inlineStr">
         <is>
           <t>goya-g-183-zx-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym</t>
         </is>
       </c>
-      <c r="AA24" s="2" t="inlineStr">
+      <c r="AB24" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-g-183-zx-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym</t>
         </is>
       </c>
-      <c r="AB24" s="3" t="inlineStr">
+      <c r="AC24" s="3" t="inlineStr">
         <is>
           <t>OKULARY PRZECIWSŁONECZNE DLA KIEROWCÓW GOYA Z FILTREM POLARYZACYJNYM I UV400 Soczewki okularów GOYA o grubości 1,1 wyposażone są w filtr polaryzacyjny oraz filtr ochronny UV-400 (UV-A, UV-B, UV-C) OPRAWKA WYKONANA W TECHNOLOGII TR-90 Wysokiej jakości odmiana nylonu, wyjątkowo odporna na rozciąganie i wyginanie. Materiał wytrzymały na uderzenia, elastyczny, przyjemny w dotyku, o właściwościach antyalergicznych. Okulary wykonane z TR-90 są lekkie, wytrzymałe i wygodne w użytkowaniu. OKULARY POSIADAJĄ CERTYFIKAT CE. Produkt odpowiada Wytycznej Europejskiej 89/686/EWG zgodnie z normą PN-EN ISO 12312-1:2014-02/A1:2016-01. Każda para okularów posiada oryginalne oznaczenia znajdujące się na wewnętrznej stronie zauszników ; logo producenta, numer modelu, kategoria filtra oraz oznaczenie CE. O POLARYZACJI: Soczewki polaryzacyjne neutralizują oślepiające refleksy, powstające wówczas gdy światło odbija się od mokrej drogi, powierzchni wody lub śniegu. Eliminacja światła odbitego zwiększ kontrast widzenia i pozwala na bardziej komfortowe widzenie. Dlatego o</t>
         </is>
@@ -7832,35 +7953,40 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/2607_1.jpg</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
           <t>/products/2607_1.jpg</t>
         </is>
       </c>
-      <c r="W25" s="2" t="inlineStr">
+      <c r="X25" s="2" t="inlineStr">
         <is>
           <t>/products/2607_1.jpg; /products/GOYA-CP-3717-BR.jpg</t>
         </is>
       </c>
-      <c r="X25" s="2" t="inlineStr">
+      <c r="Y25" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2022/11/2607_1.jpg</t>
         </is>
       </c>
-      <c r="Y25" s="2" t="inlineStr">
+      <c r="Z25" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary przeciwsłoneczne z filtrem polaryzacyjnym - G CP3717</t>
         </is>
       </c>
-      <c r="Z25" s="2" t="inlineStr">
+      <c r="AA25" s="2" t="inlineStr">
         <is>
           <t>goya-g-cp3717-r-okulary-przeciwsloneczne-polaryzacyjne</t>
         </is>
       </c>
-      <c r="AA25" s="2" t="inlineStr">
+      <c r="AB25" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-g-cp3717-r-okulary-przeciwsloneczne-polaryzacyjne</t>
         </is>
       </c>
-      <c r="AB25" s="3" t="inlineStr">
+      <c r="AC25" s="3" t="inlineStr">
         <is>
           <t>OKULARY PRZECIWSŁONECZNE MARKI GOYA Z FILTREM POLARYZACYJNYM I UV400 Soczewki okularów GOYA o grubości 1,1 wyposażone są w filtr polaryzacyjny oraz filtr ochronny UV-400 (UV-A, UV-B, UV-C) OKULARY POSIADAJĄ CERTYFIKAT CE. Produkt odpowiada Wytycznej Europejskiej 89/686/EWG zgodnie z normą PN-EN ISO 12312-1:2014-02/A1:2016-01. Każda para okularów posiada oryginalne oznaczenia znajdujące się na wewnętrznej stronie zauszników ; logo producenta, numer modelu, kategoria filtra oraz oznaczenie CE. O POLARYZACJI: Soczewki polaryzacyjne neutralizują oślepiające refleksy, powstające wówczas gdy światło odbija się od mokrej drogi, powierzchni wody lub śniegu. Eliminacja światła odbitego zwiększ kontrast widzenia i pozwala na bardziej komfortowe widzenie. Dlatego okulary z filtrem polaryzacyjnym to idealne rozwiązanie do wszelkiego rodzaju aktywności na świeżym powietrzu, pozwalające pełniej korzystać z życia. ZALETY: Eliminują oślepiające odblaski, zmniejszając zmęczenie oczu Chronią przed szkodliwym promieniowaniem UV Zwiększają kontras</t>
         </is>
@@ -7946,35 +8072,40 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/680_4.jpg</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
           <t>/products/680_4.jpg</t>
         </is>
       </c>
-      <c r="W26" s="2" t="inlineStr">
+      <c r="X26" s="2" t="inlineStr">
         <is>
           <t>/products/680_4.jpg</t>
         </is>
       </c>
-      <c r="X26" s="2" t="inlineStr">
+      <c r="Y26" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2022/11/680_4.jpg</t>
         </is>
       </c>
-      <c r="Y26" s="2" t="inlineStr">
+      <c r="Z26" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary korekcyjne - G 95541</t>
         </is>
       </c>
-      <c r="Z26" s="2" t="inlineStr">
+      <c r="AA26" s="2" t="inlineStr">
         <is>
           <t>goya-okulary-korekcyjne-g-95541-c1</t>
         </is>
       </c>
-      <c r="AA26" s="2" t="inlineStr">
+      <c r="AB26" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-okulary-korekcyjne-g-95541-c1</t>
         </is>
       </c>
-      <c r="AB26" s="3" t="inlineStr">
+      <c r="AC26" s="3" t="inlineStr">
         <is>
           <t>OKULARY KOREKCYJNE GOYA G 95541 Produkt nowy - posiadają oryginalne zabezpieczenia, metkę oraz instrukcję użytkowania, dodatkowo w zestawie twarde etui na zawias sprężynowy Marki GOYA oraz miękką ściereczkę czyszczącą. NASZE PRODUKTY WYSYŁAMY BARDZO DOBRZE ZABEZPIECZONE W FOLIĘ TRANSPORTOWĄ I ZAPAKOWANE W WYTRZYMAŁY KARTONIK</t>
         </is>
@@ -8062,35 +8193,40 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/575_6.jpg</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
           <t>/products/575_6.jpg</t>
         </is>
       </c>
-      <c r="W27" s="2" t="inlineStr">
+      <c r="X27" s="2" t="inlineStr">
         <is>
           <t>/products/575_6.jpg; /products/575_5.jpg</t>
         </is>
       </c>
-      <c r="X27" s="2" t="inlineStr">
+      <c r="Y27" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2022/11/575_6.jpg</t>
         </is>
       </c>
-      <c r="Y27" s="2" t="inlineStr">
+      <c r="Z27" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary korekcyjne - LB 8936 C5</t>
         </is>
       </c>
-      <c r="Z27" s="2" t="inlineStr">
+      <c r="AA27" s="2" t="inlineStr">
         <is>
           <t>goya-okulary-korekcyjne-lb-8936-c5</t>
         </is>
       </c>
-      <c r="AA27" s="2" t="inlineStr">
+      <c r="AB27" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-okulary-korekcyjne-lb-8936-c5</t>
         </is>
       </c>
-      <c r="AB27" s="3" t="inlineStr">
+      <c r="AC27" s="3" t="inlineStr">
         <is>
           <t>OKULARY KOREKCYJNE GOYA LB 8936 C5 Produkt nowy ! - posiadają oryginalne zabezpieczenia, metkę oraz instrukcję użytkowania, dodatkowo w zestawie twarde etui na zawias sprężynowy Marki GOYA oraz miękką ściereczkę czyszczącą. NASZE PRODUKTY SĄ BARDZO DOBRZE ZABEZPIECZONE W FOLIĘ TRANSPORTOWĄ I ZAPAKOWANE W WYTRZYMAŁY KARTONIK</t>
         </is>
@@ -8178,35 +8314,40 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/588_4.jpg</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
           <t>/products/588_4.jpg</t>
         </is>
       </c>
-      <c r="W28" s="2" t="inlineStr">
+      <c r="X28" s="2" t="inlineStr">
         <is>
           <t>/products/588_4.jpg; /products/588_3.jpg; /products/588_2.jpg; /products/588_1.jpg</t>
         </is>
       </c>
-      <c r="X28" s="2" t="inlineStr">
+      <c r="Y28" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2022/11/588_4.jpg</t>
         </is>
       </c>
-      <c r="Y28" s="2" t="inlineStr">
+      <c r="Z28" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary korekcyjne - G 2622 C3</t>
         </is>
       </c>
-      <c r="Z28" s="2" t="inlineStr">
+      <c r="AA28" s="2" t="inlineStr">
         <is>
           <t>goya-okulary-korekcyjne-g-2622-c3</t>
         </is>
       </c>
-      <c r="AA28" s="2" t="inlineStr">
+      <c r="AB28" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-okulary-korekcyjne-g-2622-c3</t>
         </is>
       </c>
-      <c r="AB28" s="3" t="inlineStr">
+      <c r="AC28" s="3" t="inlineStr">
         <is>
           <t>OKULARY KOREKCYJNE GOYA G 2622 C3 Produkt nowy - posiadają oryginalne zabezpieczenia, metkę oraz instrukcję użytkowania, dodatkowo w zestawie twarde etui na zawias sprężynowy Marki GOYA oraz miękką ściereczkę czyszczącą. NASZE PRODUKTY WYSYŁAMY BARDZO DOBRZE ZABEZPIECZONE W FOLIĘ TRANSPORTOWĄ I ZAPAKOWANE W WYTRZYMAŁY KARTONIK</t>
         </is>
@@ -8292,35 +8433,40 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/644_4.jpg</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
           <t>/products/644_4.jpg</t>
         </is>
       </c>
-      <c r="W29" s="2" t="inlineStr">
+      <c r="X29" s="2" t="inlineStr">
         <is>
           <t>/products/644_4.jpg</t>
         </is>
       </c>
-      <c r="X29" s="2" t="inlineStr">
+      <c r="Y29" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2022/11/644_4.jpg</t>
         </is>
       </c>
-      <c r="Y29" s="2" t="inlineStr">
+      <c r="Z29" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary korekcyjne - GM 7080</t>
         </is>
       </c>
-      <c r="Z29" s="2" t="inlineStr">
+      <c r="AA29" s="2" t="inlineStr">
         <is>
           <t>goya-okulary-korekcyjne-gm-7080-c5</t>
         </is>
       </c>
-      <c r="AA29" s="2" t="inlineStr">
+      <c r="AB29" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-okulary-korekcyjne-gm-7080-c5</t>
         </is>
       </c>
-      <c r="AB29" s="3" t="inlineStr">
+      <c r="AC29" s="3" t="inlineStr">
         <is>
           <t>OKULARY KOREKCYJNE GOYA GM 7080 Produkt nowy - posiadają oryginalne zabezpieczenia, metkę oraz instrukcję użytkowania, dodatkowo w zestawie twarde etui na zawias sprężynowy Marki GOYA oraz miękką ściereczkę czyszczącą. NASZE PRODUKTY WYSYŁAMY BARDZO DOBRZE ZABEZPIECZONE W FOLIĘ TRANSPORTOWĄ I ZAPAKOWANE W WYTRZYMAŁY KARTONIK</t>
         </is>
@@ -8406,35 +8552,40 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/688_4.jpg</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
           <t>/products/688_4.jpg</t>
         </is>
       </c>
-      <c r="W30" s="2" t="inlineStr">
+      <c r="X30" s="2" t="inlineStr">
         <is>
           <t>/products/688_4.jpg</t>
         </is>
       </c>
-      <c r="X30" s="2" t="inlineStr">
+      <c r="Y30" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2022/11/688_4.jpg</t>
         </is>
       </c>
-      <c r="Y30" s="2" t="inlineStr">
+      <c r="Z30" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary korekcyjne - G 95551</t>
         </is>
       </c>
-      <c r="Z30" s="2" t="inlineStr">
+      <c r="AA30" s="2" t="inlineStr">
         <is>
           <t>goya-okulary-korekcyjne-g-95551-c2</t>
         </is>
       </c>
-      <c r="AA30" s="2" t="inlineStr">
+      <c r="AB30" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-okulary-korekcyjne-g-95551-c2</t>
         </is>
       </c>
-      <c r="AB30" s="3" t="inlineStr">
+      <c r="AC30" s="3" t="inlineStr">
         <is>
           <t>OKULARY KOREKCYJNE GOYA G 95551 Produkt nowy - posiadają oryginalne zabezpieczenia, metkę oraz instrukcję użytkowania, dodatkowo w zestawie twarde etui na zawias sprężynowy Marki GOYA oraz miękką ściereczkę czyszczącą. NASZE PRODUKTY WYSYŁAMY BARDZO DOBRZE ZABEZPIECZONE W FOLIĘ TRANSPORTOWĄ I ZAPAKOWANE W WYTRZYMAŁY KARTONIK</t>
         </is>
@@ -8526,35 +8677,40 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/G_55015_GR_A.jpg</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
           <t>/products/G_55015_GR_A.jpg</t>
         </is>
       </c>
-      <c r="W31" s="2" t="inlineStr">
+      <c r="X31" s="2" t="inlineStr">
         <is>
           <t>/products/G_55015_GR_A.jpg; /products/G_55015_GR_MOD2kw.jpg; /products/G_55015_GR_G.jpg; /products/G_55015_GR_B.jpg; /products/G_55015_GR_F.jpg; /products/G_55015_GR_S.jpg; /products/G_55015_GR_F1.jpg; /products/G_55015_GR_T.jpg</t>
         </is>
       </c>
-      <c r="X31" s="2" t="inlineStr">
+      <c r="Y31" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2025/01/G_55015_GR_A.jpg</t>
         </is>
       </c>
-      <c r="Y31" s="2" t="inlineStr">
+      <c r="Z31" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary przeciwsłoneczne z filtrem polaryzacyjnym - G 55015 GR</t>
         </is>
       </c>
-      <c r="Z31" s="2" t="inlineStr">
+      <c r="AA31" s="2" t="inlineStr">
         <is>
           <t>goya-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym-g-55015-gr</t>
         </is>
       </c>
-      <c r="AA31" s="2" t="inlineStr">
+      <c r="AB31" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym-g-55015-gr</t>
         </is>
       </c>
-      <c r="AB31" s="3" t="inlineStr">
+      <c r="AC31" s="3" t="inlineStr">
         <is>
           <t>OKULARY PRZECIWSŁONECZNE DLA KIEROWCÓW GOYA Z FILTREM POLARYZACYJNYM I UV400 Zausznik wykonane w całości z aluminium - co sprawia, że okulary są bardzo lekkie i wytrzymałe. Soczewki okularów GOYA o grubości 1,1 wyposażone są w filtr polaryzacyjny oraz filtr ochronny UV-400 (UV-A, UV-B, UV-C) ZAUSZNIKI POŁĄCZONE Z OPRAWKĄ SYSTEMEM FLEX: FLEX - elastyczne połączenie zausznika z frontem oprawy. Zwiększony zakres odchylenia zausznika do ponad 110° gwarantuje wygodę noszenia i ułatwia zakładanie oraz zdejmowanie okularów. OKULARY POSIADAJĄ CERTYFIKAT CE. Produkt odpowiada Wytycznej Europejskiej 89/686/EWG zgodnie z normą PN-EN ISO 12312-1:2014-02/A1:2016-01. Każda para okularów posiada oryginalne oznaczenia znajdujące się na wewnętrznej stronie zauszników ; logo producenta, numer modelu, kategoria filtra oraz oznaczenie CE. O POLARYZACJI: Soczewki polaryzacyjne neutralizują oślepiające refleksy, powstające wówczas gdy światło odbija się od mokrej drogi, powierzchni wody lub śniegu. Eliminacja światła odbitego zwiększ kontrast widzenia i pozwala</t>
         </is>
@@ -8642,35 +8798,40 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/652_4.jpg</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
           <t>/products/652_4.jpg</t>
         </is>
       </c>
-      <c r="W32" s="2" t="inlineStr">
+      <c r="X32" s="2" t="inlineStr">
         <is>
           <t>/products/652_4.jpg; /products/652_1.jpg; /products/652_3.jpg; /products/652_2.jpg</t>
         </is>
       </c>
-      <c r="X32" s="2" t="inlineStr">
+      <c r="Y32" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2022/11/652_4.jpg</t>
         </is>
       </c>
-      <c r="Y32" s="2" t="inlineStr">
+      <c r="Z32" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary korekcyjne - MA 3021 C3</t>
         </is>
       </c>
-      <c r="Z32" s="2" t="inlineStr">
+      <c r="AA32" s="2" t="inlineStr">
         <is>
           <t>goya-okulary-korekcyjne-ma-3021-c3</t>
         </is>
       </c>
-      <c r="AA32" s="2" t="inlineStr">
+      <c r="AB32" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-okulary-korekcyjne-ma-3021-c3</t>
         </is>
       </c>
-      <c r="AB32" s="3" t="inlineStr">
+      <c r="AC32" s="3" t="inlineStr">
         <is>
           <t>OKULARY KOREKCYJNE GOYA MA 3021 C3 Produkt nowy - posiadają oryginalne zabezpieczenia, metkę oraz instrukcję użytkowania, dodatkowo w zestawie twarde etui na zawias sprężynowy Marki GOYA oraz miękką ściereczkę czyszczącą. NASZE PRODUKTY WYSYŁAMY BARDZO DOBRZE ZABEZPIECZONE W FOLIĘ TRANSPORTOWĄ I ZAPAKOWANE W WYTRZYMAŁY KARTONIK</t>
         </is>
@@ -8758,35 +8919,40 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/575_6.jpg</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
           <t>/products/575_6.jpg</t>
         </is>
       </c>
-      <c r="W33" s="2" t="inlineStr">
+      <c r="X33" s="2" t="inlineStr">
         <is>
           <t>/products/575_6.jpg; /products/575_5.jpg</t>
         </is>
       </c>
-      <c r="X33" s="2" t="inlineStr">
+      <c r="Y33" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2022/11/575_6.jpg</t>
         </is>
       </c>
-      <c r="Y33" s="2" t="inlineStr">
+      <c r="Z33" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary korekcyjne TJ 032 C3</t>
         </is>
       </c>
-      <c r="Z33" s="2" t="inlineStr">
+      <c r="AA33" s="2" t="inlineStr">
         <is>
           <t>goya-okulary-korekcyjne-tj-032-c3</t>
         </is>
       </c>
-      <c r="AA33" s="2" t="inlineStr">
+      <c r="AB33" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-okulary-korekcyjne-tj-032-c3</t>
         </is>
       </c>
-      <c r="AB33" s="3" t="inlineStr">
+      <c r="AC33" s="3" t="inlineStr">
         <is>
           <t>OKULARY KOREKCYJNE GOYA TJ 032 C3 Produkt nowy ! - posiadają oryginalne zabezpieczenia, metkę oraz instrukcję użytkowania, dodatkowo w zestawie twarde etui na zawias sprężynowy Marki GOYA oraz miękką ściereczkę czyszczącą. NASZE PRODUKTY SĄ BARDZO DOBRZE ZABEZPIECZONE W FOLIĘ TRANSPORTOWĄ I ZAPAKOWANE W WYTRZYMAŁY KARTONIK</t>
         </is>
@@ -8872,35 +9038,40 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/577_4.jpg</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
           <t>/products/577_4.jpg</t>
         </is>
       </c>
-      <c r="W34" s="2" t="inlineStr">
+      <c r="X34" s="2" t="inlineStr">
         <is>
           <t>/products/577_4.jpg</t>
         </is>
       </c>
-      <c r="X34" s="2" t="inlineStr">
+      <c r="Y34" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2022/11/577_4.jpg</t>
         </is>
       </c>
-      <c r="Y34" s="2" t="inlineStr">
+      <c r="Z34" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary korekcyjne - G 942117</t>
         </is>
       </c>
-      <c r="Z34" s="2" t="inlineStr">
+      <c r="AA34" s="2" t="inlineStr">
         <is>
           <t>goya-okulary-korekcyjne-g-942117-c1</t>
         </is>
       </c>
-      <c r="AA34" s="2" t="inlineStr">
+      <c r="AB34" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-okulary-korekcyjne-g-942117-c1</t>
         </is>
       </c>
-      <c r="AB34" s="3" t="inlineStr">
+      <c r="AC34" s="3" t="inlineStr">
         <is>
           <t>OKULARY KOREKCYJNE GOYA G 942117 Produkt nowy - posiadają oryginalne zabezpieczenia, metkę oraz instrukcję użytkowania, dodatkowo w zestawie twarde etui na zawias sprężynowy Marki GOYA oraz miękką ściereczkę czyszczącą. NASZE PRODUKTY WYSYŁAMY BARDZO DOBRZE ZABEZPIECZONE W FOLIĘ TRANSPORTOWĄ I ZAPAKOWANE W WYTRZYMAŁY KARTONIK</t>
         </is>
@@ -8990,35 +9161,40 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/2642_1.jpg</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
           <t>/products/2642_1.jpg</t>
         </is>
       </c>
-      <c r="W35" s="2" t="inlineStr">
+      <c r="X35" s="2" t="inlineStr">
         <is>
           <t>/products/2642_1.jpg; /products/GOYA-6232-N-1.jpg</t>
         </is>
       </c>
-      <c r="X35" s="2" t="inlineStr">
+      <c r="Y35" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2022/11/2642_1.jpg</t>
         </is>
       </c>
-      <c r="Y35" s="2" t="inlineStr">
+      <c r="Z35" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary przeciwsłoneczne z filtrem polaryzacyjnym - G 6232</t>
         </is>
       </c>
-      <c r="Z35" s="2" t="inlineStr">
+      <c r="AA35" s="2" t="inlineStr">
         <is>
           <t>goya-g-6232-cz-okulary-przeciwsloneczne-polaryzacyjne</t>
         </is>
       </c>
-      <c r="AA35" s="2" t="inlineStr">
+      <c r="AB35" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-g-6232-cz-okulary-przeciwsloneczne-polaryzacyjne</t>
         </is>
       </c>
-      <c r="AB35" s="3" t="inlineStr">
+      <c r="AC35" s="3" t="inlineStr">
         <is>
           <t>OKULARY PRZECIWSŁONECZNE MARKI GOYA Z FILTREM POLARYZACYJNYM I UV400 Soczewki okularów GOYA o grubości 1,1 wyposażone są w filtr polaryzacyjny oraz filtr ochronny UV-400 (UV-A, UV-B, UV-C) OKULARY POSIADAJĄ CERTYFIKAT CE. Produkt odpowiada Wytycznej Europejskiej 89/686/EWG zgodnie z normą PN-EN ISO 12312-1:2014-02/A1:2016-01. Każda para okularów posiada oryginalne oznaczenia znajdujące się na wewnętrznej stronie zauszników ; logo producenta, numer modelu, kategoria filtra oraz oznaczenie CE. O POLARYZACJI: Soczewki polaryzacyjne neutralizują oślepiające refleksy, powstające wówczas gdy światło odbija się od mokrej drogi, powierzchni wody lub śniegu. Eliminacja światła odbitego zwiększ kontrast widzenia i pozwala na bardziej komfortowe widzenie. Dlatego okulary z filtrem polaryzacyjnym to idealne rozwiązanie do wszelkiego rodzaju aktywności na świeżym powietrzu, pozwalające pełniej korzystać z życia. ZALETY: Eliminują oślepiające odblaski, zmniejszając zmęczenie oczu Chronią przed szkodliwym promieniowaniem UV Zwiększają kont</t>
         </is>
@@ -9110,35 +9286,40 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/3129_1.jpg</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
           <t>/products/3129_1.jpg</t>
         </is>
       </c>
-      <c r="W36" s="2" t="inlineStr">
+      <c r="X36" s="2" t="inlineStr">
         <is>
           <t>/products/3129_1.jpg; /products/3129_6.jpg; /products/3129_2.jpg; /products/3129_3.jpg; /products/3129_4.jpg; /products/3129_5.jpg</t>
         </is>
       </c>
-      <c r="X36" s="2" t="inlineStr">
+      <c r="Y36" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2022/11/3129_1.jpg</t>
         </is>
       </c>
-      <c r="Y36" s="2" t="inlineStr">
+      <c r="Z36" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary przeciwsłoneczne z filtrem polaryzacyjnym - G 191 BR</t>
         </is>
       </c>
-      <c r="Z36" s="2" t="inlineStr">
+      <c r="AA36" s="2" t="inlineStr">
         <is>
           <t>goya-g-191-br-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
+      <c r="AB36" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-g-191-br-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym</t>
         </is>
       </c>
-      <c r="AB36" s="3" t="inlineStr">
+      <c r="AC36" s="3" t="inlineStr">
         <is>
           <t>OKULARY PRZECIWSŁONECZNE DLA KIEROWCÓW GOYA Z FILTREM POLARYZACYJNYM I UV400 Soczewki okularów GOYA o grubości 1,1 wyposażone są w filtr polaryzacyjny oraz filtr ochronny UV-400 (UV-A, UV-B, UV-C) OKULARY POSIADAJĄ CERTYFIKAT CE. Produkt odpowiada Wytycznej Europejskiej 89/686/EWG zgodnie z normą PN-EN ISO 12312-1:2014-02/A1:2016-01. Każda para okularów posiada oryginalne oznaczenia znajdujące się na wewnętrznej stronie zauszników ; logo producenta, numer modelu, kategoria filtra oraz oznaczenie CE. O POLARYZACJI: Soczewki polaryzacyjne neutralizują oślepiające refleksy, powstające wówczas gdy światło odbija się od mokrej drogi, powierzchni wody lub śniegu. Eliminacja światła odbitego zwiększ kontrast widzenia i pozwala na bardziej komfortowe widzenie. Dlatego okulary z filtrem polaryzacyjnym to idealne rozwiązanie do wszelkiego rodzaju aktywności na świeżym powietrzu, pozwalające pełniej korzystać z życia. ZALETY: Eliminują oślepiające odblaski, zmniejszając zmęczenie oczu Chronią przed szkodliwym promieniowaniem UV Zwiększ</t>
         </is>
@@ -9224,35 +9405,40 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/684_1.jpg</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
           <t>/products/684_1.jpg</t>
         </is>
       </c>
-      <c r="W37" s="2" t="inlineStr">
+      <c r="X37" s="2" t="inlineStr">
         <is>
           <t>/products/684_1.jpg</t>
         </is>
       </c>
-      <c r="X37" s="2" t="inlineStr">
+      <c r="Y37" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2022/11/684_1.jpg</t>
         </is>
       </c>
-      <c r="Y37" s="2" t="inlineStr">
+      <c r="Z37" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary korekcyjne - G 96302</t>
         </is>
       </c>
-      <c r="Z37" s="2" t="inlineStr">
+      <c r="AA37" s="2" t="inlineStr">
         <is>
           <t>goya-okulary-korekcyjne-g-96302-c4</t>
         </is>
       </c>
-      <c r="AA37" s="2" t="inlineStr">
+      <c r="AB37" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-okulary-korekcyjne-g-96302-c4</t>
         </is>
       </c>
-      <c r="AB37" s="3" t="inlineStr">
+      <c r="AC37" s="3" t="inlineStr">
         <is>
           <t>OKULARY KOREKCYJNE GOYA G 96302 Produkt nowy - posiadają oryginalne zabezpieczenia, metkę oraz instrukcję użytkowania, dodatkowo w zestawie twarde etui na zawias sprężynowy Marki GOYA oraz miękką ściereczkę czyszczącą. NASZE PRODUKTY WYSYŁAMY BARDZO DOBRZE ZABEZPIECZONE W FOLIĘ TRANSPORTOWĄ I ZAPAKOWANE W WYTRZYMAŁY KARTONIK</t>
         </is>
@@ -9338,35 +9524,40 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/650_4.jpg</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
           <t>/products/650_4.jpg</t>
         </is>
       </c>
-      <c r="W38" s="2" t="inlineStr">
+      <c r="X38" s="2" t="inlineStr">
         <is>
           <t>/products/650_4.jpg</t>
         </is>
       </c>
-      <c r="X38" s="2" t="inlineStr">
+      <c r="Y38" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2022/11/650_4.jpg</t>
         </is>
       </c>
-      <c r="Y38" s="2" t="inlineStr">
+      <c r="Z38" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary korekcyjne - M 8209</t>
         </is>
       </c>
-      <c r="Z38" s="2" t="inlineStr">
+      <c r="AA38" s="2" t="inlineStr">
         <is>
           <t>goya-okulary-korekcyjne-m-8209-c4</t>
         </is>
       </c>
-      <c r="AA38" s="2" t="inlineStr">
+      <c r="AB38" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-okulary-korekcyjne-m-8209-c4</t>
         </is>
       </c>
-      <c r="AB38" s="3" t="inlineStr">
+      <c r="AC38" s="3" t="inlineStr">
         <is>
           <t>OKULARY KOREKCYJNE GOYA M 8209 Produkt nowy - posiadają oryginalne zabezpieczenia, metkę oraz instrukcję użytkowania, dodatkowo w zestawie twarde etui na zawias sprężynowy Marki GOYA oraz miękką ściereczkę czyszczącą. NASZE PRODUKTY WYSYŁAMY BARDZO DOBRZE ZABEZPIECZONE W FOLIĘ TRANSPORTOWĄ I ZAPAKOWANE W WYTRZYMAŁY KARTONIK</t>
         </is>
@@ -9452,35 +9643,40 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/670_4.jpg</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
           <t>/products/670_4.jpg</t>
         </is>
       </c>
-      <c r="W39" s="2" t="inlineStr">
+      <c r="X39" s="2" t="inlineStr">
         <is>
           <t>/products/670_4.jpg</t>
         </is>
       </c>
-      <c r="X39" s="2" t="inlineStr">
+      <c r="Y39" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2022/11/670_4.jpg</t>
         </is>
       </c>
-      <c r="Y39" s="2" t="inlineStr">
+      <c r="Z39" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary korekcyjne - G 93304</t>
         </is>
       </c>
-      <c r="Z39" s="2" t="inlineStr">
+      <c r="AA39" s="2" t="inlineStr">
         <is>
           <t>goya-okulary-korekcyjne-g-93304-c2</t>
         </is>
       </c>
-      <c r="AA39" s="2" t="inlineStr">
+      <c r="AB39" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-okulary-korekcyjne-g-93304-c2</t>
         </is>
       </c>
-      <c r="AB39" s="3" t="inlineStr">
+      <c r="AC39" s="3" t="inlineStr">
         <is>
           <t>OKULARY KOREKCYJNE GOYA G 93304 Produkt nowy - posiadają oryginalne zabezpieczenia, metkę oraz instrukcję użytkowania, dodatkowo w zestawie twarde etui na zawias sprężynowy Marki GOYA oraz miękką ściereczkę czyszczącą. NASZE PRODUKTY WYSYŁAMY BARDZO DOBRZE ZABEZPIECZONE W FOLIĘ TRANSPORTOWĄ I ZAPAKOWANE W WYTRZYMAŁY KARTONIK</t>
         </is>
@@ -9568,35 +9764,40 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/609_1.jpg</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
           <t>/products/609_1.jpg</t>
         </is>
       </c>
-      <c r="W40" s="2" t="inlineStr">
+      <c r="X40" s="2" t="inlineStr">
         <is>
           <t>/products/609_1.jpg; /products/609_2.jpg; /products/609_4.jpg; /products/609_3.jpg; /products/575_6.jpg; /products/575_5.jpg</t>
         </is>
       </c>
-      <c r="X40" s="2" t="inlineStr">
+      <c r="Y40" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2022/11/609_1.jpg</t>
         </is>
       </c>
-      <c r="Y40" s="2" t="inlineStr">
+      <c r="Z40" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary korekcyjne G 2694 C2</t>
         </is>
       </c>
-      <c r="Z40" s="2" t="inlineStr">
+      <c r="AA40" s="2" t="inlineStr">
         <is>
           <t>goya-okulary-korekcyjne-g-2694-c2</t>
         </is>
       </c>
-      <c r="AA40" s="2" t="inlineStr">
+      <c r="AB40" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-okulary-korekcyjne-g-2694-c2</t>
         </is>
       </c>
-      <c r="AB40" s="3" t="inlineStr">
+      <c r="AC40" s="3" t="inlineStr">
         <is>
           <t>OKULARY KOREKCYJNE GOYA G 2694 C2 Produkt nowy ! - posiadają oryginalne zabezpieczenia, metkę oraz instrukcję użytkowania, dodatkowo w zestawie twarde etui na zawias sprężynowy Marki GOYA oraz miękką ściereczkę czyszczącą. NASZE PRODUKTY SĄ BARDZO DOBRZE ZABEZPIECZONE W FOLIĘ TRANSPORTOWĄ I ZAPAKOWANE W WYTRZYMAŁY KARTONIK</t>
         </is>
@@ -9688,35 +9889,40 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/G_55051_GR_A.jpg</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
           <t>/products/G_55051_GR_A.jpg</t>
         </is>
       </c>
-      <c r="W41" s="2" t="inlineStr">
+      <c r="X41" s="2" t="inlineStr">
         <is>
           <t>/products/G_55051_GR_A.jpg; /products/G_55051_GR_MODkw.jpg; /products/G_55051_GR_G.jpg; /products/G_55051_GR_MOD.jpg; /products/G_55051_GR_B.jpg; /products/G_55051_GR_MOD1.jpg; /products/G_55051_GR_F.jpg; /products/G_55051_GR_S.jpg; /products/G_55051_GR_F1.jpg; /products/G_55051_GR_T.jpg</t>
         </is>
       </c>
-      <c r="X41" s="2" t="inlineStr">
+      <c r="Y41" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2025/02/G_55051_GR_A.jpg</t>
         </is>
       </c>
-      <c r="Y41" s="2" t="inlineStr">
+      <c r="Z41" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary przeciwsłoneczne z filtrem polaryzacyjnym - G 55051 GR</t>
         </is>
       </c>
-      <c r="Z41" s="2" t="inlineStr">
+      <c r="AA41" s="2" t="inlineStr">
         <is>
           <t>goya-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym-g-55051-gr</t>
         </is>
       </c>
-      <c r="AA41" s="2" t="inlineStr">
+      <c r="AB41" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym-g-55051-gr</t>
         </is>
       </c>
-      <c r="AB41" s="3" t="inlineStr">
+      <c r="AC41" s="3" t="inlineStr">
         <is>
           <t>OKULARY PRZECIWSŁONECZNE DLA KIEROWCÓW GOYA Z FILTREM POLARYZACYJNYM I UV400 Oprawki wykonane w całości z aluminium - co sprawia, że okulary są bardzo lekkie i wytrzymałe. Soczewki okularów GOYA o grubości 1,1 wyposażone są w filtr polaryzacyjny oraz filtr ochronny UV-400 (UV-A, UV-B, UV-C) ZAUSZNIKI POŁĄCZONE Z OPRAWKĄ SYSTEMEM FLEX: FLEX - elastyczne połączenie zausznika z frontem oprawy. Zwiększony zakres odchylenia zausznika do ponad 110° gwarantuje wygodę noszenia i ułatwia zakładanie oraz zdejmowanie okularów. OKULARY POSIADAJĄ CERTYFIKAT CE. Produkt odpowiada Wytycznej Europejskiej 89/686/EWG zgodnie z normą PN-EN ISO 12312-1:2014-02/A1:2016-01. Każda para okularów posiada oryginalne oznaczenia znajdujące się na wewnętrznej stronie zauszników ; logo producenta, numer modelu, kategoria filtra oraz oznaczenie CE. O POLARYZACJI: Soczewki polaryzacyjne neutralizują oślepiające refleksy, powstające wówczas gdy światło odbija się od mokrej drogi, powierzchni wody lub śniegu. Eliminacja światła odbitego zwiększ kontrast widzenia i pozwala</t>
         </is>
@@ -9808,35 +10014,40 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/2638_1.jpg</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
           <t>/products/2638_1.jpg</t>
         </is>
       </c>
-      <c r="W42" s="2" t="inlineStr">
+      <c r="X42" s="2" t="inlineStr">
         <is>
           <t>/products/2638_1.jpg; /products/2638_2.jpg; /products/2638_3.jpg; /products/2638_4.jpg; /products/2638_5.jpg; /products/2638_7.jpg; /products/2638_6.jpg; /products/2638_8.jpg</t>
         </is>
       </c>
-      <c r="X42" s="2" t="inlineStr">
+      <c r="Y42" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2022/11/2638_1.jpg</t>
         </is>
       </c>
-      <c r="Y42" s="2" t="inlineStr">
+      <c r="Z42" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary przeciwsłoneczne z filtrem polaryzacyjnym - G 6230 R</t>
         </is>
       </c>
-      <c r="Z42" s="2" t="inlineStr">
+      <c r="AA42" s="2" t="inlineStr">
         <is>
           <t>goya-g-6230-r-okulary-przeciwsloneczne-polaryzacyjne</t>
         </is>
       </c>
-      <c r="AA42" s="2" t="inlineStr">
+      <c r="AB42" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-g-6230-r-okulary-przeciwsloneczne-polaryzacyjne</t>
         </is>
       </c>
-      <c r="AB42" s="3" t="inlineStr">
+      <c r="AC42" s="3" t="inlineStr">
         <is>
           <t>OKULARY PRZECIWSŁONECZNE MARKI GOYA Z FILTREM POLARYZACYJNYM I UV400 Soczewki okularów GOYA o grubości 1,1 wyposażone są w filtr polaryzacyjny oraz filtr ochronny UV-400 (UV-A, UV-B, UV-C) OKULARY POSIADAJĄ CERTYFIKAT CE. Produkt odpowiada Wytycznej Europejskiej 89/686/EWG zgodnie z normą PN-EN ISO 12312-1:2014-02/A1:2016-01. Każda para okularów posiada oryginalne oznaczenia znajdujące się na wewnętrznej stronie zauszników ; logo producenta, numer modelu, kategoria filtra oraz oznaczenie CE. O POLARYZACJI: Soczewki polaryzacyjne neutralizują oślepiające refleksy, powstające wówczas gdy światło odbija się od mokrej drogi, powierzchni wody lub śniegu. Eliminacja światła odbitego zwiększ kontrast widzenia i pozwala na bardziej komfortowe widzenie. Dlatego okulary z filtrem polaryzacyjnym to idealne rozwiązanie do wszelkiego rodzaju aktywności na świeżym powietrzu, pozwalające pełniej korzystać z życia. ZALETY: Eliminują oślepiające odblaski, zmniejszając zmęczenie oczu Chronią przed szkodliwym promieniowaniem UV Zwiększają ko</t>
         </is>
@@ -9922,35 +10133,40 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/611_4.jpg</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
           <t>/products/611_4.jpg</t>
         </is>
       </c>
-      <c r="W43" s="2" t="inlineStr">
+      <c r="X43" s="2" t="inlineStr">
         <is>
           <t>/products/611_4.jpg</t>
         </is>
       </c>
-      <c r="X43" s="2" t="inlineStr">
+      <c r="Y43" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2022/11/611_4.jpg</t>
         </is>
       </c>
-      <c r="Y43" s="2" t="inlineStr">
+      <c r="Z43" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary korekcyjne - G 2682</t>
         </is>
       </c>
-      <c r="Z43" s="2" t="inlineStr">
+      <c r="AA43" s="2" t="inlineStr">
         <is>
           <t>goya-okulary-korekcyjne-g-2682-c4</t>
         </is>
       </c>
-      <c r="AA43" s="2" t="inlineStr">
+      <c r="AB43" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-okulary-korekcyjne-g-2682-c4</t>
         </is>
       </c>
-      <c r="AB43" s="3" t="inlineStr">
+      <c r="AC43" s="3" t="inlineStr">
         <is>
           <t>OKULARY KOREKCYJNE GOYA G 2682 Produkt nowy - posiadają oryginalne zabezpieczenia, metkę oraz instrukcję użytkowania, dodatkowo w zestawie twarde etui na zawias sprężynowy Marki GOYA oraz miękką ściereczkę czyszczącą. NASZE PRODUKTY WYSYŁAMY BARDZO DOBRZE ZABEZPIECZONE W FOLIĘ TRANSPORTOWĄ I ZAPAKOWANE W WYTRZYMAŁY KARTONIK</t>
         </is>
@@ -10038,35 +10254,40 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/675_4.jpg</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
           <t>/products/675_4.jpg</t>
         </is>
       </c>
-      <c r="W44" s="2" t="inlineStr">
+      <c r="X44" s="2" t="inlineStr">
         <is>
           <t>/products/675_4.jpg; /products/675_1.jpg; /products/675_3.jpg; /products/675_2.jpg</t>
         </is>
       </c>
-      <c r="X44" s="2" t="inlineStr">
+      <c r="Y44" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2022/11/675_4.jpg</t>
         </is>
       </c>
-      <c r="Y44" s="2" t="inlineStr">
+      <c r="Z44" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary korekcyjne - G 94319 C2</t>
         </is>
       </c>
-      <c r="Z44" s="2" t="inlineStr">
+      <c r="AA44" s="2" t="inlineStr">
         <is>
           <t>goya-okulary-korekcyjne-g-94319-c2</t>
         </is>
       </c>
-      <c r="AA44" s="2" t="inlineStr">
+      <c r="AB44" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-okulary-korekcyjne-g-94319-c2</t>
         </is>
       </c>
-      <c r="AB44" s="3" t="inlineStr">
+      <c r="AC44" s="3" t="inlineStr">
         <is>
           <t>OKULARY KOREKCYJNE GOYA G 94319 C2 Produkt nowy - posiadają oryginalne zabezpieczenia, metkę oraz instrukcję użytkowania, dodatkowo w zestawie twarde etui na zawias sprężynowy Marki GOYA oraz miękką ściereczkę czyszczącą. NASZE PRODUKTY WYSYŁAMY BARDZO DOBRZE ZABEZPIECZONE W FOLIĘ TRANSPORTOWĄ I ZAPAKOWANE W WYTRZYMAŁY KARTONIK</t>
         </is>
@@ -10156,35 +10377,40 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/3189_1.jpg</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
           <t>/products/3189_1.jpg</t>
         </is>
       </c>
-      <c r="W45" s="2" t="inlineStr">
+      <c r="X45" s="2" t="inlineStr">
         <is>
           <t>/products/3189_1.jpg; /products/3188_5.jpg</t>
         </is>
       </c>
-      <c r="X45" s="2" t="inlineStr">
+      <c r="Y45" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2023/01/3189_1.jpg</t>
         </is>
       </c>
-      <c r="Y45" s="2" t="inlineStr">
+      <c r="Z45" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary przeciwsłoneczne z filtrem polaryzacyjnym - G 149</t>
         </is>
       </c>
-      <c r="Z45" s="2" t="inlineStr">
+      <c r="AA45" s="2" t="inlineStr">
         <is>
           <t>goya-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym-g-149</t>
         </is>
       </c>
-      <c r="AA45" s="2" t="inlineStr">
+      <c r="AB45" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym-g-149</t>
         </is>
       </c>
-      <c r="AB45" s="3" t="inlineStr">
+      <c r="AC45" s="3" t="inlineStr">
         <is>
           <t>OKULARY PRZECIWSŁONECZNE DLA KIEROWCÓW GOYA Z FILTREM POLARYZACYJNYM I UV400 Oprawka wykonana w technologii - wycinania z płyty. Ręcznie obrabiana. Soczewki okularów GOYA o grubości 1,1 wyposażone są w filtr polaryzacyjny oraz filtr ochronny UV-400 (UV-A, UV-B, UV-C) OKULARY POSIADAJĄ CERTYFIKAT CE. Produkt odpowiada Wytycznej Europejskiej 89/686/EWG zgodnie z normą PN-EN ISO 12312-1:2014-02/A1:2016-01. Każda para okularów posiada oryginalne oznaczenia znajdujące się na wewnętrznej stronie zauszników ; logo producenta, numer modelu, kategoria filtra oraz oznaczenie CE. O POLARYZACJI: Soczewki polaryzacyjne neutralizują oślepiające refleksy, powstające wówczas gdy światło odbija się od mokrej drogi, powierzchni wody lub śniegu. Eliminacja światła odbitego zwiększ kontrast widzenia i pozwala na bardziej komfortowe widzenie. Dlatego okulary z filtrem polaryzacyjnym to idealne rozwiązanie do wszelkiego rodzaju aktywności na świeżym powietrzu, pozwalające pełniej korzystać z życia. ZALETY: Eliminują oślepiające odblaski, zmniejszaj</t>
         </is>
@@ -10276,35 +10502,40 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/G_55021_CZ_A.jpg</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
           <t>/products/G_55021_CZ_A.jpg</t>
         </is>
       </c>
-      <c r="W46" s="2" t="inlineStr">
+      <c r="X46" s="2" t="inlineStr">
         <is>
           <t>/products/G_55021_CZ_A.jpg; /products/G_55021_CZ_MOD1kw.jpg; /products/G_55021_CZ_G.jpg; /products/G_55021_CZ_MOD.jpg; /products/G_55021_CZ_B.jpg; /products/G_55021_CZ_MOD1.jpg; /products/G_55021_CZ_F.jpg; /products/G_55021_CZ_S.jpg; /products/G_55021_CZ_F1.jpg; /products/G_55021_CZ_T.jpg</t>
         </is>
       </c>
-      <c r="X46" s="2" t="inlineStr">
+      <c r="Y46" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2025/02/G_55021_CZ_A.jpg</t>
         </is>
       </c>
-      <c r="Y46" s="2" t="inlineStr">
+      <c r="Z46" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary przeciwsłoneczne z filtrem polaryzacyjnym - G 55021 CZ</t>
         </is>
       </c>
-      <c r="Z46" s="2" t="inlineStr">
+      <c r="AA46" s="2" t="inlineStr">
         <is>
           <t>goya-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym-g-55021-cz</t>
         </is>
       </c>
-      <c r="AA46" s="2" t="inlineStr">
+      <c r="AB46" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym-g-55021-cz</t>
         </is>
       </c>
-      <c r="AB46" s="3" t="inlineStr">
+      <c r="AC46" s="3" t="inlineStr">
         <is>
           <t>OKULARY PRZECIWSŁONECZNE DLA KIEROWCÓW GOYA Z FILTREM POLARYZACYJNYM I UV400 Zausznik wykonane w całości z aluminium - co sprawia, że okulary są bardzo lekkie i wytrzymałe. Soczewki okularów GOYA o grubości 1,1 wyposażone są w filtr polaryzacyjny oraz filtr ochronny UV-400 (UV-A, UV-B, UV-C) ZAUSZNIKI POŁĄCZONE Z OPRAWKĄ SYSTEMEM FLEX: FLEX - elastyczne połączenie zausznika z frontem oprawy. Zwiększony zakres odchylenia zausznika do ponad 110° gwarantuje wygodę noszenia i ułatwia zakładanie oraz zdejmowanie okularów. OKULARY POSIADAJĄ CERTYFIKAT CE. Produkt odpowiada Wytycznej Europejskiej 89/686/EWG zgodnie z normą PN-EN ISO 12312-1:2014-02/A1:2016-01. Każda para okularów posiada oryginalne oznaczenia znajdujące się na wewnętrznej stronie zauszników ; logo producenta, numer modelu, kategoria filtra oraz oznaczenie CE. O POLARYZACJI: Soczewki polaryzacyjne neutralizują oślepiające refleksy, powstające wówczas gdy światło odbija się od mokrej drogi, powierzchni wody lub śniegu. Eliminacja światła odbitego zwiększ kontrast widzenia i pozwala</t>
         </is>
@@ -10396,35 +10627,40 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/3154_6.jpg</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
           <t>/products/3154_6.jpg</t>
         </is>
       </c>
-      <c r="W47" s="2" t="inlineStr">
+      <c r="X47" s="2" t="inlineStr">
         <is>
           <t>/products/3154_6.jpg; /products/3154_1.jpg; /products/3154_5.jpg; /products/3154_4.jpg; /products/3154_3.jpg; /products/3154_2.jpg</t>
         </is>
       </c>
-      <c r="X47" s="2" t="inlineStr">
+      <c r="Y47" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2022/11/3154_6.jpg</t>
         </is>
       </c>
-      <c r="Y47" s="2" t="inlineStr">
+      <c r="Z47" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary przeciwsłoneczne z filtrem polaryzacyjnym - G 177 CZ</t>
         </is>
       </c>
-      <c r="Z47" s="2" t="inlineStr">
+      <c r="AA47" s="2" t="inlineStr">
         <is>
           <t>goya-g-177-cz-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym</t>
         </is>
       </c>
-      <c r="AA47" s="2" t="inlineStr">
+      <c r="AB47" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-g-177-cz-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym</t>
         </is>
       </c>
-      <c r="AB47" s="3" t="inlineStr">
+      <c r="AC47" s="3" t="inlineStr">
         <is>
           <t>OKULARY PRZECIWSŁONECZNE DLA KIEROWCÓW GOYA Z FILTREM POLARYZACYJNYM I UV400 Soczewki okularów GOYA o grubości 1,1 wyposażone są w filtr polaryzacyjny oraz filtr ochronny UV-400 (UV-A, UV-B, UV-C) OPRAWKA WYKONANA W TECHNOLOGII TR-90 Wysokiej jakości odmiana nylonu, wyjątkowo odporna na rozciąganie i wyginanie. Materiał wytrzymały na uderzenia, elastyczny, przyjemny w dotyku, o właściwościach antyalergicznych. Okulary wykonane z TR-90 są lekkie, wytrzymałe i wygodne w użytkowaniu. OKULARY POSIADAJĄ CERTYFIKAT CE. Produkt odpowiada Wytycznej Europejskiej 89/686/EWG zgodnie z normą PN-EN ISO 12312-1:2014-02/A1:2016-01. Każda para okularów posiada oryginalne oznaczenia znajdujące się na wewnętrznej stronie zauszników ; logo producenta, numer modelu, kategoria filtra oraz oznaczenie CE. O POLARYZACJI: Soczewki polaryzacyjne neutralizują oślepiające refleksy, powstające wówczas gdy światło odbija się od mokrej drogi, powierzchni wody lub śniegu. Eliminacja światła odbitego zwiększ kontrast widzenia i pozwala na bardziej komfortowe widzenie. Dlatego o</t>
         </is>
@@ -10516,35 +10752,40 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/G_55015_BR_A.jpg</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
           <t>/products/G_55015_BR_A.jpg</t>
         </is>
       </c>
-      <c r="W48" s="2" t="inlineStr">
+      <c r="X48" s="2" t="inlineStr">
         <is>
           <t>/products/G_55015_BR_A.jpg; /products/G_55015_BR_MODkw.jpg; /products/G_55015_BR_G.jpg; /products/G_55015_BR_MOD2.jpg; /products/G_55015_BR_B.jpg; /products/G_55015_BR_MOD3.jpg; /products/G_55015_BR_F.jpg; /products/G_55015_BR_MOD1.jpg; /products/G_55015_BR_S.jpg; /products/G_55015_BR_F1.jpg; /products/G_55015_BR_T.jpg</t>
         </is>
       </c>
-      <c r="X48" s="2" t="inlineStr">
+      <c r="Y48" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2025/01/G_55015_BR_A.jpg</t>
         </is>
       </c>
-      <c r="Y48" s="2" t="inlineStr">
+      <c r="Z48" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary przeciwsłoneczne z filtrem polaryzacyjnym - G 55015 BR</t>
         </is>
       </c>
-      <c r="Z48" s="2" t="inlineStr">
+      <c r="AA48" s="2" t="inlineStr">
         <is>
           <t>goya-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym-g-55015-br</t>
         </is>
       </c>
-      <c r="AA48" s="2" t="inlineStr">
+      <c r="AB48" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym-g-55015-br</t>
         </is>
       </c>
-      <c r="AB48" s="3" t="inlineStr">
+      <c r="AC48" s="3" t="inlineStr">
         <is>
           <t>OKULARY PRZECIWSŁONECZNE DLA KIEROWCÓW GOYA Z FILTREM POLARYZACYJNYM I UV400 Zausznik wykonane w całości z aluminium - co sprawia, że okulary są bardzo lekkie i wytrzymałe. Soczewki okularów GOYA o grubości 1,1 wyposażone są w filtr polaryzacyjny oraz filtr ochronny UV-400 (UV-A, UV-B, UV-C) ZAUSZNIKI POŁĄCZONE Z OPRAWKĄ SYSTEMEM FLEX: FLEX - elastyczne połączenie zausznika z frontem oprawy. Zwiększony zakres odchylenia zausznika do ponad 110° gwarantuje wygodę noszenia i ułatwia zakładanie oraz zdejmowanie okularów. OKULARY POSIADAJĄ CERTYFIKAT CE. Produkt odpowiada Wytycznej Europejskiej 89/686/EWG zgodnie z normą PN-EN ISO 12312-1:2014-02/A1:2016-01. Każda para okularów posiada oryginalne oznaczenia znajdujące się na wewnętrznej stronie zauszników ; logo producenta, numer modelu, kategoria filtra oraz oznaczenie CE. O POLARYZACJI: Soczewki polaryzacyjne neutralizują oślepiające refleksy, powstające wówczas gdy światło odbija się od mokrej drogi, powierzchni wody lub śniegu. Eliminacja światła odbitego zwiększ kontrast widzenia i pozwala</t>
         </is>
@@ -10634,35 +10875,40 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/674_4.jpg</t>
+        </is>
+      </c>
+      <c r="W49" s="2" t="inlineStr">
+        <is>
           <t>/products/674_4.jpg</t>
         </is>
       </c>
-      <c r="W49" s="2" t="inlineStr">
+      <c r="X49" s="2" t="inlineStr">
         <is>
           <t>/products/674_4.jpg</t>
         </is>
       </c>
-      <c r="X49" s="2" t="inlineStr">
+      <c r="Y49" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2022/11/674_4.jpg</t>
         </is>
       </c>
-      <c r="Y49" s="2" t="inlineStr">
+      <c r="Z49" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary korekcyjne - G 94402</t>
         </is>
       </c>
-      <c r="Z49" s="2" t="inlineStr">
+      <c r="AA49" s="2" t="inlineStr">
         <is>
           <t>goya-okulary-korekcyjne-g-94402-c1</t>
         </is>
       </c>
-      <c r="AA49" s="2" t="inlineStr">
+      <c r="AB49" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-okulary-korekcyjne-g-94402-c1</t>
         </is>
       </c>
-      <c r="AB49" s="3" t="inlineStr">
+      <c r="AC49" s="3" t="inlineStr">
         <is>
           <t>OKULARY KOREKCYJNE GOYA G 94402 Produkt nowy - posiadają oryginalne zabezpieczenia, metkę oraz instrukcję użytkowania, dodatkowo w zestawie twarde etui na zawias sprężynowy Marki GOYA oraz miękką ściereczkę czyszczącą. NASZE PRODUKTY WYSYŁAMY BARDZO DOBRZE ZABEZPIECZONE W FOLIĘ TRANSPORTOWĄ I ZAPAKOWANE W WYTRZYMAŁY KARTONIK</t>
         </is>
@@ -10752,35 +10998,40 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/967_1.jpg</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
           <t>/products/967_1.jpg</t>
         </is>
       </c>
-      <c r="W50" s="2" t="inlineStr">
+      <c r="X50" s="2" t="inlineStr">
         <is>
           <t>/products/967_1.jpg</t>
         </is>
       </c>
-      <c r="X50" s="2" t="inlineStr">
+      <c r="Y50" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2022/11/967_1.jpg</t>
         </is>
       </c>
-      <c r="Y50" s="2" t="inlineStr">
+      <c r="Z50" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary przeciwsłoneczne z filtrem polaryzacyjnym - G1904</t>
         </is>
       </c>
-      <c r="Z50" s="2" t="inlineStr">
+      <c r="AA50" s="2" t="inlineStr">
         <is>
           <t>goya-g1904-c2-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym-kopia</t>
         </is>
       </c>
-      <c r="AA50" s="2" t="inlineStr">
+      <c r="AB50" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-g1904-c2-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym-kopia</t>
         </is>
       </c>
-      <c r="AB50" s="3" t="inlineStr">
+      <c r="AC50" s="3" t="inlineStr">
         <is>
           <t>OKULARY PRZECIWSŁONECZNE DLA KIEROWCÓW GOYA Z FILTREM POLARYZACYJNYM I UV400 Soczewki okularów GOYA o grubości 1,1 wyposażone są w filtr polaryzacyjny oraz filtr ochronny UV-400 (UV-A, UV-B, UV-C) OPRAWKA WYKONANA W TECHNOLOGII TR-90 Wysokiej jakości odmiana nylonu, wyjątkowo odporna na rozciąganie i wyginanie. Materiał wytrzymały na uderzenia, elastyczny, przyjemny w dotyku, o właściwościach antyalergicznych. Okulary wykonane z TR-90 są lekkie, wytrzymałe i wygodne w użytkowaniu. ZAUSZNIKI POŁĄCZONE Z OPRAWKĄ SYSTEMEM FLEX: FLEX - elastyczne połączenie zausznika z frontem oprawy. Zwiększony zakres odchylenia zausznika do ponad 110° gwarantuje wygodę noszenia i ułatwia zakładanie oraz zdejmowanie okularów. OKULARY POSIADAJĄ CERTYFIKAT CE. Produkt odpowiada Wytycznej Europejskiej 89/686/EWG zgodnie z normą PN-EN ISO 12312-1:2014-02/A1:2016-01. Każda para okularów posiada oryginalne oznaczenia znajdujące się na wewnętrznej stronie zauszników ; logo producenta, numer modelu, kategoria filtra oraz oznaczenie CE. O POLARYZACJI: Soczewki pola</t>
         </is>
@@ -10870,35 +11121,40 @@
       </c>
       <c r="V51" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/3160_6.jpg</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
           <t>/products/3160_6.jpg</t>
         </is>
       </c>
-      <c r="W51" s="2" t="inlineStr">
+      <c r="X51" s="2" t="inlineStr">
         <is>
           <t>/products/3160_6.jpg; /products/3158_1.jpg</t>
         </is>
       </c>
-      <c r="X51" s="2" t="inlineStr">
+      <c r="Y51" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2022/11/3160_6.jpg</t>
         </is>
       </c>
-      <c r="Y51" s="2" t="inlineStr">
+      <c r="Z51" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary przeciwsłoneczne z filtrem polaryzacyjnym - G 172</t>
         </is>
       </c>
-      <c r="Z51" s="2" t="inlineStr">
+      <c r="AA51" s="2" t="inlineStr">
         <is>
           <t>goya-g-172-br-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym</t>
         </is>
       </c>
-      <c r="AA51" s="2" t="inlineStr">
+      <c r="AB51" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-g-172-br-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym</t>
         </is>
       </c>
-      <c r="AB51" s="3" t="inlineStr">
+      <c r="AC51" s="3" t="inlineStr">
         <is>
           <t>OKULARY PRZECIWSŁONECZNE DLA KIEROWCÓW GOYA Z FILTREM POLARYZACYJNYM I UV400 Oprawka wykonana w technologii - wycinania z płyty. Ręcznie obrabiana. Soczewki okularów GOYA o grubości 1,1 wyposażone są w filtr polaryzacyjny oraz filtr ochronny UV-400 (UV-A, UV-B, UV-C) OPRAWKA WYKONANA W TECHNOLOGII TR-90 Wysokiej jakości odmiana nylonu, wyjątkowo odporna na rozciąganie i wyginanie. Materiał wytrzymały na uderzenia, elastyczny, przyjemny w dotyku, o właściwościach antyalergicznych. Okulary wykonane z TR-90 są lekkie, wytrzymałe i wygodne w użytkowaniu. OKULARY POSIADAJĄ CERTYFIKAT CE. Produkt odpowiada Wytycznej Europejskiej 89/686/EWG zgodnie z normą PN-EN ISO 12312-1:2014-02/A1:2016-01. Każda para okularów posiada oryginalne oznaczenia znajdujące się na wewnętrznej stronie zauszników ; logo producenta, numer modelu, kategoria filtra oraz oznaczenie CE. O POLARYZACJI: Soczewki polaryzacyjne neutralizują oślepiające refleksy, powstające wówczas gdy światło odbija się od mokrej drogi, powierzchni wody lub śniegu. Eliminacja światła odbitego zwięk</t>
         </is>
@@ -10988,35 +11244,40 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/181_1.jpg</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
           <t>/products/181_1.jpg</t>
         </is>
       </c>
-      <c r="W52" s="2" t="inlineStr">
+      <c r="X52" s="2" t="inlineStr">
         <is>
           <t>/products/181_1.jpg</t>
         </is>
       </c>
-      <c r="X52" s="2" t="inlineStr">
+      <c r="Y52" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2022/11/181_1.jpg</t>
         </is>
       </c>
-      <c r="Y52" s="2" t="inlineStr">
+      <c r="Z52" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary przeciwsłoneczne z filtrem polaryzacyjnym - G 0901S</t>
         </is>
       </c>
-      <c r="Z52" s="2" t="inlineStr">
+      <c r="AA52" s="2" t="inlineStr">
         <is>
           <t>goya-g-0901s-p-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym-pilotki-lustrzanki</t>
         </is>
       </c>
-      <c r="AA52" s="2" t="inlineStr">
+      <c r="AB52" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-g-0901s-p-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym-pilotki-lustrzanki</t>
         </is>
       </c>
-      <c r="AB52" s="3" t="inlineStr">
+      <c r="AC52" s="3" t="inlineStr">
         <is>
           <t>OKULARY PRZECIWSŁONECZNE GOYA Z FILTREM POLARYZACYJNYM I UV400 Soczewki okularów GOYA o grubości 1,1 wyposażone są w filtr polaryzacyjny oraz filtr ochronny UV-400 (UV-A, UV-B, UV-C) OKULARY POSIADAJĄ CERTYFIKAT CE. Produkt odpowiada Wytycznej Europejskiej 89/686/EWG zgodnie z normą PN-EN ISO 12312-1:2014-02/A1:2016-01. Każda para okularów posiada oryginalne oznaczenia znajdujące się na wewnętrznej stronie zauszników ; logo producenta, numer modelu, kategoria filtra oraz oznaczenie CE. O POLARYZACJI: Soczewki polaryzacyjne neutralizują oślepiające refleksy, powstające wówczas gdy światło odbija się od mokrej drogi, powierzchni wody lub śniegu. Eliminacja światła odbitego zwiększ kontrast widzenia i pozwala na bardziej komfortowe widzenie. Dlatego okulary z filtrem polaryzacyjnym to idealne rozwiązanie do wszelkiego rodzaju aktywności na świeżym powietrzu, pozwalające pełniej korzystać z życia. ZALETY: Eliminują oślepiające odblaski, zmniejszając zmęczenie oczu Chronią przed szkodliwym promieniowaniem UV Zwiększają kontrast w</t>
         </is>
@@ -11104,35 +11365,40 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/584_4.jpg</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
           <t>/products/584_4.jpg</t>
         </is>
       </c>
-      <c r="W53" s="2" t="inlineStr">
+      <c r="X53" s="2" t="inlineStr">
         <is>
           <t>/products/584_4.jpg; /products/584_1.jpg; /products/584_2.jpg; /products/584_3.jpg</t>
         </is>
       </c>
-      <c r="X53" s="2" t="inlineStr">
+      <c r="Y53" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2022/11/584_4.jpg</t>
         </is>
       </c>
-      <c r="Y53" s="2" t="inlineStr">
+      <c r="Z53" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary korekcyjne - G 2615 C1</t>
         </is>
       </c>
-      <c r="Z53" s="2" t="inlineStr">
+      <c r="AA53" s="2" t="inlineStr">
         <is>
           <t>goya-okulary-korekcyjne-g-2615-c1</t>
         </is>
       </c>
-      <c r="AA53" s="2" t="inlineStr">
+      <c r="AB53" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-okulary-korekcyjne-g-2615-c1</t>
         </is>
       </c>
-      <c r="AB53" s="3" t="inlineStr">
+      <c r="AC53" s="3" t="inlineStr">
         <is>
           <t>OKULARY KOREKCYJNE GOYA G 2615 C1 Produkt nowy - posiadają oryginalne zabezpieczenia, metkę oraz instrukcję użytkowania, dodatkowo w zestawie twarde etui na zawias sprężynowy Marki GOYA oraz miękką ściereczkę czyszczącą. NASZE PRODUKTY WYSYŁAMY BARDZO DOBRZE ZABEZPIECZONE W FOLIĘ TRANSPORTOWĄ I ZAPAKOWANE W WYTRZYMAŁY KARTONIK</t>
         </is>
@@ -11222,35 +11488,40 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/1615_2.jpg</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
           <t>/products/1615_2.jpg</t>
         </is>
       </c>
-      <c r="W54" s="2" t="inlineStr">
+      <c r="X54" s="2" t="inlineStr">
         <is>
           <t>/products/1615_2.jpg</t>
         </is>
       </c>
-      <c r="X54" s="2" t="inlineStr">
+      <c r="Y54" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2023/02/1615_2.jpg</t>
         </is>
       </c>
-      <c r="Y54" s="2" t="inlineStr">
+      <c r="Z54" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary przeciwsłoneczne z filtrem polaryzacyjnym - G 55T001</t>
         </is>
       </c>
-      <c r="Z54" s="2" t="inlineStr">
+      <c r="AA54" s="2" t="inlineStr">
         <is>
           <t>okulary-przeciwsloneczne-polaryzacyjne-dla-kierowcow-goya-g-55t001-cz</t>
         </is>
       </c>
-      <c r="AA54" s="2" t="inlineStr">
+      <c r="AB54" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/okulary-przeciwsloneczne-polaryzacyjne-dla-kierowcow-goya-g-55t001-cz</t>
         </is>
       </c>
-      <c r="AB54" s="3" t="inlineStr">
+      <c r="AC54" s="3" t="inlineStr">
         <is>
           <t>OKULARY PRZECIWSŁONECZNE DLA KIEROWCÓW GOYA Z FILTREM POLARYZACYJNYM I UV400 Zauszniki oprawek wykonane z aluminium - co sprawia, że okulary są bardzo lekkie i wytrzymałe. Soczewki okularów GOYA o grubości 1,1 wyposażone są w filtr polaryzacyjny oraz filtr ochronny UV-400 (UV-A, UV-B, UV-C) OPRAWKA WYKONANA W TECHNOLOGII TR-90 Wysokiej jakości odmiana nylonu, wyjątkowo odporna na rozciąganie i wyginanie. Materiał wytrzymały na uderzenia, elastyczny, przyjemny w dotyku, o właściwościach antyalergicznych. Okulary wykonane z TR-90 są lekkie, wytrzymałe i wygodne w użytkowaniu. ZAUSZNIKI POŁĄCZONE Z OPRAWKĄ SYSTEMEM FLEX: FLEX - elastyczne połączenie zausznika z frontem oprawy. Zwiększony zakres odchylenia zausznika do ponad 110° gwarantuje wygodę noszenia i ułatwia zakładanie oraz zdejmowanie okularów. OKULARY POSIADAJĄ CERTYFIKAT CE. Produkt odpowiada Wytycznej Europejskiej 89/686/EWG zgodnie z normą PN-EN ISO 12312-1:2014-02/A1:2016-01. Każda para okularów posiada oryginalne oznaczenia znajdujące się na wewnętrznej stronie zauszników ; logo p</t>
         </is>
@@ -11342,35 +11613,40 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/G_55054_CZ_A.jpg</t>
+        </is>
+      </c>
+      <c r="W55" s="2" t="inlineStr">
+        <is>
           <t>/products/G_55054_CZ_A.jpg</t>
         </is>
       </c>
-      <c r="W55" s="2" t="inlineStr">
+      <c r="X55" s="2" t="inlineStr">
         <is>
           <t>/products/G_55054_CZ_A.jpg; /products/G_55054_CZ_MOD2kw.jpg; /products/G_55054_CZ_G.jpg; /products/G_55054_CZ_MOD1.jpg; /products/G_55054_CZ_F.jpg; /products/G_55054_CZ_MOD.jpg; /products/G_55054_CZ_B.jpg; /products/G_55054_CZ_MOD2.jpg; /products/G_55054_CZ_S.jpg; /products/G_55054_CZ_F1.jpg; /products/G_55054_CZ_T.jpg</t>
         </is>
       </c>
-      <c r="X55" s="2" t="inlineStr">
+      <c r="Y55" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2025/02/G_55054_CZ_A.jpg</t>
         </is>
       </c>
-      <c r="Y55" s="2" t="inlineStr">
+      <c r="Z55" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary przeciwsłoneczne z filtrem polaryzacyjnym - G 55054 CZ</t>
         </is>
       </c>
-      <c r="Z55" s="2" t="inlineStr">
+      <c r="AA55" s="2" t="inlineStr">
         <is>
           <t>goya-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym-g-55054-cz</t>
         </is>
       </c>
-      <c r="AA55" s="2" t="inlineStr">
+      <c r="AB55" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym-g-55054-cz</t>
         </is>
       </c>
-      <c r="AB55" s="3" t="inlineStr">
+      <c r="AC55" s="3" t="inlineStr">
         <is>
           <t>OKULARY PRZECIWSŁONECZNE DLA KIEROWCÓW GOYA Z FILTREM POLARYZACYJNYM I UV400 Oprawki wykonane w całości z aluminium - co sprawia, że okulary są bardzo lekkie i wytrzymałe. Soczewki okularów GOYA o grubości 1,1 wyposażone są w filtr polaryzacyjny oraz filtr ochronny UV-400 (UV-A, UV-B, UV-C) ZAUSZNIKI POŁĄCZONE Z OPRAWKĄ SYSTEMEM FLEX: FLEX - elastyczne połączenie zausznika z frontem oprawy. Zwiększony zakres odchylenia zausznika do ponad 110° gwarantuje wygodę noszenia i ułatwia zakładanie oraz zdejmowanie okularów. OKULARY POSIADAJĄ CERTYFIKAT CE. Produkt odpowiada Wytycznej Europejskiej 89/686/EWG zgodnie z normą PN-EN ISO 12312-1:2014-02/A1:2016-01. Każda para okularów posiada oryginalne oznaczenia znajdujące się na wewnętrznej stronie zauszników ; logo producenta, numer modelu, kategoria filtra oraz oznaczenie CE. O POLARYZACJI: Soczewki polaryzacyjne neutralizują oślepiające refleksy, powstające wówczas gdy światło odbija się od mokrej drogi, powierzchni wody lub śniegu. Eliminacja światła odbitego zwiększ kontrast widzenia i pozwala</t>
         </is>
@@ -11458,35 +11734,40 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/618_4.jpg</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
           <t>/products/618_4.jpg</t>
         </is>
       </c>
-      <c r="W56" s="2" t="inlineStr">
+      <c r="X56" s="2" t="inlineStr">
         <is>
           <t>/products/618_4.jpg; /products/618_1.jpg; /products/618_3.jpg; /products/618_2.jpg</t>
         </is>
       </c>
-      <c r="X56" s="2" t="inlineStr">
+      <c r="Y56" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2022/11/618_4.jpg</t>
         </is>
       </c>
-      <c r="Y56" s="2" t="inlineStr">
+      <c r="Z56" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary korekcyjne - G 2717 C4</t>
         </is>
       </c>
-      <c r="Z56" s="2" t="inlineStr">
+      <c r="AA56" s="2" t="inlineStr">
         <is>
           <t>goya-okulary-korekcyjne-g-2717-c4</t>
         </is>
       </c>
-      <c r="AA56" s="2" t="inlineStr">
+      <c r="AB56" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-okulary-korekcyjne-g-2717-c4</t>
         </is>
       </c>
-      <c r="AB56" s="3" t="inlineStr">
+      <c r="AC56" s="3" t="inlineStr">
         <is>
           <t>OKULARY KOREKCYJNE GOYA G 2717 C4 Produkt nowy - posiadają oryginalne zabezpieczenia, metkę oraz instrukcję użytkowania, dodatkowo w zestawie twarde etui na zawias sprężynowy Marki GOYA oraz miękką ściereczkę czyszczącą. NASZE PRODUKTY WYSYŁAMY BARDZO DOBRZE ZABEZPIECZONE W FOLIĘ TRANSPORTOWĄ I ZAPAKOWANE W WYTRZYMAŁY KARTONIK</t>
         </is>
@@ -11572,35 +11853,40 @@
       </c>
       <c r="V57" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/694_4.jpg</t>
+        </is>
+      </c>
+      <c r="W57" s="2" t="inlineStr">
+        <is>
           <t>/products/694_4.jpg</t>
         </is>
       </c>
-      <c r="W57" s="2" t="inlineStr">
+      <c r="X57" s="2" t="inlineStr">
         <is>
           <t>/products/694_4.jpg</t>
         </is>
       </c>
-      <c r="X57" s="2" t="inlineStr">
+      <c r="Y57" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2022/11/694_4.jpg</t>
         </is>
       </c>
-      <c r="Y57" s="2" t="inlineStr">
+      <c r="Z57" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary korekcyjne - G 93305</t>
         </is>
       </c>
-      <c r="Z57" s="2" t="inlineStr">
+      <c r="AA57" s="2" t="inlineStr">
         <is>
           <t>goya-okulary-korekcyjne-g-93305-c2</t>
         </is>
       </c>
-      <c r="AA57" s="2" t="inlineStr">
+      <c r="AB57" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-okulary-korekcyjne-g-93305-c2</t>
         </is>
       </c>
-      <c r="AB57" s="3" t="inlineStr">
+      <c r="AC57" s="3" t="inlineStr">
         <is>
           <t>OKULARY KOREKCYJNE GOYA G 93305 Produkt nowy - posiadają oryginalne zabezpieczenia, metkę oraz instrukcję użytkowania, dodatkowo w zestawie twarde etui na zawias sprężynowy Marki GOYA oraz miękką ściereczkę czyszczącą. NASZE PRODUKTY WYSYŁAMY BARDZO DOBRZE ZABEZPIECZONE W FOLIĘ TRANSPORTOWĄ I ZAPAKOWANE W WYTRZYMAŁY KARTONIK</t>
         </is>
@@ -11692,35 +11978,40 @@
       </c>
       <c r="V58" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/3168_1.jpg</t>
+        </is>
+      </c>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
           <t>/products/3168_1.jpg</t>
         </is>
       </c>
-      <c r="W58" s="2" t="inlineStr">
+      <c r="X58" s="2" t="inlineStr">
         <is>
           <t>/products/3168_1.jpg; /products/3168_6.jpg; /products/3168_2.jpg; /products/3168_3.jpg; /products/3168_4.jpg; /products/3168_5.jpg</t>
         </is>
       </c>
-      <c r="X58" s="2" t="inlineStr">
+      <c r="Y58" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2022/11/3168_1.jpg</t>
         </is>
       </c>
-      <c r="Y58" s="2" t="inlineStr">
+      <c r="Z58" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary przeciwsłoneczne z filtrem polaryzacyjnym - G 166 GR</t>
         </is>
       </c>
-      <c r="Z58" s="2" t="inlineStr">
+      <c r="AA58" s="2" t="inlineStr">
         <is>
           <t>goya-g-166-gr-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym</t>
         </is>
       </c>
-      <c r="AA58" s="2" t="inlineStr">
+      <c r="AB58" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-g-166-gr-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym</t>
         </is>
       </c>
-      <c r="AB58" s="3" t="inlineStr">
+      <c r="AC58" s="3" t="inlineStr">
         <is>
           <t>OKULARY PRZECIWSŁONECZNE DLA KIEROWCÓW GOYA Z FILTREM POLARYZACYJNYM I UV400 Soczewki okularów GOYA o grubości 1,1 wyposażone są w filtr polaryzacyjny oraz filtr ochronny UV-400 (UV-A, UV-B, UV-C) ZAUSZNIKI POŁĄCZONE Z OPRAWKĄ SYSTEMEM FLEX: FLEX - elastyczne połączenie zausznika z frontem oprawy. Zwiększony zakres odchylenia zausznika do ponad 110° gwarantuje wygodę noszenia i ułatwia zakładanie oraz zdejmowanie okularów. OKULARY POSIADAJĄ CERTYFIKAT CE. Produkt odpowiada Wytycznej Europejskiej 89/686/EWG zgodnie z normą PN-EN ISO 12312-1:2014-02/A1:2016-01. Każda para okularów posiada oryginalne oznaczenia znajdujące się na wewnętrznej stronie zauszników ; logo producenta, numer modelu, kategoria filtra oraz oznaczenie CE. O POLARYZACJI: Soczewki polaryzacyjne neutralizują oślepiające refleksy, powstające wówczas gdy światło odbija się od mokrej drogi, powierzchni wody lub śniegu. Eliminacja światła odbitego zwiększ kontrast widzenia i pozwala na bardziej komfortowe widzenie. Dlatego okulary z filtrem polaryzacyjnym to idealne rozwiązanie do wsz</t>
         </is>
@@ -11808,35 +12099,40 @@
       </c>
       <c r="V59" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/643_4.jpg</t>
+        </is>
+      </c>
+      <c r="W59" s="2" t="inlineStr">
+        <is>
           <t>/products/643_4.jpg</t>
         </is>
       </c>
-      <c r="W59" s="2" t="inlineStr">
+      <c r="X59" s="2" t="inlineStr">
         <is>
           <t>/products/643_4.jpg; /products/643_1.jpg; /products/643_3.jpg; /products/643_2.jpg</t>
         </is>
       </c>
-      <c r="X59" s="2" t="inlineStr">
+      <c r="Y59" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2022/11/643_4.jpg</t>
         </is>
       </c>
-      <c r="Y59" s="2" t="inlineStr">
+      <c r="Z59" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary korekcyjne - LA 9910 C4</t>
         </is>
       </c>
-      <c r="Z59" s="2" t="inlineStr">
+      <c r="AA59" s="2" t="inlineStr">
         <is>
           <t>goya-okulary-korekcyjne-la-9910-c4</t>
         </is>
       </c>
-      <c r="AA59" s="2" t="inlineStr">
+      <c r="AB59" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-okulary-korekcyjne-la-9910-c4</t>
         </is>
       </c>
-      <c r="AB59" s="3" t="inlineStr">
+      <c r="AC59" s="3" t="inlineStr">
         <is>
           <t>OKULARY KOREKCYJNE GOYA LA 9910 C4 Produkt nowy - posiadają oryginalne zabezpieczenia, metkę oraz instrukcję użytkowania, dodatkowo w zestawie twarde etui na zawias sprężynowy Marki GOYA oraz miękką ściereczkę czyszczącą. NASZE PRODUKTY WYSYŁAMY BARDZO DOBRZE ZABEZPIECZONE W FOLIĘ TRANSPORTOWĄ I ZAPAKOWANE W WYTRZYMAŁY KARTONIK</t>
         </is>
@@ -11928,35 +12224,40 @@
       </c>
       <c r="V60" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/G-201-CZ-A.jpg</t>
+        </is>
+      </c>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
           <t>/products/G-201-CZ-A.jpg</t>
         </is>
       </c>
-      <c r="W60" s="2" t="inlineStr">
+      <c r="X60" s="2" t="inlineStr">
         <is>
           <t>/products/G-201-CZ-A.jpg; /products/G-201-CZ-f.jpg; /products/G-201-CZ-s.jpg; /products/G-201-CZ-t.jpg; /products/G-201-CZ-b.jpg</t>
         </is>
       </c>
-      <c r="X60" s="2" t="inlineStr">
+      <c r="Y60" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2023/02/G-201-CZ-A.jpg</t>
         </is>
       </c>
-      <c r="Y60" s="2" t="inlineStr">
+      <c r="Z60" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary przeciwsłoneczne z filtrem polaryzacyjnym - G 201 CZ</t>
         </is>
       </c>
-      <c r="Z60" s="2" t="inlineStr">
+      <c r="AA60" s="2" t="inlineStr">
         <is>
           <t>goya-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym-g-201-cz</t>
         </is>
       </c>
-      <c r="AA60" s="2" t="inlineStr">
+      <c r="AB60" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym-g-201-cz</t>
         </is>
       </c>
-      <c r="AB60" s="3" t="inlineStr">
+      <c r="AC60" s="3" t="inlineStr">
         <is>
           <t>OKULARY PRZECIWSŁONECZNE DLA KIEROWCÓW GOYA Z FILTREM POLARYZACYJNYM I UV400 Soczewki okularów GOYA o grubości 1,1 wyposażone są w filtr polaryzacyjny oraz filtr ochronny UV-400 (UV-A, UV-B, UV-C) OPRAWKA WYKONANA W TECHNOLOGII TR-90 Wysokiej jakości odmiana nylonu, wyjątkowo odporna na rozciąganie i wyginanie. Materiał wytrzymały na uderzenia, elastyczny, przyjemny w dotyku, o właściwościach antyalergicznych. Okulary wykonane z TR-90 są lekkie, wytrzymałe i wygodne w użytkowaniu. OKULARY POSIADAJĄ CERTYFIKAT CE. Produkt odpowiada Wytycznej Europejskiej 89/686/EWG zgodnie z normą PN-EN ISO 12312-1:2014-02/A1:2016-01. Każda para okularów posiada oryginalne oznaczenia znajdujące się na wewnętrznej stronie zauszników ; logo producenta, numer modelu, kategoria filtra oraz oznaczenie CE. O POLARYZACJI: Soczewki polaryzacyjne neutralizują oślepiające refleksy, powstające wówczas gdy światło odbija się od mokrej drogi, powierzchni wody lub śniegu. Eliminacja światła odbitego zwiększ kontrast widzenia i pozwala na bardziej komfortowe widzenie. Dlatego oku</t>
         </is>
@@ -12046,35 +12347,40 @@
       </c>
       <c r="V61" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/3184_1.jpg</t>
+        </is>
+      </c>
+      <c r="W61" s="2" t="inlineStr">
+        <is>
           <t>/products/3184_1.jpg</t>
         </is>
       </c>
-      <c r="W61" s="2" t="inlineStr">
+      <c r="X61" s="2" t="inlineStr">
         <is>
           <t>/products/3184_1.jpg; /products/3184_6.jpg</t>
         </is>
       </c>
-      <c r="X61" s="2" t="inlineStr">
+      <c r="Y61" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2023/01/3184_1.jpg</t>
         </is>
       </c>
-      <c r="Y61" s="2" t="inlineStr">
+      <c r="Z61" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary przeciwsłoneczne z filtrem polaryzacyjnym - G 153</t>
         </is>
       </c>
-      <c r="Z61" s="2" t="inlineStr">
+      <c r="AA61" s="2" t="inlineStr">
         <is>
           <t>goya-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym-g-153</t>
         </is>
       </c>
-      <c r="AA61" s="2" t="inlineStr">
+      <c r="AB61" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym-g-153</t>
         </is>
       </c>
-      <c r="AB61" s="3" t="inlineStr">
+      <c r="AC61" s="3" t="inlineStr">
         <is>
           <t>OKULARY PRZECIWSŁONECZNE GOYA Z FILTREM POLARYZACYJNYM I UV400 Soczewki okularów GOYA o grubości 1,1 wyposażone są w filtr polaryzacyjny oraz filtr ochronny UV-400 (UV-A, UV-B, UV-C) OPRAWKA WYKONANA W TECHNOLOGII TR-90 Wysokiej jakości odmiana nylonu, wyjątkowo odporna na rozciąganie i wyginanie. Materiał wytrzymały na uderzenia, elastyczny, przyjemny w dotyku, o właściwościach antyalergicznych. Okulary wykonane z TR-90 są lekkie, wytrzymałe i wygodne w użytkowaniu. OKULARY POSIADAJĄ CERTYFIKAT CE. Produkt odpowiada Wytycznej Europejskiej 89/686/EWG zgodnie z normą PN-EN ISO 12312-1:2014-02/A1:2016-01. Każda para okularów posiada oryginalne oznaczenia znajdujące się na wewnętrznej stronie zauszników ; logo producenta, numer modelu, kategoria filtra oraz oznaczenie CE. O POLARYZACJI: Soczewki polaryzacyjne neutralizują oślepiające refleksy, powstające wówczas gdy światło odbija się od mokrej drogi, powierzchni wody lub śniegu. Eliminacja światła odbitego zwiększ kontrast widzenia i pozwala na bardziej komfortowe widzenie. Dlatego okulary z filt</t>
         </is>
@@ -12162,35 +12468,40 @@
       </c>
       <c r="V62" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/575_4.jpg</t>
+        </is>
+      </c>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
           <t>/products/575_4.jpg</t>
         </is>
       </c>
-      <c r="W62" s="2" t="inlineStr">
+      <c r="X62" s="2" t="inlineStr">
         <is>
           <t>/products/575_4.jpg; /products/575_1.jpg; /products/575_3.jpg; /products/575_2.jpg</t>
         </is>
       </c>
-      <c r="X62" s="2" t="inlineStr">
+      <c r="Y62" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2022/11/575_4.jpg</t>
         </is>
       </c>
-      <c r="Y62" s="2" t="inlineStr">
+      <c r="Z62" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary korekcyjne - G 1014 C8</t>
         </is>
       </c>
-      <c r="Z62" s="2" t="inlineStr">
+      <c r="AA62" s="2" t="inlineStr">
         <is>
           <t>goya-okulary-korekcyjne-g-1014-c8</t>
         </is>
       </c>
-      <c r="AA62" s="2" t="inlineStr">
+      <c r="AB62" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-okulary-korekcyjne-g-1014-c8</t>
         </is>
       </c>
-      <c r="AB62" s="3" t="inlineStr">
+      <c r="AC62" s="3" t="inlineStr">
         <is>
           <t>OKULARY KOREKCYJNE GOYA G 1014 C8 Produkt nowy - posiadają oryginalne zabezpieczenia, metkę oraz instrukcję użytkowania, dodatkowo w zestawie twarde etui na zawias sprężynowy Marki GOYA oraz miękką ściereczkę czyszczącą. NASZE PRODUKTY WYSYŁAMY BARDZO DOBRZE ZABEZPIECZONE W FOLIĘ TRANSPORTOWĄ I ZAPAKOWANE W WYTRZYMAŁY KARTONIK</t>
         </is>
@@ -12276,35 +12587,40 @@
       </c>
       <c r="V63" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/665_4.jpg</t>
+        </is>
+      </c>
+      <c r="W63" s="2" t="inlineStr">
+        <is>
           <t>/products/665_4.jpg</t>
         </is>
       </c>
-      <c r="W63" s="2" t="inlineStr">
+      <c r="X63" s="2" t="inlineStr">
         <is>
           <t>/products/665_4.jpg</t>
         </is>
       </c>
-      <c r="X63" s="2" t="inlineStr">
+      <c r="Y63" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2022/11/665_4.jpg</t>
         </is>
       </c>
-      <c r="Y63" s="2" t="inlineStr">
+      <c r="Z63" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary korekcyjne - G 93205</t>
         </is>
       </c>
-      <c r="Z63" s="2" t="inlineStr">
+      <c r="AA63" s="2" t="inlineStr">
         <is>
           <t>goya-okulary-korekcyjne-g-93205-c1</t>
         </is>
       </c>
-      <c r="AA63" s="2" t="inlineStr">
+      <c r="AB63" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-okulary-korekcyjne-g-93205-c1</t>
         </is>
       </c>
-      <c r="AB63" s="3" t="inlineStr">
+      <c r="AC63" s="3" t="inlineStr">
         <is>
           <t>OKULARY KOREKCYJNE GOYA G 93205 Produkt nowy - posiadają oryginalne zabezpieczenia, metkę oraz instrukcję użytkowania, dodatkowo w zestawie twarde etui na zawias sprężynowy Marki GOYA oraz miękką ściereczkę czyszczącą. NASZE PRODUKTY WYSYŁAMY BARDZO DOBRZE ZABEZPIECZONE W FOLIĘ TRANSPORTOWĄ I ZAPAKOWANE W WYTRZYMAŁY KARTONIK</t>
         </is>
@@ -12392,35 +12708,40 @@
       </c>
       <c r="V64" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/GOYA-2619-C4-prof.jpg</t>
+        </is>
+      </c>
+      <c r="W64" s="2" t="inlineStr">
+        <is>
           <t>/products/GOYA-2619-C4-prof.jpg</t>
         </is>
       </c>
-      <c r="W64" s="2" t="inlineStr">
+      <c r="X64" s="2" t="inlineStr">
         <is>
           <t>/products/GOYA-2619-C4-prof.jpg; /products/GOYA-2619-C4-bok.jpg; /products/575_6.jpg; /products/575_5.jpg; /products/GOYA-2619-C4-frg.jpg; /products/GOYA-2619-C4-fr.jpg</t>
         </is>
       </c>
-      <c r="X64" s="2" t="inlineStr">
+      <c r="Y64" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2022/11/GOYA-2619-C4-prof.jpg</t>
         </is>
       </c>
-      <c r="Y64" s="2" t="inlineStr">
+      <c r="Z64" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary korekcyjne G 2619 C4</t>
         </is>
       </c>
-      <c r="Z64" s="2" t="inlineStr">
+      <c r="AA64" s="2" t="inlineStr">
         <is>
           <t>goya-okulary-korekcyjne-g-2619-c4</t>
         </is>
       </c>
-      <c r="AA64" s="2" t="inlineStr">
+      <c r="AB64" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-okulary-korekcyjne-g-2619-c4</t>
         </is>
       </c>
-      <c r="AB64" s="3" t="inlineStr">
+      <c r="AC64" s="3" t="inlineStr">
         <is>
           <t>OKULARY KOREKCYJNE GOYA G 2619 C4 Produkt nowy ! - posiadają oryginalne zabezpieczenia, metkę oraz instrukcję użytkowania, dodatkowo w zestawie twarde etui na zawias sprężynowy Marki GOYA oraz miękką ściereczkę czyszczącą. NASZE PRODUKTY SĄ BARDZO DOBRZE ZABEZPIECZONE W FOLIĘ TRANSPORTOWĄ I ZAPAKOWANE W WYTRZYMAŁY KARTONIK</t>
         </is>
@@ -12508,35 +12829,40 @@
       </c>
       <c r="V65" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/575_6.jpg</t>
+        </is>
+      </c>
+      <c r="W65" s="2" t="inlineStr">
+        <is>
           <t>/products/575_6.jpg</t>
         </is>
       </c>
-      <c r="W65" s="2" t="inlineStr">
+      <c r="X65" s="2" t="inlineStr">
         <is>
           <t>/products/575_6.jpg; /products/575_5.jpg</t>
         </is>
       </c>
-      <c r="X65" s="2" t="inlineStr">
+      <c r="Y65" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2022/11/575_6.jpg</t>
         </is>
       </c>
-      <c r="Y65" s="2" t="inlineStr">
+      <c r="Z65" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary korekcyjne G 2714 C4</t>
         </is>
       </c>
-      <c r="Z65" s="2" t="inlineStr">
+      <c r="AA65" s="2" t="inlineStr">
         <is>
           <t>goya-okulary-korekcyjne-g-2714-c4</t>
         </is>
       </c>
-      <c r="AA65" s="2" t="inlineStr">
+      <c r="AB65" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-okulary-korekcyjne-g-2714-c4</t>
         </is>
       </c>
-      <c r="AB65" s="3" t="inlineStr">
+      <c r="AC65" s="3" t="inlineStr">
         <is>
           <t>OKULARY KOREKCYJNE GOYA G 2714 C4 Produkt nowy ! - posiadają oryginalne zabezpieczenia, metkę oraz instrukcję użytkowania, dodatkowo w zestawie twarde etui na zawias sprężynowy Marki GOYA oraz miękką ściereczkę czyszczącą. NASZE PRODUKTY SĄ BARDZO DOBRZE ZABEZPIECZONE W FOLIĘ TRANSPORTOWĄ I ZAPAKOWANE W WYTRZYMAŁY KARTONIK</t>
         </is>
@@ -12628,35 +12954,40 @@
       </c>
       <c r="V66" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/G_55012_GR_A.jpg</t>
+        </is>
+      </c>
+      <c r="W66" s="2" t="inlineStr">
+        <is>
           <t>/products/G_55012_GR_A.jpg</t>
         </is>
       </c>
-      <c r="W66" s="2" t="inlineStr">
+      <c r="X66" s="2" t="inlineStr">
         <is>
           <t>/products/G_55012_GR_A.jpg; /products/G_55012_GR_G.jpg; /products/G_55012_GR_B.jpg; /products/G_55012_GR_F.jpg; /products/G_55012_GR_S.jpg; /products/G_55012_GR_F1.jpg; /products/G_55012_GR_T.jpg</t>
         </is>
       </c>
-      <c r="X66" s="2" t="inlineStr">
+      <c r="Y66" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2025/01/G_55012_GR_A.jpg</t>
         </is>
       </c>
-      <c r="Y66" s="2" t="inlineStr">
+      <c r="Z66" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary przeciwsłoneczne z filtrem polaryzacyjnym - G 55012 GR</t>
         </is>
       </c>
-      <c r="Z66" s="2" t="inlineStr">
+      <c r="AA66" s="2" t="inlineStr">
         <is>
           <t>goya-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym-g-55012-gr</t>
         </is>
       </c>
-      <c r="AA66" s="2" t="inlineStr">
+      <c r="AB66" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym-g-55012-gr</t>
         </is>
       </c>
-      <c r="AB66" s="3" t="inlineStr">
+      <c r="AC66" s="3" t="inlineStr">
         <is>
           <t>OKULARY PRZECIWSŁONECZNE DLA KIEROWCÓW GOYA Z FILTREM POLARYZACYJNYM I UV400 Zausznik wykonane w całości z aluminium - co sprawia, że okulary są bardzo lekkie i wytrzymałe. Soczewki okularów GOYA o grubości 1,1 wyposażone są w filtr polaryzacyjny oraz filtr ochronny UV-400 (UV-A, UV-B, UV-C) ZAUSZNIKI POŁĄCZONE Z OPRAWKĄ SYSTEMEM FLEX: FLEX - elastyczne połączenie zausznika z frontem oprawy. Zwiększony zakres odchylenia zausznika do ponad 110° gwarantuje wygodę noszenia i ułatwia zakładanie oraz zdejmowanie okularów. OKULARY POSIADAJĄ CERTYFIKAT CE. Produkt odpowiada Wytycznej Europejskiej 89/686/EWG zgodnie z normą PN-EN ISO 12312-1:2014-02/A1:2016-01. Każda para okularów posiada oryginalne oznaczenia znajdujące się na wewnętrznej stronie zauszników ; logo producenta, numer modelu, kategoria filtra oraz oznaczenie CE. O POLARYZACJI: Soczewki polaryzacyjne neutralizują oślepiające refleksy, powstające wówczas gdy światło odbija się od mokrej drogi, powierzchni wody lub śniegu. Eliminacja światła odbitego zwiększ kontrast widzenia i pozwala</t>
         </is>
@@ -12746,35 +13077,40 @@
       </c>
       <c r="V67" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/GOYA-CP806639-BR-A.jpg</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
           <t>/products/GOYA-CP806639-BR-A.jpg</t>
         </is>
       </c>
-      <c r="W67" s="2" t="inlineStr">
+      <c r="X67" s="2" t="inlineStr">
         <is>
           <t>/products/GOYA-CP806639-BR-A.jpg; /products/CP_806639_ZL_mod.jpg</t>
         </is>
       </c>
-      <c r="X67" s="2" t="inlineStr">
+      <c r="Y67" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2023/04/GOYA-CP806639-BR-A.jpg</t>
         </is>
       </c>
-      <c r="Y67" s="2" t="inlineStr">
+      <c r="Z67" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary przeciwsłoneczne z filtrem polaryzacyjnym - GOYA CP 806639</t>
         </is>
       </c>
-      <c r="Z67" s="2" t="inlineStr">
+      <c r="AA67" s="2" t="inlineStr">
         <is>
           <t>goya-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym-goya-cp-806639</t>
         </is>
       </c>
-      <c r="AA67" s="2" t="inlineStr">
+      <c r="AB67" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym-goya-cp-806639</t>
         </is>
       </c>
-      <c r="AB67" s="3" t="inlineStr">
+      <c r="AC67" s="3" t="inlineStr">
         <is>
           <t>OKULARY PRZECIWSŁONECZNE DLA KIEROWCÓW GOYA Z FILTREM POLARYZACYJNYM I UV400 Soczewki okularów GOYA o grubości 1,1 wyposażone są w filtr polaryzacyjny oraz filtr ochronny UV-400 (UV-A, UV-B, UV-C) OKULARY POSIADAJĄ CERTYFIKAT CE. Produkt odpowiada Wytycznej Europejskiej 89/686/EWG zgodnie z normą PN-EN ISO 12312-1:2014-02/A1:2016-01. Każda para okularów posiada oryginalne oznaczenia znajdujące się na wewnętrznej stronie zauszników ; logo producenta, numer modelu, kategoria filtra oraz oznaczenie CE. O POLARYZACJI: Soczewki polaryzacyjne neutralizują oślepiające refleksy, powstające wówczas gdy światło odbija się od mokrej drogi, powierzchni wody lub śniegu. Eliminacja światła odbitego zwiększ kontrast widzenia i pozwala na bardziej komfortowe widzenie. Dlatego okulary z filtrem polaryzacyjnym to idealne rozwiązanie do wszelkiego rodzaju aktywności na świeżym powietrzu, pozwalające pełniej korzystać z życia. ZALETY: Eliminują oślepiające odblaski, zmniejszając zmęczenie oczu Chronią przed szkodliwym promieniowaniem UV Zwięk</t>
         </is>
@@ -12864,35 +13200,40 @@
       </c>
       <c r="V68" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/GOYA-PG3026-P-A.jpg</t>
+        </is>
+      </c>
+      <c r="W68" s="2" t="inlineStr">
+        <is>
           <t>/products/GOYA-PG3026-P-A.jpg</t>
         </is>
       </c>
-      <c r="W68" s="2" t="inlineStr">
+      <c r="X68" s="2" t="inlineStr">
         <is>
           <t>/products/GOYA-PG3026-P-A.jpg; /products/GOYA_PG3026_R_MOD-e1681296586339.jpg</t>
         </is>
       </c>
-      <c r="X68" s="2" t="inlineStr">
+      <c r="Y68" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2023/04/GOYA-PG3026-P-A.jpg</t>
         </is>
       </c>
-      <c r="Y68" s="2" t="inlineStr">
+      <c r="Z68" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary przeciwsłoneczne z filtrem polaryzacyjnym - GOYA PG 3026</t>
         </is>
       </c>
-      <c r="Z68" s="2" t="inlineStr">
+      <c r="AA68" s="2" t="inlineStr">
         <is>
           <t>goya-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym-goya-pg-3026</t>
         </is>
       </c>
-      <c r="AA68" s="2" t="inlineStr">
+      <c r="AB68" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym-goya-pg-3026</t>
         </is>
       </c>
-      <c r="AB68" s="3" t="inlineStr">
+      <c r="AC68" s="3" t="inlineStr">
         <is>
           <t>OKULARY PRZECIWSŁONECZNE DLA KIEROWCÓW GOYA Z FILTREM POLARYZACYJNYM I UV400 Soczewki okularów GOYA o grubości 1,1 wyposażone są w filtr polaryzacyjny oraz filtr ochronny UV-400 (UV-A, UV-B, UV-C) SOCZEWKA ANTYREFLEKS: Warstwa antyrefleksu znacznie zwiększa wartość użytkową okularów, gdyż przepuszcza przez powierzchnię soczewki okularowej więcej światła niż odbija. Dzięki tej powłoce w znacznym stopniu zredukowane zostają wszelkie odblaski. Antyrefleks poprawia również odwzorowanie barw i poprawia kontrast widzenia. Dodatkowym plusem powłoki antyrefleksyjnej jest ochrona soczewki przez zarysowaniami. OKULARY POSIADAJĄ CERTYFIKAT CE. Produkt odpowiada Wytycznej Europejskiej 89/686/EWG zgodnie z normą PN-EN ISO 12312-1:2014-02/A1:2016-01. Każda para okularów posiada oryginalne oznaczenia znajdujące się na wewnętrznej stronie zauszników ; logo producenta, numer modelu, kategoria filtra oraz oznaczenie CE. O POLARYZACJI: Soczewki polaryzacyjne neutralizują oślepiające refleksy, powstające wówczas gdy światło odbija się od mokrej drogi, powierzchni wod</t>
         </is>
@@ -12980,35 +13321,40 @@
       </c>
       <c r="V69" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/586_3.jpg</t>
+        </is>
+      </c>
+      <c r="W69" s="2" t="inlineStr">
+        <is>
           <t>/products/586_3.jpg</t>
         </is>
       </c>
-      <c r="W69" s="2" t="inlineStr">
+      <c r="X69" s="2" t="inlineStr">
         <is>
           <t>/products/586_3.jpg; /products/586_4.jpg; /products/586_2.jpg; /products/586_1.jpg</t>
         </is>
       </c>
-      <c r="X69" s="2" t="inlineStr">
+      <c r="Y69" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2022/11/586_3.jpg</t>
         </is>
       </c>
-      <c r="Y69" s="2" t="inlineStr">
+      <c r="Z69" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary korekcyjne - G 2603 C1</t>
         </is>
       </c>
-      <c r="Z69" s="2" t="inlineStr">
+      <c r="AA69" s="2" t="inlineStr">
         <is>
           <t>goya-okulary-korekcyjne-g-2603-c1</t>
         </is>
       </c>
-      <c r="AA69" s="2" t="inlineStr">
+      <c r="AB69" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-okulary-korekcyjne-g-2603-c1</t>
         </is>
       </c>
-      <c r="AB69" s="3" t="inlineStr">
+      <c r="AC69" s="3" t="inlineStr">
         <is>
           <t>OKULARY KOREKCYJNE GOYA G 2603 C1 Produkt nowy - posiadają oryginalne zabezpieczenia, metkę oraz instrukcję użytkowania, dodatkowo w zestawie twarde etui na zawias sprężynowy Marki GOYA oraz miękką ściereczkę czyszczącą. NASZE PRODUKTY WYSYŁAMY BARDZO DOBRZE ZABEZPIECZONE W FOLIĘ TRANSPORTOWĄ I ZAPAKOWANE W WYTRZYMAŁY KARTONIK</t>
         </is>
@@ -13094,35 +13440,40 @@
       </c>
       <c r="V70" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/624_4.jpg</t>
+        </is>
+      </c>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
           <t>/products/624_4.jpg</t>
         </is>
       </c>
-      <c r="W70" s="2" t="inlineStr">
+      <c r="X70" s="2" t="inlineStr">
         <is>
           <t>/products/624_4.jpg</t>
         </is>
       </c>
-      <c r="X70" s="2" t="inlineStr">
+      <c r="Y70" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2022/11/624_4.jpg</t>
         </is>
       </c>
-      <c r="Y70" s="2" t="inlineStr">
+      <c r="Z70" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary korekcyjne - G 89083</t>
         </is>
       </c>
-      <c r="Z70" s="2" t="inlineStr">
+      <c r="AA70" s="2" t="inlineStr">
         <is>
           <t>goya-okulary-korekcyjne-g-89083-c1</t>
         </is>
       </c>
-      <c r="AA70" s="2" t="inlineStr">
+      <c r="AB70" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-okulary-korekcyjne-g-89083-c1</t>
         </is>
       </c>
-      <c r="AB70" s="3" t="inlineStr">
+      <c r="AC70" s="3" t="inlineStr">
         <is>
           <t>OKULARY KOREKCYJNE GOYA G 89083 Produkt nowy - posiadają oryginalne zabezpieczenia, metkę oraz instrukcję użytkowania, dodatkowo w zestawie twarde etui na zawias sprężynowy Marki GOYA oraz miękką ściereczkę czyszczącą. NASZE PRODUKTY WYSYŁAMY BARDZO DOBRZE ZABEZPIECZONE W FOLIĘ TRANSPORTOWĄ I ZAPAKOWANE W WYTRZYMAŁY KARTONIK</t>
         </is>
@@ -13212,35 +13563,40 @@
       </c>
       <c r="V71" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/2449_1.jpg</t>
+        </is>
+      </c>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
           <t>/products/2449_1.jpg</t>
         </is>
       </c>
-      <c r="W71" s="2" t="inlineStr">
+      <c r="X71" s="2" t="inlineStr">
         <is>
           <t>/products/2449_1.jpg</t>
         </is>
       </c>
-      <c r="X71" s="2" t="inlineStr">
+      <c r="Y71" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2022/11/2449_1.jpg</t>
         </is>
       </c>
-      <c r="Y71" s="2" t="inlineStr">
+      <c r="Z71" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary przeciwsłoneczne z filtrem polaryzacyjnym - G 55010</t>
         </is>
       </c>
-      <c r="Z71" s="2" t="inlineStr">
+      <c r="AA71" s="2" t="inlineStr">
         <is>
           <t>goya-g-55010-br-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym</t>
         </is>
       </c>
-      <c r="AA71" s="2" t="inlineStr">
+      <c r="AB71" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-g-55010-br-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym</t>
         </is>
       </c>
-      <c r="AB71" s="3" t="inlineStr">
+      <c r="AC71" s="3" t="inlineStr">
         <is>
           <t>OKULARY PRZECIWSŁONECZNE DLA KIEROWCÓW GOYA Z FILTREM POLARYZACYJNYM I UV400 Oprawki wykonane w całości z aluminium - co sprawia, że okulary są bardzo lekkie i wytrzymałe. Soczewki okularów GOYA o grubości 1,1 wyposażone są w filtr polaryzacyjny oraz filtr ochronny UV-400 (UV-A, UV-B, UV-C) ZAUSZNIKI POŁĄCZONE Z OPRAWKĄ SYSTEMEM FLEX: FLEX - elastyczne połączenie zausznika z frontem oprawy. Zwiększony zakres odchylenia zausznika do ponad 110° gwarantuje wygodę noszenia i ułatwia zakładanie oraz zdejmowanie okularów. OKULARY POSIADAJĄ CERTYFIKAT CE. Produkt odpowiada Wytycznej Europejskiej 89/686/EWG zgodnie z normą PN-EN ISO 12312-1:2014-02/A1:2016-01. Każda para okularów posiada oryginalne oznaczenia znajdujące się na wewnętrznej stronie zauszników ; logo producenta, numer modelu, kategoria filtra oraz oznaczenie CE. O POLARYZACJI: Soczewki polaryzacyjne neutralizują oślepiające refleksy, powstające wówczas gdy światło odbija się od mokrej drogi, powierzchni wody lub śniegu. Eliminacja światła odbitego zwiększ kontrast widzenia i pozwala</t>
         </is>
@@ -13330,35 +13686,40 @@
       </c>
       <c r="V72" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/3177_1.jpg</t>
+        </is>
+      </c>
+      <c r="W72" s="2" t="inlineStr">
+        <is>
           <t>/products/3177_1.jpg</t>
         </is>
       </c>
-      <c r="W72" s="2" t="inlineStr">
+      <c r="X72" s="2" t="inlineStr">
         <is>
           <t>/products/3177_1.jpg; /products/3178_6.jpg</t>
         </is>
       </c>
-      <c r="X72" s="2" t="inlineStr">
+      <c r="Y72" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2022/11/3177_1.jpg</t>
         </is>
       </c>
-      <c r="Y72" s="2" t="inlineStr">
+      <c r="Z72" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary przeciwsłoneczne z filtrem polaryzacyjnym - G 160</t>
         </is>
       </c>
-      <c r="Z72" s="2" t="inlineStr">
+      <c r="AA72" s="2" t="inlineStr">
         <is>
           <t>goya-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym-g-160</t>
         </is>
       </c>
-      <c r="AA72" s="2" t="inlineStr">
+      <c r="AB72" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym-g-160</t>
         </is>
       </c>
-      <c r="AB72" s="3" t="inlineStr">
+      <c r="AC72" s="3" t="inlineStr">
         <is>
           <t>OKULARY PRZECIWSŁONECZNE DLA KIEROWCÓW GOYA Z FILTREM POLARYZACYJNYM I UV400 Oprawka wykonana w technologii - wycinania z płyty. Ręcznie obrabiana. Soczewki okularów GOYA o grubości 1,1 wyposażone są w filtr polaryzacyjny oraz filtr ochronny UV-400 (UV-A, UV-B, UV-C) OKULARY POSIADAJĄ CERTYFIKAT CE. Produkt odpowiada Wytycznej Europejskiej 89/686/EWG zgodnie z normą PN-EN ISO 12312-1:2014-02/A1:2016-01. Każda para okularów posiada oryginalne oznaczenia znajdujące się na wewnętrznej stronie zauszników ; logo producenta, numer modelu, kategoria filtra oraz oznaczenie CE. O POLARYZACJI: Soczewki polaryzacyjne neutralizują oślepiające refleksy, powstające wówczas gdy światło odbija się od mokrej drogi, powierzchni wody lub śniegu. Eliminacja światła odbitego zwiększ kontrast widzenia i pozwala na bardziej komfortowe widzenie. Dlatego okulary z filtrem polaryzacyjnym to idealne rozwiązanie do wszelkiego rodzaju aktywności na świeżym powietrzu, pozwalające pełniej korzystać z życia. ZALETY: Eliminują oślepiające odblaski, zmniejszaj</t>
         </is>
@@ -13450,35 +13811,40 @@
       </c>
       <c r="V73" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/G_55054_GR_A.jpg</t>
+        </is>
+      </c>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
           <t>/products/G_55054_GR_A.jpg</t>
         </is>
       </c>
-      <c r="W73" s="2" t="inlineStr">
+      <c r="X73" s="2" t="inlineStr">
         <is>
           <t>/products/G_55054_GR_A.jpg; /products/G_55054_GR_G.jpg; /products/G_55054_GR_B.jpg; /products/G_55054_GR_F.jpg; /products/G_55054_GR_S.jpg; /products/G_55054_GR_F1.jpg; /products/G_55054_GR_T.jpg</t>
         </is>
       </c>
-      <c r="X73" s="2" t="inlineStr">
+      <c r="Y73" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2025/02/G_55054_GR_A.jpg</t>
         </is>
       </c>
-      <c r="Y73" s="2" t="inlineStr">
+      <c r="Z73" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary przeciwsłoneczne z filtrem polaryzacyjnym - G 55054 GR</t>
         </is>
       </c>
-      <c r="Z73" s="2" t="inlineStr">
+      <c r="AA73" s="2" t="inlineStr">
         <is>
           <t>goya-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym-g-55054-gr</t>
         </is>
       </c>
-      <c r="AA73" s="2" t="inlineStr">
+      <c r="AB73" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym-g-55054-gr</t>
         </is>
       </c>
-      <c r="AB73" s="3" t="inlineStr">
+      <c r="AC73" s="3" t="inlineStr">
         <is>
           <t>OKULARY PRZECIWSŁONECZNE DLA KIEROWCÓW GOYA Z FILTREM POLARYZACYJNYM I UV400 Oprawki wykonane w całości z aluminium - co sprawia, że okulary są bardzo lekkie i wytrzymałe. Soczewki okularów GOYA o grubości 1,1 wyposażone są w filtr polaryzacyjny oraz filtr ochronny UV-400 (UV-A, UV-B, UV-C) ZAUSZNIKI POŁĄCZONE Z OPRAWKĄ SYSTEMEM FLEX: FLEX - elastyczne połączenie zausznika z frontem oprawy. Zwiększony zakres odchylenia zausznika do ponad 110° gwarantuje wygodę noszenia i ułatwia zakładanie oraz zdejmowanie okularów. OKULARY POSIADAJĄ CERTYFIKAT CE. Produkt odpowiada Wytycznej Europejskiej 89/686/EWG zgodnie z normą PN-EN ISO 12312-1:2014-02/A1:2016-01. Każda para okularów posiada oryginalne oznaczenia znajdujące się na wewnętrznej stronie zauszników ; logo producenta, numer modelu, kategoria filtra oraz oznaczenie CE. O POLARYZACJI: Soczewki polaryzacyjne neutralizują oślepiające refleksy, powstające wówczas gdy światło odbija się od mokrej drogi, powierzchni wody lub śniegu. Eliminacja światła odbitego zwiększ kontrast widzenia i pozwala</t>
         </is>
@@ -13564,35 +13930,40 @@
       </c>
       <c r="V74" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/637_4.jpg</t>
+        </is>
+      </c>
+      <c r="W74" s="2" t="inlineStr">
+        <is>
           <t>/products/637_4.jpg</t>
         </is>
       </c>
-      <c r="W74" s="2" t="inlineStr">
+      <c r="X74" s="2" t="inlineStr">
         <is>
           <t>/products/637_4.jpg</t>
         </is>
       </c>
-      <c r="X74" s="2" t="inlineStr">
+      <c r="Y74" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2022/11/637_4.jpg</t>
         </is>
       </c>
-      <c r="Y74" s="2" t="inlineStr">
+      <c r="Z74" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary korekcyjne - GK 7078</t>
         </is>
       </c>
-      <c r="Z74" s="2" t="inlineStr">
+      <c r="AA74" s="2" t="inlineStr">
         <is>
           <t>goya-okulary-korekcyjne-gk-7078-c1</t>
         </is>
       </c>
-      <c r="AA74" s="2" t="inlineStr">
+      <c r="AB74" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-okulary-korekcyjne-gk-7078-c1</t>
         </is>
       </c>
-      <c r="AB74" s="3" t="inlineStr">
+      <c r="AC74" s="3" t="inlineStr">
         <is>
           <t>OKULARY KOREKCYJNE GOYA GK 7078 Produkt nowy - posiadają oryginalne zabezpieczenia, metkę oraz instrukcję użytkowania, dodatkowo w zestawie twarde etui na zawias sprężynowy Marki GOYA oraz miękką ściereczkę czyszczącą. NASZE PRODUKTY WYSYŁAMY BARDZO DOBRZE ZABEZPIECZONE W FOLIĘ TRANSPORTOWĄ I ZAPAKOWANE W WYTRZYMAŁY KARTONIK</t>
         </is>
@@ -13684,35 +14055,40 @@
       </c>
       <c r="V75" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/3130_1.jpg</t>
+        </is>
+      </c>
+      <c r="W75" s="2" t="inlineStr">
+        <is>
           <t>/products/3130_1.jpg</t>
         </is>
       </c>
-      <c r="W75" s="2" t="inlineStr">
+      <c r="X75" s="2" t="inlineStr">
         <is>
           <t>/products/3130_1.jpg; /products/3130_5.jpg; /products/3130_2.jpg; /products/3130_3.jpg; /products/3130_4.jpg; /products/3130_6.jpg</t>
         </is>
       </c>
-      <c r="X75" s="2" t="inlineStr">
+      <c r="Y75" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2022/11/3130_1.jpg</t>
         </is>
       </c>
-      <c r="Y75" s="2" t="inlineStr">
+      <c r="Z75" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary przeciwsłoneczne z filtrem polaryzacyjnym - G 193 CZ</t>
         </is>
       </c>
-      <c r="Z75" s="2" t="inlineStr">
+      <c r="AA75" s="2" t="inlineStr">
         <is>
           <t>goya-g-193-cz-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym</t>
         </is>
       </c>
-      <c r="AA75" s="2" t="inlineStr">
+      <c r="AB75" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-g-193-cz-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym</t>
         </is>
       </c>
-      <c r="AB75" s="3" t="inlineStr">
+      <c r="AC75" s="3" t="inlineStr">
         <is>
           <t>OKULARY PRZECIWSŁONECZNE DLA KIEROWCÓW GOYA Z FILTREM POLARYZACYJNYM I UV400 Soczewki okularów GOYA o grubości 1,1 wyposażone są w filtr polaryzacyjny oraz filtr ochronny UV-400 (UV-A, UV-B, UV-C) OKULARY POSIADAJĄ CERTYFIKAT CE. Produkt odpowiada Wytycznej Europejskiej 89/686/EWG zgodnie z normą PN-EN ISO 12312-1:2014-02/A1:2016-01. Każda para okularów posiada oryginalne oznaczenia znajdujące się na wewnętrznej stronie zauszników ; logo producenta, numer modelu, kategoria filtra oraz oznaczenie CE. O POLARYZACJI: Soczewki polaryzacyjne neutralizują oślepiające refleksy, powstające wówczas gdy światło odbija się od mokrej drogi, powierzchni wody lub śniegu. Eliminacja światła odbitego zwiększ kontrast widzenia i pozwala na bardziej komfortowe widzenie. Dlatego okulary z filtrem polaryzacyjnym to idealne rozwiązanie do wszelkiego rodzaju aktywności na świeżym powietrzu, pozwalające pełniej korzystać z życia. ZALETY: Eliminują oślepiające odblaski, zmniejszając zmęczenie oczu Chronią przed szkodliwym promieniowaniem UV Zwiększ</t>
         </is>
@@ -13800,35 +14176,40 @@
       </c>
       <c r="V76" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/575_6.jpg</t>
+        </is>
+      </c>
+      <c r="W76" s="2" t="inlineStr">
+        <is>
           <t>/products/575_6.jpg</t>
         </is>
       </c>
-      <c r="W76" s="2" t="inlineStr">
+      <c r="X76" s="2" t="inlineStr">
         <is>
           <t>/products/575_6.jpg; /products/575_5.jpg</t>
         </is>
       </c>
-      <c r="X76" s="2" t="inlineStr">
+      <c r="Y76" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2022/11/575_6.jpg</t>
         </is>
       </c>
-      <c r="Y76" s="2" t="inlineStr">
+      <c r="Z76" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary korekcyjne - LF 81209 C4</t>
         </is>
       </c>
-      <c r="Z76" s="2" t="inlineStr">
+      <c r="AA76" s="2" t="inlineStr">
         <is>
           <t>goya-okulary-korekcyjne-lf-81209-c4</t>
         </is>
       </c>
-      <c r="AA76" s="2" t="inlineStr">
+      <c r="AB76" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-okulary-korekcyjne-lf-81209-c4</t>
         </is>
       </c>
-      <c r="AB76" s="3" t="inlineStr">
+      <c r="AC76" s="3" t="inlineStr">
         <is>
           <t>OKULARY KOREKCYJNE GOYA LF 81209 C4 Produkt nowy ! - posiadają oryginalne zabezpieczenia, metkę oraz instrukcję użytkowania, dodatkowo w zestawie twarde etui na zawias sprężynowy Marki GOYA oraz miękką ściereczkę czyszczącą. NASZE PRODUKTY SĄ BARDZO DOBRZE ZABEZPIECZONE W FOLIĘ TRANSPORTOWĄ I ZAPAKOWANE W WYTRZYMAŁY KARTONIK</t>
         </is>
@@ -13920,35 +14301,40 @@
       </c>
       <c r="V77" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/3128_1.jpg</t>
+        </is>
+      </c>
+      <c r="W77" s="2" t="inlineStr">
+        <is>
           <t>/products/3128_1.jpg</t>
         </is>
       </c>
-      <c r="W77" s="2" t="inlineStr">
+      <c r="X77" s="2" t="inlineStr">
         <is>
           <t>/products/3128_1.jpg; /products/3128_6.jpg; /products/3128_3.jpg; /products/3128_2.jpg; /products/3128_5.jpg; /products/3128_4.jpg</t>
         </is>
       </c>
-      <c r="X77" s="2" t="inlineStr">
+      <c r="Y77" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2022/11/3128_1.jpg</t>
         </is>
       </c>
-      <c r="Y77" s="2" t="inlineStr">
+      <c r="Z77" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary przeciwsłoneczne z filtrem polaryzacyjnym - G 190 CZ</t>
         </is>
       </c>
-      <c r="Z77" s="2" t="inlineStr">
+      <c r="AA77" s="2" t="inlineStr">
         <is>
           <t>goya-g-190-cz-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym</t>
         </is>
       </c>
-      <c r="AA77" s="2" t="inlineStr">
+      <c r="AB77" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-g-190-cz-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym</t>
         </is>
       </c>
-      <c r="AB77" s="3" t="inlineStr">
+      <c r="AC77" s="3" t="inlineStr">
         <is>
           <t>OKULARY PRZECIWSŁONECZNE DLA KIEROWCÓW GOYA Z FILTREM POLARYZACYJNYM I UV400 Soczewki okularów GOYA o grubości 1,1 wyposażone są w filtr polaryzacyjny oraz filtr ochronny UV-400 (UV-A, UV-B, UV-C) OKULARY POSIADAJĄ CERTYFIKAT CE. Produkt odpowiada Wytycznej Europejskiej 89/686/EWG zgodnie z normą PN-EN ISO 12312-1:2014-02/A1:2016-01. Każda para okularów posiada oryginalne oznaczenia znajdujące się na wewnętrznej stronie zauszników ; logo producenta, numer modelu, kategoria filtra oraz oznaczenie CE. O POLARYZACJI: Soczewki polaryzacyjne neutralizują oślepiające refleksy, powstające wówczas gdy światło odbija się od mokrej drogi, powierzchni wody lub śniegu. Eliminacja światła odbitego zwiększ kontrast widzenia i pozwala na bardziej komfortowe widzenie. Dlatego okulary z filtrem polaryzacyjnym to idealne rozwiązanie do wszelkiego rodzaju aktywności na świeżym powietrzu, pozwalające pełniej korzystać z życia. ZALETY: Eliminują oślepiające odblaski, zmniejszając zmęczenie oczu Chronią przed szkodliwym promieniowaniem UV Zwiększ</t>
         </is>
@@ -14038,35 +14424,40 @@
       </c>
       <c r="V78" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/2465_1.jpg</t>
+        </is>
+      </c>
+      <c r="W78" s="2" t="inlineStr">
+        <is>
           <t>/products/2465_1.jpg</t>
         </is>
       </c>
-      <c r="W78" s="2" t="inlineStr">
+      <c r="X78" s="2" t="inlineStr">
         <is>
           <t>/products/2465_1.jpg</t>
         </is>
       </c>
-      <c r="X78" s="2" t="inlineStr">
+      <c r="Y78" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2022/11/2465_1.jpg</t>
         </is>
       </c>
-      <c r="Y78" s="2" t="inlineStr">
+      <c r="Z78" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary przeciwsłoneczne z filtrem polaryzacyjnym - G 55042</t>
         </is>
       </c>
-      <c r="Z78" s="2" t="inlineStr">
+      <c r="AA78" s="2" t="inlineStr">
         <is>
           <t>goya-g-55042-br-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym</t>
         </is>
       </c>
-      <c r="AA78" s="2" t="inlineStr">
+      <c r="AB78" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-g-55042-br-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym</t>
         </is>
       </c>
-      <c r="AB78" s="3" t="inlineStr">
+      <c r="AC78" s="3" t="inlineStr">
         <is>
           <t>OKULARY PRZECIWSŁONECZNE DLA KIEROWCÓW GOYA Z FILTREM POLARYZACYJNYM I UV400 Zauszniki oprawek wykonane z aluminium - co sprawia, że okulary są bardzo lekkie i wytrzymałe. Soczewki okularów GOYA o grubości 1,1 wyposażone są w filtr polaryzacyjny oraz filtr ochronny UV-400 (UV-A, UV-B, UV-C) ZAUSZNIKI POŁĄCZONE Z OPRAWKĄ SYSTEMEM FLEX: FLEX - elastyczne połączenie zausznika z frontem oprawy. Zwiększony zakres odchylenia zausznika do ponad 110° gwarantuje wygodę noszenia i ułatwia zakładanie oraz zdejmowanie okularów. OKULARY POSIADAJĄ CERTYFIKAT CE. Produkt odpowiada Wytycznej Europejskiej 89/686/EWG zgodnie z normą PN-EN ISO 12312-1:2014-02/A1:2016-01. Każda para okularów posiada oryginalne oznaczenia znajdujące się na wewnętrznej stronie zauszników ; logo producenta, numer modelu, kategoria filtra oraz oznaczenie CE. O POLARYZACJI: Soczewki polaryzacyjne neutralizują oślepiające refleksy, powstające wówczas gdy światło odbija się od mokrej drogi, powierzchni wody lub śniegu. Eliminacja światła odbitego zwiększ kontrast widzenia i pozwala na</t>
         </is>
@@ -14158,35 +14549,40 @@
       </c>
       <c r="V79" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/3153_6.jpg</t>
+        </is>
+      </c>
+      <c r="W79" s="2" t="inlineStr">
+        <is>
           <t>/products/3153_6.jpg</t>
         </is>
       </c>
-      <c r="W79" s="2" t="inlineStr">
+      <c r="X79" s="2" t="inlineStr">
         <is>
           <t>/products/3153_6.jpg; /products/3153_1.jpg; /products/3153_5.jpg; /products/3153_3.jpg; /products/3153_4.jpg; /products/3153_2.jpg</t>
         </is>
       </c>
-      <c r="X79" s="2" t="inlineStr">
+      <c r="Y79" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2022/11/3153_6.jpg</t>
         </is>
       </c>
-      <c r="Y79" s="2" t="inlineStr">
+      <c r="Z79" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary przeciwsłoneczne z filtrem polaryzacyjnym - G 180 GR</t>
         </is>
       </c>
-      <c r="Z79" s="2" t="inlineStr">
+      <c r="AA79" s="2" t="inlineStr">
         <is>
           <t>goya-g-180-gr-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym-kopia</t>
         </is>
       </c>
-      <c r="AA79" s="2" t="inlineStr">
+      <c r="AB79" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-g-180-gr-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym-kopia</t>
         </is>
       </c>
-      <c r="AB79" s="3" t="inlineStr">
+      <c r="AC79" s="3" t="inlineStr">
         <is>
           <t>OKULARY PRZECIWSŁONECZNE DLA KIEROWCÓW GOYA Z FILTREM POLARYZACYJNYM I UV400 Soczewki okularów GOYA o grubości 1,1 wyposażone są w filtr polaryzacyjny oraz filtr ochronny UV-400 (UV-A, UV-B, UV-C) OKULARY POSIADAJĄ CERTYFIKAT CE. Produkt odpowiada Wytycznej Europejskiej 89/686/EWG zgodnie z normą PN-EN ISO 12312-1:2014-02/A1:2016-01. Każda para okularów posiada oryginalne oznaczenia znajdujące się na wewnętrznej stronie zauszników ; logo producenta, numer modelu, kategoria filtra oraz oznaczenie CE. O POLARYZACJI: Soczewki polaryzacyjne neutralizują oślepiające refleksy, powstające wówczas gdy światło odbija się od mokrej drogi, powierzchni wody lub śniegu. Eliminacja światła odbitego zwiększ kontrast widzenia i pozwala na bardziej komfortowe widzenie. Dlatego okulary z filtrem polaryzacyjnym to idealne rozwiązanie do wszelkiego rodzaju aktywności na świeżym powietrzu, pozwalające pełniej korzystać z życia. ZALETY: Eliminują oślepiające odblaski, zmniejszając zmęczenie oczu Chronią przed szkodliwym promieniowaniem UV Zwięk</t>
         </is>
@@ -14278,35 +14674,40 @@
       </c>
       <c r="V80" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/968_6.jpg</t>
+        </is>
+      </c>
+      <c r="W80" s="2" t="inlineStr">
+        <is>
           <t>/products/968_6.jpg</t>
         </is>
       </c>
-      <c r="W80" s="2" t="inlineStr">
+      <c r="X80" s="2" t="inlineStr">
         <is>
           <t>/products/968_6.jpg; /products/968_2.jpg; /products/968_1.jpg; /products/968_7.jpg; /products/968_3.jpg</t>
         </is>
       </c>
-      <c r="X80" s="2" t="inlineStr">
+      <c r="Y80" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2022/11/968_6.jpg</t>
         </is>
       </c>
-      <c r="Y80" s="2" t="inlineStr">
+      <c r="Z80" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary przeciwsłoneczne z filtrem polaryzacyjnym - G1835 C3</t>
         </is>
       </c>
-      <c r="Z80" s="2" t="inlineStr">
+      <c r="AA80" s="2" t="inlineStr">
         <is>
           <t>goya-g1835-c3-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym</t>
         </is>
       </c>
-      <c r="AA80" s="2" t="inlineStr">
+      <c r="AB80" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-g1835-c3-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym</t>
         </is>
       </c>
-      <c r="AB80" s="3" t="inlineStr">
+      <c r="AC80" s="3" t="inlineStr">
         <is>
           <t>OKULARY PRZECIWSŁONECZNE DLA KIEROWCÓW GOYA Z FILTREM POLARYZACYJNYM I UV400 Soczewki okularów GOYA o grubości 1,1 wyposażone są w filtr polaryzacyjny oraz filtr ochronny UV-400 (UV-A, UV-B, UV-C) OPRAWKA WYKONANA W TECHNOLOGII TR-90 Wysokiej jakości odmiana nylonu, wyjątkowo odporna na rozciąganie i wyginanie. Materiał wytrzymały na uderzenia, elastyczny, przyjemny w dotyku, o właściwościach antyalergicznych. Okulary wykonane z TR-90 są lekkie, wytrzymałe i wygodne w użytkowaniu. ZAUSZNIKI POŁĄCZONE Z OPRAWKĄ SYSTEMEM FLEX: FLEX - elastyczne połączenie zausznika z frontem oprawy. Zwiększony zakres odchylenia zausznika do ponad 110° gwarantuje wygodę noszenia i ułatwia zakładanie oraz zdejmowanie okularów. OKULARY POSIADAJĄ CERTYFIKAT CE. Produkt odpowiada Wytycznej Europejskiej 89/686/EWG zgodnie z normą PN-EN ISO 12312-1:2014-02/A1:2016-01. Każda para okularów posiada oryginalne oznaczenia znajdujące się na wewnętrznej stronie zauszników ; logo producenta, numer modelu, kategoria filtra oraz oznaczenie CE. O POLARYZACJI: Soczewki pol</t>
         </is>
@@ -14394,35 +14795,40 @@
       </c>
       <c r="V81" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/658_4.jpg</t>
+        </is>
+      </c>
+      <c r="W81" s="2" t="inlineStr">
+        <is>
           <t>/products/658_4.jpg</t>
         </is>
       </c>
-      <c r="W81" s="2" t="inlineStr">
+      <c r="X81" s="2" t="inlineStr">
         <is>
           <t>/products/658_4.jpg; /products/658_1.jpg; /products/658_3.jpg; /products/658_2.jpg</t>
         </is>
       </c>
-      <c r="X81" s="2" t="inlineStr">
+      <c r="Y81" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2022/11/658_4.jpg</t>
         </is>
       </c>
-      <c r="Y81" s="2" t="inlineStr">
+      <c r="Z81" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary korekcyjne - T 1013 C6</t>
         </is>
       </c>
-      <c r="Z81" s="2" t="inlineStr">
+      <c r="AA81" s="2" t="inlineStr">
         <is>
           <t>goya-okulary-korekcyjne-t-1013-c6</t>
         </is>
       </c>
-      <c r="AA81" s="2" t="inlineStr">
+      <c r="AB81" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-okulary-korekcyjne-t-1013-c6</t>
         </is>
       </c>
-      <c r="AB81" s="3" t="inlineStr">
+      <c r="AC81" s="3" t="inlineStr">
         <is>
           <t>OKULARY KOREKCYJNE GOYA T 1013 C6 Produkt nowy - posiadają oryginalne zabezpieczenia, metkę oraz instrukcję użytkowania, dodatkowo w zestawie twarde etui na zawias sprężynowy Marki GOYA oraz miękką ściereczkę czyszczącą. NASZE PRODUKTY WYSYŁAMY BARDZO DOBRZE ZABEZPIECZONE W FOLIĘ TRANSPORTOWĄ I ZAPAKOWANE W WYTRZYMAŁY KARTONIK</t>
         </is>
@@ -14510,35 +14916,40 @@
       </c>
       <c r="V82" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/575_6.jpg</t>
+        </is>
+      </c>
+      <c r="W82" s="2" t="inlineStr">
+        <is>
           <t>/products/575_6.jpg</t>
         </is>
       </c>
-      <c r="W82" s="2" t="inlineStr">
+      <c r="X82" s="2" t="inlineStr">
         <is>
           <t>/products/575_6.jpg; /products/575_5.jpg</t>
         </is>
       </c>
-      <c r="X82" s="2" t="inlineStr">
+      <c r="Y82" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2022/11/575_6.jpg</t>
         </is>
       </c>
-      <c r="Y82" s="2" t="inlineStr">
+      <c r="Z82" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary korekcyjne G 2635 C4</t>
         </is>
       </c>
-      <c r="Z82" s="2" t="inlineStr">
+      <c r="AA82" s="2" t="inlineStr">
         <is>
           <t>goya-okulary-korekcyjne-g-2635-c4</t>
         </is>
       </c>
-      <c r="AA82" s="2" t="inlineStr">
+      <c r="AB82" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-okulary-korekcyjne-g-2635-c4</t>
         </is>
       </c>
-      <c r="AB82" s="3" t="inlineStr">
+      <c r="AC82" s="3" t="inlineStr">
         <is>
           <t>OKULARY KOREKCYJNE GOYA G 2635 C4 Produkt nowy ! - posiadają oryginalne zabezpieczenia, metkę oraz instrukcję użytkowania, dodatkowo w zestawie twarde etui na zawias sprężynowy Marki GOYA oraz miękką ściereczkę czyszczącą. NASZE PRODUKTY SĄ BARDZO DOBRZE ZABEZPIECZONE W FOLIĘ TRANSPORTOWĄ I ZAPAKOWANE W WYTRZYMAŁY KARTONIK</t>
         </is>
@@ -14630,35 +15041,40 @@
       </c>
       <c r="V83" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/prof-298.jpeg</t>
+        </is>
+      </c>
+      <c r="W83" s="2" t="inlineStr">
+        <is>
           <t>/products/prof-298.jpeg</t>
         </is>
       </c>
-      <c r="W83" s="2" t="inlineStr">
+      <c r="X83" s="2" t="inlineStr">
         <is>
           <t>/products/prof-298.jpeg; /products/G_55004_CZ_MOD1pkw.jpg; /products/1808_1.jpeg; /products/1808_3.jpeg; /products/1808_4.jpeg; /products/1808_5.jpeg; /products/1808_6.jpeg; /products/1808_7.jpeg; /products/1808_8.jpeg; /products/1808_9.jpeg; /products/1808_11.jpeg</t>
         </is>
       </c>
-      <c r="X83" s="2" t="inlineStr">
+      <c r="Y83" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2022/03/prof-298.jpeg</t>
         </is>
       </c>
-      <c r="Y83" s="2" t="inlineStr">
+      <c r="Z83" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary przeciwsłoneczne z filtrem polaryzacyjnym - G 55004 CZ</t>
         </is>
       </c>
-      <c r="Z83" s="2" t="inlineStr">
+      <c r="AA83" s="2" t="inlineStr">
         <is>
           <t>okulary-przeciwsloneczne-polaryzacyjne-dla-kierowcow-pilotki-goya-g-55004-cz</t>
         </is>
       </c>
-      <c r="AA83" s="2" t="inlineStr">
+      <c r="AB83" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/okulary-przeciwsloneczne-polaryzacyjne-dla-kierowcow-pilotki-goya-g-55004-cz</t>
         </is>
       </c>
-      <c r="AB83" s="3" t="inlineStr">
+      <c r="AC83" s="3" t="inlineStr">
         <is>
           <t>OKULARY PRZECIWSŁONECZNE DLA KIEROWCÓW GOYA Z FILTREM POLARYZACYJNYM I UV400 Oprawki wykonane w całości z aluminium - co sprawia, że okulary są bardzo lekkie i wytrzymałe. Soczewki okularów GOYA o grubości 1,1 wyposażone są w filtr polaryzacyjny oraz filtr ochronny UV-400 (UV-A, UV-B, UV-C) ZAUSZNIKI POŁĄCZONE Z OPRAWKĄ SYSTEMEM FLEX: FLEX - elastyczne połączenie zausznika z frontem oprawy. Zwiększony zakres odchylenia zausznika do ponad 110° gwarantuje wygodę noszenia i ułatwia zakładanie oraz zdejmowanie okularów. OKULARY POSIADAJĄ CERTYFIKAT CE. Produkt odpowiada Wytycznej Europejskiej 89/686/EWG zgodnie z normą PN-EN ISO 12312-1:2014-02/A1:2016-01. Każda para okularów posiada oryginalne oznaczenia znajdujące się na wewnętrznej stronie zauszników ; logo producenta, numer modelu, kategoria filtra oraz oznaczenie CE. O POLARYZACJI: Soczewki polaryzacyjne neutralizują oślepiające refleksy, powstające wówczas gdy światło odbija się od mokrej drogi, powierzchni wody lub śniegu. Eliminacja światła odbitego zwiększ kontrast widzenia i pozwala</t>
         </is>
@@ -14746,35 +15162,40 @@
       </c>
       <c r="V84" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/619_4.jpg</t>
+        </is>
+      </c>
+      <c r="W84" s="2" t="inlineStr">
+        <is>
           <t>/products/619_4.jpg</t>
         </is>
       </c>
-      <c r="W84" s="2" t="inlineStr">
+      <c r="X84" s="2" t="inlineStr">
         <is>
           <t>/products/619_4.jpg; /products/619_1.jpg; /products/619_3.jpg; /products/619_2.jpg</t>
         </is>
       </c>
-      <c r="X84" s="2" t="inlineStr">
+      <c r="Y84" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2022/11/619_4.jpg</t>
         </is>
       </c>
-      <c r="Y84" s="2" t="inlineStr">
+      <c r="Z84" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary korekcyjne - G 89087 C3</t>
         </is>
       </c>
-      <c r="Z84" s="2" t="inlineStr">
+      <c r="AA84" s="2" t="inlineStr">
         <is>
           <t>goya-okulary-korekcyjne-g-89087-c3</t>
         </is>
       </c>
-      <c r="AA84" s="2" t="inlineStr">
+      <c r="AB84" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-okulary-korekcyjne-g-89087-c3</t>
         </is>
       </c>
-      <c r="AB84" s="3" t="inlineStr">
+      <c r="AC84" s="3" t="inlineStr">
         <is>
           <t>OKULARY KOREKCYJNE GOYA G 89087 C3 Produkt nowy - posiadają oryginalne zabezpieczenia, metkę oraz instrukcję użytkowania, dodatkowo w zestawie twarde etui na zawias sprężynowy Marki GOYA oraz miękką ściereczkę czyszczącą. NASZE PRODUKTY WYSYŁAMY BARDZO DOBRZE ZABEZPIECZONE W FOLIĘ TRANSPORTOWĄ I ZAPAKOWANE W WYTRZYMAŁY KARTONIK</t>
         </is>
@@ -14862,35 +15283,40 @@
       </c>
       <c r="V85" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/603_4.jpg</t>
+        </is>
+      </c>
+      <c r="W85" s="2" t="inlineStr">
+        <is>
           <t>/products/603_4.jpg</t>
         </is>
       </c>
-      <c r="W85" s="2" t="inlineStr">
+      <c r="X85" s="2" t="inlineStr">
         <is>
           <t>/products/603_4.jpg; /products/603_1.jpg; /products/603_3.jpg; /products/603_2.jpg</t>
         </is>
       </c>
-      <c r="X85" s="2" t="inlineStr">
+      <c r="Y85" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2022/11/603_4.jpg</t>
         </is>
       </c>
-      <c r="Y85" s="2" t="inlineStr">
+      <c r="Z85" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary korekcyjne - G 2659 C1</t>
         </is>
       </c>
-      <c r="Z85" s="2" t="inlineStr">
+      <c r="AA85" s="2" t="inlineStr">
         <is>
           <t>goya-okulary-korekcyjne-g-2659-c1</t>
         </is>
       </c>
-      <c r="AA85" s="2" t="inlineStr">
+      <c r="AB85" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-okulary-korekcyjne-g-2659-c1</t>
         </is>
       </c>
-      <c r="AB85" s="3" t="inlineStr">
+      <c r="AC85" s="3" t="inlineStr">
         <is>
           <t>OKULARY KOREKCYJNE GOYA G 2659 C1 Produkt nowy - posiadają oryginalne zabezpieczenia, metkę oraz instrukcję użytkowania, dodatkowo w zestawie twarde etui na zawias sprężynowy Marki GOYA oraz miękką ściereczkę czyszczącą. NASZE PRODUKTY WYSYŁAMY BARDZO DOBRZE ZABEZPIECZONE W FOLIĘ TRANSPORTOWĄ I ZAPAKOWANE W WYTRZYMAŁY KARTONIK</t>
         </is>
@@ -14978,35 +15404,40 @@
       </c>
       <c r="V86" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/590_3.jpg</t>
+        </is>
+      </c>
+      <c r="W86" s="2" t="inlineStr">
+        <is>
           <t>/products/590_3.jpg</t>
         </is>
       </c>
-      <c r="W86" s="2" t="inlineStr">
+      <c r="X86" s="2" t="inlineStr">
         <is>
           <t>/products/590_3.jpg; /products/590_4.jpg; /products/590_2.jpg; /products/590_1.jpg</t>
         </is>
       </c>
-      <c r="X86" s="2" t="inlineStr">
+      <c r="Y86" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2022/11/590_3.jpg</t>
         </is>
       </c>
-      <c r="Y86" s="2" t="inlineStr">
+      <c r="Z86" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary korekcyjne - G 2622 C1</t>
         </is>
       </c>
-      <c r="Z86" s="2" t="inlineStr">
+      <c r="AA86" s="2" t="inlineStr">
         <is>
           <t>goya-okulary-korekcyjne-g-2622-c1</t>
         </is>
       </c>
-      <c r="AA86" s="2" t="inlineStr">
+      <c r="AB86" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-okulary-korekcyjne-g-2622-c1</t>
         </is>
       </c>
-      <c r="AB86" s="3" t="inlineStr">
+      <c r="AC86" s="3" t="inlineStr">
         <is>
           <t>OKULARY KOREKCYJNE GOYA G 2622 C1 Produkt nowy - posiadają oryginalne zabezpieczenia, metkę oraz instrukcję użytkowania, dodatkowo w zestawie twarde etui na zawias sprężynowy Marki GOYA oraz miękką ściereczkę czyszczącą. NASZE PRODUKTY WYSYŁAMY BARDZO DOBRZE ZABEZPIECZONE W FOLIĘ TRANSPORTOWĄ I ZAPAKOWANE W WYTRZYMAŁY KARTONIK</t>
         </is>
@@ -15096,35 +15527,40 @@
       </c>
       <c r="V87" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/3163_1.jpg</t>
+        </is>
+      </c>
+      <c r="W87" s="2" t="inlineStr">
+        <is>
           <t>/products/3163_1.jpg</t>
         </is>
       </c>
-      <c r="W87" s="2" t="inlineStr">
+      <c r="X87" s="2" t="inlineStr">
         <is>
           <t>/products/3163_1.jpg; /products/3161_6.jpg</t>
         </is>
       </c>
-      <c r="X87" s="2" t="inlineStr">
+      <c r="Y87" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2022/11/3163_1.jpg</t>
         </is>
       </c>
-      <c r="Y87" s="2" t="inlineStr">
+      <c r="Z87" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary przeciwsłoneczne z filtrem polaryzacyjnym - G 171</t>
         </is>
       </c>
-      <c r="Z87" s="2" t="inlineStr">
+      <c r="AA87" s="2" t="inlineStr">
         <is>
           <t>goya-g-171-zx-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym</t>
         </is>
       </c>
-      <c r="AA87" s="2" t="inlineStr">
+      <c r="AB87" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-g-171-zx-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym</t>
         </is>
       </c>
-      <c r="AB87" s="3" t="inlineStr">
+      <c r="AC87" s="3" t="inlineStr">
         <is>
           <t>OKULARY PRZECIWSŁONECZNE DLA KIEROWCÓW GOYA Z FILTREM POLARYZACYJNYM I UV400 Oprawka wykonana w technologii - wycinania z płyty. Ręcznie obrabiana. Soczewki okularów GOYA o grubości 1,1 wyposażone są w filtr polaryzacyjny oraz filtr ochronny UV-400 (UV-A, UV-B, UV-C) OKULARY POSIADAJĄ CERTYFIKAT CE. Produkt odpowiada Wytycznej Europejskiej 89/686/EWG zgodnie z normą PN-EN ISO 12312-1:2014-02/A1:2016-01. Każda para okularów posiada oryginalne oznaczenia znajdujące się na wewnętrznej stronie zauszników ; logo producenta, numer modelu, kategoria filtra oraz oznaczenie CE. O POLARYZACJI: Soczewki polaryzacyjne neutralizują oślepiające refleksy, powstające wówczas gdy światło odbija się od mokrej drogi, powierzchni wody lub śniegu. Eliminacja światła odbitego zwiększ kontrast widzenia i pozwala na bardziej komfortowe widzenie. Dlatego okulary z filtrem polaryzacyjnym to idealne rozwiązanie do wszelkiego rodzaju aktywności na świeżym powietrzu, pozwalające pełniej korzystać z życia. ZALETY: Eliminują oślepiające odblaski, zmniejszaj</t>
         </is>
@@ -15214,35 +15650,40 @@
       </c>
       <c r="V88" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/G-21609-BR-A.jpg</t>
+        </is>
+      </c>
+      <c r="W88" s="2" t="inlineStr">
+        <is>
           <t>/products/G-21609-BR-A.jpg</t>
         </is>
       </c>
-      <c r="W88" s="2" t="inlineStr">
+      <c r="X88" s="2" t="inlineStr">
         <is>
           <t>/products/G-21609-BR-A.jpg; /products/GOYA_G21609_cz_mod.jpg</t>
         </is>
       </c>
-      <c r="X88" s="2" t="inlineStr">
+      <c r="Y88" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2023/02/G-21609-BR-A.jpg</t>
         </is>
       </c>
-      <c r="Y88" s="2" t="inlineStr">
+      <c r="Z88" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary przeciwsłoneczne z filtrem polaryzacyjnym - G 21609</t>
         </is>
       </c>
-      <c r="Z88" s="2" t="inlineStr">
+      <c r="AA88" s="2" t="inlineStr">
         <is>
           <t>goya-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym-g-21609</t>
         </is>
       </c>
-      <c r="AA88" s="2" t="inlineStr">
+      <c r="AB88" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym-g-21609</t>
         </is>
       </c>
-      <c r="AB88" s="3" t="inlineStr">
+      <c r="AC88" s="3" t="inlineStr">
         <is>
           <t>OKULARY PRZECIWSŁONECZNE DLA KIEROWCÓW GOYA Z FILTREM POLARYZACYJNYM I UV400 Soczewki okularów GOYA o grubości 1,1 wyposażone są w filtr polaryzacyjny oraz filtr ochronny UV-400 (UV-A, UV-B, UV-C) OKULARY POSIADAJĄ CERTYFIKAT CE. Produkt odpowiada Wytycznej Europejskiej 89/686/EWG zgodnie z normą PN-EN ISO 12312-1:2014-02/A1:2016-01. Każda para okularów posiada oryginalne oznaczenia znajdujące się na wewnętrznej stronie zauszników ; logo producenta, numer modelu, kategoria filtra oraz oznaczenie CE. O POLARYZACJI: Soczewki polaryzacyjne neutralizują oślepiające refleksy, powstające wówczas gdy światło odbija się od mokrej drogi, powierzchni wody lub śniegu. Eliminacja światła odbitego zwiększ kontrast widzenia i pozwala na bardziej komfortowe widzenie. Dlatego okulary z filtrem polaryzacyjnym to idealne rozwiązanie do wszelkiego rodzaju aktywności na świeżym powietrzu, pozwalające pełniej korzystać z życia. ZALETY: Eliminują oślepiające odblaski, zmniejszając zmęczenie oczu Chronią przed szkodliwym promieniowaniem UV Zwię</t>
         </is>
@@ -15330,35 +15771,40 @@
       </c>
       <c r="V89" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/585_4.jpg</t>
+        </is>
+      </c>
+      <c r="W89" s="2" t="inlineStr">
+        <is>
           <t>/products/585_4.jpg</t>
         </is>
       </c>
-      <c r="W89" s="2" t="inlineStr">
+      <c r="X89" s="2" t="inlineStr">
         <is>
           <t>/products/585_4.jpg; /products/585_1.jpg; /products/585_3.jpg; /products/585_2.jpg</t>
         </is>
       </c>
-      <c r="X89" s="2" t="inlineStr">
+      <c r="Y89" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2022/11/585_4.jpg</t>
         </is>
       </c>
-      <c r="Y89" s="2" t="inlineStr">
+      <c r="Z89" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary korekcyjne - G 2611 C2</t>
         </is>
       </c>
-      <c r="Z89" s="2" t="inlineStr">
+      <c r="AA89" s="2" t="inlineStr">
         <is>
           <t>goya-okulary-korekcyjne-g-2611-c2</t>
         </is>
       </c>
-      <c r="AA89" s="2" t="inlineStr">
+      <c r="AB89" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-okulary-korekcyjne-g-2611-c2</t>
         </is>
       </c>
-      <c r="AB89" s="3" t="inlineStr">
+      <c r="AC89" s="3" t="inlineStr">
         <is>
           <t>OKULARY KOREKCYJNE GOYA G 2611 C2 Produkt nowy - posiadają oryginalne zabezpieczenia, metkę oraz instrukcję użytkowania, dodatkowo w zestawie twarde etui na zawias sprężynowy Marki GOYA oraz miękką ściereczkę czyszczącą. NASZE PRODUKTY WYSYŁAMY BARDZO DOBRZE ZABEZPIECZONE W FOLIĘ TRANSPORTOWĄ I ZAPAKOWANE W WYTRZYMAŁY KARTONIK</t>
         </is>
@@ -15448,35 +15894,40 @@
       </c>
       <c r="V90" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/2467_1.jpg</t>
+        </is>
+      </c>
+      <c r="W90" s="2" t="inlineStr">
+        <is>
           <t>/products/2467_1.jpg</t>
         </is>
       </c>
-      <c r="W90" s="2" t="inlineStr">
+      <c r="X90" s="2" t="inlineStr">
         <is>
           <t>/products/2467_1.jpg</t>
         </is>
       </c>
-      <c r="X90" s="2" t="inlineStr">
+      <c r="Y90" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2022/11/2467_1.jpg</t>
         </is>
       </c>
-      <c r="Y90" s="2" t="inlineStr">
+      <c r="Z90" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary przeciwsłoneczne z filtrem polaryzacyjnym - G 9496</t>
         </is>
       </c>
-      <c r="Z90" s="2" t="inlineStr">
+      <c r="AA90" s="2" t="inlineStr">
         <is>
           <t>goya-g-g-9496-br-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym</t>
         </is>
       </c>
-      <c r="AA90" s="2" t="inlineStr">
+      <c r="AB90" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-g-g-9496-br-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym</t>
         </is>
       </c>
-      <c r="AB90" s="3" t="inlineStr">
+      <c r="AC90" s="3" t="inlineStr">
         <is>
           <t>OKULARY PRZECIWSŁONECZNE DLA KIEROWCÓW GOYA Z FILTREM POLARYZACYJNYM I UV400 Oprawki wykonane w całości z aluminium - co sprawia, że okulary są bardzo lekkie i wytrzymałe. Soczewki okularów GOYA o grubości 1,1 wyposażone są w filtr polaryzacyjny oraz filtr ochronny UV-400 (UV-A, UV-B, UV-C) ZAUSZNIKI POŁĄCZONE Z OPRAWKĄ SYSTEMEM FLEX: FLEX - elastyczne połączenie zausznika z frontem oprawy. Zwiększony zakres odchylenia zausznika do ponad 110° gwarantuje wygodę noszenia i ułatwia zakładanie oraz zdejmowanie okularów. OKULARY POSIADAJĄ CERTYFIKAT CE. Produkt odpowiada Wytycznej Europejskiej 89/686/EWG zgodnie z normą PN-EN ISO 12312-1:2014-02/A1:2016-01. Każda para okularów posiada oryginalne oznaczenia znajdujące się na wewnętrznej stronie zauszników ; logo producenta, numer modelu, kategoria filtra oraz oznaczenie CE. O POLARYZACJI: Soczewki polaryzacyjne neutralizują oślepiające refleksy, powstające wówczas gdy światło odbija się od mokrej drogi, powierzchni wody lub śniegu. Eliminacja światła odbitego zwiększ kontrast widzenia i pozwala na</t>
         </is>
@@ -15562,35 +16013,40 @@
       </c>
       <c r="V91" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/617_4.jpg</t>
+        </is>
+      </c>
+      <c r="W91" s="2" t="inlineStr">
+        <is>
           <t>/products/617_4.jpg</t>
         </is>
       </c>
-      <c r="W91" s="2" t="inlineStr">
+      <c r="X91" s="2" t="inlineStr">
         <is>
           <t>/products/617_4.jpg</t>
         </is>
       </c>
-      <c r="X91" s="2" t="inlineStr">
+      <c r="Y91" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2022/11/617_4.jpg</t>
         </is>
       </c>
-      <c r="Y91" s="2" t="inlineStr">
+      <c r="Z91" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary korekcyjne - G 2740</t>
         </is>
       </c>
-      <c r="Z91" s="2" t="inlineStr">
+      <c r="AA91" s="2" t="inlineStr">
         <is>
           <t>goya-okulary-korekcyjne-g-2740-c2</t>
         </is>
       </c>
-      <c r="AA91" s="2" t="inlineStr">
+      <c r="AB91" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-okulary-korekcyjne-g-2740-c2</t>
         </is>
       </c>
-      <c r="AB91" s="3" t="inlineStr">
+      <c r="AC91" s="3" t="inlineStr">
         <is>
           <t>OKULARY KOREKCYJNE GOYA G 2740 Produkt nowy - posiadają oryginalne zabezpieczenia, metkę oraz instrukcję użytkowania, dodatkowo w zestawie twarde etui na zawias sprężynowy Marki GOYA oraz miękką ściereczkę czyszczącą. NASZE PRODUKTY WYSYŁAMY BARDZO DOBRZE ZABEZPIECZONE W FOLIĘ TRANSPORTOWĄ I ZAPAKOWANE W WYTRZYMAŁY KARTONIK</t>
         </is>
@@ -15678,35 +16134,40 @@
       </c>
       <c r="V92" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/678_4.jpg</t>
+        </is>
+      </c>
+      <c r="W92" s="2" t="inlineStr">
+        <is>
           <t>/products/678_4.jpg</t>
         </is>
       </c>
-      <c r="W92" s="2" t="inlineStr">
+      <c r="X92" s="2" t="inlineStr">
         <is>
           <t>/products/678_4.jpg; /products/678_1.jpg; /products/678_3.jpg; /products/678_2.jpg</t>
         </is>
       </c>
-      <c r="X92" s="2" t="inlineStr">
+      <c r="Y92" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2022/11/678_4.jpg</t>
         </is>
       </c>
-      <c r="Y92" s="2" t="inlineStr">
+      <c r="Z92" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary korekcyjne - G 95544 C3</t>
         </is>
       </c>
-      <c r="Z92" s="2" t="inlineStr">
+      <c r="AA92" s="2" t="inlineStr">
         <is>
           <t>goya-okulary-korekcyjne-g-95544-c3</t>
         </is>
       </c>
-      <c r="AA92" s="2" t="inlineStr">
+      <c r="AB92" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-okulary-korekcyjne-g-95544-c3</t>
         </is>
       </c>
-      <c r="AB92" s="3" t="inlineStr">
+      <c r="AC92" s="3" t="inlineStr">
         <is>
           <t>OKULARY KOREKCYJNE GOYA G 95544 C3 Produkt nowy - posiadają oryginalne zabezpieczenia, metkę oraz instrukcję użytkowania, dodatkowo w zestawie twarde etui na zawias sprężynowy Marki GOYA oraz miękką ściereczkę czyszczącą. NASZE PRODUKTY WYSYŁAMY BARDZO DOBRZE ZABEZPIECZONE W FOLIĘ TRANSPORTOWĄ I ZAPAKOWANE W WYTRZYMAŁY KARTONIK</t>
         </is>
@@ -15796,35 +16257,40 @@
       </c>
       <c r="V93" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/3191_1.jpg</t>
+        </is>
+      </c>
+      <c r="W93" s="2" t="inlineStr">
+        <is>
           <t>/products/3191_1.jpg</t>
         </is>
       </c>
-      <c r="W93" s="2" t="inlineStr">
+      <c r="X93" s="2" t="inlineStr">
         <is>
           <t>/products/3191_1.jpg; /products/3190_6.jpg</t>
         </is>
       </c>
-      <c r="X93" s="2" t="inlineStr">
+      <c r="Y93" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2023/01/3191_1.jpg</t>
         </is>
       </c>
-      <c r="Y93" s="2" t="inlineStr">
+      <c r="Z93" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary przeciwsłoneczne z filtrem polaryzacyjnym - G 148</t>
         </is>
       </c>
-      <c r="Z93" s="2" t="inlineStr">
+      <c r="AA93" s="2" t="inlineStr">
         <is>
           <t>goya-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym-g-148</t>
         </is>
       </c>
-      <c r="AA93" s="2" t="inlineStr">
+      <c r="AB93" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym-g-148</t>
         </is>
       </c>
-      <c r="AB93" s="3" t="inlineStr">
+      <c r="AC93" s="3" t="inlineStr">
         <is>
           <t>OKULARY PRZECIWSŁONECZNE DLA KIEROWCÓW GOYA Z FILTREM POLARYZACYJNYM I UV400 Oprawka wykonana w technologii - wycinania z płyty. Ręcznie obrabiana. Soczewki okularów GOYA o grubości 1,1 wyposażone są w filtr polaryzacyjny oraz filtr ochronny UV-400 (UV-A, UV-B, UV-C) OKULARY POSIADAJĄ CERTYFIKAT CE. Produkt odpowiada Wytycznej Europejskiej 89/686/EWG zgodnie z normą PN-EN ISO 12312-1:2014-02/A1:2016-01. Każda para okularów posiada oryginalne oznaczenia znajdujące się na wewnętrznej stronie zauszników ; logo producenta, numer modelu, kategoria filtra oraz oznaczenie CE. O POLARYZACJI: Soczewki polaryzacyjne neutralizują oślepiające refleksy, powstające wówczas gdy światło odbija się od mokrej drogi, powierzchni wody lub śniegu. Eliminacja światła odbitego zwiększ kontrast widzenia i pozwala na bardziej komfortowe widzenie. Dlatego okulary z filtrem polaryzacyjnym to idealne rozwiązanie do wszelkiego rodzaju aktywności na świeżym powietrzu, pozwalające pełniej korzystać z życia. ZALETY: Eliminują oślepiające odblaski, zmniejszaj</t>
         </is>
@@ -15916,35 +16382,40 @@
       </c>
       <c r="V94" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/goya_A.jpg</t>
+        </is>
+      </c>
+      <c r="W94" s="2" t="inlineStr">
+        <is>
           <t>/products/goya_A.jpg</t>
         </is>
       </c>
-      <c r="W94" s="2" t="inlineStr">
+      <c r="X94" s="2" t="inlineStr">
         <is>
           <t>/products/goya_A.jpg; /products/goya-1000-model.png; /products/goya_AA.jpg; /products/goya_F.jpg; /products/goya_B.jpg; /products/goya_S.jpg</t>
         </is>
       </c>
-      <c r="X94" s="2" t="inlineStr">
+      <c r="Y94" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2026/04/goya_A.jpg</t>
         </is>
       </c>
-      <c r="Y94" s="2" t="inlineStr">
+      <c r="Z94" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary przeciwsłoneczne z filtrem UV- G 1000 BR</t>
         </is>
       </c>
-      <c r="Z94" s="2" t="inlineStr">
+      <c r="AA94" s="2" t="inlineStr">
         <is>
           <t>goya-okulary-przeciwsloneczne-z-filtrem-uv-g-1000-br</t>
         </is>
       </c>
-      <c r="AA94" s="2" t="inlineStr">
+      <c r="AB94" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-okulary-przeciwsloneczne-z-filtrem-uv-g-1000-br</t>
         </is>
       </c>
-      <c r="AB94" s="3" t="inlineStr">
+      <c r="AC94" s="3" t="inlineStr">
         <is>
           <t>OKULARY PRZECIWSŁONECZNE GOYA Z FILTREM UV400 Oprawka wykonana w technologii - wycinania z płyty. Ręcznie obrabiana. Soczewki okularów GOYA o grubości 1,1 wyposażone są w filtr ochronny UV-400 (UV-A, UV-B, UV-C) OKULARY POSIADAJĄ CERTYFIKAT CE. Produkt odpowiada Wytycznej Europejskiej 89/686/EWG zgodnie z normą PN-EN ISO 12312-1:2014-02/A1:2016-01. Każda para okularów posiada oryginalne oznaczenia znajdujące się na wewnętrznej stronie zauszników ; logo producenta, numer modelu, kategoria filtra oraz oznaczenie CE. ZALETY: Eliminują oślepiające odblaski, zmniejszając zmęczenie oczu Chronią przed szkodliwym promieniowaniem UV Zwiększają kontrast widzenia Idealne rozwiązanie dla osób wrażliwych na światło Niezastąpione dla osób uprawiających sporty wodne, łowiących ryby, grających w golfa, jeżdżących samochodem i na nartach Produkt nowy! - posiadają oryginalne zabezpieczenia, metkę oraz instrukcję użytkowania, dodatkowo w zestawie twarde etui oraz miękkie etui czyszczące (ściereczko-etui). GRATIS! NASZE PROD</t>
         </is>
@@ -16032,35 +16503,40 @@
       </c>
       <c r="V95" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/606_4.jpg</t>
+        </is>
+      </c>
+      <c r="W95" s="2" t="inlineStr">
+        <is>
           <t>/products/606_4.jpg</t>
         </is>
       </c>
-      <c r="W95" s="2" t="inlineStr">
+      <c r="X95" s="2" t="inlineStr">
         <is>
           <t>/products/606_4.jpg; /products/606_1.jpg; /products/606_3.jpg; /products/606_2.jpg</t>
         </is>
       </c>
-      <c r="X95" s="2" t="inlineStr">
+      <c r="Y95" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2022/11/606_4.jpg</t>
         </is>
       </c>
-      <c r="Y95" s="2" t="inlineStr">
+      <c r="Z95" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary korekcyjne - G 2716 C1</t>
         </is>
       </c>
-      <c r="Z95" s="2" t="inlineStr">
+      <c r="AA95" s="2" t="inlineStr">
         <is>
           <t>goya-okulary-korekcyjne-g-2716-c1</t>
         </is>
       </c>
-      <c r="AA95" s="2" t="inlineStr">
+      <c r="AB95" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-okulary-korekcyjne-g-2716-c1</t>
         </is>
       </c>
-      <c r="AB95" s="3" t="inlineStr">
+      <c r="AC95" s="3" t="inlineStr">
         <is>
           <t>OKULARY KOREKCYJNE GOYA G 2716 C1 Produkt nowy - posiadają oryginalne zabezpieczenia, metkę oraz instrukcję użytkowania, dodatkowo w zestawie twarde etui na zawias sprężynowy Marki GOYA oraz miękką ściereczkę czyszczącą. NASZE PRODUKTY WYSYŁAMY BARDZO DOBRZE ZABEZPIECZONE W FOLIĘ TRANSPORTOWĄ I ZAPAKOWANE W WYTRZYMAŁY KARTONIK</t>
         </is>
@@ -16150,35 +16626,40 @@
       </c>
       <c r="V96" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/3518_1.jpg</t>
+        </is>
+      </c>
+      <c r="W96" s="2" t="inlineStr">
+        <is>
           <t>/products/3518_1.jpg</t>
         </is>
       </c>
-      <c r="W96" s="2" t="inlineStr">
+      <c r="X96" s="2" t="inlineStr">
         <is>
           <t>/products/3518_1.jpg; /products/GOYA_A0711_CZ_MOD.jpg</t>
         </is>
       </c>
-      <c r="X96" s="2" t="inlineStr">
+      <c r="Y96" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2023/04/3518_1.jpg</t>
         </is>
       </c>
-      <c r="Y96" s="2" t="inlineStr">
+      <c r="Z96" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary przeciwsłoneczne z filtrem polaryzacyjnym - GOYA A 0711</t>
         </is>
       </c>
-      <c r="Z96" s="2" t="inlineStr">
+      <c r="AA96" s="2" t="inlineStr">
         <is>
           <t>goya-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym-goya-a-0711</t>
         </is>
       </c>
-      <c r="AA96" s="2" t="inlineStr">
+      <c r="AB96" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym-goya-a-0711</t>
         </is>
       </c>
-      <c r="AB96" s="3" t="inlineStr">
+      <c r="AC96" s="3" t="inlineStr">
         <is>
           <t>OKULARY PRZECIWSŁONECZNE GOYA Z FILTREM POLARYZACYJNYM I UV400 Soczewki okularów GOYA o grubości 1,1 wyposażone są w filtr polaryzacyjny oraz filtr ochronny UV-400 (UV-A, UV-B, UV-C) OKULARY POSIADAJĄ CERTYFIKAT CE. Produkt odpowiada Wytycznej Europejskiej 89/686/EWG zgodnie z normą PN-EN ISO 12312-1:2014-02/A1:2016-01. Każda para okularów posiada oryginalne oznaczenia znajdujące się na wewnętrznej stronie zauszników ; logo producenta, numer modelu, kategoria filtra oraz oznaczenie CE. O POLARYZACJI: Soczewki polaryzacyjne neutralizują oślepiające refleksy, powstające wówczas gdy światło odbija się od mokrej drogi, powierzchni wody lub śniegu. Eliminacja światła odbitego zwiększ kontrast widzenia i pozwala na bardziej komfortowe widzenie. Dlatego okulary z filtrem polaryzacyjnym to idealne rozwiązanie do wszelkiego rodzaju aktywności na świeżym powietrzu, pozwalające pełniej korzystać z życia. ZALETY: Eliminują oślepiające odblaski, zmniejszając zmęczenie oczu Chronią przed szkodliwym promieniowaniem UV Zwiększają kontras</t>
         </is>
@@ -16266,35 +16747,40 @@
       </c>
       <c r="V97" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/581_4.jpg</t>
+        </is>
+      </c>
+      <c r="W97" s="2" t="inlineStr">
+        <is>
           <t>/products/581_4.jpg</t>
         </is>
       </c>
-      <c r="W97" s="2" t="inlineStr">
+      <c r="X97" s="2" t="inlineStr">
         <is>
           <t>/products/581_4.jpg; /products/581_3.jpg; /products/581_2.jpg; /products/581_1.jpg</t>
         </is>
       </c>
-      <c r="X97" s="2" t="inlineStr">
+      <c r="Y97" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2022/11/581_4.jpg</t>
         </is>
       </c>
-      <c r="Y97" s="2" t="inlineStr">
+      <c r="Z97" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary korekcyjne - G 2618 C4</t>
         </is>
       </c>
-      <c r="Z97" s="2" t="inlineStr">
+      <c r="AA97" s="2" t="inlineStr">
         <is>
           <t>goya-okulary-korekcyjne-g-2618-c4</t>
         </is>
       </c>
-      <c r="AA97" s="2" t="inlineStr">
+      <c r="AB97" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-okulary-korekcyjne-g-2618-c4</t>
         </is>
       </c>
-      <c r="AB97" s="3" t="inlineStr">
+      <c r="AC97" s="3" t="inlineStr">
         <is>
           <t>OKULARY KOREKCYJNE GOYA G 2618 C4 Produkt nowy - posiadają oryginalne zabezpieczenia, metkę oraz instrukcję użytkowania, dodatkowo w zestawie twarde etui na zawias sprężynowy Marki GOYA oraz miękką ściereczkę czyszczącą. NASZE PRODUKTY WYSYŁAMY BARDZO DOBRZE ZABEZPIECZONE W FOLIĘ TRANSPORTOWĄ I ZAPAKOWANE W WYTRZYMAŁY KARTONIK</t>
         </is>
@@ -16384,35 +16870,40 @@
       </c>
       <c r="V98" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/3138_6.jpg</t>
+        </is>
+      </c>
+      <c r="W98" s="2" t="inlineStr">
+        <is>
           <t>/products/3138_6.jpg</t>
         </is>
       </c>
-      <c r="W98" s="2" t="inlineStr">
+      <c r="X98" s="2" t="inlineStr">
         <is>
           <t>/products/3138_6.jpg; /products/3137_1.jpg</t>
         </is>
       </c>
-      <c r="X98" s="2" t="inlineStr">
+      <c r="Y98" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2022/11/3138_6.jpg</t>
         </is>
       </c>
-      <c r="Y98" s="2" t="inlineStr">
+      <c r="Z98" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary przeciwsłoneczne z filtrem polaryzacyjnym - G 186</t>
         </is>
       </c>
-      <c r="Z98" s="2" t="inlineStr">
+      <c r="AA98" s="2" t="inlineStr">
         <is>
           <t>goya-g-186-br-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym</t>
         </is>
       </c>
-      <c r="AA98" s="2" t="inlineStr">
+      <c r="AB98" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-g-186-br-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym</t>
         </is>
       </c>
-      <c r="AB98" s="3" t="inlineStr">
+      <c r="AC98" s="3" t="inlineStr">
         <is>
           <t>OKULARY PRZECIWSŁONECZNE DLA KIEROWCÓW GOYA Z FILTREM POLARYZACYJNYM I UV400 Soczewki okularów GOYA o grubości 1,1 wyposażone są w filtr polaryzacyjny oraz filtr ochronny UV-400 (UV-A, UV-B, UV-C) OPRAWKA WYKONANA W TECHNOLOGII TR-90 Wysokiej jakości odmiana nylonu, wyjątkowo odporna na rozciąganie i wyginanie. Materiał wytrzymały na uderzenia, elastyczny, przyjemny w dotyku, o właściwościach antyalergicznych. Okulary wykonane z TR-90 są lekkie, wytrzymałe i wygodne w użytkowaniu. OKULARY POSIADAJĄ CERTYFIKAT CE. Produkt odpowiada Wytycznej Europejskiej 89/686/EWG zgodnie z normą PN-EN ISO 12312-1:2014-02/A1:2016-01. Każda para okularów posiada oryginalne oznaczenia znajdujące się na wewnętrznej stronie zauszników ; logo producenta, numer modelu, kategoria filtra oraz oznaczenie CE. O POLARYZACJI: Soczewki polaryzacyjne neutralizują oślepiające refleksy, powstające wówczas gdy światło odbija się od mokrej drogi, powierzchni wody lub śniegu. Eliminacja światła odbitego zwiększ kontrast widzenia i pozwala na bardziej komfortowe widzenie. Dlatego o</t>
         </is>
@@ -16504,35 +16995,40 @@
       </c>
       <c r="V99" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/973_6.jpg</t>
+        </is>
+      </c>
+      <c r="W99" s="2" t="inlineStr">
+        <is>
           <t>/products/973_6.jpg</t>
         </is>
       </c>
-      <c r="W99" s="2" t="inlineStr">
+      <c r="X99" s="2" t="inlineStr">
         <is>
           <t>/products/973_6.jpg; /products/973_2.jpg; /products/973_7.jpg; /products/973_3.jpg; /products/973_1.jpg</t>
         </is>
       </c>
-      <c r="X99" s="2" t="inlineStr">
+      <c r="Y99" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2022/11/973_6.jpg</t>
         </is>
       </c>
-      <c r="Y99" s="2" t="inlineStr">
+      <c r="Z99" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary przeciwsłoneczne z filtrem polaryzacyjnym - G1926 C1</t>
         </is>
       </c>
-      <c r="Z99" s="2" t="inlineStr">
+      <c r="AA99" s="2" t="inlineStr">
         <is>
           <t>goya-g1926-c1-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym</t>
         </is>
       </c>
-      <c r="AA99" s="2" t="inlineStr">
+      <c r="AB99" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-g1926-c1-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym</t>
         </is>
       </c>
-      <c r="AB99" s="3" t="inlineStr">
+      <c r="AC99" s="3" t="inlineStr">
         <is>
           <t>OKULARY PRZECIWSŁONECZNE DLA KIEROWCÓW GOYA Z FILTREM POLARYZACYJNYM I UV400 Soczewki okularów GOYA o grubości 1,1 wyposażone są w filtr polaryzacyjny oraz filtr ochronny UV-400 (UV-A, UV-B, UV-C) OPRAWKA WYKONANA W TECHNOLOGII TR-90 Wysokiej jakości odmiana nylonu, wyjątkowo odporna na rozciąganie i wyginanie. Materiał wytrzymały na uderzenia, elastyczny, przyjemny w dotyku, o właściwościach antyalergicznych. Okulary wykonane z TR-90 są lekkie, wytrzymałe i wygodne w użytkowaniu. ZAUSZNIKI POŁĄCZONE Z OPRAWKĄ SYSTEMEM FLEX: FLEX - elastyczne połączenie zausznika z frontem oprawy. Zwiększony zakres odchylenia zausznika do ponad 110° gwarantuje wygodę noszenia i ułatwia zakładanie oraz zdejmowanie okularów. OKULARY POSIADAJĄ CERTYFIKAT CE. Produkt odpowiada Wytycznej Europejskiej 89/686/EWG zgodnie z normą PN-EN ISO 12312-1:2014-02/A1:2016-01. Każda para okularów posiada oryginalne oznaczenia znajdujące się na wewnętrznej stronie zauszników ; logo producenta, numer modelu, kategoria filtra oraz oznaczenie CE. O POLARYZACJI: Soczewki pol</t>
         </is>
@@ -16620,35 +17116,40 @@
       </c>
       <c r="V100" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/583_4.jpg</t>
+        </is>
+      </c>
+      <c r="W100" s="2" t="inlineStr">
+        <is>
           <t>/products/583_4.jpg</t>
         </is>
       </c>
-      <c r="W100" s="2" t="inlineStr">
+      <c r="X100" s="2" t="inlineStr">
         <is>
           <t>/products/583_4.jpg; /products/583_3.jpg; /products/583_2.jpg; /products/583_1.jpg</t>
         </is>
       </c>
-      <c r="X100" s="2" t="inlineStr">
+      <c r="Y100" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2022/11/583_4.jpg</t>
         </is>
       </c>
-      <c r="Y100" s="2" t="inlineStr">
+      <c r="Z100" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary korekcyjne - G 2618 C1</t>
         </is>
       </c>
-      <c r="Z100" s="2" t="inlineStr">
+      <c r="AA100" s="2" t="inlineStr">
         <is>
           <t>goya-okulary-korekcyjne-g-2618-c1</t>
         </is>
       </c>
-      <c r="AA100" s="2" t="inlineStr">
+      <c r="AB100" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-okulary-korekcyjne-g-2618-c1</t>
         </is>
       </c>
-      <c r="AB100" s="3" t="inlineStr">
+      <c r="AC100" s="3" t="inlineStr">
         <is>
           <t>OKULARY KOREKCYJNE GOYA G 2618 C1 Produkt nowy - posiadają oryginalne zabezpieczenia, metkę oraz instrukcję użytkowania, dodatkowo w zestawie twarde etui na zawias sprężynowy Marki GOYA oraz miękką ściereczkę czyszczącą. NASZE PRODUKTY WYSYŁAMY BARDZO DOBRZE ZABEZPIECZONE W FOLIĘ TRANSPORTOWĄ I ZAPAKOWANE W WYTRZYMAŁY KARTONIK</t>
         </is>
@@ -16740,35 +17241,40 @@
       </c>
       <c r="V101" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/G_55001_BR_A.jpg</t>
+        </is>
+      </c>
+      <c r="W101" s="2" t="inlineStr">
+        <is>
           <t>/products/G_55001_BR_A.jpg</t>
         </is>
       </c>
-      <c r="W101" s="2" t="inlineStr">
+      <c r="X101" s="2" t="inlineStr">
         <is>
           <t>/products/G_55001_BR_A.jpg; /products/G_55001_BR_G.jpg; /products/G_55001_BR_F1.jpg; /products/G_55001_BR_B.jpg; /products/G_55001_BR_S.jpg; /products/G_55001_BR_T.jpg; /products/G_55001_BR_F.jpg</t>
         </is>
       </c>
-      <c r="X101" s="2" t="inlineStr">
+      <c r="Y101" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2025/01/G_55001_BR_A.jpg</t>
         </is>
       </c>
-      <c r="Y101" s="2" t="inlineStr">
+      <c r="Z101" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary przeciwsłoneczne z filtrem polaryzacyjnym - G 55001 BR</t>
         </is>
       </c>
-      <c r="Z101" s="2" t="inlineStr">
+      <c r="AA101" s="2" t="inlineStr">
         <is>
           <t>goya-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym-g-55001-br</t>
         </is>
       </c>
-      <c r="AA101" s="2" t="inlineStr">
+      <c r="AB101" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym-g-55001-br</t>
         </is>
       </c>
-      <c r="AB101" s="3" t="inlineStr">
+      <c r="AC101" s="3" t="inlineStr">
         <is>
           <t>OKULARY PRZECIWSŁONECZNE DLA KIEROWCÓW GOYA Z FILTREM POLARYZACYJNYM I UV400 Zausznik wykonane w całości z aluminium - co sprawia, że okulary są bardzo lekkie i wytrzymałe. Soczewki okularów GOYA o grubości 1,1 wyposażone są w filtr polaryzacyjny oraz filtr ochronny UV-400 (UV-A, UV-B, UV-C) ZAUSZNIKI POŁĄCZONE Z OPRAWKĄ SYSTEMEM FLEX: FLEX - elastyczne połączenie zausznika z frontem oprawy. Zwiększony zakres odchylenia zausznika do ponad 110° gwarantuje wygodę noszenia i ułatwia zakładanie oraz zdejmowanie okularów. OKULARY POSIADAJĄ CERTYFIKAT CE. Produkt odpowiada Wytycznej Europejskiej 89/686/EWG zgodnie z normą PN-EN ISO 12312-1:2014-02/A1:2016-01. Każda para okularów posiada oryginalne oznaczenia znajdujące się na wewnętrznej stronie zauszników ; logo producenta, numer modelu, kategoria filtra oraz oznaczenie CE. O POLARYZACJI: Soczewki polaryzacyjne neutralizują oślepiające refleksy, powstające wówczas gdy światło odbija się od mokrej drogi, powierzchni wody lub śniegu. Eliminacja światła odbitego zwiększ kontrast widzenia i pozwala</t>
         </is>
@@ -16858,35 +17364,40 @@
       </c>
       <c r="V102" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/692_4.jpg</t>
+        </is>
+      </c>
+      <c r="W102" s="2" t="inlineStr">
+        <is>
           <t>/products/692_4.jpg</t>
         </is>
       </c>
-      <c r="W102" s="2" t="inlineStr">
+      <c r="X102" s="2" t="inlineStr">
         <is>
           <t>/products/692_4.jpg</t>
         </is>
       </c>
-      <c r="X102" s="2" t="inlineStr">
+      <c r="Y102" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2022/11/692_4.jpg</t>
         </is>
       </c>
-      <c r="Y102" s="2" t="inlineStr">
+      <c r="Z102" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary przeciwsłoneczne - G 96512S</t>
         </is>
       </c>
-      <c r="Z102" s="2" t="inlineStr">
+      <c r="AA102" s="2" t="inlineStr">
         <is>
           <t>goya-g-96512s-c2-okulary-przeciwsloneczne</t>
         </is>
       </c>
-      <c r="AA102" s="2" t="inlineStr">
+      <c r="AB102" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-g-96512s-c2-okulary-przeciwsloneczne</t>
         </is>
       </c>
-      <c r="AB102" s="3" t="inlineStr">
+      <c r="AC102" s="3" t="inlineStr">
         <is>
           <t>OKULARY PRZECIWSŁONECZNE MARKI GOYA OKULARY POSIADAJĄ CERTYFIKAT CE. Produkt odpowiada Wytycznej Europejskiej 89/686/EWG zgodnie z normą PN-EN ISO 12312-1:2014-02/A1:2016-01. Każda para okularów posiada oryginalne oznaczenia znajdujące się na wewnętrznej stronie zauszników ; logo producenta, numer modelu, kategoria filtra oraz oznaczenie CE. Produkt nowy - posiadają oryginalne zabezpieczenia, metkę oraz instrukcję użytkowania, dodatkowo w zestawie twarde etui na zawias sprężynowy Marki GOYA oraz miękką ściereczkę czyszczącą. NASZE PRODUKTY WYSYŁAMY BARDZO DOBRZE ZABEZPIECZONE W FOLIĘ TRANSPORTOWĄ I ZAPAKOWANE W WYTRZYMAŁY KARTONIK</t>
         </is>
@@ -16978,35 +17489,40 @@
       </c>
       <c r="V103" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/G_55001_GR_A.jpg</t>
+        </is>
+      </c>
+      <c r="W103" s="2" t="inlineStr">
+        <is>
           <t>/products/G_55001_GR_A.jpg</t>
         </is>
       </c>
-      <c r="W103" s="2" t="inlineStr">
+      <c r="X103" s="2" t="inlineStr">
         <is>
           <t>/products/G_55001_GR_A.jpg; /products/G_55001_GR_T.jpg; /products/G_55001_GR_S.jpg; /products/G_55001_GR_G.jpg; /products/G_55001_GR_F1.jpg; /products/G_55001_GR_F.jpg; /products/G_55001_GR_B.jpg</t>
         </is>
       </c>
-      <c r="X103" s="2" t="inlineStr">
+      <c r="Y103" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2025/01/G_55001_GR_A.jpg</t>
         </is>
       </c>
-      <c r="Y103" s="2" t="inlineStr">
+      <c r="Z103" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary przeciwsłoneczne z filtrem polaryzacyjnym - G 55001 GR</t>
         </is>
       </c>
-      <c r="Z103" s="2" t="inlineStr">
+      <c r="AA103" s="2" t="inlineStr">
         <is>
           <t>goya-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym-g-55001-gr</t>
         </is>
       </c>
-      <c r="AA103" s="2" t="inlineStr">
+      <c r="AB103" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym-g-55001-gr</t>
         </is>
       </c>
-      <c r="AB103" s="3" t="inlineStr">
+      <c r="AC103" s="3" t="inlineStr">
         <is>
           <t>OKULARY PRZECIWSŁONECZNE DLA KIEROWCÓW GOYA Z FILTREM POLARYZACYJNYM I UV400 Zausznik wykonane w całości z aluminium - co sprawia, że okulary są bardzo lekkie i wytrzymałe. Soczewki okularów GOYA o grubości 1,1 wyposażone są w filtr polaryzacyjny oraz filtr ochronny UV-400 (UV-A, UV-B, UV-C) ZAUSZNIKI POŁĄCZONE Z OPRAWKĄ SYSTEMEM FLEX: FLEX - elastyczne połączenie zausznika z frontem oprawy. Zwiększony zakres odchylenia zausznika do ponad 110° gwarantuje wygodę noszenia i ułatwia zakładanie oraz zdejmowanie okularów. OKULARY POSIADAJĄ CERTYFIKAT CE. Produkt odpowiada Wytycznej Europejskiej 89/686/EWG zgodnie z normą PN-EN ISO 12312-1:2014-02/A1:2016-01. Każda para okularów posiada oryginalne oznaczenia znajdujące się na wewnętrznej stronie zauszników ; logo producenta, numer modelu, kategoria filtra oraz oznaczenie CE. O POLARYZACJI: Soczewki polaryzacyjne neutralizują oślepiające refleksy, powstające wówczas gdy światło odbija się od mokrej drogi, powierzchni wody lub śniegu. Eliminacja światła odbitego zwiększ kontrast widzenia i pozwala</t>
         </is>
@@ -17094,35 +17610,40 @@
       </c>
       <c r="V104" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/676_4.jpg</t>
+        </is>
+      </c>
+      <c r="W104" s="2" t="inlineStr">
+        <is>
           <t>/products/676_4.jpg</t>
         </is>
       </c>
-      <c r="W104" s="2" t="inlineStr">
+      <c r="X104" s="2" t="inlineStr">
         <is>
           <t>/products/676_4.jpg; /products/676_1.jpg; /products/676_3.jpg; /products/676_2.jpg</t>
         </is>
       </c>
-      <c r="X104" s="2" t="inlineStr">
+      <c r="Y104" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2022/11/676_4.jpg</t>
         </is>
       </c>
-      <c r="Y104" s="2" t="inlineStr">
+      <c r="Z104" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary korekcyjne - G 94317 C2</t>
         </is>
       </c>
-      <c r="Z104" s="2" t="inlineStr">
+      <c r="AA104" s="2" t="inlineStr">
         <is>
           <t>goya-okulary-korekcyjne-g-94317-c2</t>
         </is>
       </c>
-      <c r="AA104" s="2" t="inlineStr">
+      <c r="AB104" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-okulary-korekcyjne-g-94317-c2</t>
         </is>
       </c>
-      <c r="AB104" s="3" t="inlineStr">
+      <c r="AC104" s="3" t="inlineStr">
         <is>
           <t>OKULARY KOREKCYJNE GOYA G 94317 C2 Produkt nowy - posiadają oryginalne zabezpieczenia, metkę oraz instrukcję użytkowania, dodatkowo w zestawie twarde etui na zawias sprężynowy Marki GOYA oraz miękką ściereczkę czyszczącą. NASZE PRODUKTY WYSYŁAMY BARDZO DOBRZE ZABEZPIECZONE W FOLIĘ TRANSPORTOWĄ I ZAPAKOWANE W WYTRZYMAŁY KARTONIK</t>
         </is>
@@ -17212,35 +17733,40 @@
       </c>
       <c r="V105" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/3167_1.jpg</t>
+        </is>
+      </c>
+      <c r="W105" s="2" t="inlineStr">
+        <is>
           <t>/products/3167_1.jpg</t>
         </is>
       </c>
-      <c r="W105" s="2" t="inlineStr">
+      <c r="X105" s="2" t="inlineStr">
         <is>
           <t>/products/3167_1.jpg; /products/3165_6.jpg</t>
         </is>
       </c>
-      <c r="X105" s="2" t="inlineStr">
+      <c r="Y105" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2022/11/3167_1.jpg</t>
         </is>
       </c>
-      <c r="Y105" s="2" t="inlineStr">
+      <c r="Z105" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary przeciwsłoneczne z filtrem polaryzacyjnym - G 170</t>
         </is>
       </c>
-      <c r="Z105" s="2" t="inlineStr">
+      <c r="AA105" s="2" t="inlineStr">
         <is>
           <t>goya-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym-g-170</t>
         </is>
       </c>
-      <c r="AA105" s="2" t="inlineStr">
+      <c r="AB105" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym-g-170</t>
         </is>
       </c>
-      <c r="AB105" s="3" t="inlineStr">
+      <c r="AC105" s="3" t="inlineStr">
         <is>
           <t>OKULARY PRZECIWSŁONECZNE DLA KIEROWCÓW GOYA Z FILTREM POLARYZACYJNYM I UV400 Oprawka wykonana w technologii - wycinania z płyty. Ręcznie obrabiana. Soczewki okularów GOYA o grubości 1,1 wyposażone są w filtr polaryzacyjny oraz filtr ochronny UV-400 (UV-A, UV-B, UV-C) OKULARY POSIADAJĄ CERTYFIKAT CE. Produkt odpowiada Wytycznej Europejskiej 89/686/EWG zgodnie z normą PN-EN ISO 12312-1:2014-02/A1:2016-01. Każda para okularów posiada oryginalne oznaczenia znajdujące się na wewnętrznej stronie zauszników ; logo producenta, numer modelu, kategoria filtra oraz oznaczenie CE. O POLARYZACJI: Soczewki polaryzacyjne neutralizują oślepiające refleksy, powstające wówczas gdy światło odbija się od mokrej drogi, powierzchni wody lub śniegu. Eliminacja światła odbitego zwiększ kontrast widzenia i pozwala na bardziej komfortowe widzenie. Dlatego okulary z filtrem polaryzacyjnym to idealne rozwiązanie do wszelkiego rodzaju aktywności na świeżym powietrzu, pozwalające pełniej korzystać z życia. ZALETY: Eliminują oślepiające odblaski, zmniejszaj</t>
         </is>
@@ -17330,35 +17856,40 @@
       </c>
       <c r="V106" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/971_3.jpg</t>
+        </is>
+      </c>
+      <c r="W106" s="2" t="inlineStr">
+        <is>
           <t>/products/971_3.jpg</t>
         </is>
       </c>
-      <c r="W106" s="2" t="inlineStr">
+      <c r="X106" s="2" t="inlineStr">
         <is>
           <t>/products/971_3.jpg</t>
         </is>
       </c>
-      <c r="X106" s="2" t="inlineStr">
+      <c r="Y106" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2022/11/971_3.jpg</t>
         </is>
       </c>
-      <c r="Y106" s="2" t="inlineStr">
+      <c r="Z106" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary przeciwsłoneczne z filtrem polaryzacyjnym - G100</t>
         </is>
       </c>
-      <c r="Z106" s="2" t="inlineStr">
+      <c r="AA106" s="2" t="inlineStr">
         <is>
           <t>goya-g100-c1-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym</t>
         </is>
       </c>
-      <c r="AA106" s="2" t="inlineStr">
+      <c r="AB106" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-g100-c1-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym</t>
         </is>
       </c>
-      <c r="AB106" s="3" t="inlineStr">
+      <c r="AC106" s="3" t="inlineStr">
         <is>
           <t>OKULARY PRZECIWSŁONECZNE DLA KIEROWCÓW GOYA Z FILTREM POLARYZACYJNYM I UV400 Soczewki okularów GOYA o grubości 1,1 wyposażone są w filtr polaryzacyjny oraz filtr ochronny UV-400 (UV-A, UV-B, UV-C) OPRAWKA WYKONANA W TECHNOLOGII TR-90 Wysokiej jakości odmiana nylonu, wyjątkowo odporna na rozciąganie i wyginanie. Materiał wytrzymały na uderzenia, elastyczny, przyjemny w dotyku, o właściwościach antyalergicznych. Okulary wykonane z TR-90 są lekkie, wytrzymałe i wygodne w użytkowaniu. ZAUSZNIKI POŁĄCZONE Z OPRAWKĄ SYSTEMEM FLEX: FLEX - elastyczne połączenie zausznika z frontem oprawy. Zwiększony zakres odchylenia zausznika do ponad 110° gwarantuje wygodę noszenia i ułatwia zakładanie oraz zdejmowanie okularów. OKULARY POSIADAJĄ CERTYFIKAT CE. Produkt odpowiada Wytycznej Europejskiej 89/686/EWG zgodnie z normą PN-EN ISO 12312-1:2014-02/A1:2016-01. Każda para okularów posiada oryginalne oznaczenia znajdujące się na wewnętrznej stronie zauszników ; logo producenta, numer modelu, kategoria filtra oraz oznaczenie CE. O POLARYZACJI: Soczewki pol</t>
         </is>
@@ -17446,35 +17977,40 @@
       </c>
       <c r="V107" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/575_6.jpg</t>
+        </is>
+      </c>
+      <c r="W107" s="2" t="inlineStr">
+        <is>
           <t>/products/575_6.jpg</t>
         </is>
       </c>
-      <c r="W107" s="2" t="inlineStr">
+      <c r="X107" s="2" t="inlineStr">
         <is>
           <t>/products/575_6.jpg; /products/575_5.jpg</t>
         </is>
       </c>
-      <c r="X107" s="2" t="inlineStr">
+      <c r="Y107" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2022/11/575_6.jpg</t>
         </is>
       </c>
-      <c r="Y107" s="2" t="inlineStr">
+      <c r="Z107" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary korekcyjne - G 2659 C4</t>
         </is>
       </c>
-      <c r="Z107" s="2" t="inlineStr">
+      <c r="AA107" s="2" t="inlineStr">
         <is>
           <t>goya-okulary-korekcyjne-g-2659-c4</t>
         </is>
       </c>
-      <c r="AA107" s="2" t="inlineStr">
+      <c r="AB107" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-okulary-korekcyjne-g-2659-c4</t>
         </is>
       </c>
-      <c r="AB107" s="3" t="inlineStr">
+      <c r="AC107" s="3" t="inlineStr">
         <is>
           <t>OKULARY KOREKCYJNE GOYA G 2659 C4 G 2659 C4 Produkt nowy - posiadają oryginalne zabezpieczenia, metkę oraz instrukcję użytkowania, dodatkowo w zestawie twarde etui na zawias sprężynowy Marki GOYA oraz miękką ściereczkę czyszczącą. NASZE PRODUKTY WYSYŁAMY BARDZO DOBRZE ZABEZPIECZONE W FOLIĘ TRANSPORTOWĄ I ZAPAKOWANE W WYTRZYMAŁY KARTONIK</t>
         </is>
@@ -17564,35 +18100,40 @@
       </c>
       <c r="V108" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/3142_6.jpg</t>
+        </is>
+      </c>
+      <c r="W108" s="2" t="inlineStr">
+        <is>
           <t>/products/3142_6.jpg</t>
         </is>
       </c>
-      <c r="W108" s="2" t="inlineStr">
+      <c r="X108" s="2" t="inlineStr">
         <is>
           <t>/products/3142_6.jpg; /products/3140_1.jpg</t>
         </is>
       </c>
-      <c r="X108" s="2" t="inlineStr">
+      <c r="Y108" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2022/11/3142_6.jpg</t>
         </is>
       </c>
-      <c r="Y108" s="2" t="inlineStr">
+      <c r="Z108" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary przeciwsłoneczne z filtrem polaryzacyjnym - G 185</t>
         </is>
       </c>
-      <c r="Z108" s="2" t="inlineStr">
+      <c r="AA108" s="2" t="inlineStr">
         <is>
           <t>goya-g-185-cz-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym</t>
         </is>
       </c>
-      <c r="AA108" s="2" t="inlineStr">
+      <c r="AB108" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-g-185-cz-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym</t>
         </is>
       </c>
-      <c r="AB108" s="3" t="inlineStr">
+      <c r="AC108" s="3" t="inlineStr">
         <is>
           <t>OKULARY PRZECIWSŁONECZNE DLA KIEROWCÓW GOYA Z FILTREM POLARYZACYJNYM I UV400 Soczewki okularów GOYA o grubości 1,1 wyposażone są w filtr polaryzacyjny oraz filtr ochronny UV-400 (UV-A, UV-B, UV-C) OPRAWKA WYKONANA W TECHNOLOGII TR-90 Wysokiej jakości odmiana nylonu, wyjątkowo odporna na rozciąganie i wyginanie. Materiał wytrzymały na uderzenia, elastyczny, przyjemny w dotyku, o właściwościach antyalergicznych. Okulary wykonane z TR-90 są lekkie, wytrzymałe i wygodne w użytkowaniu. ZAUSZNIKI POŁĄCZONE Z OPRAWKĄ SYSTEMEM FLEX: FLEX - elastyczne połączenie zausznika z frontem oprawy. Zwiększony zakres odchylenia zausznika do ponad 110° gwarantuje wygodę noszenia i ułatwia zakładanie oraz zdejmowanie okularów. OKULARY POSIADAJĄ CERTYFIKAT CE. Produkt odpowiada Wytycznej Europejskiej 89/686/EWG zgodnie z normą PN-EN ISO 12312-1:2014-02/A1:2016-01. Każda para okularów posiada oryginalne oznaczenia znajdujące się na wewnętrznej stronie zauszników ; logo producenta, numer modelu, kategoria filtra oraz oznaczenie CE. O POLARYZACJI: Soczewki pola</t>
         </is>
@@ -17680,35 +18221,40 @@
       </c>
       <c r="V109" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/589_4.jpg</t>
+        </is>
+      </c>
+      <c r="W109" s="2" t="inlineStr">
+        <is>
           <t>/products/589_4.jpg</t>
         </is>
       </c>
-      <c r="W109" s="2" t="inlineStr">
+      <c r="X109" s="2" t="inlineStr">
         <is>
           <t>/products/589_4.jpg; /products/589_3.jpg; /products/589_2.jpg; /products/589_1.jpg</t>
         </is>
       </c>
-      <c r="X109" s="2" t="inlineStr">
+      <c r="Y109" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2022/11/589_4.jpg</t>
         </is>
       </c>
-      <c r="Y109" s="2" t="inlineStr">
+      <c r="Z109" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary korekcyjne - G 2622 C2</t>
         </is>
       </c>
-      <c r="Z109" s="2" t="inlineStr">
+      <c r="AA109" s="2" t="inlineStr">
         <is>
           <t>goya-okulary-korekcyjne-g-2622-c2</t>
         </is>
       </c>
-      <c r="AA109" s="2" t="inlineStr">
+      <c r="AB109" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-okulary-korekcyjne-g-2622-c2</t>
         </is>
       </c>
-      <c r="AB109" s="3" t="inlineStr">
+      <c r="AC109" s="3" t="inlineStr">
         <is>
           <t>OKULARY KOREKCYJNE GOYA G 2622 C2 Produkt nowy - posiadają oryginalne zabezpieczenia, metkę oraz instrukcję użytkowania, dodatkowo w zestawie twarde etui na zawias sprężynowy Marki GOYA oraz miękką ściereczkę czyszczącą. NASZE PRODUKTY WYSYŁAMY BARDZO DOBRZE ZABEZPIECZONE W FOLIĘ TRANSPORTOWĄ I ZAPAKOWANE W WYTRZYMAŁY KARTONIK</t>
         </is>
@@ -17798,35 +18344,40 @@
       </c>
       <c r="V110" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/3194_1.jpg</t>
+        </is>
+      </c>
+      <c r="W110" s="2" t="inlineStr">
+        <is>
           <t>/products/3194_1.jpg</t>
         </is>
       </c>
-      <c r="W110" s="2" t="inlineStr">
+      <c r="X110" s="2" t="inlineStr">
         <is>
           <t>/products/3194_1.jpg; /products/3193_6.jpg</t>
         </is>
       </c>
-      <c r="X110" s="2" t="inlineStr">
+      <c r="Y110" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2023/01/3194_1.jpg</t>
         </is>
       </c>
-      <c r="Y110" s="2" t="inlineStr">
+      <c r="Z110" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary przeciwsłoneczne z filtrem polaryzacyjnym - G 146</t>
         </is>
       </c>
-      <c r="Z110" s="2" t="inlineStr">
+      <c r="AA110" s="2" t="inlineStr">
         <is>
           <t>goya-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym-g-146</t>
         </is>
       </c>
-      <c r="AA110" s="2" t="inlineStr">
+      <c r="AB110" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym-g-146</t>
         </is>
       </c>
-      <c r="AB110" s="3" t="inlineStr">
+      <c r="AC110" s="3" t="inlineStr">
         <is>
           <t>OKULARY PRZECIWSŁONECZNE DLA KIEROWCÓW GOYA Z FILTREM POLARYZACYJNYM I UV400 Oprawka wykonana w technologii - wycinania z płyty. Ręcznie obrabiana. Soczewki okularów GOYA o grubości 1,1 wyposażone są w filtr polaryzacyjny oraz filtr ochronny UV-400 (UV-A, UV-B, UV-C) OKULARY POSIADAJĄ CERTYFIKAT CE. Produkt odpowiada Wytycznej Europejskiej 89/686/EWG zgodnie z normą PN-EN ISO 12312-1:2014-02/A1:2016-01. Każda para okularów posiada oryginalne oznaczenia znajdujące się na wewnętrznej stronie zauszników ; logo producenta, numer modelu, kategoria filtra oraz oznaczenie CE. O POLARYZACJI: Soczewki polaryzacyjne neutralizują oślepiające refleksy, powstające wówczas gdy światło odbija się od mokrej drogi, powierzchni wody lub śniegu. Eliminacja światła odbitego zwiększ kontrast widzenia i pozwala na bardziej komfortowe widzenie. Dlatego okulary z filtrem polaryzacyjnym to idealne rozwiązanie do wszelkiego rodzaju aktywności na świeżym powietrzu, pozwalające pełniej korzystać z życia. ZALETY: Eliminują oślepiające odblaski, zmniejszaj</t>
         </is>
@@ -17912,35 +18463,40 @@
       </c>
       <c r="V111" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/672_4.jpg</t>
+        </is>
+      </c>
+      <c r="W111" s="2" t="inlineStr">
+        <is>
           <t>/products/672_4.jpg</t>
         </is>
       </c>
-      <c r="W111" s="2" t="inlineStr">
+      <c r="X111" s="2" t="inlineStr">
         <is>
           <t>/products/672_4.jpg</t>
         </is>
       </c>
-      <c r="X111" s="2" t="inlineStr">
+      <c r="Y111" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2022/11/672_4.jpg</t>
         </is>
       </c>
-      <c r="Y111" s="2" t="inlineStr">
+      <c r="Z111" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary korekcyjne - G 94411</t>
         </is>
       </c>
-      <c r="Z111" s="2" t="inlineStr">
+      <c r="AA111" s="2" t="inlineStr">
         <is>
           <t>goya-okulary-korekcyjne-g-94411-c2</t>
         </is>
       </c>
-      <c r="AA111" s="2" t="inlineStr">
+      <c r="AB111" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-okulary-korekcyjne-g-94411-c2</t>
         </is>
       </c>
-      <c r="AB111" s="3" t="inlineStr">
+      <c r="AC111" s="3" t="inlineStr">
         <is>
           <t>OKULARY KOREKCYJNE GOYA G 94411 Produkt nowy - posiadają oryginalne zabezpieczenia, metkę oraz instrukcję użytkowania, dodatkowo w zestawie twarde etui na zawias sprężynowy Marki GOYA oraz miękką ściereczkę czyszczącą. NASZE PRODUKTY WYSYŁAMY BARDZO DOBRZE ZABEZPIECZONE W FOLIĘ TRANSPORTOWĄ I ZAPAKOWANE W WYTRZYMAŁY KARTONIK</t>
         </is>
@@ -18030,35 +18586,40 @@
       </c>
       <c r="V112" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/2457_1.jpg</t>
+        </is>
+      </c>
+      <c r="W112" s="2" t="inlineStr">
+        <is>
           <t>/products/2457_1.jpg</t>
         </is>
       </c>
-      <c r="W112" s="2" t="inlineStr">
+      <c r="X112" s="2" t="inlineStr">
         <is>
           <t>/products/2457_1.jpg</t>
         </is>
       </c>
-      <c r="X112" s="2" t="inlineStr">
+      <c r="Y112" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2022/11/2457_1.jpg</t>
         </is>
       </c>
-      <c r="Y112" s="2" t="inlineStr">
+      <c r="Z112" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary przeciwsłoneczne z filtrem polaryzacyjnym - G 55017</t>
         </is>
       </c>
-      <c r="Z112" s="2" t="inlineStr">
+      <c r="AA112" s="2" t="inlineStr">
         <is>
           <t>goya-g-55017-br-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym</t>
         </is>
       </c>
-      <c r="AA112" s="2" t="inlineStr">
+      <c r="AB112" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-g-55017-br-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym</t>
         </is>
       </c>
-      <c r="AB112" s="3" t="inlineStr">
+      <c r="AC112" s="3" t="inlineStr">
         <is>
           <t>OKULARY PRZECIWSŁONECZNE DLA KIEROWCÓW GOYA Z FILTREM POLARYZACYJNYM I UV400 Zauszniki oprawek wykonane z aluminium - co sprawia, że okulary są bardzo lekkie i wytrzymałe. Soczewki okularów GOYA o grubości 1,1 wyposażone są w filtr polaryzacyjny oraz filtr ochronny UV-400 (UV-A, UV-B, UV-C) ZAUSZNIKI POŁĄCZONE Z OPRAWKĄ SYSTEMEM FLEX: FLEX - elastyczne połączenie zausznika z frontem oprawy. Zwiększony zakres odchylenia zausznika do ponad 110° gwarantuje wygodę noszenia i ułatwia zakładanie oraz zdejmowanie okularów. OKULARY POSIADAJĄ CERTYFIKAT CE. Produkt odpowiada Wytycznej Europejskiej 89/686/EWG zgodnie z normą PN-EN ISO 12312-1:2014-02/A1:2016-01. Każda para okularów posiada oryginalne oznaczenia znajdujące się na wewnętrznej stronie zauszników ; logo producenta, numer modelu, kategoria filtra oraz oznaczenie CE. O POLARYZACJI: Soczewki polaryzacyjne neutralizują oślepiające refleksy, powstające wówczas gdy światło odbija się od mokrej drogi, powierzchni wody lub śniegu. Eliminacja światła odbitego zwiększ kontrast widzenia i pozwala na</t>
         </is>
@@ -18148,35 +18709,40 @@
       </c>
       <c r="V113" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/3175_1.jpg</t>
+        </is>
+      </c>
+      <c r="W113" s="2" t="inlineStr">
+        <is>
           <t>/products/3175_1.jpg</t>
         </is>
       </c>
-      <c r="W113" s="2" t="inlineStr">
+      <c r="X113" s="2" t="inlineStr">
         <is>
           <t>/products/3175_1.jpg; /products/3176_6.jpg</t>
         </is>
       </c>
-      <c r="X113" s="2" t="inlineStr">
+      <c r="Y113" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2022/11/3175_1.jpg</t>
         </is>
       </c>
-      <c r="Y113" s="2" t="inlineStr">
+      <c r="Z113" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary przeciwsłoneczne z filtrem polaryzacyjnym - G 161</t>
         </is>
       </c>
-      <c r="Z113" s="2" t="inlineStr">
+      <c r="AA113" s="2" t="inlineStr">
         <is>
           <t>goya-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym-g-161</t>
         </is>
       </c>
-      <c r="AA113" s="2" t="inlineStr">
+      <c r="AB113" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym-g-161</t>
         </is>
       </c>
-      <c r="AB113" s="3" t="inlineStr">
+      <c r="AC113" s="3" t="inlineStr">
         <is>
           <t>OKULARY PRZECIWSŁONECZNE DLA KIEROWCÓW GOYA Z FILTREM POLARYZACYJNYM I UV400 Oprawka wykonana w technologii - wycinania z płyty. Ręcznie obrabiana. Soczewki okularów GOYA o grubości 1,1 wyposażone są w filtr polaryzacyjny oraz filtr ochronny UV-400 (UV-A, UV-B, UV-C) OKULARY POSIADAJĄ CERTYFIKAT CE. Produkt odpowiada Wytycznej Europejskiej 89/686/EWG zgodnie z normą PN-EN ISO 12312-1:2014-02/A1:2016-01. Każda para okularów posiada oryginalne oznaczenia znajdujące się na wewnętrznej stronie zauszników ; logo producenta, numer modelu, kategoria filtra oraz oznaczenie CE. O POLARYZACJI: Soczewki polaryzacyjne neutralizują oślepiające refleksy, powstające wówczas gdy światło odbija się od mokrej drogi, powierzchni wody lub śniegu. Eliminacja światła odbitego zwiększ kontrast widzenia i pozwala na bardziej komfortowe widzenie. Dlatego okulary z filtrem polaryzacyjnym to idealne rozwiązanie do wszelkiego rodzaju aktywności na świeżym powietrzu, pozwalające pełniej korzystać z życia. ZALETY: Eliminują oślepiające odblaski, zmniejszaj</t>
         </is>
@@ -18262,35 +18828,40 @@
       </c>
       <c r="V114" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/628_4.jpg</t>
+        </is>
+      </c>
+      <c r="W114" s="2" t="inlineStr">
+        <is>
           <t>/products/628_4.jpg</t>
         </is>
       </c>
-      <c r="W114" s="2" t="inlineStr">
+      <c r="X114" s="2" t="inlineStr">
         <is>
           <t>/products/628_4.jpg</t>
         </is>
       </c>
-      <c r="X114" s="2" t="inlineStr">
+      <c r="Y114" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2022/11/628_4.jpg</t>
         </is>
       </c>
-      <c r="Y114" s="2" t="inlineStr">
+      <c r="Z114" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary korekcyjne - GH 5001</t>
         </is>
       </c>
-      <c r="Z114" s="2" t="inlineStr">
+      <c r="AA114" s="2" t="inlineStr">
         <is>
           <t>goya-okulary-korekcyjne-gh-5001-c1</t>
         </is>
       </c>
-      <c r="AA114" s="2" t="inlineStr">
+      <c r="AB114" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-okulary-korekcyjne-gh-5001-c1</t>
         </is>
       </c>
-      <c r="AB114" s="3" t="inlineStr">
+      <c r="AC114" s="3" t="inlineStr">
         <is>
           <t>OKULARY KOREKCYJNE GOYA GH 5001 Produkt nowy - posiadają oryginalne zabezpieczenia, metkę oraz instrukcję użytkowania, dodatkowo w zestawie twarde etui na zawias sprężynowy Marki GOYA oraz miękką ściereczkę czyszczącą. NASZE PRODUKTY WYSYŁAMY BARDZO DOBRZE ZABEZPIECZONE W FOLIĘ TRANSPORTOWĄ I ZAPAKOWANE W WYTRZYMAŁY KARTONIK</t>
         </is>
@@ -18378,35 +18949,40 @@
       </c>
       <c r="V115" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/575_6.jpg</t>
+        </is>
+      </c>
+      <c r="W115" s="2" t="inlineStr">
+        <is>
           <t>/products/575_6.jpg</t>
         </is>
       </c>
-      <c r="W115" s="2" t="inlineStr">
+      <c r="X115" s="2" t="inlineStr">
         <is>
           <t>/products/575_6.jpg; /products/575_5.jpg</t>
         </is>
       </c>
-      <c r="X115" s="2" t="inlineStr">
+      <c r="Y115" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2022/11/575_6.jpg</t>
         </is>
       </c>
-      <c r="Y115" s="2" t="inlineStr">
+      <c r="Z115" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary korekcyjne G 2657 C2</t>
         </is>
       </c>
-      <c r="Z115" s="2" t="inlineStr">
+      <c r="AA115" s="2" t="inlineStr">
         <is>
           <t>goya-okulary-korekcyjne-g-2657-c2</t>
         </is>
       </c>
-      <c r="AA115" s="2" t="inlineStr">
+      <c r="AB115" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-okulary-korekcyjne-g-2657-c2</t>
         </is>
       </c>
-      <c r="AB115" s="3" t="inlineStr">
+      <c r="AC115" s="3" t="inlineStr">
         <is>
           <t>OKULARY KOREKCYJNE GOYA G 2657 C2 Produkt nowy ! - posiadają oryginalne zabezpieczenia, metkę oraz instrukcję użytkowania, dodatkowo w zestawie twarde etui na zawias sprężynowy Marki GOYA oraz miękką ściereczkę czyszczącą. NASZE PRODUKTY SĄ BARDZO DOBRZE ZABEZPIECZONE W FOLIĘ TRANSPORTOWĄ I ZAPAKOWANE W WYTRZYMAŁY KARTONIK</t>
         </is>
@@ -18494,35 +19070,40 @@
       </c>
       <c r="V116" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/575_6.jpg</t>
+        </is>
+      </c>
+      <c r="W116" s="2" t="inlineStr">
+        <is>
           <t>/products/575_6.jpg</t>
         </is>
       </c>
-      <c r="W116" s="2" t="inlineStr">
+      <c r="X116" s="2" t="inlineStr">
         <is>
           <t>/products/575_6.jpg; /products/575_5.jpg</t>
         </is>
       </c>
-      <c r="X116" s="2" t="inlineStr">
+      <c r="Y116" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2022/11/575_6.jpg</t>
         </is>
       </c>
-      <c r="Y116" s="2" t="inlineStr">
+      <c r="Z116" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary korekcyjne - RD 150 C4</t>
         </is>
       </c>
-      <c r="Z116" s="2" t="inlineStr">
+      <c r="AA116" s="2" t="inlineStr">
         <is>
           <t>goya-okulary-korekcyjne-rd-150-c4</t>
         </is>
       </c>
-      <c r="AA116" s="2" t="inlineStr">
+      <c r="AB116" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-okulary-korekcyjne-rd-150-c4</t>
         </is>
       </c>
-      <c r="AB116" s="3" t="inlineStr">
+      <c r="AC116" s="3" t="inlineStr">
         <is>
           <t>OKULARY KOREKCYJNE GOYA RD 150 C4 Produkt nowy ! - posiadają oryginalne zabezpieczenia, metkę oraz instrukcję użytkowania, dodatkowo w zestawie twarde etui na zawias sprężynowy Marki GOYA oraz miękką ściereczkę czyszczącą. NASZE PRODUKTY SĄ BARDZO DOBRZE ZABEZPIECZONE W FOLIĘ TRANSPORTOWĄ I ZAPAKOWANE W WYTRZYMAŁY KARTONIK</t>
         </is>
@@ -18612,35 +19193,40 @@
       </c>
       <c r="V117" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/prof-368.jpeg</t>
+        </is>
+      </c>
+      <c r="W117" s="2" t="inlineStr">
+        <is>
           <t>/products/prof-368.jpeg</t>
         </is>
       </c>
-      <c r="W117" s="2" t="inlineStr">
+      <c r="X117" s="2" t="inlineStr">
         <is>
           <t>/products/prof-368.jpeg; /products/1650_6.jpeg</t>
         </is>
       </c>
-      <c r="X117" s="2" t="inlineStr">
+      <c r="Y117" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2022/03/prof-368.jpeg</t>
         </is>
       </c>
-      <c r="Y117" s="2" t="inlineStr">
+      <c r="Z117" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary przeciwsłoneczne z filtrem polaryzacyjnym - G 8004</t>
         </is>
       </c>
-      <c r="Z117" s="2" t="inlineStr">
+      <c r="AA117" s="2" t="inlineStr">
         <is>
           <t>brazowe-okulary-przeciwsloneczne-polaryzacyjne-goya-g-8004-br</t>
         </is>
       </c>
-      <c r="AA117" s="2" t="inlineStr">
+      <c r="AB117" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/brazowe-okulary-przeciwsloneczne-polaryzacyjne-goya-g-8004-br</t>
         </is>
       </c>
-      <c r="AB117" s="3" t="inlineStr">
+      <c r="AC117" s="3" t="inlineStr">
         <is>
           <t>OKULARY PRZECIWSŁONECZNE DLA KIEROWCÓW GOYA Z FILTREM POLARYZACYJNYM I UV400 Oprawka wykonana ze stopu metalu Soczewki okularów GOYA o grubości 1,1 wyposażone są w filtr polaryzacyjny oraz filtr ochronny UV-400 (UV-A, UV-B, UV-C) OKULARY POSIADAJĄ CERTYFIKAT CE. Produkt odpowiada Wytycznej Europejskiej 89/686/EWG zgodnie z normą PN-EN ISO 12312-1:2014-02/A1:2016-01. Każda para okularów posiada oryginalne oznaczenia znajdujące się na wewnętrznej stronie zauszników ; logo producenta, numer modelu, kategoria filtra oraz oznaczenie CE. O POLARYZACJI: Soczewki polaryzacyjne neutralizują oślepiające refleksy, powstające wówczas gdy światło odbija się od mokrej drogi, powierzchni wody lub śniegu. Eliminacja światła odbitego zwiększ kontrast widzenia i pozwala na bardziej komfortowe widzenie. Dlatego okulary z filtrem polaryzacyjnym to idealne rozwiązanie do wszelkiego rodzaju aktywności na świeżym powietrzu, pozwalające pełniej korzystać z życia. ZALETY: Eliminują oślepiające odblaski, zmniejszając zmęczenie oczu Chronią przed szkod</t>
         </is>
@@ -18728,35 +19314,40 @@
       </c>
       <c r="V118" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/575_6.jpg</t>
+        </is>
+      </c>
+      <c r="W118" s="2" t="inlineStr">
+        <is>
           <t>/products/575_6.jpg</t>
         </is>
       </c>
-      <c r="W118" s="2" t="inlineStr">
+      <c r="X118" s="2" t="inlineStr">
         <is>
           <t>/products/575_6.jpg; /products/575_5.jpg</t>
         </is>
       </c>
-      <c r="X118" s="2" t="inlineStr">
+      <c r="Y118" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2022/11/575_6.jpg</t>
         </is>
       </c>
-      <c r="Y118" s="2" t="inlineStr">
+      <c r="Z118" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary korekcyjne - GL 6503 C3</t>
         </is>
       </c>
-      <c r="Z118" s="2" t="inlineStr">
+      <c r="AA118" s="2" t="inlineStr">
         <is>
           <t>goya-okulary-korekcyjne-gl-6503-c3</t>
         </is>
       </c>
-      <c r="AA118" s="2" t="inlineStr">
+      <c r="AB118" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-okulary-korekcyjne-gl-6503-c3</t>
         </is>
       </c>
-      <c r="AB118" s="3" t="inlineStr">
+      <c r="AC118" s="3" t="inlineStr">
         <is>
           <t>OKULARY KOREKCYJNE GOYA GL 6503 C3 Produkt nowy ! - posiadają oryginalne zabezpieczenia, metkę oraz instrukcję użytkowania, dodatkowo w zestawie twarde etui na zawias sprężynowy Marki GOYA oraz miękką ściereczkę czyszczącą. NASZE PRODUKTY SĄ BARDZO DOBRZE ZABEZPIECZONE W FOLIĘ TRANSPORTOWĄ I ZAPAKOWANE W WYTRZYMAŁY KARTONIK</t>
         </is>
@@ -18846,35 +19437,40 @@
       </c>
       <c r="V119" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/3132_1.jpg</t>
+        </is>
+      </c>
+      <c r="W119" s="2" t="inlineStr">
+        <is>
           <t>/products/3132_1.jpg</t>
         </is>
       </c>
-      <c r="W119" s="2" t="inlineStr">
+      <c r="X119" s="2" t="inlineStr">
         <is>
           <t>/products/3132_1.jpg; /products/3132_6.jpg</t>
         </is>
       </c>
-      <c r="X119" s="2" t="inlineStr">
+      <c r="Y119" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2022/11/3132_1.jpg</t>
         </is>
       </c>
-      <c r="Y119" s="2" t="inlineStr">
+      <c r="Z119" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary przeciwsłoneczne z filtrem polaryzacyjnym - G 189</t>
         </is>
       </c>
-      <c r="Z119" s="2" t="inlineStr">
+      <c r="AA119" s="2" t="inlineStr">
         <is>
           <t>goya-g-189-czm-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym</t>
         </is>
       </c>
-      <c r="AA119" s="2" t="inlineStr">
+      <c r="AB119" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-g-189-czm-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym</t>
         </is>
       </c>
-      <c r="AB119" s="3" t="inlineStr">
+      <c r="AC119" s="3" t="inlineStr">
         <is>
           <t>OKULARY PRZECIWSŁONECZNE DLA KIEROWCÓW GOYA Z FILTREM POLARYZACYJNYM I UV400 Soczewki okularów GOYA o grubości 1,1 wyposażone są w filtr polaryzacyjny oraz filtr ochronny UV-400 (UV-A, UV-B, UV-C). Antyrefleks OPRAWKA WYKONANA W TECHNOLOGII TR-90 Wysokiej jakości odmiana nylonu, wyjątkowo odporna na rozciąganie i wyginanie. Materiał wytrzymały na uderzenia, elastyczny, przyjemny w dotyku, o właściwościach antyalergicznych. Okulary wykonane z TR-90 są lekkie, wytrzymałe i wygodne w użytkowaniu. OKULARY POSIADAJĄ CERTYFIKAT CE. Produkt odpowiada Wytycznej Europejskiej 89/686/EWG zgodnie z normą PN-EN ISO 12312-1:2014-02/A1:2016-01. Każda para okularów posiada oryginalne oznaczenia znajdujące się na wewnętrznej stronie zauszników ; logo producenta, numer modelu, kategoria filtra oraz oznaczenie CE. O POLARYZACJI: Soczewki polaryzacyjne neutralizują oślepiające refleksy, powstające wówczas gdy światło odbija się od mokrej drogi, powierzchni wody lub śniegu. Eliminacja światła odbitego zwiększ kontrast widzenia i pozwala na bardziej komfortowe widzen</t>
         </is>
@@ -18966,35 +19562,40 @@
       </c>
       <c r="V120" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/3157_6.jpg</t>
+        </is>
+      </c>
+      <c r="W120" s="2" t="inlineStr">
+        <is>
           <t>/products/3157_6.jpg</t>
         </is>
       </c>
-      <c r="W120" s="2" t="inlineStr">
+      <c r="X120" s="2" t="inlineStr">
         <is>
           <t>/products/3157_6.jpg; /products/3157_1.jpg; /products/3157_5.jpg; /products/3157_4.jpg; /products/3157_3.jpg; /products/3157_2.jpg</t>
         </is>
       </c>
-      <c r="X120" s="2" t="inlineStr">
+      <c r="Y120" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2022/11/3157_6.jpg</t>
         </is>
       </c>
-      <c r="Y120" s="2" t="inlineStr">
+      <c r="Z120" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary przeciwsłoneczne z filtrem polaryzacyjnym - G 175 CZ</t>
         </is>
       </c>
-      <c r="Z120" s="2" t="inlineStr">
+      <c r="AA120" s="2" t="inlineStr">
         <is>
           <t>goya-g-175-cz-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym</t>
         </is>
       </c>
-      <c r="AA120" s="2" t="inlineStr">
+      <c r="AB120" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-g-175-cz-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym</t>
         </is>
       </c>
-      <c r="AB120" s="3" t="inlineStr">
+      <c r="AC120" s="3" t="inlineStr">
         <is>
           <t>OKULARY PRZECIWSŁONECZNE DLA KIEROWCÓW GOYA Z FILTREM POLARYZACYJNYM I UV400 Soczewki okularów GOYA o grubości 1,1 wyposażone są w filtr polaryzacyjny oraz filtr ochronny UV-400 (UV-A, UV-B, UV-C) OPRAWKA WYKONANA W TECHNOLOGII TR-90 Wysokiej jakości odmiana nylonu, wyjątkowo odporna na rozciąganie i wyginanie. Materiał wytrzymały na uderzenia, elastyczny, przyjemny w dotyku, o właściwościach antyalergicznych. Okulary wykonane z TR-90 są lekkie, wytrzymałe i wygodne w użytkowaniu. OKULARY POSIADAJĄ CERTYFIKAT CE. Produkt odpowiada Wytycznej Europejskiej 89/686/EWG zgodnie z normą PN-EN ISO 12312-1:2014-02/A1:2016-01. Każda para okularów posiada oryginalne oznaczenia znajdujące się na wewnętrznej stronie zauszników ; logo producenta, numer modelu, kategoria filtra oraz oznaczenie CE. O POLARYZACJI: Soczewki polaryzacyjne neutralizują oślepiające refleksy, powstające wówczas gdy światło odbija się od mokrej drogi, powierzchni wody lub śniegu. Eliminacja światła odbitego zwiększ kontrast widzenia i pozwala na bardziej komfortowe widzenie. Dlatego o</t>
         </is>
@@ -19082,35 +19683,40 @@
       </c>
       <c r="V121" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/608_3.jpg</t>
+        </is>
+      </c>
+      <c r="W121" s="2" t="inlineStr">
+        <is>
           <t>/products/608_3.jpg</t>
         </is>
       </c>
-      <c r="W121" s="2" t="inlineStr">
+      <c r="X121" s="2" t="inlineStr">
         <is>
           <t>/products/608_3.jpg; /products/608_1.jpg; /products/608_4.jpg; /products/608_2.jpg</t>
         </is>
       </c>
-      <c r="X121" s="2" t="inlineStr">
+      <c r="Y121" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2022/11/608_3.jpg</t>
         </is>
       </c>
-      <c r="Y121" s="2" t="inlineStr">
+      <c r="Z121" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary korekcyjne - G 2714 C1</t>
         </is>
       </c>
-      <c r="Z121" s="2" t="inlineStr">
+      <c r="AA121" s="2" t="inlineStr">
         <is>
           <t>goya-okulary-korekcyjne-g-2714-c1</t>
         </is>
       </c>
-      <c r="AA121" s="2" t="inlineStr">
+      <c r="AB121" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-okulary-korekcyjne-g-2714-c1</t>
         </is>
       </c>
-      <c r="AB121" s="3" t="inlineStr">
+      <c r="AC121" s="3" t="inlineStr">
         <is>
           <t>OKULARY KOREKCYJNE GOYA G 2714 C1 Produkt nowy - posiadają oryginalne zabezpieczenia, metkę oraz instrukcję użytkowania, dodatkowo w zestawie twarde etui na zawias sprężynowy Marki GOYA oraz miękką ściereczkę czyszczącą. NASZE PRODUKTY WYSYŁAMY BARDZO DOBRZE ZABEZPIECZONE W FOLIĘ TRANSPORTOWĄ I ZAPAKOWANE W WYTRZYMAŁY KARTONIK</t>
         </is>
@@ -19200,35 +19806,40 @@
       </c>
       <c r="V122" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/prof-479.jpeg</t>
+        </is>
+      </c>
+      <c r="W122" s="2" t="inlineStr">
+        <is>
           <t>/products/prof-479.jpeg</t>
         </is>
       </c>
-      <c r="W122" s="2" t="inlineStr">
+      <c r="X122" s="2" t="inlineStr">
         <is>
           <t>/products/prof-479.jpeg; /products/GOYA-55T002-BR-1.jpg</t>
         </is>
       </c>
-      <c r="X122" s="2" t="inlineStr">
+      <c r="Y122" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2022/03/prof-479.jpeg</t>
         </is>
       </c>
-      <c r="Y122" s="2" t="inlineStr">
+      <c r="Z122" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary przeciwsłoneczne z filtrem polaryzacyjnym - G 55T002</t>
         </is>
       </c>
-      <c r="Z122" s="2" t="inlineStr">
+      <c r="AA122" s="2" t="inlineStr">
         <is>
           <t>okulary-przeciwsloneczne-polaryzacyjne-dla-kierowcow-goya-g-55t002-br</t>
         </is>
       </c>
-      <c r="AA122" s="2" t="inlineStr">
+      <c r="AB122" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/okulary-przeciwsloneczne-polaryzacyjne-dla-kierowcow-goya-g-55t002-br</t>
         </is>
       </c>
-      <c r="AB122" s="3" t="inlineStr">
+      <c r="AC122" s="3" t="inlineStr">
         <is>
           <t>OKULARY PRZECIWSŁONECZNE DLA KIEROWCÓW GOYA Z FILTREM POLARYZACYJNYM I UV400 Zauszniki oprawek wykonane z aluminium - co sprawia, że okulary są bardzo lekkie i wytrzymałe. Soczewki okularów GOYA o grubości 1,1 wyposażone są w filtr polaryzacyjny oraz filtr ochronny UV-400 (UV-A, UV-B, UV-C) OPRAWKA WYKONANA W TECHNOLOGII TR-90 Wysokiej jakości odmiana nylonu, wyjątkowo odporna na rozciąganie i wyginanie. Materiał wytrzymały na uderzenia, elastyczny, przyjemny w dotyku, o właściwościach antyalergicznych. Okulary wykonane z TR-90 są lekkie, wytrzymałe i wygodne w użytkowaniu. ZAUSZNIKI POŁĄCZONE Z OPRAWKĄ SYSTEMEM FLEX: FLEX - elastyczne połączenie zausznika z frontem oprawy. Zwiększony zakres odchylenia zausznika do ponad 110° gwarantuje wygodę noszenia i ułatwia zakładanie oraz zdejmowanie okularów. OKULARY POSIADAJĄ CERTYFIKAT CE. Produkt odpowiada Wytycznej Europejskiej 89/686/EWG zgodnie z normą PN-EN ISO 12312-1:2014-02/A1:2016-01. Każda para okularów posiada oryginalne oznaczenia znajdujące się na wewnętrznej stronie zauszników ; logo p</t>
         </is>
@@ -19320,35 +19931,40 @@
       </c>
       <c r="V123" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/G_55029_GR_A.jpg</t>
+        </is>
+      </c>
+      <c r="W123" s="2" t="inlineStr">
+        <is>
           <t>/products/G_55029_GR_A.jpg</t>
         </is>
       </c>
-      <c r="W123" s="2" t="inlineStr">
+      <c r="X123" s="2" t="inlineStr">
         <is>
           <t>/products/G_55029_GR_A.jpg; /products/G_55029_GR_MODkw.jpg; /products/G_55029_GR_G.jpg; /products/G_55029_GR_MOD1.jpg; /products/G_55029_GR_B.jpg; /products/G_55029_GR_MOD.jpg; /products/G_55029_GR_F.jpg; /products/G_55029_GR_S.jpg; /products/G_55029_GR_F1.jpg; /products/G_55029_GR_T.jpg</t>
         </is>
       </c>
-      <c r="X123" s="2" t="inlineStr">
+      <c r="Y123" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2025/02/G_55029_GR_A.jpg</t>
         </is>
       </c>
-      <c r="Y123" s="2" t="inlineStr">
+      <c r="Z123" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary przeciwsłoneczne z filtrem polaryzacyjnym - G 55029 GR</t>
         </is>
       </c>
-      <c r="Z123" s="2" t="inlineStr">
+      <c r="AA123" s="2" t="inlineStr">
         <is>
           <t>goya-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym-g-55029-gr</t>
         </is>
       </c>
-      <c r="AA123" s="2" t="inlineStr">
+      <c r="AB123" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym-g-55029-gr</t>
         </is>
       </c>
-      <c r="AB123" s="3" t="inlineStr">
+      <c r="AC123" s="3" t="inlineStr">
         <is>
           <t>OKULARY PRZECIWSŁONECZNE DLA KIEROWCÓW GOYA Z FILTREM POLARYZACYJNYM I UV400 Oprawki wykonane w całości z aluminium - co sprawia, że okulary są bardzo lekkie i wytrzymałe. Soczewki okularów GOYA o grubości 1,1 wyposażone są w filtr polaryzacyjny oraz filtr ochronny UV-400 (UV-A, UV-B, UV-C) ZAUSZNIKI POŁĄCZONE Z OPRAWKĄ SYSTEMEM FLEX: FLEX - elastyczne połączenie zausznika z frontem oprawy. Zwiększony zakres odchylenia zausznika do ponad 110° gwarantuje wygodę noszenia i ułatwia zakładanie oraz zdejmowanie okularów. OKULARY POSIADAJĄ CERTYFIKAT CE. Produkt odpowiada Wytycznej Europejskiej 89/686/EWG zgodnie z normą PN-EN ISO 12312-1:2014-02/A1:2016-01. Każda para okularów posiada oryginalne oznaczenia znajdujące się na wewnętrznej stronie zauszników ; logo producenta, numer modelu, kategoria filtra oraz oznaczenie CE. O POLARYZACJI: Soczewki polaryzacyjne neutralizują oślepiające refleksy, powstające wówczas gdy światło odbija się od mokrej drogi, powierzchni wody lub śniegu. Eliminacja światła odbitego zwiększ kontrast widzenia i pozwala</t>
         </is>
@@ -19440,35 +20056,40 @@
       </c>
       <c r="V124" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/3143_6.jpg</t>
+        </is>
+      </c>
+      <c r="W124" s="2" t="inlineStr">
+        <is>
           <t>/products/3143_6.jpg</t>
         </is>
       </c>
-      <c r="W124" s="2" t="inlineStr">
+      <c r="X124" s="2" t="inlineStr">
         <is>
           <t>/products/3143_6.jpg; /products/3143_1.jpg; /products/3143_4.jpg; /products/3143_5.jpg; /products/3143_3.jpg; /products/3143_2.jpg</t>
         </is>
       </c>
-      <c r="X124" s="2" t="inlineStr">
+      <c r="Y124" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2022/11/3143_6.jpg</t>
         </is>
       </c>
-      <c r="Y124" s="2" t="inlineStr">
+      <c r="Z124" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary przeciwsłoneczne z filtrem polaryzacyjnym - G 184 C</t>
         </is>
       </c>
-      <c r="Z124" s="2" t="inlineStr">
+      <c r="AA124" s="2" t="inlineStr">
         <is>
           <t>goya-g-184-c-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym</t>
         </is>
       </c>
-      <c r="AA124" s="2" t="inlineStr">
+      <c r="AB124" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-g-184-c-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym</t>
         </is>
       </c>
-      <c r="AB124" s="3" t="inlineStr">
+      <c r="AC124" s="3" t="inlineStr">
         <is>
           <t>OKULARY PRZECIWSŁONECZNE DLA KIEROWCÓW GOYA Z FILTREM POLARYZACYJNYM I UV400 Soczewki okularów GOYA o grubości 1,1 wyposażone są w filtr polaryzacyjny oraz filtr ochronny UV-400 (UV-A, UV-B, UV-C) OPRAWKA WYKONANA W TECHNOLOGII TR-90 Wysokiej jakości odmiana nylonu, wyjątkowo odporna na rozciąganie i wyginanie. Materiał wytrzymały na uderzenia, elastyczny, przyjemny w dotyku, o właściwościach antyalergicznych. Okulary wykonane z TR-90 są lekkie, wytrzymałe i wygodne w użytkowaniu. ZAUSZNIKI POŁĄCZONE Z OPRAWKĄ SYSTEMEM FLEX: FLEX - elastyczne połączenie zausznika z frontem oprawy. Zwiększony zakres odchylenia zausznika do ponad 110° gwarantuje wygodę noszenia i ułatwia zakładanie oraz zdejmowanie okularów. OKULARY POSIADAJĄ CERTYFIKAT CE. Produkt odpowiada Wytycznej Europejskiej 89/686/EWG zgodnie z normą PN-EN ISO 12312-1:2014-02/A1:2016-01. Każda para okularów posiada oryginalne oznaczenia znajdujące się na wewnętrznej stronie zauszników ; logo producenta, numer modelu, kategoria filtra oraz oznaczenie CE. O POLARYZACJI: Soczewki pola</t>
         </is>
@@ -19560,35 +20181,40 @@
       </c>
       <c r="V125" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/G_55001_CZ_A.jpg</t>
+        </is>
+      </c>
+      <c r="W125" s="2" t="inlineStr">
+        <is>
           <t>/products/G_55001_CZ_A.jpg</t>
         </is>
       </c>
-      <c r="W125" s="2" t="inlineStr">
+      <c r="X125" s="2" t="inlineStr">
         <is>
           <t>/products/G_55001_CZ_A.jpg; /products/G_55001_CZ_MODkw.jpg; /products/G_55001_CZ_G.jpg; /products/G_55001_CZ_MOD1.jpg; /products/G_55001_CZ_F.jpg; /products/G_55001_CZ_MOD.jpg; /products/G_55001_CZ_B.jpg; /products/G_55001_CZ_S.jpg; /products/G_55001_CZ_T.jpg; /products/G_55001_CZ_F1.jpg</t>
         </is>
       </c>
-      <c r="X125" s="2" t="inlineStr">
+      <c r="Y125" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2025/01/G_55001_CZ_A.jpg</t>
         </is>
       </c>
-      <c r="Y125" s="2" t="inlineStr">
+      <c r="Z125" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary przeciwsłoneczne z filtrem polaryzacyjnym - G 55001 CZ</t>
         </is>
       </c>
-      <c r="Z125" s="2" t="inlineStr">
+      <c r="AA125" s="2" t="inlineStr">
         <is>
           <t>goya-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym-g-55001-cz</t>
         </is>
       </c>
-      <c r="AA125" s="2" t="inlineStr">
+      <c r="AB125" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym-g-55001-cz</t>
         </is>
       </c>
-      <c r="AB125" s="3" t="inlineStr">
+      <c r="AC125" s="3" t="inlineStr">
         <is>
           <t>OKULARY PRZECIWSŁONECZNE DLA KIEROWCÓW GOYA Z FILTREM POLARYZACYJNYM I UV400 Zausznik wykonane w całości z aluminium - co sprawia, że okulary są bardzo lekkie i wytrzymałe. Soczewki okularów GOYA o grubości 1,1 wyposażone są w filtr polaryzacyjny oraz filtr ochronny UV-400 (UV-A, UV-B, UV-C) ZAUSZNIKI POŁĄCZONE Z OPRAWKĄ SYSTEMEM FLEX: FLEX - elastyczne połączenie zausznika z frontem oprawy. Zwiększony zakres odchylenia zausznika do ponad 110° gwarantuje wygodę noszenia i ułatwia zakładanie oraz zdejmowanie okularów. OKULARY POSIADAJĄ CERTYFIKAT CE. Produkt odpowiada Wytycznej Europejskiej 89/686/EWG zgodnie z normą PN-EN ISO 12312-1:2014-02/A1:2016-01. Każda para okularów posiada oryginalne oznaczenia znajdujące się na wewnętrznej stronie zauszników ; logo producenta, numer modelu, kategoria filtra oraz oznaczenie CE. O POLARYZACJI: Soczewki polaryzacyjne neutralizują oślepiające refleksy, powstające wówczas gdy światło odbija się od mokrej drogi, powierzchni wody lub śniegu. Eliminacja światła odbitego zwiększ kontrast widzenia i pozwala</t>
         </is>
@@ -19676,35 +20302,40 @@
       </c>
       <c r="V126" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/575_6.jpg</t>
+        </is>
+      </c>
+      <c r="W126" s="2" t="inlineStr">
+        <is>
           <t>/products/575_6.jpg</t>
         </is>
       </c>
-      <c r="W126" s="2" t="inlineStr">
+      <c r="X126" s="2" t="inlineStr">
         <is>
           <t>/products/575_6.jpg; /products/575_5.jpg</t>
         </is>
       </c>
-      <c r="X126" s="2" t="inlineStr">
+      <c r="Y126" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2022/11/575_6.jpg</t>
         </is>
       </c>
-      <c r="Y126" s="2" t="inlineStr">
+      <c r="Z126" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary korekcyjne G 2619 C3</t>
         </is>
       </c>
-      <c r="Z126" s="2" t="inlineStr">
+      <c r="AA126" s="2" t="inlineStr">
         <is>
           <t>goya-okulary-korekcyjne-g-2619-c3</t>
         </is>
       </c>
-      <c r="AA126" s="2" t="inlineStr">
+      <c r="AB126" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-okulary-korekcyjne-g-2619-c3</t>
         </is>
       </c>
-      <c r="AB126" s="3" t="inlineStr">
+      <c r="AC126" s="3" t="inlineStr">
         <is>
           <t>OKULARY KOREKCYJNE GOYA G 2619 C3 Produkt nowy ! - posiadają oryginalne zabezpieczenia, metkę oraz instrukcję użytkowania, dodatkowo w zestawie twarde etui na zawias sprężynowy Marki GOYA oraz miękką ściereczkę czyszczącą. NASZE PRODUKTY SĄ BARDZO DOBRZE ZABEZPIECZONE W FOLIĘ TRANSPORTOWĄ I ZAPAKOWANE W WYTRZYMAŁY KARTONIK</t>
         </is>
@@ -19794,35 +20425,40 @@
       </c>
       <c r="V127" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/2445_1.jpg</t>
+        </is>
+      </c>
+      <c r="W127" s="2" t="inlineStr">
+        <is>
           <t>/products/2445_1.jpg</t>
         </is>
       </c>
-      <c r="W127" s="2" t="inlineStr">
+      <c r="X127" s="2" t="inlineStr">
         <is>
           <t>/products/2445_1.jpg</t>
         </is>
       </c>
-      <c r="X127" s="2" t="inlineStr">
+      <c r="Y127" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2022/11/2445_1.jpg</t>
         </is>
       </c>
-      <c r="Y127" s="2" t="inlineStr">
+      <c r="Z127" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary przeciwsłoneczne z filtrem polaryzacyjnym - G 55006</t>
         </is>
       </c>
-      <c r="Z127" s="2" t="inlineStr">
+      <c r="AA127" s="2" t="inlineStr">
         <is>
           <t>goya-g-55006-br-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym</t>
         </is>
       </c>
-      <c r="AA127" s="2" t="inlineStr">
+      <c r="AB127" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-g-55006-br-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym</t>
         </is>
       </c>
-      <c r="AB127" s="3" t="inlineStr">
+      <c r="AC127" s="3" t="inlineStr">
         <is>
           <t>OKULARY PRZECIWSŁONECZNE DLA KIEROWCÓW GOYA Z FILTREM POLARYZACYJNYM I UV400 Zauszniki oprawek wykonane z aluminium - co sprawia, że okulary są bardzo lekkie i wytrzymałe. Soczewki okularów GOYA o grubości 1,1 wyposażone są w filtr polaryzacyjny oraz filtr ochronny UV-400 (UV-A, UV-B, UV-C) ZAUSZNIKI POŁĄCZONE Z OPRAWKĄ SYSTEMEM FLEX: FLEX - elastyczne połączenie zausznika z frontem oprawy. Zwiększony zakres odchylenia zausznika do ponad 110° gwarantuje wygodę noszenia i ułatwia zakładanie oraz zdejmowanie okularów. OKULARY POSIADAJĄ CERTYFIKAT CE. Produkt odpowiada Wytycznej Europejskiej 89/686/EWG zgodnie z normą PN-EN ISO 12312-1:2014-02/A1:2016-01. Każda para okularów posiada oryginalne oznaczenia znajdujące się na wewnętrznej stronie zauszników ; logo producenta, numer modelu, kategoria filtra oraz oznaczenie CE. O POLARYZACJI: Soczewki polaryzacyjne neutralizują oślepiające refleksy, powstające wówczas gdy światło odbija się od mokrej drogi, powierzchni wody lub śniegu. Eliminacja światła odbitego zwiększ kontrast widzenia i pozwala na</t>
         </is>
@@ -19910,35 +20546,40 @@
       </c>
       <c r="V128" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/593_4.jpg</t>
+        </is>
+      </c>
+      <c r="W128" s="2" t="inlineStr">
+        <is>
           <t>/products/593_4.jpg</t>
         </is>
       </c>
-      <c r="W128" s="2" t="inlineStr">
+      <c r="X128" s="2" t="inlineStr">
         <is>
           <t>/products/593_4.jpg; /products/593_1.jpg; /products/593_2.jpg; /products/593_3.jpg; /products/575_6.jpg; /products/575_5.jpg</t>
         </is>
       </c>
-      <c r="X128" s="2" t="inlineStr">
+      <c r="Y128" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2022/11/593_4.jpg</t>
         </is>
       </c>
-      <c r="Y128" s="2" t="inlineStr">
+      <c r="Z128" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary korekcyjne - G 2652 C3</t>
         </is>
       </c>
-      <c r="Z128" s="2" t="inlineStr">
+      <c r="AA128" s="2" t="inlineStr">
         <is>
           <t>goya-okulary-korekcyjne-g-2652-c3</t>
         </is>
       </c>
-      <c r="AA128" s="2" t="inlineStr">
+      <c r="AB128" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-okulary-korekcyjne-g-2652-c3</t>
         </is>
       </c>
-      <c r="AB128" s="3" t="inlineStr">
+      <c r="AC128" s="3" t="inlineStr">
         <is>
           <t>OKULARY KOREKCYJNE GOYA G 2652 C3 Produkt nowy - posiadają oryginalne zabezpieczenia, metkę oraz instrukcję użytkowania, dodatkowo w zestawie twarde etui na zawias sprężynowy Marki GOYA oraz miękką ściereczkę czyszczącą. NASZE PRODUKTY WYSYŁAMY BARDZO DOBRZE ZABEZPIECZONE W FOLIĘ TRANSPORTOWĄ I ZAPAKOWANE W WYTRZYMAŁY KARTONIK</t>
         </is>
@@ -20030,35 +20671,40 @@
       </c>
       <c r="V129" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/3182_1.jpg</t>
+        </is>
+      </c>
+      <c r="W129" s="2" t="inlineStr">
+        <is>
           <t>/products/3182_1.jpg</t>
         </is>
       </c>
-      <c r="W129" s="2" t="inlineStr">
+      <c r="X129" s="2" t="inlineStr">
         <is>
           <t>/products/3182_1.jpg; /products/3182_6.jpg; /products/3182_5.jpg; /products/3182_4.jpg; /products/3182_3.jpg; /products/3182_2.jpg</t>
         </is>
       </c>
-      <c r="X129" s="2" t="inlineStr">
+      <c r="Y129" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2023/01/3182_1.jpg</t>
         </is>
       </c>
-      <c r="Y129" s="2" t="inlineStr">
+      <c r="Z129" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary przeciwsłoneczne z filtrem polaryzacyjnym - G 154 CZ</t>
         </is>
       </c>
-      <c r="Z129" s="2" t="inlineStr">
+      <c r="AA129" s="2" t="inlineStr">
         <is>
           <t>goya-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym-g-154-cz</t>
         </is>
       </c>
-      <c r="AA129" s="2" t="inlineStr">
+      <c r="AB129" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym-g-154-cz</t>
         </is>
       </c>
-      <c r="AB129" s="3" t="inlineStr">
+      <c r="AC129" s="3" t="inlineStr">
         <is>
           <t>OKULARY PRZECIWSŁONECZNE DLA KIEROWCÓW GOYA Z FILTREM POLARYZACYJNYM I UV400 Oprawka wykonana w technologii - wycinania z płyty. Ręcznie obrabiana. Soczewki okularów GOYA o grubości 1,1 wyposażone są w filtr polaryzacyjny oraz filtr ochronny UV-400 (UV-A, UV-B, UV-C) OKULARY POSIADAJĄ CERTYFIKAT CE. Produkt odpowiada Wytycznej Europejskiej 89/686/EWG zgodnie z normą PN-EN ISO 12312-1:2014-02/A1:2016-01. Każda para okularów posiada oryginalne oznaczenia znajdujące się na wewnętrznej stronie zauszników ; logo producenta, numer modelu, kategoria filtra oraz oznaczenie CE. O POLARYZACJI: Soczewki polaryzacyjne neutralizują oślepiające refleksy, powstające wówczas gdy światło odbija się od mokrej drogi, powierzchni wody lub śniegu. Eliminacja światła odbitego zwiększ kontrast widzenia i pozwala na bardziej komfortowe widzenie. Dlatego okulary z filtrem polaryzacyjnym to idealne rozwiązanie do wszelkiego rodzaju aktywności na świeżym powietrzu, pozwalające pełniej korzystać z życia. ZALETY: Eliminują oślepiające odblaski, zmniejsz</t>
         </is>
@@ -20148,35 +20794,40 @@
       </c>
       <c r="V130" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/2649_1.jpg</t>
+        </is>
+      </c>
+      <c r="W130" s="2" t="inlineStr">
+        <is>
           <t>/products/2649_1.jpg</t>
         </is>
       </c>
-      <c r="W130" s="2" t="inlineStr">
+      <c r="X130" s="2" t="inlineStr">
         <is>
           <t>/products/2649_1.jpg</t>
         </is>
       </c>
-      <c r="X130" s="2" t="inlineStr">
+      <c r="Y130" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2022/11/2649_1.jpg</t>
         </is>
       </c>
-      <c r="Y130" s="2" t="inlineStr">
+      <c r="Z130" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary przeciwsłoneczne z filtrem polaryzacyjnym - G 7107</t>
         </is>
       </c>
-      <c r="Z130" s="2" t="inlineStr">
+      <c r="AA130" s="2" t="inlineStr">
         <is>
           <t>goya-g-7107-z-okulary-przeciwsloneczne-polaryzacyjne-dla-kierowcow</t>
         </is>
       </c>
-      <c r="AA130" s="2" t="inlineStr">
+      <c r="AB130" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-g-7107-z-okulary-przeciwsloneczne-polaryzacyjne-dla-kierowcow</t>
         </is>
       </c>
-      <c r="AB130" s="3" t="inlineStr">
+      <c r="AC130" s="3" t="inlineStr">
         <is>
           <t>OKULARY PRZECIWSŁONECZNE DLA KIEROWCÓW GOYA Z FILTREM POLARYZACYJNYM I UV400 Oprawki wykonane z monelu - co sprawia, że okulary są bardzo lekkie i wytrzymałe. Soczewki okularów GOYA o grubości 1,1 wyposażone są w filtr polaryzacyjny oraz filtr ochronny UV-400 (UV-A, UV-B, UV-C) OKULARY POSIADAJĄ CERTYFIKAT CE. Produkt odpowiada Wytycznej Europejskiej 89/686/EWG zgodnie z normą PN-EN ISO 12312-1:2014-02/A1:2016-01. Każda para okularów posiada oryginalne oznaczenia znajdujące się na wewnętrznej stronie zauszników ; logo producenta, numer modelu, kategoria filtra oraz oznaczenie CE. O POLARYZACJI: Soczewki polaryzacyjne neutralizują oślepiające refleksy, powstające wówczas gdy światło odbija się od mokrej drogi, powierzchni wody lub śniegu. Eliminacja światła odbitego zwiększ kontrast widzenia i pozwala na bardziej komfortowe widzenie. Dlatego okulary z filtrem polaryzacyjnym to idealne rozwiązanie do wszelkiego rodzaju aktywności na świeżym powietrzu, pozwalające pełniej korzystać z życia. ZALETY: Eliminują oślepiające odblas</t>
         </is>
@@ -20262,35 +20913,40 @@
       </c>
       <c r="V131" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/683_4.jpg</t>
+        </is>
+      </c>
+      <c r="W131" s="2" t="inlineStr">
+        <is>
           <t>/products/683_4.jpg</t>
         </is>
       </c>
-      <c r="W131" s="2" t="inlineStr">
+      <c r="X131" s="2" t="inlineStr">
         <is>
           <t>/products/683_4.jpg</t>
         </is>
       </c>
-      <c r="X131" s="2" t="inlineStr">
+      <c r="Y131" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2022/11/683_4.jpg</t>
         </is>
       </c>
-      <c r="Y131" s="2" t="inlineStr">
+      <c r="Z131" s="2" t="inlineStr">
         <is>
           <t>GGOYA okulary korekcyjne - G 96303</t>
         </is>
       </c>
-      <c r="Z131" s="2" t="inlineStr">
+      <c r="AA131" s="2" t="inlineStr">
         <is>
           <t>goya-okulary-korekcyjne-g-96303-c3</t>
         </is>
       </c>
-      <c r="AA131" s="2" t="inlineStr">
+      <c r="AB131" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-okulary-korekcyjne-g-96303-c3</t>
         </is>
       </c>
-      <c r="AB131" s="3" t="inlineStr">
+      <c r="AC131" s="3" t="inlineStr">
         <is>
           <t>OKULARY KOREKCYJNE GOYA G 96303 Produkt nowy - posiadają oryginalne zabezpieczenia, metkę oraz instrukcję użytkowania, dodatkowo w zestawie twarde etui na zawias sprężynowy Marki GOYA oraz miękką ściereczkę czyszczącą. NASZE PRODUKTY WYSYŁAMY BARDZO DOBRZE ZABEZPIECZONE W FOLIĘ TRANSPORTOWĄ I ZAPAKOWANE W WYTRZYMAŁY KARTONIK</t>
         </is>
@@ -20382,35 +21038,40 @@
       </c>
       <c r="V132" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/3170_1.jpg</t>
+        </is>
+      </c>
+      <c r="W132" s="2" t="inlineStr">
+        <is>
           <t>/products/3170_1.jpg</t>
         </is>
       </c>
-      <c r="W132" s="2" t="inlineStr">
+      <c r="X132" s="2" t="inlineStr">
         <is>
           <t>/products/3170_1.jpg; /products/3170_6.jpg; /products/3170_2.jpg; /products/3170_3.jpg; /products/3170_4.jpg; /products/3170_5.jpg</t>
         </is>
       </c>
-      <c r="X132" s="2" t="inlineStr">
+      <c r="Y132" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2022/11/3170_1.jpg</t>
         </is>
       </c>
-      <c r="Y132" s="2" t="inlineStr">
+      <c r="Z132" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary przeciwsłoneczne z filtrem polaryzacyjnym - G 164</t>
         </is>
       </c>
-      <c r="Z132" s="2" t="inlineStr">
+      <c r="AA132" s="2" t="inlineStr">
         <is>
           <t>goya-g-164-cz-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym</t>
         </is>
       </c>
-      <c r="AA132" s="2" t="inlineStr">
+      <c r="AB132" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-g-164-cz-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym</t>
         </is>
       </c>
-      <c r="AB132" s="3" t="inlineStr">
+      <c r="AC132" s="3" t="inlineStr">
         <is>
           <t>OKULARY PRZECIWSŁONECZNE DLA KIEROWCÓW GOYA Z FILTREM POLARYZACYJNYM I UV400 Oprawka wykonana w technologii - wycinania z płyty. Ręcznie obrabiana. Soczewki okularów GOYA o grubości 1,1 wyposażone są w filtr polaryzacyjny oraz filtr ochronny UV-400 (UV-A, UV-B, UV-C) ZAUSZNIKI POŁĄCZONE Z OPRAWKĄ SYSTEMEM FLEX: FLEX - elastyczne połączenie zausznika z frontem oprawy. Zwiększony zakres odchylenia zausznika do ponad 110° gwarantuje wygodę noszenia i ułatwia zakładanie oraz zdejmowanie okularów. OKULARY POSIADAJĄ CERTYFIKAT CE. Produkt odpowiada Wytycznej Europejskiej 89/686/EWG zgodnie z normą PN-EN ISO 12312-1:2014-02/A1:2016-01. Każda para okularów posiada oryginalne oznaczenia znajdujące się na wewnętrznej stronie zauszników ; logo producenta, numer modelu, kategoria filtra oraz oznaczenie CE. O POLARYZACJI: Soczewki polaryzacyjne neutralizują oślepiające refleksy, powstające wówczas gdy światło odbija się od mokrej drogi, powierzchni wody lub śniegu. Eliminacja światła odbitego zwiększ kontrast widzenia i pozwala na bardziej komfortowe wid</t>
         </is>
@@ -20502,35 +21163,40 @@
       </c>
       <c r="V133" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/G-21611-CZ-A.jpg</t>
+        </is>
+      </c>
+      <c r="W133" s="2" t="inlineStr">
+        <is>
           <t>/products/G-21611-CZ-A.jpg</t>
         </is>
       </c>
-      <c r="W133" s="2" t="inlineStr">
+      <c r="X133" s="2" t="inlineStr">
         <is>
           <t>/products/G-21611-CZ-A.jpg; /products/GOYA_G21611_cz_mod.jpg; /products/G-21611-CZ-Z.jpg; /products/G-21611-CZ-t.jpg; /products/G-21611-CZ-s.jpg; /products/G-21611-CZ-f.jpg; /products/G-21611-CZ-b.jpg</t>
         </is>
       </c>
-      <c r="X133" s="2" t="inlineStr">
+      <c r="Y133" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2023/02/G-21611-CZ-A.jpg</t>
         </is>
       </c>
-      <c r="Y133" s="2" t="inlineStr">
+      <c r="Z133" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary przeciwsłoneczne z filtrem polaryzacyjnym - G 21611 CZ</t>
         </is>
       </c>
-      <c r="Z133" s="2" t="inlineStr">
+      <c r="AA133" s="2" t="inlineStr">
         <is>
           <t>goya-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym-g-21611-cz</t>
         </is>
       </c>
-      <c r="AA133" s="2" t="inlineStr">
+      <c r="AB133" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym-g-21611-cz</t>
         </is>
       </c>
-      <c r="AB133" s="3" t="inlineStr">
+      <c r="AC133" s="3" t="inlineStr">
         <is>
           <t>OKULARY PRZECIWSŁONECZNE DLA KIEROWCÓW GOYA Z FILTREM POLARYZACYJNYM I UV400 Soczewki okularów GOYA o grubości 1,1 wyposażone są w filtr polaryzacyjny oraz filtr ochronny UV-400 (UV-A, UV-B, UV-C) ZAUSZNIKI POŁĄCZONE Z OPRAWKĄ SYSTEMEM FLEX: FLEX - elastyczne połączenie zausznika z frontem oprawy. Zwiększony zakres odchylenia zausznika do ponad 110° gwarantuje wygodę noszenia i ułatwia zakładanie oraz zdejmowanie okularów. OKULARY POSIADAJĄ CERTYFIKAT CE. Produkt odpowiada Wytycznej Europejskiej 89/686/EWG zgodnie z normą PN-EN ISO 12312-1:2014-02/A1:2016-01. Każda para okularów posiada oryginalne oznaczenia znajdujące się na wewnętrznej stronie zauszników ; logo producenta, numer modelu, kategoria filtra oraz oznaczenie CE. O POLARYZACJI: Soczewki polaryzacyjne neutralizują oślepiające refleksy, powstające wówczas gdy światło odbija się od mokrej drogi, powierzchni wody lub śniegu. Eliminacja światła odbitego zwiększ kontrast widzenia i pozwala na bardziej komfortowe widzenie. Dlatego okulary z filtrem polaryzacyjnym to idealne rozwiązanie do</t>
         </is>
@@ -20616,35 +21282,40 @@
       </c>
       <c r="V134" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/666_4.jpg</t>
+        </is>
+      </c>
+      <c r="W134" s="2" t="inlineStr">
+        <is>
           <t>/products/666_4.jpg</t>
         </is>
       </c>
-      <c r="W134" s="2" t="inlineStr">
+      <c r="X134" s="2" t="inlineStr">
         <is>
           <t>/products/666_4.jpg</t>
         </is>
       </c>
-      <c r="X134" s="2" t="inlineStr">
+      <c r="Y134" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2022/11/666_4.jpg</t>
         </is>
       </c>
-      <c r="Y134" s="2" t="inlineStr">
+      <c r="Z134" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary korekcyjne - G 94313</t>
         </is>
       </c>
-      <c r="Z134" s="2" t="inlineStr">
+      <c r="AA134" s="2" t="inlineStr">
         <is>
           <t>goya-okulary-korekcyjne-g-94313-c4</t>
         </is>
       </c>
-      <c r="AA134" s="2" t="inlineStr">
+      <c r="AB134" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-okulary-korekcyjne-g-94313-c4</t>
         </is>
       </c>
-      <c r="AB134" s="3" t="inlineStr">
+      <c r="AC134" s="3" t="inlineStr">
         <is>
           <t>OKULARY KOREKCYJNE GOYA G 94313 Produkt nowy - posiadają oryginalne zabezpieczenia, metkę oraz instrukcję użytkowania, dodatkowo w zestawie twarde etui na zawias sprężynowy Marki GOYA oraz miękką ściereczkę czyszczącą. NASZE PRODUKTY WYSYŁAMY BARDZO DOBRZE ZABEZPIECZONE W FOLIĘ TRANSPORTOWĄ I ZAPAKOWANE W WYTRZYMAŁY KARTONIK</t>
         </is>
@@ -20732,35 +21403,40 @@
       </c>
       <c r="V135" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/642_4.jpg</t>
+        </is>
+      </c>
+      <c r="W135" s="2" t="inlineStr">
+        <is>
           <t>/products/642_4.jpg</t>
         </is>
       </c>
-      <c r="W135" s="2" t="inlineStr">
+      <c r="X135" s="2" t="inlineStr">
         <is>
           <t>/products/642_4.jpg; /products/642_1.jpg; /products/642_3.jpg; /products/642_2.jpg</t>
         </is>
       </c>
-      <c r="X135" s="2" t="inlineStr">
+      <c r="Y135" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2022/11/642_4.jpg</t>
         </is>
       </c>
-      <c r="Y135" s="2" t="inlineStr">
+      <c r="Z135" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary korekcyjne - LB 8936 C3</t>
         </is>
       </c>
-      <c r="Z135" s="2" t="inlineStr">
+      <c r="AA135" s="2" t="inlineStr">
         <is>
           <t>goya-okulary-korekcyjne-lb-8936-c3</t>
         </is>
       </c>
-      <c r="AA135" s="2" t="inlineStr">
+      <c r="AB135" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-okulary-korekcyjne-lb-8936-c3</t>
         </is>
       </c>
-      <c r="AB135" s="3" t="inlineStr">
+      <c r="AC135" s="3" t="inlineStr">
         <is>
           <t>OKULARY KOREKCYJNE GOYA LB 8936 C3 Produkt nowy - posiadają oryginalne zabezpieczenia, metkę oraz instrukcję użytkowania, dodatkowo w zestawie twarde etui na zawias sprężynowy Marki GOYA oraz miękką ściereczkę czyszczącą. NASZE PRODUKTY WYSYŁAMY BARDZO DOBRZE ZABEZPIECZONE W FOLIĘ TRANSPORTOWĄ I ZAPAKOWANE W WYTRZYMAŁY KARTONIK</t>
         </is>
@@ -20852,35 +21528,40 @@
       </c>
       <c r="V136" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/GOYA-A0709-CZ-A.jpg</t>
+        </is>
+      </c>
+      <c r="W136" s="2" t="inlineStr">
+        <is>
           <t>/products/GOYA-A0709-CZ-A.jpg</t>
         </is>
       </c>
-      <c r="W136" s="2" t="inlineStr">
+      <c r="X136" s="2" t="inlineStr">
         <is>
           <t>/products/GOYA-A0709-CZ-A.jpg; /products/GOYA_A0709_CZ_mod.jpg; /products/GOYA-A0709-CZ-Z.jpg; /products/GOYA-A0709-CZ-b.jpg; /products/GOYA-A0709-CZ-f.jpg; /products/GOYA-A0709-CZ-s.jpg; /products/GOYA-A0709-CZ-t.jpg</t>
         </is>
       </c>
-      <c r="X136" s="2" t="inlineStr">
+      <c r="Y136" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2023/04/GOYA-A0709-CZ-A.jpg</t>
         </is>
       </c>
-      <c r="Y136" s="2" t="inlineStr">
+      <c r="Z136" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary przeciwsłoneczne z filtrem polaryzacyjnym - GOYA A 0709 CZ</t>
         </is>
       </c>
-      <c r="Z136" s="2" t="inlineStr">
+      <c r="AA136" s="2" t="inlineStr">
         <is>
           <t>goya-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym-goya-a-0709-cz</t>
         </is>
       </c>
-      <c r="AA136" s="2" t="inlineStr">
+      <c r="AB136" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym-goya-a-0709-cz</t>
         </is>
       </c>
-      <c r="AB136" s="3" t="inlineStr">
+      <c r="AC136" s="3" t="inlineStr">
         <is>
           <t>OKULARY PRZECIWSŁONECZNE GOYA Z FILTREM POLARYZACYJNYM I UV400 Soczewki okularów GOYA o grubości 1,1 wyposażone są w filtr polaryzacyjny oraz filtr ochronny UV-400 (UV-A, UV-B, UV-C) OKULARY POSIADAJĄ CERTYFIKAT CE. Produkt odpowiada Wytycznej Europejskiej 89/686/EWG zgodnie z normą PN-EN ISO 12312-1:2014-02/A1:2016-01. Każda para okularów posiada oryginalne oznaczenia znajdujące się na wewnętrznej stronie zauszników ; logo producenta, numer modelu, kategoria filtra oraz oznaczenie CE. O POLARYZACJI: Soczewki polaryzacyjne neutralizują oślepiające refleksy, powstające wówczas gdy światło odbija się od mokrej drogi, powierzchni wody lub śniegu. Eliminacja światła odbitego zwiększ kontrast widzenia i pozwala na bardziej komfortowe widzenie. Dlatego okulary z filtrem polaryzacyjnym to idealne rozwiązanie do wszelkiego rodzaju aktywności na świeżym powietrzu, pozwalające pełniej korzystać z życia. ZALETY: Eliminują oślepiające odblaski, zmniejszając zmęczenie oczu Chronią przed szkodliwym promieniowaniem UV Zwiększają kontras</t>
         </is>
@@ -20966,35 +21647,40 @@
       </c>
       <c r="V137" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/646_4.jpg</t>
+        </is>
+      </c>
+      <c r="W137" s="2" t="inlineStr">
+        <is>
           <t>/products/646_4.jpg</t>
         </is>
       </c>
-      <c r="W137" s="2" t="inlineStr">
+      <c r="X137" s="2" t="inlineStr">
         <is>
           <t>/products/646_4.jpg</t>
         </is>
       </c>
-      <c r="X137" s="2" t="inlineStr">
+      <c r="Y137" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2022/11/646_4.jpg</t>
         </is>
       </c>
-      <c r="Y137" s="2" t="inlineStr">
+      <c r="Z137" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary korekcyjne - M 9010</t>
         </is>
       </c>
-      <c r="Z137" s="2" t="inlineStr">
+      <c r="AA137" s="2" t="inlineStr">
         <is>
           <t>goya-okulary-korekcyjne-m-9010-c2</t>
         </is>
       </c>
-      <c r="AA137" s="2" t="inlineStr">
+      <c r="AB137" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-okulary-korekcyjne-m-9010-c2</t>
         </is>
       </c>
-      <c r="AB137" s="3" t="inlineStr">
+      <c r="AC137" s="3" t="inlineStr">
         <is>
           <t>OKULARY KOREKCYJNE GOYA M 9010 Produkt nowy - posiadają oryginalne zabezpieczenia, metkę oraz instrukcję użytkowania, dodatkowo w zestawie twarde etui na zawias sprężynowy Marki GOYA oraz miękką ściereczkę czyszczącą. NASZE PRODUKTY WYSYŁAMY BARDZO DOBRZE ZABEZPIECZONE W FOLIĘ TRANSPORTOWĄ I ZAPAKOWANE W WYTRZYMAŁY KARTONIK</t>
         </is>
@@ -21082,35 +21768,40 @@
       </c>
       <c r="V138" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/655_4.jpg</t>
+        </is>
+      </c>
+      <c r="W138" s="2" t="inlineStr">
+        <is>
           <t>/products/655_4.jpg</t>
         </is>
       </c>
-      <c r="W138" s="2" t="inlineStr">
+      <c r="X138" s="2" t="inlineStr">
         <is>
           <t>/products/655_4.jpg; /products/655_1.jpg; /products/655_3.jpg; /products/655_2.jpg</t>
         </is>
       </c>
-      <c r="X138" s="2" t="inlineStr">
+      <c r="Y138" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2022/11/655_4.jpg</t>
         </is>
       </c>
-      <c r="Y138" s="2" t="inlineStr">
+      <c r="Z138" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary korekcyjne - RD 654 C3</t>
         </is>
       </c>
-      <c r="Z138" s="2" t="inlineStr">
+      <c r="AA138" s="2" t="inlineStr">
         <is>
           <t>goya-okulary-korekcyjne-rd-654-c3</t>
         </is>
       </c>
-      <c r="AA138" s="2" t="inlineStr">
+      <c r="AB138" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-okulary-korekcyjne-rd-654-c3</t>
         </is>
       </c>
-      <c r="AB138" s="3" t="inlineStr">
+      <c r="AC138" s="3" t="inlineStr">
         <is>
           <t>OKULARY KOREKCYJNE GOYA RD 654 C3 Produkt nowy - posiadają oryginalne zabezpieczenia, metkę oraz instrukcję użytkowania, dodatkowo w zestawie twarde etui na zawias sprężynowy Marki GOYA oraz miękką ściereczkę czyszczącą. NASZE PRODUKTY WYSYŁAMY BARDZO DOBRZE ZABEZPIECZONE W FOLIĘ TRANSPORTOWĄ I ZAPAKOWANE W WYTRZYMAŁY KARTONIK</t>
         </is>
@@ -21196,35 +21887,40 @@
       </c>
       <c r="V139" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/595_4.jpg</t>
+        </is>
+      </c>
+      <c r="W139" s="2" t="inlineStr">
+        <is>
           <t>/products/595_4.jpg</t>
         </is>
       </c>
-      <c r="W139" s="2" t="inlineStr">
+      <c r="X139" s="2" t="inlineStr">
         <is>
           <t>/products/595_4.jpg</t>
         </is>
       </c>
-      <c r="X139" s="2" t="inlineStr">
+      <c r="Y139" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2022/11/595_4.jpg</t>
         </is>
       </c>
-      <c r="Y139" s="2" t="inlineStr">
+      <c r="Z139" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary korekcyjne - G 2637</t>
         </is>
       </c>
-      <c r="Z139" s="2" t="inlineStr">
+      <c r="AA139" s="2" t="inlineStr">
         <is>
           <t>goya-okulary-korekcyjne-g-2637-c2</t>
         </is>
       </c>
-      <c r="AA139" s="2" t="inlineStr">
+      <c r="AB139" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-okulary-korekcyjne-g-2637-c2</t>
         </is>
       </c>
-      <c r="AB139" s="3" t="inlineStr">
+      <c r="AC139" s="3" t="inlineStr">
         <is>
           <t>OKULARY KOREKCYJNE GOYA G 2637 Produkt nowy - posiadają oryginalne zabezpieczenia, metkę oraz instrukcję użytkowania, dodatkowo w zestawie twarde etui na zawias sprężynowy Marki GOYA oraz miękką ściereczkę czyszczącą. NASZE PRODUKTY WYSYŁAMY BARDZO DOBRZE ZABEZPIECZONE W FOLIĘ TRANSPORTOWĄ I ZAPAKOWANE W WYTRZYMAŁY KARTONIK</t>
         </is>
@@ -21314,35 +22010,40 @@
       </c>
       <c r="V140" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/2454_1.jpg</t>
+        </is>
+      </c>
+      <c r="W140" s="2" t="inlineStr">
+        <is>
           <t>/products/2454_1.jpg</t>
         </is>
       </c>
-      <c r="W140" s="2" t="inlineStr">
+      <c r="X140" s="2" t="inlineStr">
         <is>
           <t>/products/2454_1.jpg</t>
         </is>
       </c>
-      <c r="X140" s="2" t="inlineStr">
+      <c r="Y140" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2022/11/2454_1.jpg</t>
         </is>
       </c>
-      <c r="Y140" s="2" t="inlineStr">
+      <c r="Z140" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary przeciwsłoneczne z filtrem polaryzacyjnym - G 55016</t>
         </is>
       </c>
-      <c r="Z140" s="2" t="inlineStr">
+      <c r="AA140" s="2" t="inlineStr">
         <is>
           <t>goya-g-55016-br-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym</t>
         </is>
       </c>
-      <c r="AA140" s="2" t="inlineStr">
+      <c r="AB140" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-g-55016-br-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym</t>
         </is>
       </c>
-      <c r="AB140" s="3" t="inlineStr">
+      <c r="AC140" s="3" t="inlineStr">
         <is>
           <t>OKULARY PRZECIWSŁONECZNE DLA KIEROWCÓW GOYA Z FILTREM POLARYZACYJNYM I UV400 Zauszniki oprawek wykonane z aluminium - co sprawia, że okulary są bardzo lekkie i wytrzymałe. Soczewki okularów GOYA o grubości 1,1 wyposażone są w filtr polaryzacyjny oraz filtr ochronny UV-400 (UV-A, UV-B, UV-C) ZAUSZNIKI POŁĄCZONE Z OPRAWKĄ SYSTEMEM FLEX: FLEX - elastyczne połączenie zausznika z frontem oprawy. Zwiększony zakres odchylenia zausznika do ponad 110° gwarantuje wygodę noszenia i ułatwia zakładanie oraz zdejmowanie okularów. OKULARY POSIADAJĄ CERTYFIKAT CE. Produkt odpowiada Wytycznej Europejskiej 89/686/EWG zgodnie z normą PN-EN ISO 12312-1:2014-02/A1:2016-01. Każda para okularów posiada oryginalne oznaczenia znajdujące się na wewnętrznej stronie zauszników ; logo producenta, numer modelu, kategoria filtra oraz oznaczenie CE. O POLARYZACJI: Soczewki polaryzacyjne neutralizują oślepiające refleksy, powstające wówczas gdy światło odbija się od mokrej drogi, powierzchni wody lub śniegu. Eliminacja światła odbitego zwiększ kontrast widzenia i pozwala na</t>
         </is>
@@ -21430,35 +22131,40 @@
       </c>
       <c r="V141" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/682_4.jpg</t>
+        </is>
+      </c>
+      <c r="W141" s="2" t="inlineStr">
+        <is>
           <t>/products/682_4.jpg</t>
         </is>
       </c>
-      <c r="W141" s="2" t="inlineStr">
+      <c r="X141" s="2" t="inlineStr">
         <is>
           <t>/products/682_4.jpg; /products/682_1.jpg; /products/682_3.jpg; /products/682_2.jpg</t>
         </is>
       </c>
-      <c r="X141" s="2" t="inlineStr">
+      <c r="Y141" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2022/11/682_4.jpg</t>
         </is>
       </c>
-      <c r="Y141" s="2" t="inlineStr">
+      <c r="Z141" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary korekcyjne - G 1478 C2</t>
         </is>
       </c>
-      <c r="Z141" s="2" t="inlineStr">
+      <c r="AA141" s="2" t="inlineStr">
         <is>
           <t>goya-okulary-korekcyjne-g-1478-c2</t>
         </is>
       </c>
-      <c r="AA141" s="2" t="inlineStr">
+      <c r="AB141" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-okulary-korekcyjne-g-1478-c2</t>
         </is>
       </c>
-      <c r="AB141" s="3" t="inlineStr">
+      <c r="AC141" s="3" t="inlineStr">
         <is>
           <t>OKULARY KOREKCYJNE GOYA G 1478 C2 Produkt nowy - posiadają oryginalne zabezpieczenia, metkę oraz instrukcję użytkowania, dodatkowo w zestawie twarde etui na zawias sprężynowy Marki GOYA oraz miękką ściereczkę czyszczącą. NASZE PRODUKTY WYSYŁAMY BARDZO DOBRZE ZABEZPIECZONE W FOLIĘ TRANSPORTOWĄ I ZAPAKOWANE W WYTRZYMAŁY KARTONIK</t>
         </is>
@@ -21546,35 +22252,40 @@
       </c>
       <c r="V142" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/575_6.jpg</t>
+        </is>
+      </c>
+      <c r="W142" s="2" t="inlineStr">
+        <is>
           <t>/products/575_6.jpg</t>
         </is>
       </c>
-      <c r="W142" s="2" t="inlineStr">
+      <c r="X142" s="2" t="inlineStr">
         <is>
           <t>/products/575_6.jpg; /products/575_5.jpg</t>
         </is>
       </c>
-      <c r="X142" s="2" t="inlineStr">
+      <c r="Y142" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2022/11/575_6.jpg</t>
         </is>
       </c>
-      <c r="Y142" s="2" t="inlineStr">
+      <c r="Z142" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary korekcyjne G 2635 C1</t>
         </is>
       </c>
-      <c r="Z142" s="2" t="inlineStr">
+      <c r="AA142" s="2" t="inlineStr">
         <is>
           <t>goya-okulary-korekcyjne-g-2635-c1</t>
         </is>
       </c>
-      <c r="AA142" s="2" t="inlineStr">
+      <c r="AB142" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-okulary-korekcyjne-g-2635-c1</t>
         </is>
       </c>
-      <c r="AB142" s="3" t="inlineStr">
+      <c r="AC142" s="3" t="inlineStr">
         <is>
           <t>OKULARY KOREKCYJNE GOYA G 2635 C1 Produkt nowy ! - posiadają oryginalne zabezpieczenia, metkę oraz instrukcję użytkowania, dodatkowo w zestawie twarde etui na zawias sprężynowy Marki GOYA oraz miękką ściereczkę czyszczącą. NASZE PRODUKTY SĄ BARDZO DOBRZE ZABEZPIECZONE W FOLIĘ TRANSPORTOWĄ I ZAPAKOWANE W WYTRZYMAŁY KARTONIK</t>
         </is>
@@ -21664,35 +22375,40 @@
       </c>
       <c r="V143" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/1867_4.jpg</t>
+        </is>
+      </c>
+      <c r="W143" s="2" t="inlineStr">
+        <is>
           <t>/products/1867_4.jpg</t>
         </is>
       </c>
-      <c r="W143" s="2" t="inlineStr">
+      <c r="X143" s="2" t="inlineStr">
         <is>
           <t>/products/1867_4.jpg</t>
         </is>
       </c>
-      <c r="X143" s="2" t="inlineStr">
+      <c r="Y143" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2023/01/1867_4.jpg</t>
         </is>
       </c>
-      <c r="Y143" s="2" t="inlineStr">
+      <c r="Z143" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary przeciwsłoneczne z filtrem polaryzacyjnym - G 217</t>
         </is>
       </c>
-      <c r="Z143" s="2" t="inlineStr">
+      <c r="AA143" s="2" t="inlineStr">
         <is>
           <t>okulary-przeciwsloneczne-polaryzacyjne-dla-kierowcow-pilotki-lustrzanki-goya-g-217-n</t>
         </is>
       </c>
-      <c r="AA143" s="2" t="inlineStr">
+      <c r="AB143" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/okulary-przeciwsloneczne-polaryzacyjne-dla-kierowcow-pilotki-lustrzanki-goya-g-217-n</t>
         </is>
       </c>
-      <c r="AB143" s="3" t="inlineStr">
+      <c r="AC143" s="3" t="inlineStr">
         <is>
           <t>OKULARY PRZECIWSŁONECZNE DLA KIEROWCÓW GOYA Z FILTREM POLARYZACYJNYM I UV400 Oprawki wykonane z monelu (stop miedzi i niklu z domieszką żelaza i manganu, charakteryzujący się dużą odpornością na korozję) - co sprawia, że okulary są bardzo lekkie i wytrzymałe. Soczewki okularów GOYA o grubości 1,1 wyposażone są w filtr polaryzacyjny oraz filtr ochronny UV-400 (UV-A, UV-B, UV-C) OKULARY POSIADAJĄ CERTYFIKAT CE. Produkt odpowiada Wytycznej Europejskiej 89/686/EWG zgodnie z normą PN-EN ISO 12312-1:2014-02/A1:2016-01. Każda para okularów posiada oryginalne oznaczenia znajdujące się na wewnętrznej stronie zauszników ; logo producenta, numer modelu, kategoria filtra oraz oznaczenie CE. O POLARYZACJI: Soczewki polaryzacyjne neutralizują oślepiające refleksy, powstające wówczas gdy światło odbija się od mokrej drogi, powierzchni wody lub śniegu. Eliminacja światła odbitego zwiększ kontrast widzenia i pozwala na bardziej komfortowe widzenie. Dlatego okulary z filtrem polaryzacyjnym to idealne rozwiązanie do wszelkiego rodzaju aktywności na świeżym powietrzu, poz</t>
         </is>
@@ -21786,35 +22502,40 @@
       </c>
       <c r="V144" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/prof-235.jpeg</t>
+        </is>
+      </c>
+      <c r="W144" s="2" t="inlineStr">
+        <is>
           <t>/products/prof-235.jpeg</t>
         </is>
       </c>
-      <c r="W144" s="2" t="inlineStr">
+      <c r="X144" s="2" t="inlineStr">
         <is>
           <t>/products/prof-235.jpeg</t>
         </is>
       </c>
-      <c r="X144" s="2" t="inlineStr">
+      <c r="Y144" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2022/03/prof-235.jpeg</t>
         </is>
       </c>
-      <c r="Y144" s="2" t="inlineStr">
+      <c r="Z144" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary przeciwsłoneczne z filtrem polaryzacyjnym - G 214</t>
         </is>
       </c>
-      <c r="Z144" s="2" t="inlineStr">
+      <c r="AA144" s="2" t="inlineStr">
         <is>
           <t>okulary-przeciwsloneczne-polaryzacyjne-dla-kierowcow-goya-g-214-cz-tr90</t>
         </is>
       </c>
-      <c r="AA144" s="2" t="inlineStr">
+      <c r="AB144" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/okulary-przeciwsloneczne-polaryzacyjne-dla-kierowcow-goya-g-214-cz-tr90</t>
         </is>
       </c>
-      <c r="AB144" s="3" t="inlineStr">
+      <c r="AC144" s="3" t="inlineStr">
         <is>
           <t>OKULARY PRZECIWSŁONECZNE DLA KIEROWCÓW GOYA Z FILTREM POLARYZACYJNYM I UV400 Soczewki okularów GOYA o grubości 1,1 wyposażone są w filtr polaryzacyjny oraz filtr ochronny UV-400 (UV-A, UV-B, UV-C) OPRAWKA WYKONANA W TECHNOLOGII TR-90 Wysokiej jakości odmiana nylonu, wyjątkowo odporna na rozciąganie i wyginanie. Materiał wytrzymały na uderzenia, elastyczny, przyjemny w dotyku, o właściwościach antyalergicznych. Okulary wykonane z TR-90 są lekkie, wytrzymałe i wygodne w użytkowaniu. OKULARY POSIADAJĄ CERTYFIKAT CE. Produkt odpowiada Wytycznej Europejskiej 89/686/EWG zgodnie z normą PN-EN ISO 12312-1:2014-02/A1:2016-01. Każda para okularów posiada oryginalne oznaczenia znajdujące się na wewnętrznej stronie zauszników ; logo producenta, numer modelu, kategoria filtra oraz oznaczenie CE. O POLARYZACJI: Soczewki polaryzacyjne neutralizują oślepiające refleksy, powstające wówczas gdy światło odbija się od mokrej drogi, powierzchni wody lub śniegu. Eliminacja światła odbitego zwiększ kontrast widzenia i pozwala na bardziej komfortowe widzenie. Dlatego okul</t>
         </is>
@@ -21902,35 +22623,40 @@
       </c>
       <c r="V145" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/575_6.jpg</t>
+        </is>
+      </c>
+      <c r="W145" s="2" t="inlineStr">
+        <is>
           <t>/products/575_6.jpg</t>
         </is>
       </c>
-      <c r="W145" s="2" t="inlineStr">
+      <c r="X145" s="2" t="inlineStr">
         <is>
           <t>/products/575_6.jpg; /products/575_5.jpg</t>
         </is>
       </c>
-      <c r="X145" s="2" t="inlineStr">
+      <c r="Y145" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2022/11/575_6.jpg</t>
         </is>
       </c>
-      <c r="Y145" s="2" t="inlineStr">
+      <c r="Z145" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary korekcyjne G 2672 C1</t>
         </is>
       </c>
-      <c r="Z145" s="2" t="inlineStr">
+      <c r="AA145" s="2" t="inlineStr">
         <is>
           <t>goya-okulary-korekcyjne-g-2672-c1</t>
         </is>
       </c>
-      <c r="AA145" s="2" t="inlineStr">
+      <c r="AB145" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-okulary-korekcyjne-g-2672-c1</t>
         </is>
       </c>
-      <c r="AB145" s="3" t="inlineStr">
+      <c r="AC145" s="3" t="inlineStr">
         <is>
           <t>OKULARY KOREKCYJNE GOYA G 2672 C1 Produkt nowy ! - posiadają oryginalne zabezpieczenia, metkę oraz instrukcję użytkowania, dodatkowo w zestawie twarde etui na zawias sprężynowy Marki GOYA oraz miękką ściereczkę czyszczącą. NASZE PRODUKTY SĄ BARDZO DOBRZE ZABEZPIECZONE W FOLIĘ TRANSPORTOWĄ I ZAPAKOWANE W WYTRZYMAŁY KARTONIK</t>
         </is>
@@ -22020,35 +22746,40 @@
       </c>
       <c r="V146" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/3414_1.jpg</t>
+        </is>
+      </c>
+      <c r="W146" s="2" t="inlineStr">
+        <is>
           <t>/products/3414_1.jpg</t>
         </is>
       </c>
-      <c r="W146" s="2" t="inlineStr">
+      <c r="X146" s="2" t="inlineStr">
         <is>
           <t>/products/3414_1.jpg; /products/3413_7-e1681286823562.jpg</t>
         </is>
       </c>
-      <c r="X146" s="2" t="inlineStr">
+      <c r="Y146" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2023/04/3414_1.jpg</t>
         </is>
       </c>
-      <c r="Y146" s="2" t="inlineStr">
+      <c r="Z146" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary przeciwsłoneczne z filtrem polaryzacyjnym - GOYA CP 806632</t>
         </is>
       </c>
-      <c r="Z146" s="2" t="inlineStr">
+      <c r="AA146" s="2" t="inlineStr">
         <is>
           <t>goya-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym-goya-cp-806632</t>
         </is>
       </c>
-      <c r="AA146" s="2" t="inlineStr">
+      <c r="AB146" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym-goya-cp-806632</t>
         </is>
       </c>
-      <c r="AB146" s="3" t="inlineStr">
+      <c r="AC146" s="3" t="inlineStr">
         <is>
           <t>OKULARY PRZECIWSŁONECZNE DLA KIEROWCÓW GOYA Z FILTREM POLARYZACYJNYM I UV400 Soczewki okularów GOYA o grubości 1,1 wyposażone są w filtr polaryzacyjny oraz filtr ochronny UV-400 (UV-A, UV-B, UV-C) OKULARY POSIADAJĄ CERTYFIKAT CE. Produkt odpowiada Wytycznej Europejskiej 89/686/EWG zgodnie z normą PN-EN ISO 12312-1:2014-02/A1:2016-01. Każda para okularów posiada oryginalne oznaczenia znajdujące się na wewnętrznej stronie zauszników ; logo producenta, numer modelu, kategoria filtra oraz oznaczenie CE. O POLARYZACJI: Soczewki polaryzacyjne neutralizują oślepiające refleksy, powstające wówczas gdy światło odbija się od mokrej drogi, powierzchni wody lub śniegu. Eliminacja światła odbitego zwiększ kontrast widzenia i pozwala na bardziej komfortowe widzenie. Dlatego okulary z filtrem polaryzacyjnym to idealne rozwiązanie do wszelkiego rodzaju aktywności na świeżym powietrzu, pozwalające pełniej korzystać z życia. ZALETY: Eliminują oślepiające odblaski, zmniejszając zmęczenie oczu Chronią przed szkodliwym promieniowaniem UV Zwięk</t>
         </is>
@@ -22136,35 +22867,40 @@
       </c>
       <c r="V147" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/575_6.jpg</t>
+        </is>
+      </c>
+      <c r="W147" s="2" t="inlineStr">
+        <is>
           <t>/products/575_6.jpg</t>
         </is>
       </c>
-      <c r="W147" s="2" t="inlineStr">
+      <c r="X147" s="2" t="inlineStr">
         <is>
           <t>/products/575_6.jpg; /products/575_5.jpg</t>
         </is>
       </c>
-      <c r="X147" s="2" t="inlineStr">
+      <c r="Y147" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2022/11/575_6.jpg</t>
         </is>
       </c>
-      <c r="Y147" s="2" t="inlineStr">
+      <c r="Z147" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary korekcyjne - RD 396 C2</t>
         </is>
       </c>
-      <c r="Z147" s="2" t="inlineStr">
+      <c r="AA147" s="2" t="inlineStr">
         <is>
           <t>goya-okulary-korekcyjne-rd-396-c2</t>
         </is>
       </c>
-      <c r="AA147" s="2" t="inlineStr">
+      <c r="AB147" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-okulary-korekcyjne-rd-396-c2</t>
         </is>
       </c>
-      <c r="AB147" s="3" t="inlineStr">
+      <c r="AC147" s="3" t="inlineStr">
         <is>
           <t>OKULARY KOREKCYJNE GOYA RD 396 C2 Produkt nowy ! - posiadają oryginalne zabezpieczenia, metkę oraz instrukcję użytkowania, dodatkowo w zestawie twarde etui na zawias sprężynowy Marki GOYA oraz miękką ściereczkę czyszczącą. NASZE PRODUKTY SĄ BARDZO DOBRZE ZABEZPIECZONE W FOLIĘ TRANSPORTOWĄ I ZAPAKOWANE W WYTRZYMAŁY KARTONIK</t>
         </is>
@@ -22252,35 +22988,40 @@
       </c>
       <c r="V148" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/575_6.jpg</t>
+        </is>
+      </c>
+      <c r="W148" s="2" t="inlineStr">
+        <is>
           <t>/products/575_6.jpg</t>
         </is>
       </c>
-      <c r="W148" s="2" t="inlineStr">
+      <c r="X148" s="2" t="inlineStr">
         <is>
           <t>/products/575_6.jpg; /products/575_5.jpg</t>
         </is>
       </c>
-      <c r="X148" s="2" t="inlineStr">
+      <c r="Y148" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2022/11/575_6.jpg</t>
         </is>
       </c>
-      <c r="Y148" s="2" t="inlineStr">
+      <c r="Z148" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary korekcyjne - RD 396 C3</t>
         </is>
       </c>
-      <c r="Z148" s="2" t="inlineStr">
+      <c r="AA148" s="2" t="inlineStr">
         <is>
           <t>goya-okulary-korekcyjne-rd-396-c3</t>
         </is>
       </c>
-      <c r="AA148" s="2" t="inlineStr">
+      <c r="AB148" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-okulary-korekcyjne-rd-396-c3</t>
         </is>
       </c>
-      <c r="AB148" s="3" t="inlineStr">
+      <c r="AC148" s="3" t="inlineStr">
         <is>
           <t>OKULARY KOREKCYJNE GOYA RD 396 C3 Produkt nowy ! - posiadają oryginalne zabezpieczenia, metkę oraz instrukcję użytkowania, dodatkowo w zestawie twarde etui na zawias sprężynowy Marki GOYA oraz miękką ściereczkę czyszczącą. NASZE PRODUKTY SĄ BARDZO DOBRZE ZABEZPIECZONE W FOLIĘ TRANSPORTOWĄ I ZAPAKOWANE W WYTRZYMAŁY KARTONIK</t>
         </is>
@@ -22370,35 +23111,40 @@
       </c>
       <c r="V149" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/2460_1.jpg</t>
+        </is>
+      </c>
+      <c r="W149" s="2" t="inlineStr">
+        <is>
           <t>/products/2460_1.jpg</t>
         </is>
       </c>
-      <c r="W149" s="2" t="inlineStr">
+      <c r="X149" s="2" t="inlineStr">
         <is>
           <t>/products/2460_1.jpg</t>
         </is>
       </c>
-      <c r="X149" s="2" t="inlineStr">
+      <c r="Y149" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2022/11/2460_1.jpg</t>
         </is>
       </c>
-      <c r="Y149" s="2" t="inlineStr">
+      <c r="Z149" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary przeciwsłoneczne z filtrem polaryzacyjnym - G 55032</t>
         </is>
       </c>
-      <c r="Z149" s="2" t="inlineStr">
+      <c r="AA149" s="2" t="inlineStr">
         <is>
           <t>goya-g-55032-br-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym</t>
         </is>
       </c>
-      <c r="AA149" s="2" t="inlineStr">
+      <c r="AB149" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-g-55032-br-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym</t>
         </is>
       </c>
-      <c r="AB149" s="3" t="inlineStr">
+      <c r="AC149" s="3" t="inlineStr">
         <is>
           <t>OKULARY PRZECIWSŁONECZNE DLA KIEROWCÓW GOYA Z FILTREM POLARYZACYJNYM I UV400 Zauszniki oprawek wykonane z aluminium - co sprawia, że okulary są bardzo lekkie i wytrzymałe. Soczewki okularów GOYA o grubości 1,1 wyposażone są w filtr polaryzacyjny oraz filtr ochronny UV-400 (UV-A, UV-B, UV-C) ZAUSZNIKI POŁĄCZONE Z OPRAWKĄ SYSTEMEM FLEX: FLEX - elastyczne połączenie zausznika z frontem oprawy. Zwiększony zakres odchylenia zausznika do ponad 110° gwarantuje wygodę noszenia i ułatwia zakładanie oraz zdejmowanie okularów. OKULARY POSIADAJĄ CERTYFIKAT CE. Produkt odpowiada Wytycznej Europejskiej 89/686/EWG zgodnie z normą PN-EN ISO 12312-1:2014-02/A1:2016-01. Każda para okularów posiada oryginalne oznaczenia znajdujące się na wewnętrznej stronie zauszników ; logo producenta, numer modelu, kategoria filtra oraz oznaczenie CE. O POLARYZACJI: Soczewki polaryzacyjne neutralizują oślepiające refleksy, powstające wówczas gdy światło odbija się od mokrej drogi, powierzchni wody lub śniegu. Eliminacja światła odbitego zwiększ kontrast widzenia i pozwala na</t>
         </is>
@@ -22488,35 +23234,40 @@
       </c>
       <c r="V150" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/GOYA-CP8802-S-A.jpg</t>
+        </is>
+      </c>
+      <c r="W150" s="2" t="inlineStr">
+        <is>
           <t>/products/GOYA-CP8802-S-A.jpg</t>
         </is>
       </c>
-      <c r="W150" s="2" t="inlineStr">
+      <c r="X150" s="2" t="inlineStr">
         <is>
           <t>/products/GOYA-CP8802-S-A.jpg; /products/3425_7-e1681287007440.jpg</t>
         </is>
       </c>
-      <c r="X150" s="2" t="inlineStr">
+      <c r="Y150" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2023/04/GOYA-CP8802-S-A.jpg</t>
         </is>
       </c>
-      <c r="Y150" s="2" t="inlineStr">
+      <c r="Z150" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary przeciwsłoneczne z filtrem polaryzacyjnym - GOYA CP 8802</t>
         </is>
       </c>
-      <c r="Z150" s="2" t="inlineStr">
+      <c r="AA150" s="2" t="inlineStr">
         <is>
           <t>goya-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym-goya-cp-8802</t>
         </is>
       </c>
-      <c r="AA150" s="2" t="inlineStr">
+      <c r="AB150" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym-goya-cp-8802</t>
         </is>
       </c>
-      <c r="AB150" s="3" t="inlineStr">
+      <c r="AC150" s="3" t="inlineStr">
         <is>
           <t>OKULARY PRZECIWSŁONECZNE DLA KIEROWCÓW GOYA Z FILTREM POLARYZACYJNYM I UV400 Soczewki okularów GOYA o grubości 1,1 wyposażone są w filtr polaryzacyjny oraz filtr ochronny UV-400 (UV-A, UV-B, UV-C) OKULARY POSIADAJĄ CERTYFIKAT CE. Produkt odpowiada Wytycznej Europejskiej 89/686/EWG zgodnie z normą PN-EN ISO 12312-1:2014-02/A1:2016-01. Każda para okularów posiada oryginalne oznaczenia znajdujące się na wewnętrznej stronie zauszników ; logo producenta, numer modelu, kategoria filtra oraz oznaczenie CE. O POLARYZACJI: Soczewki polaryzacyjne neutralizują oślepiające refleksy, powstające wówczas gdy światło odbija się od mokrej drogi, powierzchni wody lub śniegu. Eliminacja światła odbitego zwiększ kontrast widzenia i pozwala na bardziej komfortowe widzenie. Dlatego okulary z filtrem polaryzacyjnym to idealne rozwiązanie do wszelkiego rodzaju aktywności na świeżym powietrzu, pozwalające pełniej korzystać z życia. ZALETY: Eliminują oślepiające odblaski, zmniejszając zmęczenie oczu Chronią przed szkodliwym promieniowaniem UV Zwięk</t>
         </is>
@@ -22606,35 +23357,40 @@
       </c>
       <c r="V151" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/3185_1.jpg</t>
+        </is>
+      </c>
+      <c r="W151" s="2" t="inlineStr">
+        <is>
           <t>/products/3185_1.jpg</t>
         </is>
       </c>
-      <c r="W151" s="2" t="inlineStr">
+      <c r="X151" s="2" t="inlineStr">
         <is>
           <t>/products/3185_1.jpg; /products/3186_6.jpg</t>
         </is>
       </c>
-      <c r="X151" s="2" t="inlineStr">
+      <c r="Y151" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2023/01/3185_1.jpg</t>
         </is>
       </c>
-      <c r="Y151" s="2" t="inlineStr">
+      <c r="Z151" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary przeciwsłoneczne z filtrem polaryzacyjnym - G 151</t>
         </is>
       </c>
-      <c r="Z151" s="2" t="inlineStr">
+      <c r="AA151" s="2" t="inlineStr">
         <is>
           <t>goya-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym-g-151</t>
         </is>
       </c>
-      <c r="AA151" s="2" t="inlineStr">
+      <c r="AB151" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym-g-151</t>
         </is>
       </c>
-      <c r="AB151" s="3" t="inlineStr">
+      <c r="AC151" s="3" t="inlineStr">
         <is>
           <t>OKULARY PRZECIWSŁONECZNE DLA KIEROWCÓW GOYA Z FILTREM POLARYZACYJNYM I UV400 Oprawka wykonana w technologii - wycinania z płyty. Ręcznie obrabiana. Soczewki okularów GOYA o grubości 1,1 wyposażone są w filtr polaryzacyjny oraz filtr ochronny UV-400 (UV-A, UV-B, UV-C) OKULARY POSIADAJĄ CERTYFIKAT CE. Produkt odpowiada Wytycznej Europejskiej 89/686/EWG zgodnie z normą PN-EN ISO 12312-1:2014-02/A1:2016-01. Każda para okularów posiada oryginalne oznaczenia znajdujące się na wewnętrznej stronie zauszników ; logo producenta, numer modelu, kategoria filtra oraz oznaczenie CE. O POLARYZACJI: Soczewki polaryzacyjne neutralizują oślepiające refleksy, powstające wówczas gdy światło odbija się od mokrej drogi, powierzchni wody lub śniegu. Eliminacja światła odbitego zwiększ kontrast widzenia i pozwala na bardziej komfortowe widzenie. Dlatego okulary z filtrem polaryzacyjnym to idealne rozwiązanie do wszelkiego rodzaju aktywności na świeżym powietrzu, pozwalające pełniej korzystać z życia. ZALETY: Eliminują oślepiające odblaski, zmniejszaj</t>
         </is>
@@ -22724,35 +23480,40 @@
       </c>
       <c r="V152" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/975_6.jpg</t>
+        </is>
+      </c>
+      <c r="W152" s="2" t="inlineStr">
+        <is>
           <t>/products/975_6.jpg</t>
         </is>
       </c>
-      <c r="W152" s="2" t="inlineStr">
+      <c r="X152" s="2" t="inlineStr">
         <is>
           <t>/products/975_6.jpg</t>
         </is>
       </c>
-      <c r="X152" s="2" t="inlineStr">
+      <c r="Y152" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2022/11/975_6.jpg</t>
         </is>
       </c>
-      <c r="Y152" s="2" t="inlineStr">
+      <c r="Z152" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary przeciwsłoneczne z filtrem polaryzacyjnym - G1921</t>
         </is>
       </c>
-      <c r="Z152" s="2" t="inlineStr">
+      <c r="AA152" s="2" t="inlineStr">
         <is>
           <t>goya-g1921-c2-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym</t>
         </is>
       </c>
-      <c r="AA152" s="2" t="inlineStr">
+      <c r="AB152" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-g1921-c2-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym</t>
         </is>
       </c>
-      <c r="AB152" s="3" t="inlineStr">
+      <c r="AC152" s="3" t="inlineStr">
         <is>
           <t>OKULARY PRZECIWSŁONECZNE DLA KIEROWCÓW GOYA Z FILTREM POLARYZACYJNYM I UV400 Soczewki okularów GOYA o grubości 1,1 wyposażone są w filtr polaryzacyjny oraz filtr ochronny UV-400 (UV-A, UV-B, UV-C) OPRAWKA WYKONANA W TECHNOLOGII TR-90 Wysokiej jakości odmiana nylonu, wyjątkowo odporna na rozciąganie i wyginanie. Materiał wytrzymały na uderzenia, elastyczny, przyjemny w dotyku, o właściwościach antyalergicznych. Okulary wykonane z TR-90 są lekkie, wytrzymałe i wygodne w użytkowaniu. ZAUSZNIKI POŁĄCZONE Z OPRAWKĄ SYSTEMEM FLEX: FLEX - elastyczne połączenie zausznika z frontem oprawy. Zwiększony zakres odchylenia zausznika do ponad 110° gwarantuje wygodę noszenia i ułatwia zakładanie oraz zdejmowanie okularów. OKULARY POSIADAJĄ CERTYFIKAT CE. Produkt odpowiada Wytycznej Europejskiej 89/686/EWG zgodnie z normą PN-EN ISO 12312-1:2014-02/A1:2016-01. Każda para okularów posiada oryginalne oznaczenia znajdujące się na wewnętrznej stronie zauszników ; logo producenta, numer modelu, kategoria filtra oraz oznaczenie CE. O POLARYZACJI: Soczewki pol</t>
         </is>
@@ -22842,35 +23603,40 @@
       </c>
       <c r="V153" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/GOYA-A0710-CZ-A.jpg</t>
+        </is>
+      </c>
+      <c r="W153" s="2" t="inlineStr">
+        <is>
           <t>/products/GOYA-A0710-CZ-A.jpg</t>
         </is>
       </c>
-      <c r="W153" s="2" t="inlineStr">
+      <c r="X153" s="2" t="inlineStr">
         <is>
           <t>/products/GOYA-A0710-CZ-A.jpg; /products/GOYA_A0710_gr_mod2.jpg</t>
         </is>
       </c>
-      <c r="X153" s="2" t="inlineStr">
+      <c r="Y153" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2023/04/GOYA-A0710-CZ-A.jpg</t>
         </is>
       </c>
-      <c r="Y153" s="2" t="inlineStr">
+      <c r="Z153" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary przeciwsłoneczne z filtrem polaryzacyjnym - GOYA A 0710</t>
         </is>
       </c>
-      <c r="Z153" s="2" t="inlineStr">
+      <c r="AA153" s="2" t="inlineStr">
         <is>
           <t>goya-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym-goya-a-0710</t>
         </is>
       </c>
-      <c r="AA153" s="2" t="inlineStr">
+      <c r="AB153" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym-goya-a-0710</t>
         </is>
       </c>
-      <c r="AB153" s="3" t="inlineStr">
+      <c r="AC153" s="3" t="inlineStr">
         <is>
           <t>OKULARY PRZECIWSŁONECZNE GOYA Z FILTREM POLARYZACYJNYM I UV400 Soczewki okularów GOYA o grubości 1,1 wyposażone są w filtr polaryzacyjny oraz filtr ochronny UV-400 (UV-A, UV-B, UV-C) OKULARY POSIADAJĄ CERTYFIKAT CE. Produkt odpowiada Wytycznej Europejskiej 89/686/EWG zgodnie z normą PN-EN ISO 12312-1:2014-02/A1:2016-01. Każda para okularów posiada oryginalne oznaczenia znajdujące się na wewnętrznej stronie zauszników ; logo producenta, numer modelu, kategoria filtra oraz oznaczenie CE. O POLARYZACJI: Soczewki polaryzacyjne neutralizują oślepiające refleksy, powstające wówczas gdy światło odbija się od mokrej drogi, powierzchni wody lub śniegu. Eliminacja światła odbitego zwiększ kontrast widzenia i pozwala na bardziej komfortowe widzenie. Dlatego okulary z filtrem polaryzacyjnym to idealne rozwiązanie do wszelkiego rodzaju aktywności na świeżym powietrzu, pozwalające pełniej korzystać z życia. ZALETY: Eliminują oślepiające odblaski, zmniejszając zmęczenie oczu Chronią przed szkodliwym promieniowaniem UV Zwiększają kontras</t>
         </is>
@@ -22962,35 +23728,40 @@
       </c>
       <c r="V154" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/G_55051_CZ_A.jpg</t>
+        </is>
+      </c>
+      <c r="W154" s="2" t="inlineStr">
+        <is>
           <t>/products/G_55051_CZ_A.jpg</t>
         </is>
       </c>
-      <c r="W154" s="2" t="inlineStr">
+      <c r="X154" s="2" t="inlineStr">
         <is>
           <t>/products/G_55051_CZ_A.jpg; /products/G_55051_CZ_MODkw.jpg; /products/G_55051_CZ_G.jpg; /products/G_55051_CZ_B.jpg; /products/G_55051_CZ_F.jpg; /products/G_55051_CZ_S.jpg; /products/G_55051_CZ_F1.jpg; /products/G_55051_CZ_T.jpg</t>
         </is>
       </c>
-      <c r="X154" s="2" t="inlineStr">
+      <c r="Y154" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2025/02/G_55051_CZ_A.jpg</t>
         </is>
       </c>
-      <c r="Y154" s="2" t="inlineStr">
+      <c r="Z154" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary przeciwsłoneczne z filtrem polaryzacyjnym - G 55051 CZ</t>
         </is>
       </c>
-      <c r="Z154" s="2" t="inlineStr">
+      <c r="AA154" s="2" t="inlineStr">
         <is>
           <t>goya-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym-g-55051-cz</t>
         </is>
       </c>
-      <c r="AA154" s="2" t="inlineStr">
+      <c r="AB154" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym-g-55051-cz</t>
         </is>
       </c>
-      <c r="AB154" s="3" t="inlineStr">
+      <c r="AC154" s="3" t="inlineStr">
         <is>
           <t>OKULARY PRZECIWSŁONECZNE DLA KIEROWCÓW GOYA Z FILTREM POLARYZACYJNYM I UV400 Oprawki wykonane w całości z aluminium - co sprawia, że okulary są bardzo lekkie i wytrzymałe. Soczewki okularów GOYA o grubości 1,1 wyposażone są w filtr polaryzacyjny oraz filtr ochronny UV-400 (UV-A, UV-B, UV-C) ZAUSZNIKI POŁĄCZONE Z OPRAWKĄ SYSTEMEM FLEX: FLEX - elastyczne połączenie zausznika z frontem oprawy. Zwiększony zakres odchylenia zausznika do ponad 110° gwarantuje wygodę noszenia i ułatwia zakładanie oraz zdejmowanie okularów. OKULARY POSIADAJĄ CERTYFIKAT CE. Produkt odpowiada Wytycznej Europejskiej 89/686/EWG zgodnie z normą PN-EN ISO 12312-1:2014-02/A1:2016-01. Każda para okularów posiada oryginalne oznaczenia znajdujące się na wewnętrznej stronie zauszników ; logo producenta, numer modelu, kategoria filtra oraz oznaczenie CE. O POLARYZACJI: Soczewki polaryzacyjne neutralizują oślepiające refleksy, powstające wówczas gdy światło odbija się od mokrej drogi, powierzchni wody lub śniegu. Eliminacja światła odbitego zwiększ kontrast widzenia i pozwala</t>
         </is>
@@ -23078,35 +23849,40 @@
       </c>
       <c r="V155" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/575_6.jpg</t>
+        </is>
+      </c>
+      <c r="W155" s="2" t="inlineStr">
+        <is>
           <t>/products/575_6.jpg</t>
         </is>
       </c>
-      <c r="W155" s="2" t="inlineStr">
+      <c r="X155" s="2" t="inlineStr">
         <is>
           <t>/products/575_6.jpg; /products/575_5.jpg</t>
         </is>
       </c>
-      <c r="X155" s="2" t="inlineStr">
+      <c r="Y155" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2022/11/575_6.jpg</t>
         </is>
       </c>
-      <c r="Y155" s="2" t="inlineStr">
+      <c r="Z155" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary korekcyjne - MA 3021 C2</t>
         </is>
       </c>
-      <c r="Z155" s="2" t="inlineStr">
+      <c r="AA155" s="2" t="inlineStr">
         <is>
           <t>goya-okulary-korekcyjne-ma-3021-c2-2</t>
         </is>
       </c>
-      <c r="AA155" s="2" t="inlineStr">
+      <c r="AB155" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-okulary-korekcyjne-ma-3021-c2-2</t>
         </is>
       </c>
-      <c r="AB155" s="3" t="inlineStr">
+      <c r="AC155" s="3" t="inlineStr">
         <is>
           <t>OKULARY KOREKCYJNE GOYA MA 3021 C2 Produkt nowy ! - posiadają oryginalne zabezpieczenia, metkę oraz instrukcję użytkowania, dodatkowo w zestawie twarde etui na zawias sprężynowy Marki GOYA oraz miękką ściereczkę czyszczącą. NASZE PRODUKTY SĄ BARDZO DOBRZE ZABEZPIECZONE W FOLIĘ TRANSPORTOWĄ I ZAPAKOWANE W WYTRZYMAŁY KARTONIK</t>
         </is>
@@ -23192,35 +23968,40 @@
       </c>
       <c r="V156" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/687_4.jpg</t>
+        </is>
+      </c>
+      <c r="W156" s="2" t="inlineStr">
+        <is>
           <t>/products/687_4.jpg</t>
         </is>
       </c>
-      <c r="W156" s="2" t="inlineStr">
+      <c r="X156" s="2" t="inlineStr">
         <is>
           <t>/products/687_4.jpg</t>
         </is>
       </c>
-      <c r="X156" s="2" t="inlineStr">
+      <c r="Y156" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2022/11/687_4.jpg</t>
         </is>
       </c>
-      <c r="Y156" s="2" t="inlineStr">
+      <c r="Z156" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary korekcyjne - G 96301</t>
         </is>
       </c>
-      <c r="Z156" s="2" t="inlineStr">
+      <c r="AA156" s="2" t="inlineStr">
         <is>
           <t>goya-okulary-korekcyjne-g-96301-c1</t>
         </is>
       </c>
-      <c r="AA156" s="2" t="inlineStr">
+      <c r="AB156" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-okulary-korekcyjne-g-96301-c1</t>
         </is>
       </c>
-      <c r="AB156" s="3" t="inlineStr">
+      <c r="AC156" s="3" t="inlineStr">
         <is>
           <t>OKULARY KOREKCYJNE GOYA G 96301 Produkt nowy - posiadają oryginalne zabezpieczenia, metkę oraz instrukcję użytkowania, dodatkowo w zestawie twarde etui na zawias sprężynowy Marki GOYA oraz miękką ściereczkę czyszczącą. NASZE PRODUKTY WYSYŁAMY BARDZO DOBRZE ZABEZPIECZONE W FOLIĘ TRANSPORTOWĄ I ZAPAKOWANE W WYTRZYMAŁY KARTONIK</t>
         </is>
@@ -23312,35 +24093,40 @@
       </c>
       <c r="V157" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/3180_1.jpg</t>
+        </is>
+      </c>
+      <c r="W157" s="2" t="inlineStr">
+        <is>
           <t>/products/3180_1.jpg</t>
         </is>
       </c>
-      <c r="W157" s="2" t="inlineStr">
+      <c r="X157" s="2" t="inlineStr">
         <is>
           <t>/products/3180_1.jpg; /products/3180_6.jpg; /products/3180_5.jpg; /products/3180_4.jpg; /products/3180_3.jpg; /products/3180_2.jpg</t>
         </is>
       </c>
-      <c r="X157" s="2" t="inlineStr">
+      <c r="Y157" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2023/01/3180_1.jpg</t>
         </is>
       </c>
-      <c r="Y157" s="2" t="inlineStr">
+      <c r="Z157" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary przeciwsłoneczne z filtrem polaryzacyjnym - G 157 BR</t>
         </is>
       </c>
-      <c r="Z157" s="2" t="inlineStr">
+      <c r="AA157" s="2" t="inlineStr">
         <is>
           <t>goya-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym-g-157-br</t>
         </is>
       </c>
-      <c r="AA157" s="2" t="inlineStr">
+      <c r="AB157" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym-g-157-br</t>
         </is>
       </c>
-      <c r="AB157" s="3" t="inlineStr">
+      <c r="AC157" s="3" t="inlineStr">
         <is>
           <t>OKULARY PRZECIWSŁONECZNE DLA KIEROWCÓW GOYA Z FILTREM POLARYZACYJNYM I UV400 Oprawka wykonana z monelu, zauszniki aluminiowe. Soczewki okularów GOYA o grubości 1,1 wyposażone są w filtr polaryzacyjny oraz filtr ochronny UV-400 (UV-A, UV-B, UV-C) ZAUSZNIKI POŁĄCZONE Z OPRAWKĄ SYSTEMEM FLEX: FLEX - elastyczne połączenie zausznika z frontem oprawy. Zwiększony zakres odchylenia zausznika do ponad 110° gwarantuje wygodę noszenia i ułatwia zakładanie oraz zdejmowanie okularów. OKULARY POSIADAJĄ CERTYFIKAT CE. Produkt odpowiada Wytycznej Europejskiej 89/686/EWG zgodnie z normą PN-EN ISO 12312-1:2014-02/A1:2016-01. Każda para okularów posiada oryginalne oznaczenia znajdujące się na wewnętrznej stronie zauszników ; logo producenta, numer modelu, kategoria filtra oraz oznaczenie CE. O POLARYZACJI: Soczewki polaryzacyjne neutralizują oślepiające refleksy, powstające wówczas gdy światło odbija się od mokrej drogi, powierzchni wody lub śniegu. Eliminacja światła odbitego zwiększ kontrast widzenia i pozwala na bardziej komfortowe widzenie. Dlatego okulary</t>
         </is>
@@ -23426,35 +24212,40 @@
       </c>
       <c r="V158" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/580_4.jpg</t>
+        </is>
+      </c>
+      <c r="W158" s="2" t="inlineStr">
+        <is>
           <t>/products/580_4.jpg</t>
         </is>
       </c>
-      <c r="W158" s="2" t="inlineStr">
+      <c r="X158" s="2" t="inlineStr">
         <is>
           <t>/products/580_4.jpg</t>
         </is>
       </c>
-      <c r="X158" s="2" t="inlineStr">
+      <c r="Y158" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2022/11/580_4.jpg</t>
         </is>
       </c>
-      <c r="Y158" s="2" t="inlineStr">
+      <c r="Z158" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary korekcyjne - G 942115</t>
         </is>
       </c>
-      <c r="Z158" s="2" t="inlineStr">
+      <c r="AA158" s="2" t="inlineStr">
         <is>
           <t>goya-okulary-korekcyjne-g-942115-c1</t>
         </is>
       </c>
-      <c r="AA158" s="2" t="inlineStr">
+      <c r="AB158" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-okulary-korekcyjne-g-942115-c1</t>
         </is>
       </c>
-      <c r="AB158" s="3" t="inlineStr">
+      <c r="AC158" s="3" t="inlineStr">
         <is>
           <t>OKULARY KOREKCYJNE GOYA G 942115 Produkt nowy - posiadają oryginalne zabezpieczenia, metkę oraz instrukcję użytkowania, dodatkowo w zestawie twarde etui na zawias sprężynowy Marki GOYA oraz miękką ściereczkę czyszczącą. NASZE PRODUKTY WYSYŁAMY BARDZO DOBRZE ZABEZPIECZONE W FOLIĘ TRANSPORTOWĄ I ZAPAKOWANE W WYTRZYMAŁY KARTONIK</t>
         </is>
@@ -23544,35 +24335,40 @@
       </c>
       <c r="V159" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/3156_6.jpg</t>
+        </is>
+      </c>
+      <c r="W159" s="2" t="inlineStr">
+        <is>
           <t>/products/3156_6.jpg</t>
         </is>
       </c>
-      <c r="W159" s="2" t="inlineStr">
+      <c r="X159" s="2" t="inlineStr">
         <is>
           <t>/products/3156_6.jpg; /products/3156_1.jpg</t>
         </is>
       </c>
-      <c r="X159" s="2" t="inlineStr">
+      <c r="Y159" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2022/11/3156_6.jpg</t>
         </is>
       </c>
-      <c r="Y159" s="2" t="inlineStr">
+      <c r="Z159" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary przeciwsłoneczne z filtrem polaryzacyjnym - G 176</t>
         </is>
       </c>
-      <c r="Z159" s="2" t="inlineStr">
+      <c r="AA159" s="2" t="inlineStr">
         <is>
           <t>goya-g-176-s-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym</t>
         </is>
       </c>
-      <c r="AA159" s="2" t="inlineStr">
+      <c r="AB159" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-g-176-s-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym</t>
         </is>
       </c>
-      <c r="AB159" s="3" t="inlineStr">
+      <c r="AC159" s="3" t="inlineStr">
         <is>
           <t>OKULARY PRZECIWSŁONECZNE DLA KIEROWCÓW GOYA Z FILTREM POLARYZACYJNYM I UV400 Soczewki okularów GOYA o grubości 1,1 wyposażone są w filtr polaryzacyjny oraz filtr ochronny UV-400 (UV-A, UV-B, UV-C) OPRAWKA WYKONANA W TECHNOLOGII TR-90 Wysokiej jakości odmiana nylonu, wyjątkowo odporna na rozciąganie i wyginanie. Materiał wytrzymały na uderzenia, elastyczny, przyjemny w dotyku, o właściwościach antyalergicznych. Okulary wykonane z TR-90 są lekkie, wytrzymałe i wygodne w użytkowaniu. OKULARY POSIADAJĄ CERTYFIKAT CE. Produkt odpowiada Wytycznej Europejskiej 89/686/EWG zgodnie z normą PN-EN ISO 12312-1:2014-02/A1:2016-01. Każda para okularów posiada oryginalne oznaczenia znajdujące się na wewnętrznej stronie zauszników ; logo producenta, numer modelu, kategoria filtra oraz oznaczenie CE. O POLARYZACJI: Soczewki polaryzacyjne neutralizują oślepiające refleksy, powstające wówczas gdy światło odbija się od mokrej drogi, powierzchni wody lub śniegu. Eliminacja światła odbitego zwiększ kontrast widzenia i pozwala na bardziej komfortowe widzenie. Dlatego o</t>
         </is>
@@ -23660,35 +24456,40 @@
       </c>
       <c r="V160" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/659_4.jpg</t>
+        </is>
+      </c>
+      <c r="W160" s="2" t="inlineStr">
+        <is>
           <t>/products/659_4.jpg</t>
         </is>
       </c>
-      <c r="W160" s="2" t="inlineStr">
+      <c r="X160" s="2" t="inlineStr">
         <is>
           <t>/products/659_4.jpg; /products/659_1.jpg; /products/659_3.jpg; /products/659_2.jpg</t>
         </is>
       </c>
-      <c r="X160" s="2" t="inlineStr">
+      <c r="Y160" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2022/11/659_4.jpg</t>
         </is>
       </c>
-      <c r="Y160" s="2" t="inlineStr">
+      <c r="Z160" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary korekcyjne - SD 1368 C8</t>
         </is>
       </c>
-      <c r="Z160" s="2" t="inlineStr">
+      <c r="AA160" s="2" t="inlineStr">
         <is>
           <t>goya-okulary-korekcyjne-sd-1368-c8</t>
         </is>
       </c>
-      <c r="AA160" s="2" t="inlineStr">
+      <c r="AB160" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-okulary-korekcyjne-sd-1368-c8</t>
         </is>
       </c>
-      <c r="AB160" s="3" t="inlineStr">
+      <c r="AC160" s="3" t="inlineStr">
         <is>
           <t>OKULARY KOREKCYJNE GOYA SD 1368 C8 Produkt nowy - posiadają oryginalne zabezpieczenia, metkę oraz instrukcję użytkowania, dodatkowo w zestawie twarde etui na zawias sprężynowy Marki GOYA oraz miękką ściereczkę czyszczącą. NASZE PRODUKTY WYSYŁAMY BARDZO DOBRZE ZABEZPIECZONE W FOLIĘ TRANSPORTOWĄ I ZAPAKOWANE W WYTRZYMAŁY KARTONIK</t>
         </is>
@@ -23776,35 +24577,40 @@
       </c>
       <c r="V161" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/575_6.jpg</t>
+        </is>
+      </c>
+      <c r="W161" s="2" t="inlineStr">
+        <is>
           <t>/products/575_6.jpg</t>
         </is>
       </c>
-      <c r="W161" s="2" t="inlineStr">
+      <c r="X161" s="2" t="inlineStr">
         <is>
           <t>/products/575_6.jpg; /products/575_5.jpg</t>
         </is>
       </c>
-      <c r="X161" s="2" t="inlineStr">
+      <c r="Y161" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2022/11/575_6.jpg</t>
         </is>
       </c>
-      <c r="Y161" s="2" t="inlineStr">
+      <c r="Z161" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary korekcyjne G 2635 C3</t>
         </is>
       </c>
-      <c r="Z161" s="2" t="inlineStr">
+      <c r="AA161" s="2" t="inlineStr">
         <is>
           <t>goya-okulary-korekcyjne-g-2635-c3</t>
         </is>
       </c>
-      <c r="AA161" s="2" t="inlineStr">
+      <c r="AB161" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-okulary-korekcyjne-g-2635-c3</t>
         </is>
       </c>
-      <c r="AB161" s="3" t="inlineStr">
+      <c r="AC161" s="3" t="inlineStr">
         <is>
           <t>OKULARY KOREKCYJNE GOYA G 2635 C3 Produkt nowy ! - posiadają oryginalne zabezpieczenia, metkę oraz instrukcję użytkowania, dodatkowo w zestawie twarde etui na zawias sprężynowy Marki GOYA oraz miękką ściereczkę czyszczącą. NASZE PRODUKTY SĄ BARDZO DOBRZE ZABEZPIECZONE W FOLIĘ TRANSPORTOWĄ I ZAPAKOWANE W WYTRZYMAŁY KARTONIK</t>
         </is>
@@ -23896,35 +24702,40 @@
       </c>
       <c r="V162" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/977_6.jpg</t>
+        </is>
+      </c>
+      <c r="W162" s="2" t="inlineStr">
+        <is>
           <t>/products/977_6.jpg</t>
         </is>
       </c>
-      <c r="W162" s="2" t="inlineStr">
+      <c r="X162" s="2" t="inlineStr">
         <is>
           <t>/products/977_6.jpg; /products/977_3.jpg; /products/977_7.jpg; /products/977_2.jpg; /products/977_1.jpg</t>
         </is>
       </c>
-      <c r="X162" s="2" t="inlineStr">
+      <c r="Y162" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2022/11/977_6.jpg</t>
         </is>
       </c>
-      <c r="Y162" s="2" t="inlineStr">
+      <c r="Z162" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary przeciwsłoneczne z filtrem polaryzacyjnym - G1905 C1</t>
         </is>
       </c>
-      <c r="Z162" s="2" t="inlineStr">
+      <c r="AA162" s="2" t="inlineStr">
         <is>
           <t>goya-g1905-c1-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym</t>
         </is>
       </c>
-      <c r="AA162" s="2" t="inlineStr">
+      <c r="AB162" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-g1905-c1-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym</t>
         </is>
       </c>
-      <c r="AB162" s="3" t="inlineStr">
+      <c r="AC162" s="3" t="inlineStr">
         <is>
           <t>OKULARY PRZECIWSŁONECZNE DLA KIEROWCÓW GOYA Z FILTREM POLARYZACYJNYM I UV400 Soczewki okularów GOYA o grubości 1,1 wyposażone są w filtr polaryzacyjny oraz filtr ochronny UV-400 (UV-A, UV-B, UV-C) OPRAWKA WYKONANA W TECHNOLOGII TR-90 Wysokiej jakości odmiana nylonu, wyjątkowo odporna na rozciąganie i wyginanie. Materiał wytrzymały na uderzenia, elastyczny, przyjemny w dotyku, o właściwościach antyalergicznych. Okulary wykonane z TR-90 są lekkie, wytrzymałe i wygodne w użytkowaniu. ZAUSZNIKI POŁĄCZONE Z OPRAWKĄ SYSTEMEM FLEX: FLEX - elastyczne połączenie zausznika z frontem oprawy. Zwiększony zakres odchylenia zausznika do ponad 110° gwarantuje wygodę noszenia i ułatwia zakładanie oraz zdejmowanie okularów. OKULARY POSIADAJĄ CERTYFIKAT CE. Produkt odpowiada Wytycznej Europejskiej 89/686/EWG zgodnie z normą PN-EN ISO 12312-1:2014-02/A1:2016-01. Każda para okularów posiada oryginalne oznaczenia znajdujące się na wewnętrznej stronie zauszników ; logo producenta, numer modelu, kategoria filtra oraz oznaczenie CE. O POLARYZACJI: Soczewki pol</t>
         </is>
@@ -24014,35 +24825,40 @@
       </c>
       <c r="V163" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/1877_2.jpg</t>
+        </is>
+      </c>
+      <c r="W163" s="2" t="inlineStr">
+        <is>
           <t>/products/1877_2.jpg</t>
         </is>
       </c>
-      <c r="W163" s="2" t="inlineStr">
+      <c r="X163" s="2" t="inlineStr">
         <is>
           <t>/products/1877_2.jpg; /products/1876_7.jpeg</t>
         </is>
       </c>
-      <c r="X163" s="2" t="inlineStr">
+      <c r="Y163" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2023/01/1877_2.jpg</t>
         </is>
       </c>
-      <c r="Y163" s="2" t="inlineStr">
+      <c r="Z163" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary przeciwsłoneczne z filtrem polaryzacyjnym - G 210</t>
         </is>
       </c>
-      <c r="Z163" s="2" t="inlineStr">
+      <c r="AA163" s="2" t="inlineStr">
         <is>
           <t>goya-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym-g-210</t>
         </is>
       </c>
-      <c r="AA163" s="2" t="inlineStr">
+      <c r="AB163" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym-g-210</t>
         </is>
       </c>
-      <c r="AB163" s="3" t="inlineStr">
+      <c r="AC163" s="3" t="inlineStr">
         <is>
           <t>OKULARY PRZECIWSŁONECZNE DLA KIEROWCÓW GOYA Z FILTREM POLARYZACYJNYM I UV400 Soczewki okularów GOYA o grubości 1,1 wyposażone są w filtr polaryzacyjny oraz filtr ochronny UV-400 (UV-A, UV-B, UV-C) OKULARY POSIADAJĄ CERTYFIKAT CE. Produkt odpowiada Wytycznej Europejskiej 89/686/EWG zgodnie z normą PN-EN ISO 12312-1:2014-02/A1:2016-01. Każda para okularów posiada oryginalne oznaczenia znajdujące się na wewnętrznej stronie zauszników ; logo producenta, numer modelu, kategoria filtra oraz oznaczenie CE. O POLARYZACJI: Soczewki polaryzacyjne neutralizują oślepiające refleksy, powstające wówczas gdy światło odbija się od mokrej drogi, powierzchni wody lub śniegu. Eliminacja światła odbitego zwiększ kontrast widzenia i pozwala na bardziej komfortowe widzenie. Dlatego okulary z filtrem polaryzacyjnym to idealne rozwiązanie do wszelkiego rodzaju aktywności na świeżym powietrzu, pozwalające pełniej korzystać z życia. ZALETY: Eliminują oślepiające odblaski, zmniejszając zmęczenie oczu Chronią przed szkodliwym promieniowaniem UV Zwiększ</t>
         </is>
@@ -24128,35 +24944,40 @@
       </c>
       <c r="V164" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/631_4.jpg</t>
+        </is>
+      </c>
+      <c r="W164" s="2" t="inlineStr">
+        <is>
           <t>/products/631_4.jpg</t>
         </is>
       </c>
-      <c r="W164" s="2" t="inlineStr">
+      <c r="X164" s="2" t="inlineStr">
         <is>
           <t>/products/631_4.jpg</t>
         </is>
       </c>
-      <c r="X164" s="2" t="inlineStr">
+      <c r="Y164" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2022/11/631_4.jpg</t>
         </is>
       </c>
-      <c r="Y164" s="2" t="inlineStr">
+      <c r="Z164" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary korekcyjne - DC 8039</t>
         </is>
       </c>
-      <c r="Z164" s="2" t="inlineStr">
+      <c r="AA164" s="2" t="inlineStr">
         <is>
           <t>goya-okulary-korekcyjne-dc-8039-c1</t>
         </is>
       </c>
-      <c r="AA164" s="2" t="inlineStr">
+      <c r="AB164" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-okulary-korekcyjne-dc-8039-c1</t>
         </is>
       </c>
-      <c r="AB164" s="3" t="inlineStr">
+      <c r="AC164" s="3" t="inlineStr">
         <is>
           <t>OKULARY KOREKCYJNE GOYA DC 8039 Produkt nowy - posiadają oryginalne zabezpieczenia, metkę oraz instrukcję użytkowania, dodatkowo w zestawie twarde etui na zawias sprężynowy Marki GOYA oraz miękką ściereczkę czyszczącą. NASZE PRODUKTY WYSYŁAMY BARDZO DOBRZE ZABEZPIECZONE W FOLIĘ TRANSPORTOWĄ I ZAPAKOWANE W WYTRZYMAŁY KARTONIK</t>
         </is>
@@ -24246,35 +25067,40 @@
       </c>
       <c r="V165" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/3127_1.jpg</t>
+        </is>
+      </c>
+      <c r="W165" s="2" t="inlineStr">
+        <is>
           <t>/products/3127_1.jpg</t>
         </is>
       </c>
-      <c r="W165" s="2" t="inlineStr">
+      <c r="X165" s="2" t="inlineStr">
         <is>
           <t>/products/3127_1.jpg</t>
         </is>
       </c>
-      <c r="X165" s="2" t="inlineStr">
+      <c r="Y165" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2022/11/3127_1.jpg</t>
         </is>
       </c>
-      <c r="Y165" s="2" t="inlineStr">
+      <c r="Z165" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary przeciwsłoneczne z filtrem polaryzacyjnym - G 195</t>
         </is>
       </c>
-      <c r="Z165" s="2" t="inlineStr">
+      <c r="AA165" s="2" t="inlineStr">
         <is>
           <t>goya-g-195-cz-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym</t>
         </is>
       </c>
-      <c r="AA165" s="2" t="inlineStr">
+      <c r="AB165" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-g-195-cz-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym</t>
         </is>
       </c>
-      <c r="AB165" s="3" t="inlineStr">
+      <c r="AC165" s="3" t="inlineStr">
         <is>
           <t>OKULARY PRZECIWSŁONECZNE DLA KIEROWCÓW GOYA Z FILTREM POLARYZACYJNYM I UV400 Soczewki okularów GOYA o grubości 1,1 wyposażone są w filtr polaryzacyjny oraz filtr ochronny UV-400 (UV-A, UV-B, UV-C) OKULARY POSIADAJĄ CERTYFIKAT CE. Produkt odpowiada Wytycznej Europejskiej 89/686/EWG zgodnie z normą PN-EN ISO 12312-1:2014-02/A1:2016-01. Każda para okularów posiada oryginalne oznaczenia znajdujące się na wewnętrznej stronie zauszników ; logo producenta, numer modelu, kategoria filtra oraz oznaczenie CE. O POLARYZACJI: Soczewki polaryzacyjne neutralizują oślepiające refleksy, powstające wówczas gdy światło odbija się od mokrej drogi, powierzchni wody lub śniegu. Eliminacja światła odbitego zwiększ kontrast widzenia i pozwala na bardziej komfortowe widzenie. Dlatego okulary z filtrem polaryzacyjnym to idealne rozwiązanie do wszelkiego rodzaju aktywności na świeżym powietrzu, pozwalające pełniej korzystać z życia. ZALETY: Eliminują oślepiające odblaski, zmniejszając zmęczenie oczu Chronią przed szkodliwym promieniowaniem UV Zwiększ</t>
         </is>
@@ -24356,35 +25182,40 @@
       </c>
       <c r="V166" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/3171_1.jpg</t>
+        </is>
+      </c>
+      <c r="W166" s="2" t="inlineStr">
+        <is>
           <t>/products/3171_1.jpg</t>
         </is>
       </c>
-      <c r="W166" s="2" t="inlineStr">
+      <c r="X166" s="2" t="inlineStr">
         <is>
           <t>/products/3171_1.jpg; /products/3172_5-1.jpg</t>
         </is>
       </c>
-      <c r="X166" s="2" t="inlineStr">
+      <c r="Y166" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2022/11/3171_1.jpg</t>
         </is>
       </c>
-      <c r="Y166" s="2" t="inlineStr">
+      <c r="Z166" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary przeciwsłoneczne z filtrem polaryzacyjnym - G 162</t>
         </is>
       </c>
-      <c r="Z166" s="2" t="inlineStr">
+      <c r="AA166" s="2" t="inlineStr">
         <is>
           <t>goya-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym-g-162-2</t>
         </is>
       </c>
-      <c r="AA166" s="2" t="inlineStr">
+      <c r="AB166" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym-g-162-2</t>
         </is>
       </c>
-      <c r="AB166" s="3" t="inlineStr">
+      <c r="AC166" s="3" t="inlineStr">
         <is>
           <t>OKULARY PRZECIWSŁONECZNE DLA KIEROWCÓW GOYA Z FILTREM POLARYZACYJNYM I UV400 Oprawka wykonana w technologii - wycinania z płyty. Ręcznie obrabiana. Soczewki okularów GOYA o grubości 1,1 wyposażone są w filtr polaryzacyjny oraz filtr ochronny UV-400 (UV-A, UV-B, UV-C) OKULARY POSIADAJĄ CERTYFIKAT CE. Produkt odpowiada Wytycznej Europejskiej 89/686/EWG zgodnie z normą PN-EN ISO 12312-1:2014-02/A1:2016-01. Każda para okularów posiada oryginalne oznaczenia znajdujące się na wewnętrznej stronie zauszników ; logo producenta, numer modelu, kategoria filtra oraz oznaczenie CE. O POLARYZACJI: Soczewki polaryzacyjne neutralizują oślepiające refleksy, powstające wówczas gdy światło odbija się od mokrej drogi, powierzchni wody lub śniegu. Eliminacja światła odbitego zwiększ kontrast widzenia i pozwala na bardziej komfortowe widzenie. Dlatego okulary z filtrem polaryzacyjnym to idealne rozwiązanie do wszelkiego rodzaju aktywności na świeżym powietrzu, pozwalające pełniej korzystać z życia. ZALETY: Eliminują oślepiające odblaski, zmniejszaj</t>
         </is>
@@ -24472,35 +25303,40 @@
       </c>
       <c r="V167" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/662_4.jpg</t>
+        </is>
+      </c>
+      <c r="W167" s="2" t="inlineStr">
+        <is>
           <t>/products/662_4.jpg</t>
         </is>
       </c>
-      <c r="W167" s="2" t="inlineStr">
+      <c r="X167" s="2" t="inlineStr">
         <is>
           <t>/products/662_4.jpg; /products/662_1.jpg; /products/662_3.jpg; /products/662_2.jpg</t>
         </is>
       </c>
-      <c r="X167" s="2" t="inlineStr">
+      <c r="Y167" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2022/11/662_4.jpg</t>
         </is>
       </c>
-      <c r="Y167" s="2" t="inlineStr">
+      <c r="Z167" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary korekcyjne - G 93212 C1</t>
         </is>
       </c>
-      <c r="Z167" s="2" t="inlineStr">
+      <c r="AA167" s="2" t="inlineStr">
         <is>
           <t>goya-okulary-korekcyjne-g-93212-c1</t>
         </is>
       </c>
-      <c r="AA167" s="2" t="inlineStr">
+      <c r="AB167" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-okulary-korekcyjne-g-93212-c1</t>
         </is>
       </c>
-      <c r="AB167" s="3" t="inlineStr">
+      <c r="AC167" s="3" t="inlineStr">
         <is>
           <t>OKULARY KOREKCYJNE GOYA G 93212 C1 Produkt nowy - posiadają oryginalne zabezpieczenia, metkę oraz instrukcję użytkowania, dodatkowo w zestawie twarde etui na zawias sprężynowy Marki GOYA oraz miękką ściereczkę czyszczącą. NASZE PRODUKTY WYSYŁAMY BARDZO DOBRZE ZABEZPIECZONE W FOLIĘ TRANSPORTOWĄ I ZAPAKOWANE W WYTRZYMAŁY KARTONIK</t>
         </is>
@@ -24592,35 +25428,40 @@
       </c>
       <c r="V168" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/G_55012_CZ_A.jpg</t>
+        </is>
+      </c>
+      <c r="W168" s="2" t="inlineStr">
+        <is>
           <t>/products/G_55012_CZ_A.jpg</t>
         </is>
       </c>
-      <c r="W168" s="2" t="inlineStr">
+      <c r="X168" s="2" t="inlineStr">
         <is>
           <t>/products/G_55012_CZ_A.jpg; /products/G_55012_CZ_MODkw-1.jpg; /products/G_55012_CZ_G.jpg; /products/G_55012_CZ_MOD1-1.jpg; /products/G_55012_CZ_B.jpg; /products/G_55012_CZ_MOD-1.jpg; /products/G_55012_CZ_F.jpg; /products/G_55012_CZ_S.jpg; /products/G_55012_CZ_F1.jpg; /products/G_55012_CZ_T.jpg</t>
         </is>
       </c>
-      <c r="X168" s="2" t="inlineStr">
+      <c r="Y168" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2025/01/G_55012_CZ_A.jpg</t>
         </is>
       </c>
-      <c r="Y168" s="2" t="inlineStr">
+      <c r="Z168" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary przeciwsłoneczne z filtrem polaryzacyjnym - G 55012 CZ</t>
         </is>
       </c>
-      <c r="Z168" s="2" t="inlineStr">
+      <c r="AA168" s="2" t="inlineStr">
         <is>
           <t>goya-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym-g-55012-cz</t>
         </is>
       </c>
-      <c r="AA168" s="2" t="inlineStr">
+      <c r="AB168" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym-g-55012-cz</t>
         </is>
       </c>
-      <c r="AB168" s="3" t="inlineStr">
+      <c r="AC168" s="3" t="inlineStr">
         <is>
           <t>OKULARY PRZECIWSŁONECZNE DLA KIEROWCÓW GOYA Z FILTREM POLARYZACYJNYM I UV400 Zausznik wykonane w całości z aluminium - co sprawia, że okulary są bardzo lekkie i wytrzymałe. Soczewki okularów GOYA o grubości 1,1 wyposażone są w filtr polaryzacyjny oraz filtr ochronny UV-400 (UV-A, UV-B, UV-C) ZAUSZNIKI POŁĄCZONE Z OPRAWKĄ SYSTEMEM FLEX: FLEX - elastyczne połączenie zausznika z frontem oprawy. Zwiększony zakres odchylenia zausznika do ponad 110° gwarantuje wygodę noszenia i ułatwia zakładanie oraz zdejmowanie okularów. OKULARY POSIADAJĄ CERTYFIKAT CE. Produkt odpowiada Wytycznej Europejskiej 89/686/EWG zgodnie z normą PN-EN ISO 12312-1:2014-02/A1:2016-01. Każda para okularów posiada oryginalne oznaczenia znajdujące się na wewnętrznej stronie zauszników ; logo producenta, numer modelu, kategoria filtra oraz oznaczenie CE. O POLARYZACJI: Soczewki polaryzacyjne neutralizują oślepiające refleksy, powstające wówczas gdy światło odbija się od mokrej drogi, powierzchni wody lub śniegu. Eliminacja światła odbitego zwiększ kontrast widzenia i pozwala</t>
         </is>
@@ -24710,35 +25551,40 @@
       </c>
       <c r="V169" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/prof-230.jpeg</t>
+        </is>
+      </c>
+      <c r="W169" s="2" t="inlineStr">
+        <is>
           <t>/products/prof-230.jpeg</t>
         </is>
       </c>
-      <c r="W169" s="2" t="inlineStr">
+      <c r="X169" s="2" t="inlineStr">
         <is>
           <t>/products/prof-230.jpeg</t>
         </is>
       </c>
-      <c r="X169" s="2" t="inlineStr">
+      <c r="Y169" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2022/03/prof-230.jpeg</t>
         </is>
       </c>
-      <c r="Y169" s="2" t="inlineStr">
+      <c r="Z169" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary przeciwsłoneczne z filtrem polaryzacyjnym  - G 218</t>
         </is>
       </c>
-      <c r="Z169" s="2" t="inlineStr">
+      <c r="AA169" s="2" t="inlineStr">
         <is>
           <t>srebrne-okulary-przeciwsloneczne-polaryzacyjne-dla-kierowcow-goya-g-218-c</t>
         </is>
       </c>
-      <c r="AA169" s="2" t="inlineStr">
+      <c r="AB169" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/srebrne-okulary-przeciwsloneczne-polaryzacyjne-dla-kierowcow-goya-g-218-c</t>
         </is>
       </c>
-      <c r="AB169" s="3" t="inlineStr">
+      <c r="AC169" s="3" t="inlineStr">
         <is>
           <t>OKULARY PRZECIWSŁONECZNE DLA KIEROWCÓW GOYA Z FILTREM POLARYZACYJNYM I UV400 Okulary wykonane z aluminium są bardzo lekkie, wytrzymałe i wygodne w użytkowaniu. Oprawka wykonana ze stali szlachetnej - kwasoodpornej. Soczewki okularów GOYA o grubości 1,1 wyposażone są w filtr polaryzacyjny oraz filtr ochronny UV-400 (UV-A, UV-B, UV-C) ZAUSZNIKI POŁĄCZONE Z OPRAWKĄ SYSTEMEM FLEX: FLEX - elastyczne połączenie zausznika z frontem oprawy. Zwiększony zakres odchylenia zausznika do ponad 110° gwarantuje wygodę noszenia i ułatwia zakładanie oraz zdejmowanie okularów. OKULARY POSIADAJĄ CERTYFIKAT CE. Produkt odpowiada Wytycznej Europejskiej 89/686/EWG zgodnie z normą PN-EN ISO 12312-1:2014-02/A1:2016-01. Każda para okularów posiada oryginalne oznaczenia znajdujące się na wewnętrznej stronie zauszników ; logo producenta, numer modelu, kategoria filtra oraz oznaczenie CE. O POLARYZACJI: Soczewki polaryzacyjne neutralizują oślepiające refleksy, powstające wówczas gdy światło odbija się od mokrej drogi, powierzchni wody lub śniegu. Eliminacja światła o</t>
         </is>
@@ -24828,35 +25674,40 @@
       </c>
       <c r="V170" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/GOYA-CP8803-CZ-A.jpg</t>
+        </is>
+      </c>
+      <c r="W170" s="2" t="inlineStr">
+        <is>
           <t>/products/GOYA-CP8803-CZ-A.jpg</t>
         </is>
       </c>
-      <c r="W170" s="2" t="inlineStr">
+      <c r="X170" s="2" t="inlineStr">
         <is>
           <t>/products/GOYA-CP8803-CZ-A.jpg; /products/3422_7-e1681287259505.jpg</t>
         </is>
       </c>
-      <c r="X170" s="2" t="inlineStr">
+      <c r="Y170" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2023/04/GOYA-CP8803-CZ-A.jpg</t>
         </is>
       </c>
-      <c r="Y170" s="2" t="inlineStr">
+      <c r="Z170" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary przeciwsłoneczne z filtrem polaryzacyjnym - GOYA CP 8803</t>
         </is>
       </c>
-      <c r="Z170" s="2" t="inlineStr">
+      <c r="AA170" s="2" t="inlineStr">
         <is>
           <t>goya-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym-goya-cp-8803</t>
         </is>
       </c>
-      <c r="AA170" s="2" t="inlineStr">
+      <c r="AB170" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym-goya-cp-8803</t>
         </is>
       </c>
-      <c r="AB170" s="3" t="inlineStr">
+      <c r="AC170" s="3" t="inlineStr">
         <is>
           <t>OKULARY PRZECIWSŁONECZNE DLA KIEROWCÓW GOYA Z FILTREM POLARYZACYJNYM I UV400 Soczewki okularów GOYA o grubości 1,1 wyposażone są w filtr polaryzacyjny oraz filtr ochronny UV-400 (UV-A, UV-B, UV-C) SOCZEWKA ANTYREFLEKS: Warstwa antyrefleksu znacznie zwiększa wartość użytkową okularów, gdyż przepuszcza przez powierzchnię soczewki okularowej więcej światła niż odbija. Dzięki tej powłoce w znacznym stopniu zredukowane zostają wszelkie odblaski. Antyrefleks poprawia również odwzorowanie barw i poprawia kontrast widzenia. Dodatkowym plusem powłoki antyrefleksyjnej jest ochrona soczewki przez zarysowaniami. OKULARY POSIADAJĄ CERTYFIKAT CE. Produkt odpowiada Wytycznej Europejskiej 89/686/EWG zgodnie z normą PN-EN ISO 12312-1:2014-02/A1:2016-01. Każda para okularów posiada oryginalne oznaczenia znajdujące się na wewnętrznej stronie zauszników ; logo producenta, numer modelu, kategoria filtra oraz oznaczenie CE. O POLARYZACJI: Soczewki polaryzacyjne neutralizują oślepiające refleksy, powstające wówczas gdy światło odbija się od mokrej drogi, powierzchni wod</t>
         </is>
@@ -24946,35 +25797,40 @@
       </c>
       <c r="V171" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/GOYA-A0736-CZ-A.jpg</t>
+        </is>
+      </c>
+      <c r="W171" s="2" t="inlineStr">
+        <is>
           <t>/products/GOYA-A0736-CZ-A.jpg</t>
         </is>
       </c>
-      <c r="W171" s="2" t="inlineStr">
+      <c r="X171" s="2" t="inlineStr">
         <is>
           <t>/products/GOYA-A0736-CZ-A.jpg; /products/GOYA_A0736_CZ_mod.jpg</t>
         </is>
       </c>
-      <c r="X171" s="2" t="inlineStr">
+      <c r="Y171" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2023/04/GOYA-A0736-CZ-A.jpg</t>
         </is>
       </c>
-      <c r="Y171" s="2" t="inlineStr">
+      <c r="Z171" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary przeciwsłoneczne z filtrem polaryzacyjnym - GOYA A 0736</t>
         </is>
       </c>
-      <c r="Z171" s="2" t="inlineStr">
+      <c r="AA171" s="2" t="inlineStr">
         <is>
           <t>goya-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym-goya-a-0736</t>
         </is>
       </c>
-      <c r="AA171" s="2" t="inlineStr">
+      <c r="AB171" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym-goya-a-0736</t>
         </is>
       </c>
-      <c r="AB171" s="3" t="inlineStr">
+      <c r="AC171" s="3" t="inlineStr">
         <is>
           <t>OKULARY PRZECIWSŁONECZNE GOYA Z FILTREM POLARYZACYJNYM I UV400 Soczewki okularów GOYA o grubości 1,1 wyposażone są w filtr polaryzacyjny oraz filtr ochronny UV-400 (UV-A, UV-B, UV-C) OKULARY POSIADAJĄ CERTYFIKAT CE. Produkt odpowiada Wytycznej Europejskiej 89/686/EWG zgodnie z normą PN-EN ISO 12312-1:2014-02/A1:2016-01. Każda para okularów posiada oryginalne oznaczenia znajdujące się na wewnętrznej stronie zauszników ; logo producenta, numer modelu, kategoria filtra oraz oznaczenie CE. O POLARYZACJI: Soczewki polaryzacyjne neutralizują oślepiające refleksy, powstające wówczas gdy światło odbija się od mokrej drogi, powierzchni wody lub śniegu. Eliminacja światła odbitego zwiększ kontrast widzenia i pozwala na bardziej komfortowe widzenie. Dlatego okulary z filtrem polaryzacyjnym to idealne rozwiązanie do wszelkiego rodzaju aktywności na świeżym powietrzu, pozwalające pełniej korzystać z życia. ZALETY: Eliminują oślepiające odblaski, zmniejszając zmęczenie oczu Chronią przed szkodliwym promieniowaniem UV Zwiększają kontras</t>
         </is>
@@ -25062,35 +25918,40 @@
       </c>
       <c r="V172" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/582_3.jpg</t>
+        </is>
+      </c>
+      <c r="W172" s="2" t="inlineStr">
+        <is>
           <t>/products/582_3.jpg</t>
         </is>
       </c>
-      <c r="W172" s="2" t="inlineStr">
+      <c r="X172" s="2" t="inlineStr">
         <is>
           <t>/products/582_3.jpg; /products/582_4.jpg; /products/582_2.jpg; /products/582_1.jpg</t>
         </is>
       </c>
-      <c r="X172" s="2" t="inlineStr">
+      <c r="Y172" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2022/11/582_3.jpg</t>
         </is>
       </c>
-      <c r="Y172" s="2" t="inlineStr">
+      <c r="Z172" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary korekcyjne - G 2618 C2</t>
         </is>
       </c>
-      <c r="Z172" s="2" t="inlineStr">
+      <c r="AA172" s="2" t="inlineStr">
         <is>
           <t>goya-okulary-korekcyjne-g-2618-c2</t>
         </is>
       </c>
-      <c r="AA172" s="2" t="inlineStr">
+      <c r="AB172" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-okulary-korekcyjne-g-2618-c2</t>
         </is>
       </c>
-      <c r="AB172" s="3" t="inlineStr">
+      <c r="AC172" s="3" t="inlineStr">
         <is>
           <t>OKULARY KOREKCYJNE GOYA G 2618 C2 Produkt nowy - posiadają oryginalne zabezpieczenia, metkę oraz instrukcję użytkowania, dodatkowo w zestawie twarde etui na zawias sprężynowy Marki GOYA oraz miękką ściereczkę czyszczącą. NASZE PRODUKTY WYSYŁAMY BARDZO DOBRZE ZABEZPIECZONE W FOLIĘ TRANSPORTOWĄ I ZAPAKOWANE W WYTRZYMAŁY KARTONIK</t>
         </is>
@@ -25180,35 +26041,40 @@
       </c>
       <c r="V173" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/prof-380.jpeg</t>
+        </is>
+      </c>
+      <c r="W173" s="2" t="inlineStr">
+        <is>
           <t>/products/prof-380.jpeg</t>
         </is>
       </c>
-      <c r="W173" s="2" t="inlineStr">
+      <c r="X173" s="2" t="inlineStr">
         <is>
           <t>/products/prof-380.jpeg</t>
         </is>
       </c>
-      <c r="X173" s="2" t="inlineStr">
+      <c r="Y173" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2022/03/prof-380.jpeg</t>
         </is>
       </c>
-      <c r="Y173" s="2" t="inlineStr">
+      <c r="Z173" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary przeciwsłoneczne z filtrem polaryzacyjnym - G 55007</t>
         </is>
       </c>
-      <c r="Z173" s="2" t="inlineStr">
+      <c r="AA173" s="2" t="inlineStr">
         <is>
           <t>okulary-przeciwsloneczne-polaryzacyjne-dla-kierowcow-goya-g-55007-br</t>
         </is>
       </c>
-      <c r="AA173" s="2" t="inlineStr">
+      <c r="AB173" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/okulary-przeciwsloneczne-polaryzacyjne-dla-kierowcow-goya-g-55007-br</t>
         </is>
       </c>
-      <c r="AB173" s="3" t="inlineStr">
+      <c r="AC173" s="3" t="inlineStr">
         <is>
           <t>OKULARY PRZECIWSŁONECZNE DLA KIEROWCÓW GOYA Z FILTREM POLARYZACYJNYM I UV400 Zauszniki oraz mostek wykonane z aluminium - co sprawia, że okulary są bardzo lekkie i wytrzymałe. Soczewki okularów GOYA o grubości 1,1 wyposażone są w filtr polaryzacyjny oraz filtr ochronny UV-400 (UV-A, UV-B, UV-C) ZAUSZNIKI POŁĄCZONE Z OPRAWKĄ SYSTEMEM FLEX: FLEX - elastyczne połączenie zausznika z frontem oprawy. Zwiększony zakres odchylenia zausznika do ponad 110° gwarantuje wygodę noszenia i ułatwia zakładanie oraz zdejmowanie okularów. OKULARY POSIADAJĄ CERTYFIKAT CE. Produkt odpowiada Wytycznej Europejskiej 89/686/EWG zgodnie z normą PN-EN ISO 12312-1:2014-02/A1:2016-01. Każda para okularów posiada oryginalne oznaczenia znajdujące się na wewnętrznej stronie zauszników ; logo producenta, numer modelu, kategoria filtra oraz oznaczenie CE. O POLARYZACJI: Soczewki polaryzacyjne neutralizują oślepiające refleksy, powstające wówczas gdy światło odbija się od mokrej drogi, powierzchni wody lub śniegu. Eliminacja światła odbitego zwiększ kontrast widzenia i pozwala</t>
         </is>
@@ -25300,35 +26166,40 @@
       </c>
       <c r="V174" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/3133_1.jpg</t>
+        </is>
+      </c>
+      <c r="W174" s="2" t="inlineStr">
+        <is>
           <t>/products/3133_1.jpg</t>
         </is>
       </c>
-      <c r="W174" s="2" t="inlineStr">
+      <c r="X174" s="2" t="inlineStr">
         <is>
           <t>/products/3133_1.jpg; /products/3133_6.jpg; /products/3133_2.jpg; /products/3133_3.jpg; /products/3133_4.jpg; /products/3133_5.jpg</t>
         </is>
       </c>
-      <c r="X174" s="2" t="inlineStr">
+      <c r="Y174" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2022/11/3133_1.jpg</t>
         </is>
       </c>
-      <c r="Y174" s="2" t="inlineStr">
+      <c r="Z174" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary przeciwsłoneczne z filtrem polaryzacyjnym - G 188 GR</t>
         </is>
       </c>
-      <c r="Z174" s="2" t="inlineStr">
+      <c r="AA174" s="2" t="inlineStr">
         <is>
           <t>goya-g-188-gr-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym</t>
         </is>
       </c>
-      <c r="AA174" s="2" t="inlineStr">
+      <c r="AB174" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-g-188-gr-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym</t>
         </is>
       </c>
-      <c r="AB174" s="3" t="inlineStr">
+      <c r="AC174" s="3" t="inlineStr">
         <is>
           <t>OKULARY PRZECIWSŁONECZNE DLA KIEROWCÓW GOYA Z FILTREM POLARYZACYJNYM I UV400 Antyrefleks Soczewki okularów GOYA o grubości 1,1 wyposażone są w filtr polaryzacyjny oraz filtr ochronny UV-400 (UV-A, UV-B, UV-C) ZAUSZNIKI POŁĄCZONE Z OPRAWKĄ SYSTEMEM FLEX: FLEX - elastyczne połączenie zausznika z frontem oprawy. Zwiększony zakres odchylenia zausznika do ponad 110° gwarantuje wygodę noszenia i ułatwia zakładanie oraz zdejmowanie okularów. OKULARY POSIADAJĄ CERTYFIKAT CE. Produkt odpowiada Wytycznej Europejskiej 89/686/EWG zgodnie z normą PN-EN ISO 12312-1:2014-02/A1:2016-01. Każda para okularów posiada oryginalne oznaczenia znajdujące się na wewnętrznej stronie zauszników ; logo producenta, numer modelu, kategoria filtra oraz oznaczenie CE. O POLARYZACJI: Soczewki polaryzacyjne neutralizują oślepiające refleksy, powstające wówczas gdy światło odbija się od mokrej drogi, powierzchni wody lub śniegu. Eliminacja światła odbitego zwiększ kontrast widzenia i pozwala na bardziej komfortowe widzenie. Dlatego okulary z filtrem polaryzacyjnym to idealne</t>
         </is>
@@ -25420,35 +26291,40 @@
       </c>
       <c r="V175" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/3187_1.jpg</t>
+        </is>
+      </c>
+      <c r="W175" s="2" t="inlineStr">
+        <is>
           <t>/products/3187_1.jpg</t>
         </is>
       </c>
-      <c r="W175" s="2" t="inlineStr">
+      <c r="X175" s="2" t="inlineStr">
         <is>
           <t>/products/3187_1.jpg; /products/3187_6.jpg; /products/3187_5.jpg; /products/3187_4.jpg; /products/3187_3.jpg; /products/3187_2.jpg</t>
         </is>
       </c>
-      <c r="X175" s="2" t="inlineStr">
+      <c r="Y175" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2023/01/3187_1.jpg</t>
         </is>
       </c>
-      <c r="Y175" s="2" t="inlineStr">
+      <c r="Z175" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary przeciwsłoneczne z filtrem polaryzacyjnym - G 150 GR C</t>
         </is>
       </c>
-      <c r="Z175" s="2" t="inlineStr">
+      <c r="AA175" s="2" t="inlineStr">
         <is>
           <t>goya-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym-g-150-gr-c</t>
         </is>
       </c>
-      <c r="AA175" s="2" t="inlineStr">
+      <c r="AB175" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-okulary-przeciwsloneczne-z-filtrem-polaryzacyjnym-g-150-gr-c</t>
         </is>
       </c>
-      <c r="AB175" s="3" t="inlineStr">
+      <c r="AC175" s="3" t="inlineStr">
         <is>
           <t>OKULARY PRZECIWSŁONECZNE DLA KIEROWCÓW GOYA Z FILTREM POLARYZACYJNYM I UV400 Oprawka wykonana w technologii - wycinania z płyty. Ręcznie obrabiana. Soczewki okularów GOYA o grubości 1,1 wyposażone są w filtr polaryzacyjny oraz filtr ochronny UV-400 (UV-A, UV-B, UV-C) OKULARY POSIADAJĄ CERTYFIKAT CE. Produkt odpowiada Wytycznej Europejskiej 89/686/EWG zgodnie z normą PN-EN ISO 12312-1:2014-02/A1:2016-01. Każda para okularów posiada oryginalne oznaczenia znajdujące się na wewnętrznej stronie zauszników ; logo producenta, numer modelu, kategoria filtra oraz oznaczenie CE. O POLARYZACJI: Soczewki polaryzacyjne neutralizują oślepiające refleksy, powstające wówczas gdy światło odbija się od mokrej drogi, powierzchni wody lub śniegu. Eliminacja światła odbitego zwiększ kontrast widzenia i pozwala na bardziej komfortowe widzenie. Dlatego okulary z filtrem polaryzacyjnym to idealne rozwiązanie do wszelkiego rodzaju aktywności na świeżym powietrzu, pozwalające pełniej korzystać z życia. ZALETY: Eliminują oślepiające odblaski, zmniejszaj</t>
         </is>
@@ -25534,35 +26410,40 @@
       </c>
       <c r="V176" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/2604_1.jpg</t>
+        </is>
+      </c>
+      <c r="W176" s="2" t="inlineStr">
+        <is>
           <t>/products/2604_1.jpg</t>
         </is>
       </c>
-      <c r="W176" s="2" t="inlineStr">
+      <c r="X176" s="2" t="inlineStr">
         <is>
           <t>/products/2604_1.jpg; /products/GOYA-CP3718-CZ.jpg</t>
         </is>
       </c>
-      <c r="X176" s="2" t="inlineStr">
+      <c r="Y176" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2022/11/2604_1.jpg</t>
         </is>
       </c>
-      <c r="Y176" s="2" t="inlineStr">
+      <c r="Z176" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary przeciwsłoneczne z filtrem polaryzacyjnym - G CP3718</t>
         </is>
       </c>
-      <c r="Z176" s="2" t="inlineStr">
+      <c r="AA176" s="2" t="inlineStr">
         <is>
           <t>goya-g-cp3718-r-okulary-przeciwsloneczne-polaryzacyjne</t>
         </is>
       </c>
-      <c r="AA176" s="2" t="inlineStr">
+      <c r="AB176" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-g-cp3718-r-okulary-przeciwsloneczne-polaryzacyjne</t>
         </is>
       </c>
-      <c r="AB176" s="3" t="inlineStr">
+      <c r="AC176" s="3" t="inlineStr">
         <is>
           <t>OKULARY PRZECIWSŁONECZNE MARKI GOYA Z FILTREM POLARYZACYJNYM I UV400 Soczewki okularów GOYA o grubości 1,1 wyposażone są w filtr polaryzacyjny oraz filtr ochronny UV-400 (UV-A, UV-B, UV-C) OKULARY POSIADAJĄ CERTYFIKAT CE. Produkt odpowiada Wytycznej Europejskiej 89/686/EWG zgodnie z normą PN-EN ISO 12312-1:2014-02/A1:2016-01. Każda para okularów posiada oryginalne oznaczenia znajdujące się na wewnętrznej stronie zauszników ; logo producenta, numer modelu, kategoria filtra oraz oznaczenie CE. O POLARYZACJI: Soczewki polaryzacyjne neutralizują oślepiające refleksy, powstające wówczas gdy światło odbija się od mokrej drogi, powierzchni wody lub śniegu. Eliminacja światła odbitego zwiększ kontrast widzenia i pozwala na bardziej komfortowe widzenie. Dlatego okulary z filtrem polaryzacyjnym to idealne rozwiązanie do wszelkiego rodzaju aktywności na świeżym powietrzu, pozwalające pełniej korzystać z życia. ZALETY: Eliminują oślepiające odblaski, zmniejszając zmęczenie oczu Chronią przed szkodliwym promieniowaniem UV Zwiększają kontras</t>
         </is>
@@ -25648,35 +26529,40 @@
       </c>
       <c r="V177" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/635_4.jpg</t>
+        </is>
+      </c>
+      <c r="W177" s="2" t="inlineStr">
+        <is>
           <t>/products/635_4.jpg</t>
         </is>
       </c>
-      <c r="W177" s="2" t="inlineStr">
+      <c r="X177" s="2" t="inlineStr">
         <is>
           <t>/products/635_4.jpg</t>
         </is>
       </c>
-      <c r="X177" s="2" t="inlineStr">
+      <c r="Y177" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2022/11/635_4.jpg</t>
         </is>
       </c>
-      <c r="Y177" s="2" t="inlineStr">
+      <c r="Z177" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary korekcyjne - GK 7107</t>
         </is>
       </c>
-      <c r="Z177" s="2" t="inlineStr">
+      <c r="AA177" s="2" t="inlineStr">
         <is>
           <t>goya-okulary-korekcyjne-gk-7107-c1</t>
         </is>
       </c>
-      <c r="AA177" s="2" t="inlineStr">
+      <c r="AB177" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-okulary-korekcyjne-gk-7107-c1</t>
         </is>
       </c>
-      <c r="AB177" s="3" t="inlineStr">
+      <c r="AC177" s="3" t="inlineStr">
         <is>
           <t>OKULARY KOREKCYJNE GOYA GK 7107 Produkt nowy - posiadają oryginalne zabezpieczenia, metkę oraz instrukcję użytkowania, dodatkowo w zestawie twarde etui na zawias sprężynowy Marki GOYA oraz miękką ściereczkę czyszczącą. NASZE PRODUKTY WYSYŁAMY BARDZO DOBRZE ZABEZPIECZONE W FOLIĘ TRANSPORTOWĄ I ZAPAKOWANE W WYTRZYMAŁY KARTONIK</t>
         </is>
@@ -25764,42 +26650,47 @@
       </c>
       <c r="V178" s="2" t="inlineStr">
         <is>
+          <t>https://goya-eight.vercel.app/products/661_4.jpg</t>
+        </is>
+      </c>
+      <c r="W178" s="2" t="inlineStr">
+        <is>
           <t>/products/661_4.jpg</t>
         </is>
       </c>
-      <c r="W178" s="2" t="inlineStr">
+      <c r="X178" s="2" t="inlineStr">
         <is>
           <t>/products/661_4.jpg; /products/661_1.jpg; /products/661_3.jpg; /products/661_2.jpg</t>
         </is>
       </c>
-      <c r="X178" s="2" t="inlineStr">
+      <c r="Y178" s="2" t="inlineStr">
         <is>
           <t>https://okulary.pl/wp-content/uploads/2022/11/661_4.jpg</t>
         </is>
       </c>
-      <c r="Y178" s="2" t="inlineStr">
+      <c r="Z178" s="2" t="inlineStr">
         <is>
           <t>GOYA okulary korekcyjne - G 93234 C2</t>
         </is>
       </c>
-      <c r="Z178" s="2" t="inlineStr">
+      <c r="AA178" s="2" t="inlineStr">
         <is>
           <t>goya-okulary-korekcyjne-g-93234-c2</t>
         </is>
       </c>
-      <c r="AA178" s="2" t="inlineStr">
+      <c r="AB178" s="2" t="inlineStr">
         <is>
           <t>https://goya-eight.vercel.app/okulary/goya-okulary-korekcyjne-g-93234-c2</t>
         </is>
       </c>
-      <c r="AB178" s="3" t="inlineStr">
+      <c r="AC178" s="3" t="inlineStr">
         <is>
           <t>OKULARY KOREKCYJNE GOYA G 93234 C2 Produkt nowy - posiadają oryginalne zabezpieczenia, metkę oraz instrukcję użytkowania, dodatkowo w zestawie twarde etui na zawias sprężynowy Marki GOYA oraz miękką ściereczkę czyszczącą. NASZE PRODUKTY WYSYŁAMY BARDZO DOBRZE ZABEZPIECZONE W FOLIĘ TRANSPORTOWĄ I ZAPAKOWANE W WYTRZYMAŁY KARTONIK</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B1:AB178"/>
+  <autoFilter ref="B1:AC178"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
